--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2389894E-4936-4B7A-8F1C-D5320D17F580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AAF25F-C036-4990-BC77-255166C50F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="156" windowWidth="21156" windowHeight="12828" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -2900,19 +2900,21 @@
         <v>2</v>
       </c>
       <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
+      <c r="L52" s="14">
+        <v>1</v>
+      </c>
       <c r="M52" s="14"/>
       <c r="N52" s="14">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O52" s="14">
         <f t="shared" si="0"/>
-        <v>248</v>
+        <v>310</v>
       </c>
       <c r="P52" s="14">
         <f t="shared" si="1"/>
-        <v>496</v>
+        <v>620</v>
       </c>
       <c r="Q52" s="14"/>
     </row>
@@ -3443,53 +3445,53 @@
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
       <c r="D67" s="12">
-        <f>SUM(D2:D65)</f>
+        <f t="shared" ref="D67:M67" si="6">SUM(D2:D65)</f>
         <v>5</v>
       </c>
       <c r="E67" s="12">
-        <f>SUM(E2:E65)</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="F67" s="12">
-        <f>SUM(F2:F65)</f>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="G67" s="12">
-        <f>SUM(G2:G65)</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="H67" s="12">
-        <f>SUM(H2:H65)</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="I67" s="12">
-        <f>SUM(I2:I65)</f>
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
       <c r="J67" s="12">
-        <f>SUM(J2:J65)</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="K67" s="12">
-        <f>SUM(K2:K65)</f>
+        <f t="shared" si="6"/>
         <v>27</v>
       </c>
       <c r="L67" s="12">
-        <f>SUM(L2:L65)</f>
-        <v>15</v>
+        <f t="shared" si="6"/>
+        <v>16</v>
       </c>
       <c r="M67" s="12">
-        <f>SUM(M2:M65)</f>
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
       <c r="N67" s="12">
         <f>SUM(D67:M67)</f>
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O67" s="12"/>
       <c r="P67" s="7">
         <f>SUM(P2:P65)</f>
-        <v>22529</v>
+        <v>22653</v>
       </c>
       <c r="Q67" s="13">
         <f>SUM(Q2:Q65)</f>
@@ -3720,11 +3722,11 @@
         <v>14</v>
       </c>
       <c r="C78" s="8">
-        <f>C2*2</f>
+        <f t="shared" ref="C78:C101" si="7">C2*2</f>
         <v>16</v>
       </c>
       <c r="D78" s="8">
-        <f>C78*D2</f>
+        <f t="shared" ref="D78:D89" si="8">C78*D2</f>
         <v>0</v>
       </c>
       <c r="E78" s="8">
@@ -3782,11 +3784,11 @@
         <v>15</v>
       </c>
       <c r="C79" s="8">
-        <f>C3*2</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="D79" s="8">
-        <f>C79*D3</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E79" s="8">
@@ -3828,7 +3830,7 @@
       <c r="N79" s="8"/>
       <c r="O79" s="8"/>
       <c r="P79" s="8">
-        <f t="shared" ref="P79:P141" si="6">SUM(D79:M79)</f>
+        <f t="shared" ref="P79:P141" si="9">SUM(D79:M79)</f>
         <v>4</v>
       </c>
       <c r="Q79" s="8"/>
@@ -3841,11 +3843,11 @@
         <v>16</v>
       </c>
       <c r="C80" s="8">
-        <f>C4*2</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="D80" s="8">
-        <f>C80*D4</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="E80" s="8">
@@ -3887,7 +3889,7 @@
       <c r="N80" s="8"/>
       <c r="O80" s="8"/>
       <c r="P80" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>80</v>
       </c>
       <c r="Q80" s="8"/>
@@ -3900,11 +3902,11 @@
         <v>18</v>
       </c>
       <c r="C81" s="6">
-        <f>C5*2</f>
+        <f t="shared" si="7"/>
         <v>564</v>
       </c>
       <c r="D81" s="6">
-        <f>C81*D5</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E81" s="6">
@@ -3946,7 +3948,7 @@
       <c r="N81" s="6"/>
       <c r="O81" s="6"/>
       <c r="P81" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1128</v>
       </c>
       <c r="Q81" s="6">
@@ -3962,53 +3964,53 @@
         <v>130</v>
       </c>
       <c r="C82" s="8">
-        <f>C6*2</f>
+        <f t="shared" si="7"/>
         <v>148</v>
       </c>
       <c r="D82" s="8">
-        <f>C82*D6</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E82" s="8">
-        <f>D82*E6</f>
+        <f t="shared" ref="E82:M82" si="10">D82*E6</f>
         <v>0</v>
       </c>
       <c r="F82" s="8">
-        <f>E82*F6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G82" s="8">
-        <f>F82*G6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H82" s="8">
-        <f>G82*H6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I82" s="8">
-        <f>H82*I6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J82" s="8">
-        <f>I82*J6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="K82" s="8">
-        <f>J82*K6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="L82" s="8">
-        <f>K82*L6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M82" s="8">
-        <f>L82*M6</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="N82" s="8"/>
       <c r="O82" s="8"/>
       <c r="P82" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q82" s="8">
@@ -4024,53 +4026,53 @@
         <v>20</v>
       </c>
       <c r="C83" s="14">
-        <f>C7*2</f>
+        <f t="shared" si="7"/>
         <v>278</v>
       </c>
       <c r="D83" s="14">
-        <f>C83*D7</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E83" s="14">
-        <f>C83*E7</f>
+        <f t="shared" ref="E83:E89" si="11">C83*E7</f>
         <v>0</v>
       </c>
       <c r="F83" s="14">
-        <f>C83*F7</f>
+        <f t="shared" ref="F83:F89" si="12">C83*F7</f>
         <v>0</v>
       </c>
       <c r="G83" s="14">
-        <f>C83*G7</f>
+        <f t="shared" ref="G83:G89" si="13">C83*G7</f>
         <v>0</v>
       </c>
       <c r="H83" s="14">
-        <f>C83*H7</f>
+        <f t="shared" ref="H83:H89" si="14">C83*H7</f>
         <v>0</v>
       </c>
       <c r="I83" s="14">
-        <f>C83*I7</f>
+        <f t="shared" ref="I83:I89" si="15">C83*I7</f>
         <v>0</v>
       </c>
       <c r="J83" s="14">
-        <f>C83*J7</f>
+        <f t="shared" ref="J83:J89" si="16">C83*J7</f>
         <v>0</v>
       </c>
       <c r="K83" s="14">
-        <f>C83*K7</f>
+        <f t="shared" ref="K83:K89" si="17">C83*K7</f>
         <v>278</v>
       </c>
       <c r="L83" s="14">
-        <f>C83*L7</f>
+        <f t="shared" ref="L83:L89" si="18">C83*L7</f>
         <v>0</v>
       </c>
       <c r="M83" s="14">
-        <f>C83*M7</f>
+        <f t="shared" ref="M83:M89" si="19">C83*M7</f>
         <v>834</v>
       </c>
       <c r="N83" s="14"/>
       <c r="O83" s="14"/>
       <c r="P83" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1112</v>
       </c>
       <c r="Q83" s="14">
@@ -4086,53 +4088,53 @@
         <v>21</v>
       </c>
       <c r="C84" s="14">
-        <f>C8*2</f>
+        <f t="shared" si="7"/>
         <v>282</v>
       </c>
       <c r="D84" s="14">
-        <f>C84*D8</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E84" s="14">
-        <f>C84*E8</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F84" s="14">
-        <f>C84*F8</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G84" s="14">
-        <f>C84*G8</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H84" s="14">
-        <f>C84*H8</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I84" s="14">
-        <f>C84*I8</f>
+        <f t="shared" si="15"/>
         <v>282</v>
       </c>
       <c r="J84" s="14">
-        <f>C84*J8</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K84" s="14">
-        <f>C84*K8</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L84" s="14">
-        <f>C84*L8</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M84" s="14">
-        <f>C84*M8</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N84" s="14"/>
       <c r="O84" s="14"/>
       <c r="P84" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>282</v>
       </c>
       <c r="Q84" s="14"/>
@@ -4145,53 +4147,53 @@
         <v>23</v>
       </c>
       <c r="C85" s="8">
-        <f>C9*2</f>
+        <f t="shared" si="7"/>
         <v>66</v>
       </c>
       <c r="D85" s="8">
-        <f>C85*D9</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E85" s="8">
-        <f>C85*E9</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F85" s="8">
-        <f>C85*F9</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G85" s="8">
-        <f>C85*G9</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H85" s="8">
-        <f>C85*H9</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I85" s="8">
-        <f>C85*I9</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J85" s="8">
-        <f>C85*J9</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K85" s="8">
-        <f>C85*K9</f>
+        <f t="shared" si="17"/>
         <v>66</v>
       </c>
       <c r="L85" s="8">
-        <f>C85*L9</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M85" s="8">
-        <f>C85*M9</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N85" s="8"/>
       <c r="O85" s="8"/>
       <c r="P85" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>66</v>
       </c>
       <c r="Q85" s="8">
@@ -4207,53 +4209,53 @@
         <v>24</v>
       </c>
       <c r="C86" s="8">
-        <f>C10*2</f>
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
       <c r="D86" s="8">
-        <f>C86*D10</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E86" s="8">
-        <f>C86*E10</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F86" s="8">
-        <f>C86*F10</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G86" s="8">
-        <f>C86*G10</f>
+        <f t="shared" si="13"/>
         <v>92</v>
       </c>
       <c r="H86" s="8">
-        <f>C86*H10</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I86" s="8">
-        <f>C86*I10</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J86" s="8">
-        <f>C86*J10</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K86" s="8">
-        <f>C86*K10</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L86" s="8">
-        <f>C86*L10</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M86" s="8">
-        <f>C86*M10</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N86" s="8"/>
       <c r="O86" s="8"/>
       <c r="P86" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="Q86" s="8"/>
@@ -4266,53 +4268,53 @@
         <v>25</v>
       </c>
       <c r="C87" s="8">
-        <f>C11*2</f>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="D87" s="8">
-        <f>C87*D11</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E87" s="8">
-        <f>C87*E11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F87" s="8">
-        <f>C87*F11</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G87" s="8">
-        <f>C87*G11</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H87" s="8">
-        <f>C87*H11</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I87" s="8">
-        <f>C87*I11</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J87" s="8">
-        <f>C87*J11</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K87" s="8">
-        <f>C87*K11</f>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="L87" s="8">
-        <f>C87*L11</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M87" s="8">
-        <f>C87*M11</f>
+        <f t="shared" si="19"/>
         <v>756</v>
       </c>
       <c r="N87" s="8"/>
       <c r="O87" s="8"/>
       <c r="P87" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>840</v>
       </c>
       <c r="Q87" s="8"/>
@@ -4325,53 +4327,53 @@
         <v>26</v>
       </c>
       <c r="C88" s="8">
-        <f>C12*2</f>
+        <f t="shared" si="7"/>
         <v>120</v>
       </c>
       <c r="D88" s="8">
-        <f>C88*D12</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E88" s="8">
-        <f>C88*E12</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F88" s="8">
-        <f>C88*F12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G88" s="8">
-        <f>C88*G12</f>
+        <f t="shared" si="13"/>
         <v>120</v>
       </c>
       <c r="H88" s="8">
-        <f>C88*H12</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I88" s="8">
-        <f>C88*I12</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J88" s="8">
-        <f>C88*J12</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K88" s="8">
-        <f>C88*K12</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L88" s="8">
-        <f>C88*L12</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M88" s="8">
-        <f>C88*M12</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N88" s="8"/>
       <c r="O88" s="8"/>
       <c r="P88" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>120</v>
       </c>
       <c r="Q88" s="8"/>
@@ -4384,53 +4386,53 @@
         <v>27</v>
       </c>
       <c r="C89" s="8">
-        <f>C13*2</f>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="D89" s="8">
-        <f>C89*D13</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E89" s="8">
-        <f>C89*E13</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F89" s="8">
-        <f>C89*F13</f>
+        <f t="shared" si="12"/>
         <v>86</v>
       </c>
       <c r="G89" s="8">
-        <f>C89*G13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H89" s="8">
-        <f>C89*H13</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I89" s="8">
-        <f>C89*I13</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J89" s="8">
-        <f>C89*J13</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="K89" s="8">
-        <f>C89*K13</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L89" s="8">
-        <f>C89*L13</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M89" s="8">
-        <f>C89*M13</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N89" s="8"/>
       <c r="O89" s="8"/>
       <c r="P89" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>86</v>
       </c>
       <c r="Q89" s="8"/>
@@ -4443,7 +4445,7 @@
         <v>126</v>
       </c>
       <c r="C90" s="14">
-        <f>C14*2</f>
+        <f t="shared" si="7"/>
         <v>364</v>
       </c>
       <c r="D90" s="14">
@@ -4480,7 +4482,7 @@
       <c r="N90" s="14"/>
       <c r="O90" s="14"/>
       <c r="P90" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>364</v>
       </c>
       <c r="Q90" s="14">
@@ -4496,11 +4498,11 @@
         <v>29</v>
       </c>
       <c r="C91" s="8">
-        <f>C15*2</f>
+        <f t="shared" si="7"/>
         <v>370</v>
       </c>
       <c r="D91" s="8">
-        <f>C91*D15</f>
+        <f t="shared" ref="D91:D101" si="20">C91*D15</f>
         <v>0</v>
       </c>
       <c r="E91" s="8">
@@ -4536,13 +4538,13 @@
         <v>0</v>
       </c>
       <c r="M91" s="8">
-        <f>C91*M15</f>
+        <f t="shared" ref="M91:M105" si="21">C91*M15</f>
         <v>370</v>
       </c>
       <c r="N91" s="8"/>
       <c r="O91" s="8"/>
       <c r="P91" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>370</v>
       </c>
       <c r="Q91" s="8">
@@ -4558,11 +4560,11 @@
         <v>29</v>
       </c>
       <c r="C92" s="8">
-        <f>C16*2</f>
+        <f t="shared" si="7"/>
         <v>416</v>
       </c>
       <c r="D92" s="8">
-        <f>C92*D16</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E92" s="8">
@@ -4598,13 +4600,13 @@
         <v>416</v>
       </c>
       <c r="M92" s="8">
-        <f>C92*M16</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N92" s="8"/>
       <c r="O92" s="8"/>
       <c r="P92" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>832</v>
       </c>
       <c r="Q92" s="8"/>
@@ -4617,53 +4619,53 @@
         <v>132</v>
       </c>
       <c r="C93" s="14">
-        <f>C17*2</f>
+        <f t="shared" si="7"/>
         <v>236</v>
       </c>
       <c r="D93" s="14">
-        <f>C93*D17</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E93" s="14">
-        <f>D93*E17</f>
+        <f t="shared" ref="E93:L93" si="22">D93*E17</f>
         <v>0</v>
       </c>
       <c r="F93" s="14">
-        <f>E93*F17</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="G93" s="14">
-        <f>F93*G17</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H93" s="14">
-        <f>G93*H17</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I93" s="14">
-        <f>H93*I17</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J93" s="14">
-        <f>I93*J17</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K93" s="14">
-        <f>J93*K17</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L93" s="14">
-        <f>K93*L17</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="M93" s="14">
-        <f>C93*M17</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N93" s="14"/>
       <c r="O93" s="14"/>
       <c r="P93" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="Q93" s="14">
@@ -4679,53 +4681,53 @@
         <v>31</v>
       </c>
       <c r="C94" s="8">
-        <f>C18*2</f>
+        <f t="shared" si="7"/>
         <v>110</v>
       </c>
       <c r="D94" s="8">
-        <f>C94*D18</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E94" s="8">
-        <f>C94*E18</f>
+        <f t="shared" ref="E94:E101" si="23">C94*E18</f>
         <v>110</v>
       </c>
       <c r="F94" s="8">
-        <f>C94*F18</f>
+        <f t="shared" ref="F94:F101" si="24">C94*F18</f>
         <v>110</v>
       </c>
       <c r="G94" s="8">
-        <f>C94*G18</f>
+        <f t="shared" ref="G94:G101" si="25">C94*G18</f>
         <v>0</v>
       </c>
       <c r="H94" s="8">
-        <f>C94*H18</f>
+        <f t="shared" ref="H94:H101" si="26">C94*H18</f>
         <v>0</v>
       </c>
       <c r="I94" s="8">
-        <f>C94*I18</f>
+        <f t="shared" ref="I94:I101" si="27">C94*I18</f>
         <v>0</v>
       </c>
       <c r="J94" s="8">
-        <f>C94*J18</f>
+        <f t="shared" ref="J94:J101" si="28">C94*J18</f>
         <v>0</v>
       </c>
       <c r="K94" s="8">
-        <f>C94*K18</f>
+        <f t="shared" ref="K94:K101" si="29">C94*K18</f>
         <v>0</v>
       </c>
       <c r="L94" s="8">
-        <f>C94*L18</f>
+        <f t="shared" ref="L94:L101" si="30">C94*L18</f>
         <v>0</v>
       </c>
       <c r="M94" s="8">
-        <f>C94*M18</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N94" s="8"/>
       <c r="O94" s="8"/>
       <c r="P94" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>220</v>
       </c>
       <c r="Q94" s="8">
@@ -4741,53 +4743,53 @@
         <v>32</v>
       </c>
       <c r="C95" s="8">
-        <f>C19*2</f>
+        <f t="shared" si="7"/>
         <v>108</v>
       </c>
       <c r="D95" s="8">
-        <f>C95*D19</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E95" s="8">
-        <f>C95*E19</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F95" s="8">
-        <f>C95*F19</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G95" s="8">
-        <f>C95*G19</f>
+        <f t="shared" si="25"/>
         <v>108</v>
       </c>
       <c r="H95" s="8">
-        <f>C95*H19</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I95" s="8">
-        <f>C95*I19</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J95" s="8">
-        <f>C95*J19</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K95" s="8">
-        <f>C95*K19</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L95" s="8">
-        <f>C95*L19</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M95" s="8">
-        <f>C95*M19</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N95" s="8"/>
       <c r="O95" s="8"/>
       <c r="P95" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>108</v>
       </c>
       <c r="Q95" s="8"/>
@@ -4800,53 +4802,53 @@
         <v>33</v>
       </c>
       <c r="C96" s="8">
-        <f>C20*2</f>
+        <f t="shared" si="7"/>
         <v>110</v>
       </c>
       <c r="D96" s="8">
-        <f>C96*D20</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E96" s="8">
-        <f>C96*E20</f>
+        <f t="shared" si="23"/>
         <v>110</v>
       </c>
       <c r="F96" s="8">
-        <f>C96*F20</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G96" s="8">
-        <f>C96*G20</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H96" s="8">
-        <f>C96*H20</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I96" s="8">
-        <f>C96*I20</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J96" s="8">
-        <f>C96*J20</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K96" s="8">
-        <f>C96*K20</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L96" s="8">
-        <f>C96*L20</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M96" s="8">
-        <f>C96*M20</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N96" s="8"/>
       <c r="O96" s="8"/>
       <c r="P96" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>110</v>
       </c>
       <c r="Q96" s="8"/>
@@ -4859,53 +4861,53 @@
         <v>34</v>
       </c>
       <c r="C97" s="8">
-        <f>C21*2</f>
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
       <c r="D97" s="8">
-        <f>C97*D21</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E97" s="8">
-        <f>C97*E21</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F97" s="8">
-        <f>C97*F21</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G97" s="8">
-        <f>C97*G21</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H97" s="8">
-        <f>C97*H21</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I97" s="8">
-        <f>C97*I21</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J97" s="8">
-        <f>C97*J21</f>
+        <f t="shared" si="28"/>
         <v>92</v>
       </c>
       <c r="K97" s="8">
-        <f>C97*K21</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L97" s="8">
-        <f>C97*L21</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M97" s="8">
-        <f>C97*M21</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N97" s="8"/>
       <c r="O97" s="8"/>
       <c r="P97" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>92</v>
       </c>
       <c r="Q97" s="8"/>
@@ -4918,53 +4920,53 @@
         <v>35</v>
       </c>
       <c r="C98" s="8">
-        <f>C22*2</f>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="D98" s="8">
-        <f>C98*D22</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E98" s="8">
-        <f>C98*E22</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F98" s="8">
-        <f>C98*F22</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G98" s="8">
-        <f>C98*G22</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H98" s="8">
-        <f>C98*H22</f>
+        <f t="shared" si="26"/>
         <v>94</v>
       </c>
       <c r="I98" s="8">
-        <f>C98*I22</f>
+        <f t="shared" si="27"/>
         <v>188</v>
       </c>
       <c r="J98" s="8">
-        <f>C98*J22</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K98" s="8">
-        <f>C98*K22</f>
+        <f t="shared" si="29"/>
         <v>94</v>
       </c>
       <c r="L98" s="8">
-        <f>C98*L22</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M98" s="8">
-        <f>C98*M22</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N98" s="8"/>
       <c r="O98" s="8"/>
       <c r="P98" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>376</v>
       </c>
       <c r="Q98" s="8"/>
@@ -4977,57 +4979,57 @@
         <v>101</v>
       </c>
       <c r="C99" s="14">
-        <f>C23*2</f>
+        <f t="shared" si="7"/>
         <v>800</v>
       </c>
       <c r="D99" s="14">
-        <f>C99*D23</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E99" s="14">
-        <f>C99*E23</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F99" s="14">
-        <f>C99*F23</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G99" s="14">
-        <f>C99*G23</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <f>C99*H23</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I99" s="14">
-        <f>C99*I23</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J99" s="14">
-        <f>C99*J23</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K99" s="14">
-        <f>C99*K23</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L99" s="14">
-        <f>C99*L23</f>
+        <f t="shared" si="30"/>
         <v>800</v>
       </c>
       <c r="M99" s="14">
-        <f>C99*M23</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N99" s="14"/>
       <c r="O99" s="14"/>
       <c r="P99" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>800</v>
       </c>
       <c r="Q99" s="14">
-        <f t="shared" ref="Q99:Q104" si="7">P99</f>
+        <f t="shared" ref="Q99:Q104" si="31">P99</f>
         <v>800</v>
       </c>
     </row>
@@ -5039,57 +5041,57 @@
         <v>37</v>
       </c>
       <c r="C100" s="8">
-        <f>C24*2</f>
+        <f t="shared" si="7"/>
         <v>726</v>
       </c>
       <c r="D100" s="8">
-        <f>C100*D24</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E100" s="8">
-        <f>C100*E24</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F100" s="8">
-        <f>C100*F24</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G100" s="8">
-        <f>C100*G24</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H100" s="8">
-        <f>C100*H24</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I100" s="8">
-        <f>C100*I24</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J100" s="8">
-        <f>C100*J24</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K100" s="8">
-        <f>C100*K24</f>
+        <f t="shared" si="29"/>
         <v>726</v>
       </c>
       <c r="L100" s="8">
-        <f>C100*L24</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M100" s="8">
-        <f>C100*M24</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N100" s="8"/>
       <c r="O100" s="8"/>
       <c r="P100" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>726</v>
       </c>
       <c r="Q100" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="31"/>
         <v>726</v>
       </c>
     </row>
@@ -5101,47 +5103,47 @@
         <v>95</v>
       </c>
       <c r="C101" s="14">
-        <f>C25*2</f>
+        <f t="shared" si="7"/>
         <v>186</v>
       </c>
       <c r="D101" s="14">
-        <f>C101*D25</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E101" s="14">
-        <f>C101*E25</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="F101" s="14">
-        <f>C101*F25</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G101" s="14">
-        <f>C101*G25</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
-        <f>C101*H25</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="I101" s="14">
-        <f>C101*I25</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="J101" s="14">
-        <f>C101*J25</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K101" s="14">
-        <f>C101*K25</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L101" s="14">
-        <f>C101*L25</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M101" s="14">
-        <f>C101*M25</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N101" s="14"/>
@@ -5194,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="8">
-        <f>C102*M26</f>
+        <f t="shared" si="21"/>
         <v>348</v>
       </c>
       <c r="N102" s="8"/>
@@ -5220,35 +5222,35 @@
         <v>418</v>
       </c>
       <c r="D103" s="14">
-        <f>C103*D28</f>
+        <f t="shared" ref="D103:K103" si="32">C103*D28</f>
         <v>0</v>
       </c>
       <c r="E103" s="14">
-        <f>D103*E28</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="F103" s="14">
-        <f>E103*F28</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="G103" s="14">
-        <f>F103*G28</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
-        <f>G103*H28</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="I103" s="14">
-        <f>H103*I28</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J103" s="14">
-        <f>I103*J28</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K103" s="14">
-        <f>J103*K28</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L103" s="14">
@@ -5256,17 +5258,17 @@
         <v>418</v>
       </c>
       <c r="M103" s="14">
-        <f>C103*M27</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N103" s="14"/>
       <c r="O103" s="14"/>
       <c r="P103" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>418</v>
       </c>
       <c r="Q103" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="31"/>
         <v>418</v>
       </c>
     </row>
@@ -5278,11 +5280,11 @@
         <v>39</v>
       </c>
       <c r="C104" s="8">
-        <f>C28*2</f>
+        <f t="shared" ref="C104:C116" si="33">C28*2</f>
         <v>516</v>
       </c>
       <c r="D104" s="8">
-        <f>C104*D28</f>
+        <f t="shared" ref="D104:D116" si="34">C104*D28</f>
         <v>0</v>
       </c>
       <c r="E104" s="8">
@@ -5298,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="8">
-        <f>C104*H28</f>
+        <f t="shared" ref="H104:H116" si="35">C104*H28</f>
         <v>0</v>
       </c>
       <c r="I104" s="8">
@@ -5318,17 +5320,17 @@
         <v>0</v>
       </c>
       <c r="M104" s="8">
-        <f>C104*M28</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N104" s="8"/>
       <c r="O104" s="8"/>
       <c r="P104" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>516</v>
       </c>
       <c r="Q104" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="31"/>
         <v>516</v>
       </c>
     </row>
@@ -5340,11 +5342,11 @@
         <v>45</v>
       </c>
       <c r="C105" s="14">
-        <f>C29*2</f>
+        <f t="shared" si="33"/>
         <v>50</v>
       </c>
       <c r="D105" s="14">
-        <f>C105*D29</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E105" s="14">
@@ -5360,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="H105" s="14">
-        <f>C105*H29</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I105" s="14">
@@ -5380,13 +5382,13 @@
         <v>0</v>
       </c>
       <c r="M105" s="14">
-        <f>C105*M29</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="N105" s="14"/>
       <c r="O105" s="14"/>
       <c r="P105" s="14">
-        <f t="shared" ref="P105:P110" si="8">SUM(D105:M105)</f>
+        <f t="shared" ref="P105:P110" si="36">SUM(D105:M105)</f>
         <v>100</v>
       </c>
       <c r="Q105" s="14">
@@ -5402,11 +5404,11 @@
         <v>128</v>
       </c>
       <c r="C106" s="14">
-        <f>C30*2</f>
+        <f t="shared" si="33"/>
         <v>38</v>
       </c>
       <c r="D106" s="14">
-        <f>C106*D30</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E106" s="14">
@@ -5422,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="14">
-        <f>C106*H30</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I106" s="14">
@@ -5448,7 +5450,7 @@
       <c r="N106" s="14"/>
       <c r="O106" s="14"/>
       <c r="P106" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="Q106" s="14"/>
@@ -5461,53 +5463,53 @@
         <v>46</v>
       </c>
       <c r="C107" s="14">
-        <f>C31*2</f>
+        <f t="shared" si="33"/>
         <v>54</v>
       </c>
       <c r="D107" s="14">
-        <f>C107*D31</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E107" s="14">
-        <f>C107*E31</f>
+        <f t="shared" ref="E107:E116" si="37">C107*E31</f>
         <v>0</v>
       </c>
       <c r="F107" s="14">
-        <f>C107*F31</f>
+        <f t="shared" ref="F107:F116" si="38">C107*F31</f>
         <v>0</v>
       </c>
       <c r="G107" s="14">
-        <f>C107*G31</f>
+        <f t="shared" ref="G107:G116" si="39">C107*G31</f>
         <v>54</v>
       </c>
       <c r="H107" s="14">
-        <f>C107*H31</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I107" s="14">
-        <f>C107*I31</f>
+        <f t="shared" ref="I107:I116" si="40">C107*I31</f>
         <v>54</v>
       </c>
       <c r="J107" s="14">
-        <f>C107*J31</f>
+        <f t="shared" ref="J107:J116" si="41">C107*J31</f>
         <v>108</v>
       </c>
       <c r="K107" s="14">
-        <f>C107*K31</f>
+        <f t="shared" ref="K107:K116" si="42">C107*K31</f>
         <v>0</v>
       </c>
       <c r="L107" s="14">
-        <f>C107*L31</f>
+        <f t="shared" ref="L107:L116" si="43">C107*L31</f>
         <v>0</v>
       </c>
       <c r="M107" s="14">
-        <f>C107*M31</f>
+        <f t="shared" ref="M107:M116" si="44">C107*M31</f>
         <v>0</v>
       </c>
       <c r="N107" s="20"/>
       <c r="O107" s="20"/>
       <c r="P107" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="36"/>
         <v>216</v>
       </c>
       <c r="Q107" s="14"/>
@@ -5520,53 +5522,53 @@
         <v>47</v>
       </c>
       <c r="C108" s="14">
-        <f>C32*2</f>
+        <f t="shared" si="33"/>
         <v>54</v>
       </c>
       <c r="D108" s="14">
-        <f>C108*D32</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E108" s="14">
-        <f>C108*E32</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F108" s="14">
-        <f>C108*F32</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="G108" s="14">
-        <f>C108*G32</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="H108" s="14">
-        <f>C108*H32</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f>C108*I32</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="J108" s="14">
-        <f>C108*J32</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K108" s="14">
-        <f>C108*K32</f>
+        <f t="shared" si="42"/>
         <v>54</v>
       </c>
       <c r="L108" s="14">
-        <f>C108*L32</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M108" s="14">
-        <f>C108*M32</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N108" s="14"/>
       <c r="O108" s="14"/>
       <c r="P108" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="36"/>
         <v>54</v>
       </c>
       <c r="Q108" s="14"/>
@@ -5579,53 +5581,53 @@
         <v>48</v>
       </c>
       <c r="C109" s="14">
-        <f>C33*2</f>
+        <f t="shared" si="33"/>
         <v>54</v>
       </c>
       <c r="D109" s="14">
-        <f>C109*D33</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E109" s="14">
-        <f>C109*E33</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F109" s="14">
-        <f>C109*F33</f>
+        <f t="shared" si="38"/>
         <v>54</v>
       </c>
       <c r="G109" s="14">
-        <f>C109*G33</f>
+        <f t="shared" si="39"/>
         <v>108</v>
       </c>
       <c r="H109" s="14">
-        <f>C109*H33</f>
+        <f t="shared" si="35"/>
         <v>54</v>
       </c>
       <c r="I109" s="14">
-        <f>C109*I33</f>
+        <f t="shared" si="40"/>
         <v>54</v>
       </c>
       <c r="J109" s="14">
-        <f>C109*J33</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K109" s="14">
-        <f>C109*K33</f>
+        <f t="shared" si="42"/>
         <v>54</v>
       </c>
       <c r="L109" s="14">
-        <f>C109*L33</f>
+        <f t="shared" si="43"/>
         <v>54</v>
       </c>
       <c r="M109" s="14">
-        <f>C109*M33</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N109" s="14"/>
       <c r="O109" s="14"/>
       <c r="P109" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="36"/>
         <v>378</v>
       </c>
       <c r="Q109" s="14"/>
@@ -5638,53 +5640,53 @@
         <v>49</v>
       </c>
       <c r="C110" s="14">
-        <f>C34*2</f>
+        <f t="shared" si="33"/>
         <v>62</v>
       </c>
       <c r="D110" s="14">
-        <f>C110*D34</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E110" s="14">
-        <f>C110*E34</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F110" s="14">
-        <f>C110*F34</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="G110" s="14">
-        <f>C110*G34</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <f>C110*H34</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I110" s="14">
-        <f>C110*I34</f>
+        <f t="shared" si="40"/>
         <v>62</v>
       </c>
       <c r="J110" s="14">
-        <f>C110*J34</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K110" s="14">
-        <f>C110*K34</f>
+        <f t="shared" si="42"/>
         <v>186</v>
       </c>
       <c r="L110" s="14">
-        <f>C110*L34</f>
+        <f t="shared" si="43"/>
         <v>124</v>
       </c>
       <c r="M110" s="14">
-        <f>C110*M34</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N110" s="14"/>
       <c r="O110" s="14"/>
       <c r="P110" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="36"/>
         <v>372</v>
       </c>
       <c r="Q110" s="14"/>
@@ -5697,53 +5699,53 @@
         <v>41</v>
       </c>
       <c r="C111" s="8">
-        <f>C35*2</f>
+        <f t="shared" si="33"/>
         <v>158</v>
       </c>
       <c r="D111" s="8">
-        <f>C111*D35</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E111" s="8">
-        <f>C111*E35</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F111" s="8">
-        <f>C111*F35</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="G111" s="8">
-        <f>C111*G35</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="H111" s="8">
-        <f>C111*H35</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I111" s="8">
-        <f>C111*I35</f>
+        <f t="shared" si="40"/>
         <v>158</v>
       </c>
       <c r="J111" s="8">
-        <f>C111*J35</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K111" s="8">
-        <f>C111*K35</f>
+        <f t="shared" si="42"/>
         <v>158</v>
       </c>
       <c r="L111" s="8">
-        <f>C111*L35</f>
+        <f t="shared" si="43"/>
         <v>158</v>
       </c>
       <c r="M111" s="8">
-        <f>C111*M35</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N111" s="8"/>
       <c r="O111" s="8"/>
       <c r="P111" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>474</v>
       </c>
       <c r="Q111" s="8">
@@ -5759,53 +5761,53 @@
         <v>42</v>
       </c>
       <c r="C112" s="8">
-        <f>C36*2</f>
+        <f t="shared" si="33"/>
         <v>140</v>
       </c>
       <c r="D112" s="8">
-        <f>C112*D36</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E112" s="8">
-        <f>C112*E36</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F112" s="8">
-        <f>C112*F36</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="G112" s="8">
-        <f>C112*G36</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="H112" s="8">
-        <f>C112*H36</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I112" s="8">
-        <f>C112*I36</f>
+        <f t="shared" si="40"/>
         <v>280</v>
       </c>
       <c r="J112" s="8">
-        <f>C112*J36</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K112" s="8">
-        <f>C112*K36</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L112" s="8">
-        <f>C112*L36</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M112" s="8">
-        <f>C112*M36</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N112" s="8"/>
       <c r="O112" s="8"/>
       <c r="P112" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>280</v>
       </c>
       <c r="Q112" s="8"/>
@@ -5818,53 +5820,53 @@
         <v>43</v>
       </c>
       <c r="C113" s="8">
-        <f>C37*2</f>
+        <f t="shared" si="33"/>
         <v>132</v>
       </c>
       <c r="D113" s="8">
-        <f>C113*D37</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E113" s="8">
-        <f>C113*E37</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F113" s="8">
-        <f>C113*F37</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="G113" s="8">
-        <f>C113*G37</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="H113" s="8">
-        <f>C113*H37</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I113" s="8">
-        <f>C113*I37</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="J113" s="8">
-        <f>C113*J37</f>
+        <f t="shared" si="41"/>
         <v>132</v>
       </c>
       <c r="K113" s="8">
-        <f>C113*K37</f>
+        <f t="shared" si="42"/>
         <v>132</v>
       </c>
       <c r="L113" s="8">
-        <f>C113*L37</f>
+        <f t="shared" si="43"/>
         <v>132</v>
       </c>
       <c r="M113" s="8">
-        <f>C113*M37</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N113" s="8"/>
       <c r="O113" s="8"/>
       <c r="P113" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>396</v>
       </c>
       <c r="Q113" s="8"/>
@@ -5877,53 +5879,53 @@
         <v>51</v>
       </c>
       <c r="C114" s="14">
-        <f>C38*2</f>
+        <f t="shared" si="33"/>
         <v>840</v>
       </c>
       <c r="D114" s="14">
-        <f>C114*D38</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E114" s="14">
-        <f>C114*E38</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F114" s="14">
-        <f>C114*F38</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="G114" s="14">
-        <f>C114*G38</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <f>C114*H38</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I114" s="14">
-        <f>C114*I38</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="J114" s="14">
-        <f>C114*J38</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K114" s="14">
-        <f>C114*K38</f>
+        <f t="shared" si="42"/>
         <v>840</v>
       </c>
       <c r="L114" s="14">
-        <f>C114*L38</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M114" s="14">
-        <f>C114*M38</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N114" s="14"/>
       <c r="O114" s="14"/>
       <c r="P114" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>840</v>
       </c>
       <c r="Q114" s="14">
@@ -5939,53 +5941,53 @@
         <v>53</v>
       </c>
       <c r="C115" s="8">
-        <f>C39*2</f>
+        <f t="shared" si="33"/>
         <v>282</v>
       </c>
       <c r="D115" s="8">
-        <f>C115*D39</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E115" s="8">
-        <f>C115*E39</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="F115" s="8">
-        <f>C115*F39</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="G115" s="8">
-        <f>C115*G39</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="H115" s="8">
-        <f>C115*H39</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I115" s="8">
-        <f>C115*I39</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="J115" s="8">
-        <f>C115*J39</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K115" s="8">
-        <f>C115*K39</f>
+        <f t="shared" si="42"/>
         <v>282</v>
       </c>
       <c r="L115" s="8">
-        <f>C115*L39</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M115" s="8">
-        <f>C115*M39</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N115" s="8"/>
       <c r="O115" s="8"/>
       <c r="P115" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>282</v>
       </c>
       <c r="Q115" s="8">
@@ -6001,53 +6003,53 @@
         <v>55</v>
       </c>
       <c r="C116" s="14">
-        <f>C40*2</f>
+        <f t="shared" si="33"/>
         <v>160</v>
       </c>
       <c r="D116" s="14">
-        <f>C116*D40</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="E116" s="14">
-        <f>C116*E40</f>
+        <f t="shared" si="37"/>
         <v>160</v>
       </c>
       <c r="F116" s="14">
-        <f>C116*F40</f>
+        <f t="shared" si="38"/>
         <v>160</v>
       </c>
       <c r="G116" s="14">
-        <f>C116*G40</f>
+        <f t="shared" si="39"/>
         <v>320</v>
       </c>
       <c r="H116" s="14">
-        <f>C116*H40</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="I116" s="14">
-        <f>C116*I40</f>
+        <f t="shared" si="40"/>
         <v>480</v>
       </c>
       <c r="J116" s="14">
-        <f>C116*J40</f>
+        <f t="shared" si="41"/>
         <v>160</v>
       </c>
       <c r="K116" s="14">
-        <f>C116*K40</f>
+        <f t="shared" si="42"/>
         <v>160</v>
       </c>
       <c r="L116" s="14">
-        <f>C116*L40</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M116" s="14">
-        <f>C116*M40</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N116" s="14"/>
       <c r="O116" s="14"/>
       <c r="P116" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1440</v>
       </c>
       <c r="Q116" s="14">
@@ -6063,53 +6065,53 @@
         <v>119</v>
       </c>
       <c r="C117" s="8">
-        <f t="shared" ref="C117:C141" si="9">C41*2</f>
+        <f t="shared" ref="C117:C141" si="45">C41*2</f>
         <v>1044</v>
       </c>
       <c r="D117" s="8">
-        <f t="shared" ref="D117:D135" si="10">C117*D41</f>
+        <f t="shared" ref="D117:D135" si="46">C117*D41</f>
         <v>0</v>
       </c>
       <c r="E117" s="8">
-        <f t="shared" ref="E117:E135" si="11">C117*E41</f>
+        <f t="shared" ref="E117:E135" si="47">C117*E41</f>
         <v>0</v>
       </c>
       <c r="F117" s="8">
-        <f t="shared" ref="F117:F135" si="12">C117*F41</f>
+        <f t="shared" ref="F117:F135" si="48">C117*F41</f>
         <v>0</v>
       </c>
       <c r="G117" s="8">
-        <f t="shared" ref="G117:G135" si="13">C117*G41</f>
+        <f t="shared" ref="G117:G135" si="49">C117*G41</f>
         <v>0</v>
       </c>
       <c r="H117" s="8">
-        <f t="shared" ref="H117:H135" si="14">C117*H41</f>
+        <f t="shared" ref="H117:H135" si="50">C117*H41</f>
         <v>0</v>
       </c>
       <c r="I117" s="8">
-        <f t="shared" ref="I117:I135" si="15">C117*I41</f>
+        <f t="shared" ref="I117:I135" si="51">C117*I41</f>
         <v>0</v>
       </c>
       <c r="J117" s="8">
-        <f t="shared" ref="J117:J135" si="16">C117*J41</f>
+        <f t="shared" ref="J117:J135" si="52">C117*J41</f>
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <f t="shared" ref="K117:K135" si="17">C117*K41</f>
+        <f t="shared" ref="K117:K135" si="53">C117*K41</f>
         <v>0</v>
       </c>
       <c r="L117" s="8">
-        <f t="shared" ref="L117:L141" si="18">C117*L41</f>
+        <f t="shared" ref="L117:L141" si="54">C117*L41</f>
         <v>0</v>
       </c>
       <c r="M117" s="8">
-        <f t="shared" ref="M117:M141" si="19">C117*M41</f>
+        <f t="shared" ref="M117:M141" si="55">C117*M41</f>
         <v>1044</v>
       </c>
       <c r="N117" s="8"/>
       <c r="O117" s="8"/>
       <c r="P117" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1044</v>
       </c>
       <c r="Q117" s="8">
@@ -6125,53 +6127,53 @@
         <v>57</v>
       </c>
       <c r="C118" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>68</v>
       </c>
       <c r="D118" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E118" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F118" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G118" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>68</v>
       </c>
       <c r="H118" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I118" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>136</v>
       </c>
       <c r="J118" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K118" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>136</v>
       </c>
       <c r="L118" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>68</v>
       </c>
       <c r="M118" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N118" s="14"/>
       <c r="O118" s="14"/>
       <c r="P118" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>408</v>
       </c>
       <c r="Q118" s="14">
@@ -6187,53 +6189,53 @@
         <v>58</v>
       </c>
       <c r="C119" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>90</v>
       </c>
       <c r="D119" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E119" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F119" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>90</v>
       </c>
       <c r="G119" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J119" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K119" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L119" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M119" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N119" s="14"/>
       <c r="O119" s="14"/>
       <c r="P119" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="Q119" s="14"/>
@@ -6246,53 +6248,53 @@
         <v>60</v>
       </c>
       <c r="C120" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>264</v>
       </c>
       <c r="D120" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E120" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F120" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G120" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H120" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>264</v>
       </c>
       <c r="I120" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J120" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K120" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L120" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M120" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N120" s="8"/>
       <c r="O120" s="8"/>
       <c r="P120" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>264</v>
       </c>
       <c r="Q120" s="8">
@@ -6308,53 +6310,53 @@
         <v>61</v>
       </c>
       <c r="C121" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>262</v>
       </c>
       <c r="D121" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E121" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F121" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>262</v>
       </c>
       <c r="G121" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H121" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I121" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J121" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K121" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L121" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M121" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N121" s="8"/>
       <c r="O121" s="8"/>
       <c r="P121" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>262</v>
       </c>
       <c r="Q121" s="8"/>
@@ -6367,53 +6369,53 @@
         <v>62</v>
       </c>
       <c r="C122" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>262</v>
       </c>
       <c r="D122" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>262</v>
       </c>
       <c r="E122" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F122" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G122" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H122" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I122" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J122" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K122" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>262</v>
       </c>
       <c r="L122" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M122" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N122" s="8"/>
       <c r="O122" s="8"/>
       <c r="P122" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>524</v>
       </c>
       <c r="Q122" s="8"/>
@@ -6426,53 +6428,53 @@
         <v>64</v>
       </c>
       <c r="C123" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>272</v>
       </c>
       <c r="D123" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E123" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F123" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G123" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I123" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J123" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>544</v>
       </c>
       <c r="K123" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>272</v>
       </c>
       <c r="L123" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M123" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N123" s="14"/>
       <c r="O123" s="14"/>
       <c r="P123" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>816</v>
       </c>
       <c r="Q123" s="14">
@@ -6488,53 +6490,53 @@
         <v>66</v>
       </c>
       <c r="C124" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>266</v>
       </c>
       <c r="D124" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E124" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F124" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G124" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H124" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>266</v>
       </c>
       <c r="I124" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J124" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K124" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>266</v>
       </c>
       <c r="L124" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M124" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N124" s="8"/>
       <c r="O124" s="8"/>
       <c r="P124" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>532</v>
       </c>
       <c r="Q124" s="8">
@@ -6550,53 +6552,53 @@
         <v>67</v>
       </c>
       <c r="C125" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>304</v>
       </c>
       <c r="D125" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E125" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F125" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G125" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H125" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I125" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J125" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K125" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>304</v>
       </c>
       <c r="L125" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M125" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N125" s="8"/>
       <c r="O125" s="8"/>
       <c r="P125" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>304</v>
       </c>
       <c r="Q125" s="8"/>
@@ -6609,53 +6611,53 @@
         <v>68</v>
       </c>
       <c r="C126" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>254</v>
       </c>
       <c r="D126" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E126" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F126" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G126" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H126" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I126" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>254</v>
       </c>
       <c r="J126" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K126" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L126" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M126" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N126" s="8"/>
       <c r="O126" s="8"/>
       <c r="P126" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>254</v>
       </c>
       <c r="Q126" s="8"/>
@@ -6668,53 +6670,53 @@
         <v>69</v>
       </c>
       <c r="C127" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>306</v>
       </c>
       <c r="D127" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E127" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F127" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G127" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H127" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I127" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>306</v>
       </c>
       <c r="J127" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K127" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L127" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M127" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N127" s="8"/>
       <c r="O127" s="8"/>
       <c r="P127" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>306</v>
       </c>
       <c r="Q127" s="8"/>
@@ -6727,58 +6729,58 @@
         <v>71</v>
       </c>
       <c r="C128" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>124</v>
       </c>
       <c r="D128" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E128" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>124</v>
       </c>
       <c r="F128" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G128" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>124</v>
       </c>
       <c r="I128" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J128" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>248</v>
       </c>
       <c r="K128" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L128" s="14">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f t="shared" si="54"/>
+        <v>124</v>
       </c>
       <c r="M128" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N128" s="14"/>
       <c r="O128" s="14"/>
       <c r="P128" s="14">
-        <f t="shared" si="6"/>
-        <v>496</v>
+        <f t="shared" si="9"/>
+        <v>620</v>
       </c>
       <c r="Q128" s="14">
         <f>SUM(P128:P130)</f>
-        <v>880</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="129" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6789,53 +6791,53 @@
         <v>72</v>
       </c>
       <c r="C129" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>130</v>
       </c>
       <c r="D129" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E129" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F129" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G129" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>260</v>
       </c>
       <c r="H129" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I129" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J129" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K129" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L129" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M129" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N129" s="14"/>
       <c r="O129" s="14"/>
       <c r="P129" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>260</v>
       </c>
       <c r="Q129" s="14"/>
@@ -6848,53 +6850,53 @@
         <v>73</v>
       </c>
       <c r="C130" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>124</v>
       </c>
       <c r="D130" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E130" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F130" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G130" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I130" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J130" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K130" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>124</v>
       </c>
       <c r="L130" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M130" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N130" s="14"/>
       <c r="O130" s="14"/>
       <c r="P130" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>124</v>
       </c>
       <c r="Q130" s="14"/>
@@ -6907,53 +6909,53 @@
         <v>124</v>
       </c>
       <c r="C131" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>90</v>
       </c>
       <c r="D131" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E131" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F131" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G131" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H131" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I131" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J131" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>90</v>
       </c>
       <c r="K131" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L131" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M131" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N131" s="8"/>
       <c r="O131" s="8"/>
       <c r="P131" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="Q131" s="8">
@@ -6969,53 +6971,53 @@
         <v>76</v>
       </c>
       <c r="C132" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>106</v>
       </c>
       <c r="D132" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>106</v>
       </c>
       <c r="E132" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F132" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G132" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H132" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I132" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J132" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K132" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L132" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M132" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N132" s="8"/>
       <c r="O132" s="8"/>
       <c r="P132" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>106</v>
       </c>
       <c r="Q132" s="8"/>
@@ -7028,53 +7030,53 @@
         <v>77</v>
       </c>
       <c r="C133" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>90</v>
       </c>
       <c r="D133" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E133" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>90</v>
       </c>
       <c r="F133" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G133" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H133" s="8">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I133" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J133" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K133" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L133" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M133" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N133" s="8"/>
       <c r="O133" s="8"/>
       <c r="P133" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>90</v>
       </c>
       <c r="Q133" s="8"/>
@@ -7087,53 +7089,53 @@
         <v>79</v>
       </c>
       <c r="C134" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>40</v>
       </c>
       <c r="D134" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E134" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F134" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G134" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>80</v>
       </c>
       <c r="H134" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I134" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>160</v>
       </c>
       <c r="J134" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>160</v>
       </c>
       <c r="K134" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="L134" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>40</v>
       </c>
       <c r="M134" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N134" s="14"/>
       <c r="O134" s="14"/>
       <c r="P134" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>440</v>
       </c>
       <c r="Q134" s="14">
@@ -7149,53 +7151,53 @@
         <v>80</v>
       </c>
       <c r="C135" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>34</v>
       </c>
       <c r="D135" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="E135" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="F135" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="G135" s="14">
-        <f t="shared" si="13"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H135" s="14">
-        <f t="shared" si="14"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="I135" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J135" s="14">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="K135" s="14">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>136</v>
       </c>
       <c r="L135" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>68</v>
       </c>
       <c r="M135" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N135" s="14"/>
       <c r="O135" s="14"/>
       <c r="P135" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>204</v>
       </c>
       <c r="Q135" s="14"/>
@@ -7208,7 +7210,7 @@
         <v>102</v>
       </c>
       <c r="C136" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>34</v>
       </c>
       <c r="D136" s="14">
@@ -7236,17 +7238,17 @@
         <v>0</v>
       </c>
       <c r="L136" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>68</v>
       </c>
       <c r="M136" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N136" s="14"/>
       <c r="O136" s="14"/>
       <c r="P136" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>68</v>
       </c>
       <c r="Q136" s="14"/>
@@ -7259,7 +7261,7 @@
         <v>82</v>
       </c>
       <c r="C137" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>248</v>
       </c>
       <c r="D137" s="8">
@@ -7295,17 +7297,17 @@
         <v>0</v>
       </c>
       <c r="L137" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M137" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N137" s="8"/>
       <c r="O137" s="8"/>
       <c r="P137" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>1240</v>
       </c>
       <c r="Q137" s="8">
@@ -7321,7 +7323,7 @@
         <v>84</v>
       </c>
       <c r="C138" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>124</v>
       </c>
       <c r="D138" s="14">
@@ -7357,17 +7359,17 @@
         <v>0</v>
       </c>
       <c r="L138" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M138" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N138" s="14"/>
       <c r="O138" s="14"/>
       <c r="P138" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>248</v>
       </c>
       <c r="Q138" s="14">
@@ -7383,7 +7385,7 @@
         <v>85</v>
       </c>
       <c r="C139" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>118</v>
       </c>
       <c r="D139" s="14">
@@ -7419,17 +7421,17 @@
         <v>0</v>
       </c>
       <c r="L139" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M139" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N139" s="14"/>
       <c r="O139" s="14"/>
       <c r="P139" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>118</v>
       </c>
       <c r="Q139" s="14"/>
@@ -7442,7 +7444,7 @@
         <v>86</v>
       </c>
       <c r="C140" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>116</v>
       </c>
       <c r="D140" s="14">
@@ -7478,17 +7480,17 @@
         <v>0</v>
       </c>
       <c r="L140" s="14">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M140" s="14">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N140" s="14"/>
       <c r="O140" s="14"/>
       <c r="P140" s="14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>116</v>
       </c>
       <c r="Q140" s="14"/>
@@ -7501,7 +7503,7 @@
         <v>88</v>
       </c>
       <c r="C141" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="45"/>
         <v>138</v>
       </c>
       <c r="D141" s="8">
@@ -7537,17 +7539,17 @@
         <v>0</v>
       </c>
       <c r="L141" s="8">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="M141" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="N141" s="8"/>
       <c r="O141" s="8"/>
       <c r="P141" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>138</v>
       </c>
       <c r="Q141" s="8">
@@ -7605,60 +7607,60 @@
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
       <c r="D146" s="8">
-        <f t="shared" ref="D146:M146" si="20">SUM(D78:D141)</f>
+        <f t="shared" ref="D146:M146" si="56">SUM(D78:D141)</f>
         <v>750</v>
       </c>
       <c r="E146" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>892</v>
       </c>
       <c r="F146" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>1166</v>
       </c>
       <c r="G146" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>1830</v>
       </c>
       <c r="H146" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>802</v>
       </c>
       <c r="I146" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>3046</v>
       </c>
       <c r="J146" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>2704</v>
       </c>
       <c r="K146" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>4664</v>
       </c>
       <c r="L146" s="8">
-        <f t="shared" si="20"/>
-        <v>2362</v>
+        <f t="shared" si="56"/>
+        <v>2486</v>
       </c>
       <c r="M146" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>4312</v>
       </c>
       <c r="N146" s="8">
         <f>SUM(D146:M146)</f>
-        <v>22528</v>
+        <v>22652</v>
       </c>
       <c r="O146" s="15">
         <f>N146/N67</f>
-        <v>152.21621621621622</v>
+        <v>152.0268456375839</v>
       </c>
       <c r="P146" s="8">
         <f>SUM(P78:P141)</f>
-        <v>22528</v>
+        <v>22652</v>
       </c>
       <c r="Q146" s="8">
         <f>SUM(Q78:Q141)</f>
-        <v>22528</v>
+        <v>22652</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.3">
@@ -7666,48 +7668,48 @@
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
       <c r="D147" s="16">
-        <f t="shared" ref="D147:N147" si="21">D146/D67</f>
+        <f t="shared" ref="D147:N147" si="57">D146/D67</f>
         <v>150</v>
       </c>
       <c r="E147" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="57"/>
         <v>89.2</v>
       </c>
       <c r="F147" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="57"/>
         <v>116.6</v>
       </c>
       <c r="G147" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="57"/>
         <v>114.375</v>
       </c>
       <c r="H147" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="57"/>
         <v>160.4</v>
       </c>
       <c r="I147" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="57"/>
         <v>138.45454545454547</v>
       </c>
       <c r="J147" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="57"/>
         <v>142.31578947368422</v>
       </c>
       <c r="K147" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="57"/>
         <v>172.74074074074073</v>
       </c>
       <c r="L147" s="16">
-        <f t="shared" si="21"/>
-        <v>157.46666666666667</v>
+        <f t="shared" si="57"/>
+        <v>155.375</v>
       </c>
       <c r="M147" s="16">
-        <f t="shared" si="21"/>
+        <f t="shared" si="57"/>
         <v>226.94736842105263</v>
       </c>
       <c r="N147" s="16">
-        <f t="shared" si="21"/>
-        <v>152.21621621621622</v>
+        <f t="shared" si="57"/>
+        <v>152.0268456375839</v>
       </c>
       <c r="O147" s="6" t="s">
         <v>97</v>
@@ -8011,11 +8013,11 @@
       </c>
       <c r="D235">
         <f>SUM(N52:N54)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E235">
         <f>SUM(P52:P54)</f>
-        <v>880</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.3">
@@ -8107,11 +8109,11 @@
       <c r="C242" s="1"/>
       <c r="D242" s="1">
         <f>SUM(D218:D240)</f>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E242" s="1">
         <f>SUM(E218:E240)</f>
-        <v>20682</v>
+        <v>20806</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B290DA9C-DD22-481C-8AAB-3EBE078EFBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D455D5D-051A-4CD9-829C-51B557623C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -2259,18 +2259,20 @@
         <v>1</v>
       </c>
       <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
+      <c r="M33" s="14">
+        <v>4</v>
+      </c>
       <c r="N33" s="14">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O33" s="14">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>135</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="5"/>
-        <v>54</v>
+        <v>270</v>
       </c>
       <c r="Q33" s="14"/>
     </row>
@@ -3849,16 +3851,16 @@
       </c>
       <c r="M68" s="12">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="N68" s="12">
         <f>SUM(D68:M68)</f>
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>23237</v>
+        <v>23453</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
@@ -5849,7 +5851,7 @@
       </c>
       <c r="Q107" s="14">
         <f>SUM(P107:P112)</f>
-        <v>1120</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="108" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6019,13 +6021,13 @@
       </c>
       <c r="M110" s="14">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="N110" s="14"/>
       <c r="O110" s="14"/>
       <c r="P110" s="14">
         <f t="shared" si="28"/>
-        <v>54</v>
+        <v>270</v>
       </c>
       <c r="Q110" s="14"/>
     </row>
@@ -8321,23 +8323,23 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="37"/>
-        <v>4728</v>
+        <v>4944</v>
       </c>
       <c r="N148" s="8">
         <f>SUM(D148:M148)</f>
-        <v>22944</v>
+        <v>23160</v>
       </c>
       <c r="O148" s="15">
         <f>N148/N68</f>
-        <v>151.94701986754967</v>
+        <v>149.41935483870967</v>
       </c>
       <c r="P148" s="8">
         <f>SUM(P79:P143)</f>
-        <v>22944</v>
+        <v>23160</v>
       </c>
       <c r="Q148" s="8">
         <f>SUM(Q79:Q143)</f>
-        <v>22944</v>
+        <v>23160</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
@@ -8382,11 +8384,11 @@
       </c>
       <c r="M149" s="16">
         <f t="shared" si="38"/>
-        <v>225.14285714285714</v>
+        <v>197.76</v>
       </c>
       <c r="N149" s="16">
         <f t="shared" si="38"/>
-        <v>151.94701986754967</v>
+        <v>149.41935483870967</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>97</v>
@@ -8562,11 +8564,11 @@
       </c>
       <c r="D229">
         <f>SUM(N30:N35)</f>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E229">
         <f>SUM(P30:P35)</f>
-        <v>1120</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -8786,11 +8788,11 @@
       <c r="C244" s="1"/>
       <c r="D244" s="1">
         <f>SUM(D220:D242)</f>
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E244" s="1">
         <f>SUM(E220:E242)</f>
-        <v>20806</v>
+        <v>21022</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D455D5D-051A-4CD9-829C-51B557623C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569BD0FF-1310-4BF4-B946-004EC9DBF9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -1003,7 +1003,10 @@
         <f t="shared" ref="P2:P66" si="1">2*O2</f>
         <v>64</v>
       </c>
-      <c r="Q2" s="8"/>
+      <c r="Q2" s="8">
+        <f>SUM(N2:N4)</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
@@ -1197,7 +1200,10 @@
         <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="Q7" s="14"/>
+      <c r="Q7" s="14">
+        <f>SUM(N7:N9)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
@@ -1309,7 +1315,10 @@
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="Q10" s="8"/>
+      <c r="Q10" s="8">
+        <f>SUM(N10:N14)</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
@@ -1369,19 +1378,19 @@
       </c>
       <c r="L12" s="8"/>
       <c r="M12" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N12" s="8">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" s="8">
         <f t="shared" si="0"/>
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="P12" s="8">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>924</v>
       </c>
       <c r="Q12" s="8"/>
     </row>
@@ -1531,7 +1540,10 @@
         <f t="shared" si="1"/>
         <v>370</v>
       </c>
-      <c r="Q16" s="8"/>
+      <c r="Q16" s="8">
+        <f>SUM(N16:N17)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -1645,7 +1657,10 @@
         <f t="shared" si="1"/>
         <v>220</v>
       </c>
-      <c r="Q19" s="8"/>
+      <c r="Q19" s="8">
+        <f>SUM(N19:N23)</f>
+        <v>9</v>
+      </c>
       <c r="R19" s="18"/>
       <c r="S19" s="18"/>
       <c r="T19" s="18"/>
@@ -2162,7 +2177,10 @@
         <f t="shared" ref="P30:P35" si="5">2*O30</f>
         <v>100</v>
       </c>
-      <c r="Q30" s="14"/>
+      <c r="Q30" s="14">
+        <f>SUM(N30:N35)</f>
+        <v>25</v>
+      </c>
     </row>
     <row r="31" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
@@ -2183,18 +2201,20 @@
       <c r="J31" s="14"/>
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
+      <c r="M31" s="14">
+        <v>1</v>
+      </c>
       <c r="N31" s="14">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="14">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P31" s="14">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q31" s="14"/>
     </row>
@@ -2402,7 +2422,10 @@
         <f t="shared" si="1"/>
         <v>474</v>
       </c>
-      <c r="Q36" s="8"/>
+      <c r="Q36" s="8">
+        <f>SUM(N36:N38)</f>
+        <v>8</v>
+      </c>
       <c r="R36" s="18"/>
       <c r="S36" s="18"/>
       <c r="T36" s="18"/>
@@ -2749,7 +2772,10 @@
         <f t="shared" si="1"/>
         <v>408</v>
       </c>
-      <c r="Q43" s="14"/>
+      <c r="Q43" s="14">
+        <f>SUM(N43:N44)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="44" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
@@ -2823,7 +2849,10 @@
         <f t="shared" si="1"/>
         <v>264</v>
       </c>
-      <c r="Q45" s="8"/>
+      <c r="Q45" s="8">
+        <f>SUM(N45:N47)</f>
+        <v>4</v>
+      </c>
       <c r="R45" s="18"/>
       <c r="S45" s="18"/>
       <c r="T45" s="18"/>
@@ -3016,7 +3045,10 @@
         <f t="shared" si="1"/>
         <v>532</v>
       </c>
-      <c r="Q49" s="8"/>
+      <c r="Q49" s="8">
+        <f>SUM(N49:N52)</f>
+        <v>5</v>
+      </c>
       <c r="R49" s="18"/>
       <c r="S49" s="18"/>
       <c r="T49" s="18"/>
@@ -3220,7 +3252,10 @@
         <f t="shared" si="1"/>
         <v>620</v>
       </c>
-      <c r="Q53" s="14"/>
+      <c r="Q53" s="14">
+        <f>SUM(N53:N55)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="54" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
@@ -3330,7 +3365,10 @@
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="Q56" s="8"/>
+      <c r="Q56" s="8">
+        <f>SUM(N56:N58)</f>
+        <v>3</v>
+      </c>
       <c r="R56" s="18"/>
       <c r="S56" s="18"/>
       <c r="T56" s="18"/>
@@ -3485,7 +3523,10 @@
         <f t="shared" si="1"/>
         <v>440</v>
       </c>
-      <c r="Q59" s="14"/>
+      <c r="Q59" s="14">
+        <f>SUM(N59:N61)</f>
+        <v>19</v>
+      </c>
     </row>
     <row r="60" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
@@ -3656,7 +3697,10 @@
         <f t="shared" si="1"/>
         <v>248</v>
       </c>
-      <c r="Q63" s="14"/>
+      <c r="Q63" s="14">
+        <f>SUM(N63:N65)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="64" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
@@ -3851,20 +3895,20 @@
       </c>
       <c r="M68" s="12">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N68" s="12">
         <f>SUM(D68:M68)</f>
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>23453</v>
+        <v>23575</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
-        <v>65</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.3">
@@ -4617,7 +4661,7 @@
       </c>
       <c r="Q87" s="8">
         <f>SUM(P87:P91)</f>
-        <v>1204</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.3">
@@ -4728,13 +4772,13 @@
       </c>
       <c r="M89" s="8">
         <f t="shared" si="11"/>
-        <v>756</v>
+        <v>840</v>
       </c>
       <c r="N89" s="8"/>
       <c r="O89" s="8"/>
       <c r="P89" s="8">
         <f t="shared" si="9"/>
-        <v>840</v>
+        <v>924</v>
       </c>
       <c r="Q89" s="8"/>
     </row>
@@ -5851,7 +5895,7 @@
       </c>
       <c r="Q107" s="14">
         <f>SUM(P107:P112)</f>
-        <v>1336</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="108" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -5902,14 +5946,14 @@
         <v>0</v>
       </c>
       <c r="M108" s="14">
-        <f>H108*M31</f>
-        <v>0</v>
+        <f>C108*M31</f>
+        <v>38</v>
       </c>
       <c r="N108" s="14"/>
       <c r="O108" s="14"/>
       <c r="P108" s="14">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q108" s="14"/>
     </row>
@@ -8323,23 +8367,23 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="37"/>
-        <v>4944</v>
+        <v>5066</v>
       </c>
       <c r="N148" s="8">
         <f>SUM(D148:M148)</f>
-        <v>23160</v>
+        <v>23282</v>
       </c>
       <c r="O148" s="15">
         <f>N148/N68</f>
-        <v>149.41935483870967</v>
+        <v>148.29299363057325</v>
       </c>
       <c r="P148" s="8">
         <f>SUM(P79:P143)</f>
-        <v>23160</v>
+        <v>23282</v>
       </c>
       <c r="Q148" s="8">
         <f>SUM(Q79:Q143)</f>
-        <v>23160</v>
+        <v>23282</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
@@ -8384,11 +8428,11 @@
       </c>
       <c r="M149" s="16">
         <f t="shared" si="38"/>
-        <v>197.76</v>
+        <v>187.62962962962962</v>
       </c>
       <c r="N149" s="16">
         <f t="shared" si="38"/>
-        <v>149.41935483870967</v>
+        <v>148.29299363057325</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>97</v>
@@ -8468,11 +8512,11 @@
       </c>
       <c r="D223">
         <f>SUM(N10:N17)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E223">
         <f>SUM(P10:P17)</f>
-        <v>2770</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.3">
@@ -8564,11 +8608,11 @@
       </c>
       <c r="D229">
         <f>SUM(N30:N35)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E229">
         <f>SUM(P30:P35)</f>
-        <v>1336</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -8788,11 +8832,11 @@
       <c r="C244" s="1"/>
       <c r="D244" s="1">
         <f>SUM(D220:D242)</f>
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E244" s="1">
         <f>SUM(E220:E242)</f>
-        <v>21022</v>
+        <v>21144</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{569BD0FF-1310-4BF4-B946-004EC9DBF9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05EBFDB-BDB7-4862-B6B1-0722F944A1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="Q30" s="14">
         <f>SUM(N30:N35)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -2280,19 +2280,19 @@
       </c>
       <c r="L33" s="14"/>
       <c r="M33" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N33" s="14">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O33" s="14">
         <f t="shared" si="4"/>
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="5"/>
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="Q33" s="14"/>
     </row>
@@ -3895,20 +3895,20 @@
       </c>
       <c r="M68" s="12">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N68" s="12">
         <f>SUM(D68:M68)</f>
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>23575</v>
+        <v>23629</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.3">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="Q107" s="14">
         <f>SUM(P107:P112)</f>
-        <v>1374</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="108" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6065,13 +6065,13 @@
       </c>
       <c r="M110" s="14">
         <f t="shared" si="36"/>
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="N110" s="14"/>
       <c r="O110" s="14"/>
       <c r="P110" s="14">
         <f t="shared" si="28"/>
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="Q110" s="14"/>
     </row>
@@ -8367,23 +8367,23 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="37"/>
-        <v>5066</v>
+        <v>5120</v>
       </c>
       <c r="N148" s="8">
         <f>SUM(D148:M148)</f>
-        <v>23282</v>
+        <v>23336</v>
       </c>
       <c r="O148" s="15">
         <f>N148/N68</f>
-        <v>148.29299363057325</v>
+        <v>147.69620253164558</v>
       </c>
       <c r="P148" s="8">
         <f>SUM(P79:P143)</f>
-        <v>23282</v>
+        <v>23336</v>
       </c>
       <c r="Q148" s="8">
         <f>SUM(Q79:Q143)</f>
-        <v>23282</v>
+        <v>23336</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
@@ -8428,11 +8428,11 @@
       </c>
       <c r="M149" s="16">
         <f t="shared" si="38"/>
-        <v>187.62962962962962</v>
+        <v>182.85714285714286</v>
       </c>
       <c r="N149" s="16">
         <f t="shared" si="38"/>
-        <v>148.29299363057325</v>
+        <v>147.69620253164558</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>97</v>
@@ -8608,11 +8608,11 @@
       </c>
       <c r="D229">
         <f>SUM(N30:N35)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E229">
         <f>SUM(P30:P35)</f>
-        <v>1374</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -8832,11 +8832,11 @@
       <c r="C244" s="1"/>
       <c r="D244" s="1">
         <f>SUM(D220:D242)</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E244" s="1">
         <f>SUM(E220:E242)</f>
-        <v>21144</v>
+        <v>21198</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05EBFDB-BDB7-4862-B6B1-0722F944A1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C612BBE-975B-426B-8672-7C9C08C9E3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -1147,18 +1147,20 @@
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
+      <c r="M6" s="8">
+        <v>1</v>
+      </c>
       <c r="N6" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="Q6" s="8">
         <v>1</v>
@@ -2179,7 +2181,7 @@
       </c>
       <c r="Q30" s="14">
         <f>SUM(N30:N35)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -2280,19 +2282,19 @@
       </c>
       <c r="L33" s="14"/>
       <c r="M33" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N33" s="14">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O33" s="14">
         <f t="shared" si="4"/>
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="5"/>
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="Q33" s="14"/>
     </row>
@@ -3895,20 +3897,20 @@
       </c>
       <c r="M68" s="12">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N68" s="12">
         <f>SUM(D68:M68)</f>
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>23629</v>
+        <v>23831</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.3">
@@ -4417,18 +4419,18 @@
         <v>0</v>
       </c>
       <c r="M83" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f>C83*M6</f>
+        <v>148</v>
       </c>
       <c r="N83" s="8"/>
       <c r="O83" s="8"/>
       <c r="P83" s="8">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="Q83" s="8">
         <f>SUM(P83)</f>
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.3">
@@ -5895,7 +5897,7 @@
       </c>
       <c r="Q107" s="14">
         <f>SUM(P107:P112)</f>
-        <v>1428</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="108" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6065,13 +6067,13 @@
       </c>
       <c r="M110" s="14">
         <f t="shared" si="36"/>
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="N110" s="14"/>
       <c r="O110" s="14"/>
       <c r="P110" s="14">
         <f t="shared" si="28"/>
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="Q110" s="14"/>
     </row>
@@ -8367,23 +8369,23 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="37"/>
-        <v>5120</v>
+        <v>5322</v>
       </c>
       <c r="N148" s="8">
         <f>SUM(D148:M148)</f>
-        <v>23336</v>
+        <v>23538</v>
       </c>
       <c r="O148" s="15">
         <f>N148/N68</f>
-        <v>147.69620253164558</v>
+        <v>147.11250000000001</v>
       </c>
       <c r="P148" s="8">
         <f>SUM(P79:P143)</f>
-        <v>23336</v>
+        <v>23538</v>
       </c>
       <c r="Q148" s="8">
         <f>SUM(Q79:Q143)</f>
-        <v>23336</v>
+        <v>23538</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
@@ -8428,11 +8430,11 @@
       </c>
       <c r="M149" s="16">
         <f t="shared" si="38"/>
-        <v>182.85714285714286</v>
+        <v>177.4</v>
       </c>
       <c r="N149" s="16">
         <f t="shared" si="38"/>
-        <v>147.69620253164558</v>
+        <v>147.11250000000001</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>97</v>
@@ -8608,11 +8610,11 @@
       </c>
       <c r="D229">
         <f>SUM(N30:N35)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E229">
         <f>SUM(P30:P35)</f>
-        <v>1428</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -8832,11 +8834,11 @@
       <c r="C244" s="1"/>
       <c r="D244" s="1">
         <f>SUM(D220:D242)</f>
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E244" s="1">
         <f>SUM(E220:E242)</f>
-        <v>21198</v>
+        <v>21252</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C612BBE-975B-426B-8672-7C9C08C9E3CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4077F46-3568-49C9-B65B-3980A3A5BE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -565,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -587,6 +587,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -909,10 +910,11 @@
     <col min="3" max="11" width="9.77734375" customWidth="1"/>
     <col min="12" max="12" width="10.5546875" customWidth="1"/>
     <col min="13" max="16" width="9.77734375" customWidth="1"/>
-    <col min="18" max="30" width="8.88671875" style="18"/>
+    <col min="18" max="18" width="9.109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="30" width="8.88671875" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -964,8 +966,11 @@
       <c r="Q1" s="11" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R1" s="21">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
@@ -1008,7 +1013,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
@@ -1046,7 +1051,7 @@
       </c>
       <c r="Q3" s="8"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
@@ -1088,7 +1093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
@@ -1128,7 +1133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>129</v>
       </c>
@@ -1166,7 +1171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>19</v>
       </c>
@@ -1207,7 +1212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>19</v>
       </c>
@@ -1243,7 +1248,7 @@
       </c>
       <c r="Q8" s="14"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
@@ -1283,7 +1288,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>22</v>
       </c>
@@ -1322,7 +1327,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>22</v>
       </c>
@@ -1358,7 +1363,7 @@
       </c>
       <c r="Q11" s="8"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>22</v>
       </c>
@@ -1396,7 +1401,7 @@
       </c>
       <c r="Q12" s="8"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Q13" s="8"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>22</v>
       </c>
@@ -1470,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>125</v>
       </c>
@@ -1508,7 +1513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>28</v>
       </c>
@@ -2181,7 +2186,7 @@
       </c>
       <c r="Q30" s="14">
         <f>SUM(N30:N35)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -2282,19 +2287,19 @@
       </c>
       <c r="L33" s="14"/>
       <c r="M33" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N33" s="14">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O33" s="14">
         <f t="shared" si="4"/>
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="5"/>
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="Q33" s="14"/>
     </row>
@@ -3897,20 +3902,20 @@
       </c>
       <c r="M68" s="12">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N68" s="12">
         <f>SUM(D68:M68)</f>
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>23831</v>
+        <v>23885</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.3">
@@ -4387,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="8">
-        <f t="shared" ref="E83:M83" si="10">D83*E6</f>
+        <f t="shared" ref="E83:L83" si="10">D83*E6</f>
         <v>0</v>
       </c>
       <c r="F83" s="8">
@@ -5897,7 +5902,7 @@
       </c>
       <c r="Q107" s="14">
         <f>SUM(P107:P112)</f>
-        <v>1482</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="108" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -6067,13 +6072,13 @@
       </c>
       <c r="M110" s="14">
         <f t="shared" si="36"/>
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="N110" s="14"/>
       <c r="O110" s="14"/>
       <c r="P110" s="14">
         <f t="shared" si="28"/>
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="Q110" s="14"/>
     </row>
@@ -8369,23 +8374,23 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="37"/>
-        <v>5322</v>
+        <v>5376</v>
       </c>
       <c r="N148" s="8">
         <f>SUM(D148:M148)</f>
-        <v>23538</v>
+        <v>23592</v>
       </c>
       <c r="O148" s="15">
         <f>N148/N68</f>
-        <v>147.11250000000001</v>
+        <v>146.53416149068323</v>
       </c>
       <c r="P148" s="8">
         <f>SUM(P79:P143)</f>
-        <v>23538</v>
+        <v>23592</v>
       </c>
       <c r="Q148" s="8">
         <f>SUM(Q79:Q143)</f>
-        <v>23538</v>
+        <v>23592</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
@@ -8430,11 +8435,11 @@
       </c>
       <c r="M149" s="16">
         <f t="shared" si="38"/>
-        <v>177.4</v>
+        <v>173.41935483870967</v>
       </c>
       <c r="N149" s="16">
         <f t="shared" si="38"/>
-        <v>147.11250000000001</v>
+        <v>146.53416149068323</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>97</v>
@@ -8610,11 +8615,11 @@
       </c>
       <c r="D229">
         <f>SUM(N30:N35)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E229">
         <f>SUM(P30:P35)</f>
-        <v>1482</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -8834,11 +8839,11 @@
       <c r="C244" s="1"/>
       <c r="D244" s="1">
         <f>SUM(D220:D242)</f>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E244" s="1">
         <f>SUM(E220:E242)</f>
-        <v>21252</v>
+        <v>21306</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4077F46-3568-49C9-B65B-3980A3A5BE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420F5AEC-9B83-487D-BC2E-342B10FC56F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -2708,19 +2708,19 @@
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
       <c r="M42" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="0"/>
-        <v>522</v>
+        <v>1044</v>
       </c>
       <c r="P42" s="8">
         <f t="shared" si="1"/>
-        <v>1044</v>
+        <v>2088</v>
       </c>
       <c r="Q42" s="8">
         <v>1</v>
@@ -3902,16 +3902,16 @@
       </c>
       <c r="M68" s="12">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N68" s="12">
         <f>SUM(D68:M68)</f>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>23885</v>
+        <v>24929</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
@@ -6667,17 +6667,17 @@
       </c>
       <c r="M119" s="8">
         <f t="shared" si="36"/>
-        <v>1044</v>
+        <v>2088</v>
       </c>
       <c r="N119" s="8"/>
       <c r="O119" s="8"/>
       <c r="P119" s="8">
         <f t="shared" si="9"/>
-        <v>1044</v>
+        <v>2088</v>
       </c>
       <c r="Q119" s="8">
         <f>P119</f>
-        <v>1044</v>
+        <v>2088</v>
       </c>
       <c r="R119" s="18"/>
       <c r="S119" s="18"/>
@@ -8374,23 +8374,23 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="37"/>
-        <v>5376</v>
+        <v>6420</v>
       </c>
       <c r="N148" s="8">
         <f>SUM(D148:M148)</f>
-        <v>23592</v>
+        <v>24636</v>
       </c>
       <c r="O148" s="15">
         <f>N148/N68</f>
-        <v>146.53416149068323</v>
+        <v>152.07407407407408</v>
       </c>
       <c r="P148" s="8">
         <f>SUM(P79:P143)</f>
-        <v>23592</v>
+        <v>24636</v>
       </c>
       <c r="Q148" s="8">
         <f>SUM(Q79:Q143)</f>
-        <v>23592</v>
+        <v>24636</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
@@ -8435,11 +8435,11 @@
       </c>
       <c r="M149" s="16">
         <f t="shared" si="38"/>
-        <v>173.41935483870967</v>
+        <v>200.625</v>
       </c>
       <c r="N149" s="16">
         <f t="shared" si="38"/>
-        <v>146.53416149068323</v>
+        <v>152.07407407407408</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>97</v>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{420F5AEC-9B83-487D-BC2E-342B10FC56F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACB0B4F-94D0-4244-9581-89AF50C8CBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Q30" s="14">
         <f>SUM(N30:N35)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -2290,16 +2290,15 @@
         <v>7</v>
       </c>
       <c r="N33" s="14">
-        <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O33" s="14">
         <f t="shared" si="4"/>
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="5"/>
-        <v>432</v>
+        <v>486</v>
       </c>
       <c r="Q33" s="14"/>
     </row>
@@ -3911,11 +3910,11 @@
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>24929</v>
+        <v>24983</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.3">
@@ -8615,11 +8614,11 @@
       </c>
       <c r="D229">
         <f>SUM(N30:N35)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E229">
         <f>SUM(P30:P35)</f>
-        <v>1536</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -8839,11 +8838,11 @@
       <c r="C244" s="1"/>
       <c r="D244" s="1">
         <f>SUM(D220:D242)</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E244" s="1">
         <f>SUM(E220:E242)</f>
-        <v>21306</v>
+        <v>21360</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACB0B4F-94D0-4244-9581-89AF50C8CBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1ECF4C-206E-4B70-AB8D-65724E46C2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Q30" s="14">
         <f>SUM(N30:N35)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -2290,15 +2290,15 @@
         <v>7</v>
       </c>
       <c r="N33" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O33" s="14">
         <f t="shared" si="4"/>
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="5"/>
-        <v>486</v>
+        <v>540</v>
       </c>
       <c r="Q33" s="14"/>
     </row>
@@ -3910,11 +3910,11 @@
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>24983</v>
+        <v>25037</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.3">
@@ -8614,11 +8614,11 @@
       </c>
       <c r="D229">
         <f>SUM(N30:N35)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E229">
         <f>SUM(P30:P35)</f>
-        <v>1590</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.3">
@@ -8838,11 +8838,11 @@
       <c r="C244" s="1"/>
       <c r="D244" s="1">
         <f>SUM(D220:D242)</f>
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E244" s="1">
         <f>SUM(E220:E242)</f>
-        <v>21360</v>
+        <v>21414</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1ECF4C-206E-4B70-AB8D-65724E46C2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F91518-A286-48C4-A623-F9F01F6120FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -1611,18 +1611,20 @@
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
+      <c r="M18" s="14">
+        <v>1</v>
+      </c>
       <c r="N18" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="P18" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="Q18" s="14">
         <v>1</v>
@@ -3901,16 +3903,16 @@
       </c>
       <c r="M68" s="12">
         <f t="shared" si="6"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N68" s="12">
         <f>SUM(D68:M68)</f>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>25037</v>
+        <v>25273</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
@@ -5129,13 +5131,13 @@
       </c>
       <c r="M95" s="14">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="N95" s="14"/>
       <c r="O95" s="14"/>
       <c r="P95" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="Q95" s="14">
         <f>O95</f>
@@ -8373,19 +8375,19 @@
       </c>
       <c r="M148" s="8">
         <f t="shared" si="37"/>
-        <v>6420</v>
+        <v>6656</v>
       </c>
       <c r="N148" s="8">
         <f>SUM(D148:M148)</f>
-        <v>24636</v>
+        <v>24872</v>
       </c>
       <c r="O148" s="15">
         <f>N148/N68</f>
-        <v>152.07407407407408</v>
+        <v>152.58895705521473</v>
       </c>
       <c r="P148" s="8">
         <f>SUM(P79:P143)</f>
-        <v>24636</v>
+        <v>24872</v>
       </c>
       <c r="Q148" s="8">
         <f>SUM(Q79:Q143)</f>
@@ -8434,11 +8436,11 @@
       </c>
       <c r="M149" s="16">
         <f t="shared" si="38"/>
-        <v>200.625</v>
+        <v>201.69696969696969</v>
       </c>
       <c r="N149" s="16">
         <f t="shared" si="38"/>
-        <v>152.07407407407408</v>
+        <v>152.58895705521473</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>97</v>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F91518-A286-48C4-A623-F9F01F6120FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BED0825-E9FD-432A-BA01-48B1763F575C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="135">
   <si>
     <t>Paikkakunta</t>
   </si>
@@ -439,6 +439,9 @@
   </si>
   <si>
     <t>Viikin normaalikoulu</t>
+  </si>
+  <si>
+    <t>Kiurusvesi</t>
   </si>
 </sst>
 </file>
@@ -565,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -588,6 +591,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,7 +906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1185CB8-B7D3-4EC5-84DD-BC18A741831D}">
-  <dimension ref="A1:AD244"/>
+  <dimension ref="A1:AD185"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
@@ -967,7 +971,7 @@
         <v>118</v>
       </c>
       <c r="R1" s="21">
-        <v>46104</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -1009,8 +1013,7 @@
         <v>64</v>
       </c>
       <c r="Q2" s="8">
-        <f>SUM(N2:N4)</f>
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -1089,8 +1092,8 @@
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="Q4" s="8">
-        <v>3</v>
+      <c r="Q4" s="8" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -1208,8 +1211,7 @@
         <v>1112</v>
       </c>
       <c r="Q7" s="14">
-        <f>SUM(N7:N9)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -1284,9 +1286,7 @@
         <f t="shared" si="1"/>
         <v>584</v>
       </c>
-      <c r="Q9" s="14">
-        <v>3</v>
-      </c>
+      <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
@@ -1323,8 +1323,7 @@
         <v>66</v>
       </c>
       <c r="Q10" s="8">
-        <f>SUM(N10:N14)</f>
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -1471,9 +1470,7 @@
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="Q14" s="8">
-        <v>5</v>
-      </c>
+      <c r="Q14" s="8"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
@@ -1548,8 +1545,7 @@
         <v>370</v>
       </c>
       <c r="Q16" s="8">
-        <f>SUM(N16:N17)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
@@ -1588,9 +1584,7 @@
         <f t="shared" si="1"/>
         <v>832</v>
       </c>
-      <c r="Q17" s="8">
-        <v>2</v>
-      </c>
+      <c r="Q17" s="8"/>
     </row>
     <row r="18" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
@@ -1667,8 +1661,7 @@
         <v>220</v>
       </c>
       <c r="Q19" s="8">
-        <f>SUM(N19:N23)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R19" s="18"/>
       <c r="S19" s="18"/>
@@ -1869,9 +1862,7 @@
         <f t="shared" si="1"/>
         <v>376</v>
       </c>
-      <c r="Q23" s="8">
-        <v>5</v>
-      </c>
+      <c r="Q23" s="8"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
       <c r="T23" s="18"/>
@@ -1994,17 +1985,20 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
+      <c r="M26" s="14">
+        <v>1</v>
+      </c>
       <c r="N26" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="P26" s="14">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>186</v>
       </c>
       <c r="Q26" s="14">
         <v>1</v>
@@ -2187,8 +2181,7 @@
         <v>100</v>
       </c>
       <c r="Q30" s="14">
-        <f>SUM(N30:N35)</f>
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -2292,15 +2285,16 @@
         <v>7</v>
       </c>
       <c r="N33" s="14">
-        <v>10</v>
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="O33" s="14">
         <f t="shared" si="4"/>
-        <v>270</v>
+        <v>216</v>
       </c>
       <c r="P33" s="14">
         <f t="shared" si="5"/>
-        <v>540</v>
+        <v>432</v>
       </c>
       <c r="Q33" s="14"/>
     </row>
@@ -2388,9 +2382,7 @@
         <f t="shared" si="5"/>
         <v>372</v>
       </c>
-      <c r="Q35" s="14">
-        <v>6</v>
-      </c>
+      <c r="Q35" s="14"/>
     </row>
     <row r="36" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
@@ -2431,8 +2423,7 @@
         <v>474</v>
       </c>
       <c r="Q36" s="8">
-        <f>SUM(N36:N38)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R36" s="18"/>
       <c r="S36" s="18"/>
@@ -2535,9 +2526,7 @@
         <f t="shared" si="1"/>
         <v>396</v>
       </c>
-      <c r="Q38" s="8">
-        <v>3</v>
-      </c>
+      <c r="Q38" s="8"/>
       <c r="R38" s="18"/>
       <c r="S38" s="18"/>
       <c r="T38" s="18"/>
@@ -2781,8 +2770,7 @@
         <v>408</v>
       </c>
       <c r="Q43" s="14">
-        <f>SUM(N43:N44)</f>
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -2819,9 +2807,7 @@
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="Q44" s="14">
-        <v>2</v>
-      </c>
+      <c r="Q44" s="14"/>
     </row>
     <row r="45" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
@@ -2858,8 +2844,7 @@
         <v>264</v>
       </c>
       <c r="Q45" s="8">
-        <f>SUM(N45:N47)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R45" s="18"/>
       <c r="S45" s="18"/>
@@ -2960,9 +2945,7 @@
         <f t="shared" si="1"/>
         <v>524</v>
       </c>
-      <c r="Q47" s="8">
-        <v>3</v>
-      </c>
+      <c r="Q47" s="8"/>
       <c r="R47" s="18"/>
       <c r="S47" s="18"/>
       <c r="T47" s="18"/>
@@ -3054,8 +3037,7 @@
         <v>532</v>
       </c>
       <c r="Q49" s="8">
-        <f>SUM(N49:N52)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R49" s="18"/>
       <c r="S49" s="18"/>
@@ -3203,9 +3185,7 @@
         <f t="shared" si="1"/>
         <v>306</v>
       </c>
-      <c r="Q52" s="8">
-        <v>4</v>
-      </c>
+      <c r="Q52" s="8"/>
       <c r="R52" s="18"/>
       <c r="S52" s="18"/>
       <c r="T52" s="18"/>
@@ -3261,8 +3241,7 @@
         <v>620</v>
       </c>
       <c r="Q53" s="14">
-        <f>SUM(N53:N55)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -3335,9 +3314,7 @@
         <f t="shared" si="1"/>
         <v>124</v>
       </c>
-      <c r="Q55" s="14">
-        <v>3</v>
-      </c>
+      <c r="Q55" s="14"/>
     </row>
     <row r="56" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
@@ -3374,7 +3351,6 @@
         <v>90</v>
       </c>
       <c r="Q56" s="8">
-        <f>SUM(N56:N58)</f>
         <v>3</v>
       </c>
       <c r="R56" s="18"/>
@@ -3474,9 +3450,7 @@
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="Q58" s="8">
-        <v>3</v>
-      </c>
+      <c r="Q58" s="8"/>
       <c r="R58" s="18"/>
       <c r="S58" s="18"/>
       <c r="T58" s="18"/>
@@ -3532,8 +3506,7 @@
         <v>440</v>
       </c>
       <c r="Q59" s="14">
-        <f>SUM(N59:N61)</f>
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -3608,9 +3581,7 @@
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="Q61" s="14">
-        <v>3</v>
-      </c>
+      <c r="Q61" s="14"/>
     </row>
     <row r="62" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
@@ -3706,8 +3677,7 @@
         <v>248</v>
       </c>
       <c r="Q63" s="14">
-        <f>SUM(N63:N65)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -3780,9 +3750,7 @@
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
-      <c r="Q65" s="14">
-        <v>3</v>
-      </c>
+      <c r="Q65" s="14"/>
     </row>
     <row r="66" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
@@ -3852,8 +3820,9 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
-      <c r="N67" s="6" t="s">
-        <v>89</v>
+      <c r="N67" s="6">
+        <f>SUM(N2:N66)</f>
+        <v>164</v>
       </c>
       <c r="O67" s="6"/>
       <c r="P67" s="6"/>
@@ -3903,20 +3872,20 @@
       </c>
       <c r="M68" s="12">
         <f t="shared" si="6"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N68" s="12">
         <f>SUM(D68:M68)</f>
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O68" s="12"/>
       <c r="P68" s="7">
         <f>SUM(P2:P66)</f>
-        <v>25273</v>
+        <v>25350</v>
       </c>
       <c r="Q68" s="13">
         <f>SUM(Q2:Q66)</f>
-        <v>198</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.3">
@@ -4143,7 +4112,7 @@
         <v>14</v>
       </c>
       <c r="C79" s="8">
-        <f t="shared" ref="C79:C103" si="7">C2*2</f>
+        <f t="shared" ref="C79:C105" si="7">C2*2</f>
         <v>16</v>
       </c>
       <c r="D79" s="8">
@@ -4367,7 +4336,7 @@
         <v>564</v>
       </c>
       <c r="N82" s="6"/>
-      <c r="O82" s="6"/>
+      <c r="O82" s="14"/>
       <c r="P82" s="14">
         <f t="shared" si="9"/>
         <v>1128</v>
@@ -4431,7 +4400,7 @@
       <c r="N83" s="8"/>
       <c r="O83" s="8"/>
       <c r="P83" s="8">
-        <f t="shared" si="9"/>
+        <f>SUM(D83:M83)</f>
         <v>148</v>
       </c>
       <c r="Q83" s="8">
@@ -4487,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="14">
-        <f t="shared" ref="M84:M91" si="11">C84*M7</f>
+        <f t="shared" ref="L84:M91" si="11">C84*M7</f>
         <v>834</v>
       </c>
       <c r="N84" s="14"/>
@@ -4498,7 +4467,7 @@
       </c>
       <c r="Q84" s="14">
         <f>SUM(P84:P86)</f>
-        <v>1686</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.3">
@@ -4596,7 +4565,8 @@
         <v>0</v>
       </c>
       <c r="L86" s="14">
-        <v>0</v>
+        <f>C86*L9</f>
+        <v>292</v>
       </c>
       <c r="M86" s="14">
         <f t="shared" si="11"/>
@@ -4606,7 +4576,7 @@
       <c r="O86" s="14"/>
       <c r="P86" s="14">
         <f t="shared" si="9"/>
-        <v>292</v>
+        <v>584</v>
       </c>
       <c r="Q86" s="14"/>
     </row>
@@ -5140,8 +5110,8 @@
         <v>236</v>
       </c>
       <c r="Q95" s="14">
-        <f>O95</f>
-        <v>0</v>
+        <f>P95</f>
+        <v>236</v>
       </c>
     </row>
     <row r="96" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -5628,17 +5598,17 @@
       </c>
       <c r="M103" s="14">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="N103" s="14"/>
       <c r="O103" s="14"/>
       <c r="P103" s="14">
-        <f>SUM(D103:M103)</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>186</v>
       </c>
       <c r="Q103" s="14">
         <f>P103</f>
-        <v>0</v>
+        <v>186</v>
       </c>
     </row>
     <row r="104" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
@@ -5649,7 +5619,7 @@
         <v>123</v>
       </c>
       <c r="C104" s="8">
-        <f>174*2</f>
+        <f t="shared" si="7"/>
         <v>348</v>
       </c>
       <c r="D104" s="8">
@@ -5715,7 +5685,7 @@
         <v>100</v>
       </c>
       <c r="C105" s="14">
-        <f>209*2</f>
+        <f t="shared" si="7"/>
         <v>418</v>
       </c>
       <c r="D105" s="14">
@@ -6017,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="N109" s="20"/>
-      <c r="O109" s="20"/>
+      <c r="O109" s="14"/>
       <c r="P109" s="14">
         <f t="shared" si="28"/>
         <v>216</v>
@@ -8371,27 +8341,27 @@
       </c>
       <c r="L148" s="8">
         <f t="shared" si="37"/>
-        <v>2362</v>
+        <v>2654</v>
       </c>
       <c r="M148" s="8">
         <f t="shared" si="37"/>
-        <v>6656</v>
+        <v>6842</v>
       </c>
       <c r="N148" s="8">
         <f>SUM(D148:M148)</f>
-        <v>24872</v>
+        <v>25350</v>
       </c>
       <c r="O148" s="15">
         <f>N148/N68</f>
-        <v>152.58895705521473</v>
+        <v>154.57317073170731</v>
       </c>
       <c r="P148" s="8">
         <f>SUM(P79:P143)</f>
-        <v>24872</v>
+        <v>25350</v>
       </c>
       <c r="Q148" s="8">
         <f>SUM(Q79:Q143)</f>
-        <v>24636</v>
+        <v>25350</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.3">
@@ -8432,15 +8402,15 @@
       </c>
       <c r="L149" s="16">
         <f t="shared" si="38"/>
-        <v>147.625</v>
+        <v>165.875</v>
       </c>
       <c r="M149" s="16">
         <f t="shared" si="38"/>
-        <v>201.69696969696969</v>
+        <v>201.23529411764707</v>
       </c>
       <c r="N149" s="16">
         <f t="shared" si="38"/>
-        <v>152.58895705521473</v>
+        <v>154.57317073170731</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>97</v>
@@ -8448,403 +8418,566 @@
       <c r="P149" s="6"/>
       <c r="Q149" s="6"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A219" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B219" s="1" t="s">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A152" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B152" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C219" s="1"/>
-      <c r="D219" s="1" t="s">
+      <c r="C152" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E219" s="1" t="s">
+      <c r="D152" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A153" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B220">
+      <c r="B153" s="8">
+        <f>Q2</f>
         <v>3</v>
       </c>
-      <c r="D220">
+      <c r="C153" s="8">
         <f>SUM(N2:N4)</f>
         <v>11</v>
       </c>
-      <c r="E220">
-        <f>SUM(P2:P4)</f>
+      <c r="D153" s="8">
+        <f>Q79</f>
         <v>148</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A154" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B221">
-        <v>1</v>
-      </c>
-      <c r="D221">
+      <c r="B154" s="14">
+        <f>Q5</f>
+        <v>1</v>
+      </c>
+      <c r="C154" s="14">
         <f>N5</f>
         <v>2</v>
       </c>
-      <c r="E221">
-        <f>P5</f>
+      <c r="D154" s="14">
+        <f>Q82</f>
         <v>1128</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A155" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B155" s="8">
+        <f>Q6</f>
+        <v>1</v>
+      </c>
+      <c r="C155" s="8">
+        <f>Q6</f>
+        <v>1</v>
+      </c>
+      <c r="D155" s="8">
+        <f>Q83</f>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A156" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B222">
+      <c r="B156" s="14">
+        <f>Q7</f>
+        <v>3</v>
+      </c>
+      <c r="C156" s="14">
+        <f>SUM(N7:N9)</f>
+        <v>7</v>
+      </c>
+      <c r="D156" s="14">
+        <f>Q84</f>
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A157" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B157" s="8">
+        <f>Q10</f>
+        <v>5</v>
+      </c>
+      <c r="C157" s="8">
+        <f>SUM(N10:N14)</f>
+        <v>15</v>
+      </c>
+      <c r="D157" s="8">
+        <f>Q87</f>
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A158" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B158" s="14">
+        <f>Q15</f>
+        <v>1</v>
+      </c>
+      <c r="C158" s="14">
+        <f>N15</f>
+        <v>1</v>
+      </c>
+      <c r="D158" s="14">
+        <f>Q92</f>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A159" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B159" s="8">
+        <f>Q16</f>
         <v>2</v>
       </c>
-      <c r="D222">
-        <f>N7</f>
-        <v>4</v>
-      </c>
-      <c r="E222">
-        <f>SUM(P7:P8)</f>
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A223" t="s">
-        <v>22</v>
-      </c>
-      <c r="B223">
+      <c r="C159" s="8">
+        <f>SUM(N16:N17)</f>
+        <v>3</v>
+      </c>
+      <c r="D159" s="8">
+        <f>Q93</f>
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A160" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B160" s="14">
+        <f>Q18</f>
+        <v>1</v>
+      </c>
+      <c r="C160" s="14">
+        <f>N18</f>
+        <v>1</v>
+      </c>
+      <c r="D160" s="14">
+        <f>Q95</f>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B161" s="8">
+        <f>Q19</f>
         <v>5</v>
       </c>
-      <c r="D223">
-        <f>SUM(N10:N17)</f>
-        <v>19</v>
-      </c>
-      <c r="E223">
-        <f>SUM(P10:P17)</f>
-        <v>2854</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>28</v>
-      </c>
-      <c r="B224">
-        <v>1</v>
-      </c>
-      <c r="D224">
-        <f>N17</f>
-        <v>2</v>
-      </c>
-      <c r="E224">
-        <f>SUM(P17)</f>
-        <v>832</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
-        <v>30</v>
-      </c>
-      <c r="B225">
-        <v>5</v>
-      </c>
-      <c r="D225">
+      <c r="C161" s="8">
         <f>SUM(N19:N23)</f>
         <v>9</v>
       </c>
-      <c r="E225">
-        <f>SUM(P19:P23)</f>
+      <c r="D161" s="8">
+        <f>Q96</f>
         <v>906</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B162" s="14">
+        <f>Q24</f>
+        <v>1</v>
+      </c>
+      <c r="C162" s="14">
+        <f>N24</f>
+        <v>1</v>
+      </c>
+      <c r="D162" s="14">
+        <f>Q101</f>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B226">
-        <v>1</v>
-      </c>
-      <c r="D226">
+      <c r="B163" s="8">
+        <f>Q25</f>
+        <v>1</v>
+      </c>
+      <c r="C163" s="8">
         <f>N25</f>
         <v>1</v>
       </c>
-      <c r="E226">
-        <f>P25</f>
+      <c r="D163" s="8">
+        <f>Q102</f>
         <v>726</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B164" s="14">
+        <f>Q26</f>
+        <v>1</v>
+      </c>
+      <c r="C164" s="14">
+        <f>N26</f>
+        <v>1</v>
+      </c>
+      <c r="D164" s="14">
+        <f>Q103</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B165" s="8">
+        <f>N27</f>
+        <v>1</v>
+      </c>
+      <c r="C165" s="8">
+        <f>Q27</f>
+        <v>1</v>
+      </c>
+      <c r="D165" s="8">
+        <f>Q104</f>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B166" s="14">
+        <f>Q28</f>
+        <v>1</v>
+      </c>
+      <c r="C166" s="14">
+        <f>N28</f>
+        <v>1</v>
+      </c>
+      <c r="D166" s="14">
+        <f>Q105</f>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B227">
-        <v>1</v>
-      </c>
-      <c r="D227">
+      <c r="B167" s="8">
         <f>N29</f>
         <v>1</v>
       </c>
-      <c r="E227">
-        <f>P29</f>
+      <c r="C167" s="8">
+        <f>Q29</f>
+        <v>1</v>
+      </c>
+      <c r="D167" s="8">
+        <f>Q106</f>
         <v>516</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B168" s="14">
+        <f>Q30</f>
+        <v>6</v>
+      </c>
+      <c r="C168" s="14">
+        <f>SUM(N30:N35)</f>
+        <v>28</v>
+      </c>
+      <c r="D168" s="14">
+        <f>Q107</f>
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B228">
+      <c r="B169" s="8">
+        <f>Q36</f>
         <v>3</v>
       </c>
-      <c r="D228">
+      <c r="C169" s="8">
         <f>SUM(N36:N38)</f>
         <v>8</v>
       </c>
-      <c r="E228">
-        <f>SUM(P36:P38)</f>
+      <c r="D169" s="8">
+        <f>Q113</f>
         <v>1150</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>44</v>
-      </c>
-      <c r="B229">
-        <v>5</v>
-      </c>
-      <c r="D229">
-        <f>SUM(N30:N35)</f>
-        <v>30</v>
-      </c>
-      <c r="E229">
-        <f>SUM(P30:P35)</f>
-        <v>1644</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A230" t="s">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B230">
-        <v>1</v>
-      </c>
-      <c r="D230">
+      <c r="B170" s="14">
+        <f>Q39</f>
+        <v>1</v>
+      </c>
+      <c r="C170" s="14">
         <f>N39</f>
         <v>1</v>
       </c>
-      <c r="E230">
-        <f>P39</f>
+      <c r="D170" s="14">
+        <f>Q116</f>
         <v>840</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B231">
-        <v>1</v>
-      </c>
-      <c r="D231">
+      <c r="B171" s="8">
+        <f>Q40</f>
+        <v>1</v>
+      </c>
+      <c r="C171" s="8">
         <f>N40</f>
         <v>1</v>
       </c>
-      <c r="E231">
-        <f>P40</f>
+      <c r="D171" s="8">
+        <f>Q117</f>
         <v>282</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B232">
-        <v>1</v>
-      </c>
-      <c r="D232">
+      <c r="B172" s="14">
+        <f>Q41</f>
+        <v>1</v>
+      </c>
+      <c r="C172" s="14">
         <f>N41</f>
         <v>9</v>
       </c>
-      <c r="E232">
-        <f>P41</f>
+      <c r="D172" s="14">
+        <f>Q118</f>
         <v>1440</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B173" s="8">
+        <f>Q42</f>
+        <v>1</v>
+      </c>
+      <c r="C173" s="8">
+        <f>M42</f>
+        <v>2</v>
+      </c>
+      <c r="D173" s="8">
+        <f>Q119</f>
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B233">
+      <c r="B174" s="14">
+        <f>Q43</f>
         <v>2</v>
       </c>
-      <c r="D233">
+      <c r="C174" s="14">
         <f>SUM(N43:N44)</f>
         <v>7</v>
       </c>
-      <c r="E233">
-        <f>SUM(P43:P44)</f>
+      <c r="D174" s="14">
+        <f>Q120</f>
         <v>498</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B234">
+      <c r="B175" s="8">
+        <f>Q45</f>
         <v>3</v>
       </c>
-      <c r="D234">
+      <c r="C175" s="8">
         <f>SUM(N45:N47)</f>
         <v>4</v>
       </c>
-      <c r="E234">
-        <f>SUM(P45:P47)</f>
+      <c r="D175" s="8">
+        <f>Q122</f>
         <v>1050</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B235">
-        <v>1</v>
-      </c>
-      <c r="D235">
-        <f>SUM(N48)</f>
+      <c r="B176" s="14">
+        <f>Q48</f>
+        <v>1</v>
+      </c>
+      <c r="C176" s="14">
+        <f>N48</f>
         <v>3</v>
       </c>
-      <c r="E235">
-        <f>P48</f>
+      <c r="D176" s="14">
+        <f>Q125</f>
         <v>816</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B236">
+      <c r="B177" s="8">
+        <f>Q49</f>
         <v>4</v>
       </c>
-      <c r="D236">
+      <c r="C177" s="8">
         <f>SUM(N49:N52)</f>
         <v>5</v>
       </c>
-      <c r="E236">
-        <f>SUM(P49:P52)</f>
+      <c r="D177" s="8">
+        <f>Q126</f>
         <v>1396</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B237">
+      <c r="B178" s="14">
+        <f>Q53</f>
         <v>3</v>
       </c>
-      <c r="D237">
+      <c r="C178" s="14">
         <f>SUM(N53:N55)</f>
         <v>8</v>
       </c>
-      <c r="E237">
-        <f>SUM(P53:P55)</f>
+      <c r="D178" s="14">
+        <f>Q130</f>
         <v>1004</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B238">
+      <c r="B179" s="8">
+        <f>Q56</f>
         <v>3</v>
       </c>
-      <c r="D238">
+      <c r="C179" s="8">
         <f>SUM(N56:N58)</f>
         <v>3</v>
       </c>
-      <c r="E238">
-        <f>SUM(P56:P58)</f>
+      <c r="D179" s="8">
+        <f>Q133</f>
         <v>286</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B239">
-        <v>2</v>
-      </c>
-      <c r="D239">
-        <f>SUM(N59:N60)</f>
-        <v>17</v>
-      </c>
-      <c r="E239">
-        <f>SUM(P59:P60)</f>
-        <v>644</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
+      <c r="B180" s="14">
+        <f>Q59</f>
+        <v>3</v>
+      </c>
+      <c r="C180" s="14">
+        <f>SUM(N59:N61)</f>
+        <v>19</v>
+      </c>
+      <c r="D180" s="14">
+        <f>Q136</f>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B240">
-        <v>1</v>
-      </c>
-      <c r="D240">
-        <f>SUM(N62)</f>
+      <c r="B181" s="8">
+        <f>Q62</f>
+        <v>1</v>
+      </c>
+      <c r="C181" s="8">
+        <f>N62</f>
         <v>5</v>
       </c>
-      <c r="E240">
-        <f>P62</f>
+      <c r="D181" s="8">
+        <f>Q139</f>
         <v>1240</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B241">
+      <c r="B182" s="14">
+        <f>Q63</f>
         <v>3</v>
       </c>
-      <c r="D241">
+      <c r="C182" s="14">
         <f>SUM(N63:N65)</f>
         <v>4</v>
       </c>
-      <c r="E241">
-        <f>SUM(P63:P65)</f>
+      <c r="D182" s="14">
+        <f>Q140</f>
         <v>482</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B242">
-        <v>1</v>
-      </c>
-      <c r="D242">
+      <c r="B183" s="8">
+        <f>Q66</f>
+        <v>1</v>
+      </c>
+      <c r="C183" s="8">
         <f>N66</f>
         <v>1</v>
       </c>
-      <c r="E242">
-        <f>P66</f>
+      <c r="D183" s="8">
+        <f>Q143</f>
         <v>138</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A244" s="1"/>
-      <c r="B244" s="1">
-        <f>SUM(B220:B242)</f>
-        <v>53</v>
-      </c>
-      <c r="C244" s="1"/>
-      <c r="D244" s="1">
-        <f>SUM(D220:D242)</f>
-        <v>155</v>
-      </c>
-      <c r="E244" s="1">
-        <f>SUM(E220:E242)</f>
-        <v>21414</v>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="8"/>
+      <c r="B184" s="8"/>
+      <c r="C184" s="8"/>
+      <c r="D184" s="8"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="22"/>
+      <c r="B185" s="22">
+        <f>SUM(B153:B183)</f>
+        <v>65</v>
+      </c>
+      <c r="C185" s="22">
+        <f>SUM(C153:C183)</f>
+        <v>164</v>
+      </c>
+      <c r="D185" s="22">
+        <f>SUM(D153:D183)</f>
+        <v>25350</v>
       </c>
     </row>
   </sheetData>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7712BFD6-D658-4D01-B691-AB86BB4C8CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4E23CC-D3F6-4D5E-833F-F09221F23C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1548" yWindow="420" windowWidth="19212" windowHeight="12228" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="20952" windowHeight="12816" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
   <sheets>
     <sheet name="pelipaikat" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="138">
   <si>
     <t>Paikkakunta</t>
   </si>
@@ -445,6 +445,12 @@
   </si>
   <si>
     <t>Suutarinkylän peruskoulu</t>
+  </si>
+  <si>
+    <t>Ähtäri</t>
+  </si>
+  <si>
+    <t>Ähtärin liikuntahalli</t>
   </si>
 </sst>
 </file>
@@ -571,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -595,6 +601,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -909,7 +916,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1185CB8-B7D3-4EC5-84DD-BC18A741831D}">
-  <dimension ref="A1:AD187"/>
+  <dimension ref="A1:AD188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
@@ -1008,11 +1015,11 @@
         <v>4</v>
       </c>
       <c r="O2" s="8">
-        <f t="shared" ref="O2:O67" si="0">C2*N2</f>
+        <f t="shared" ref="O2:O68" si="0">C2*N2</f>
         <v>32</v>
       </c>
       <c r="P2" s="8">
-        <f t="shared" ref="P2:P67" si="1">2*O2</f>
+        <f t="shared" ref="P2:P68" si="1">2*O2</f>
         <v>64</v>
       </c>
       <c r="Q2" s="8">
@@ -1044,7 +1051,7 @@
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
       <c r="N3" s="8">
-        <f t="shared" ref="N3:N67" si="2">SUM(D3:M3)</f>
+        <f t="shared" ref="N3:N68" si="2">SUM(D3:M3)</f>
         <v>2</v>
       </c>
       <c r="O3" s="8">
@@ -3846,9 +3853,15 @@
       <c r="AD67" s="18"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
+      <c r="A68" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C68" s="6">
+        <v>188</v>
+      </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
@@ -3859,92 +3872,109 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
-      <c r="N68" s="6">
-        <f>SUM(N2:N67)</f>
+      <c r="N68" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P68" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6">
+        <f>SUM(N2:N68)</f>
         <v>166</v>
       </c>
-      <c r="O68" s="6"/>
-      <c r="P68" s="6"/>
-      <c r="Q68" s="6"/>
-    </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A69" s="12" t="s">
+      <c r="O69" s="6">
+        <f>SUM(O2:O68)</f>
+        <v>12729</v>
+      </c>
+      <c r="P69" s="6">
+        <f>SUM(P2:P68)</f>
+        <v>25458</v>
+      </c>
+      <c r="Q69" s="6"/>
+    </row>
+    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A70" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12">
-        <f t="shared" ref="D69:M69" si="6">SUM(D2:D67)</f>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12">
+        <f t="shared" ref="D70:M70" si="6">SUM(D2:D67)</f>
         <v>5</v>
       </c>
-      <c r="E69" s="12">
+      <c r="E70" s="12">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F70" s="12">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G70" s="12">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="H69" s="12">
+      <c r="H70" s="12">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="I69" s="12">
+      <c r="I70" s="12">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="J69" s="12">
+      <c r="J70" s="12">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
-      <c r="K69" s="12">
+      <c r="K70" s="12">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
-      <c r="L69" s="12">
+      <c r="L70" s="12">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="M69" s="12">
+      <c r="M70" s="12">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="N69" s="12">
-        <f>SUM(D69:M69)</f>
+      <c r="N70" s="12">
+        <f>SUM(D70:M70)</f>
         <v>166</v>
       </c>
-      <c r="O69" s="12"/>
-      <c r="P69" s="7">
-        <f>SUM(P2:P67)</f>
+      <c r="O70" s="12"/>
+      <c r="P70" s="7">
+        <f>SUM(P2:P68)</f>
         <v>25458</v>
       </c>
-      <c r="Q69" s="13">
-        <f>SUM(Q2:Q67)</f>
+      <c r="Q70" s="13">
+        <f>SUM(Q2:Q68)</f>
         <v>66</v>
       </c>
-    </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
@@ -4080,433 +4110,390 @@
       <c r="Q77" s="6"/>
     </row>
     <row r="78" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
-      <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="5"/>
-      <c r="M78" s="5"/>
-      <c r="N78" s="5"/>
-      <c r="O78" s="5"/>
-      <c r="P78" s="5"/>
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
+      <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A79" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C79" s="7" t="s">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="6"/>
+    </row>
+    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="D80" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E80" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F80" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G80" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H79" s="7" t="s">
+      <c r="H80" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I79" s="7" t="s">
+      <c r="I80" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J79" s="7" t="s">
+      <c r="J80" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K79" s="7" t="s">
+      <c r="K80" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L79" s="7" t="s">
+      <c r="L80" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="M79" s="9" t="s">
+      <c r="M80" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="N79" s="9"/>
-      <c r="O79" s="9"/>
-      <c r="P79" s="9"/>
-      <c r="Q79" s="9"/>
-    </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A80" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C80" s="8">
-        <f t="shared" ref="C80:C111" si="7">C2*2</f>
-        <v>16</v>
-      </c>
-      <c r="D80" s="8">
-        <f t="shared" ref="D80:D87" si="8">C80*D2</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="8">
-        <f>C80*E2</f>
-        <v>0</v>
-      </c>
-      <c r="F80" s="8">
-        <f>C80*F2</f>
-        <v>0</v>
-      </c>
-      <c r="G80" s="8">
-        <f>C80*G2</f>
-        <v>0</v>
-      </c>
-      <c r="H80" s="8">
-        <f>C80*H2</f>
-        <v>0</v>
-      </c>
-      <c r="I80" s="8">
-        <f>C80*I2</f>
-        <v>0</v>
-      </c>
-      <c r="J80" s="8">
-        <f>C80*J2</f>
-        <v>16</v>
-      </c>
-      <c r="K80" s="8">
-        <f>C80*K2</f>
-        <v>0</v>
-      </c>
-      <c r="L80" s="8">
-        <f>C80*L2</f>
-        <v>16</v>
-      </c>
-      <c r="M80" s="8">
-        <f t="shared" ref="M80:M93" si="9">C80*M2</f>
-        <v>32</v>
-      </c>
-      <c r="N80" s="8"/>
-      <c r="O80" s="8"/>
-      <c r="P80" s="8">
-        <f>SUM(D80:M80)</f>
-        <v>64</v>
-      </c>
-      <c r="Q80" s="8">
-        <f>SUM(P80:P82)</f>
-        <v>148</v>
-      </c>
+      <c r="N80" s="9"/>
+      <c r="O80" s="9"/>
+      <c r="P80" s="9"/>
+      <c r="Q80" s="9"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C81" s="8">
-        <f t="shared" si="7"/>
-        <v>2</v>
+        <f>C2*2</f>
+        <v>16</v>
       </c>
       <c r="D81" s="8">
-        <f t="shared" si="8"/>
+        <f>C81*D2</f>
         <v>0</v>
       </c>
       <c r="E81" s="8">
-        <f>C81*E3</f>
-        <v>2</v>
+        <f>C81*E2</f>
+        <v>0</v>
       </c>
       <c r="F81" s="8">
-        <f>C81*F3</f>
-        <v>2</v>
+        <f>C81*F2</f>
+        <v>0</v>
       </c>
       <c r="G81" s="8">
-        <f>C81*G3</f>
+        <f>C81*G2</f>
         <v>0</v>
       </c>
       <c r="H81" s="8">
-        <f>C81*H3</f>
+        <f>C81*H2</f>
         <v>0</v>
       </c>
       <c r="I81" s="8">
-        <f>C81*I3</f>
+        <f>C81*I2</f>
         <v>0</v>
       </c>
       <c r="J81" s="8">
-        <f>C81*J3</f>
-        <v>0</v>
+        <f>C81*J2</f>
+        <v>16</v>
       </c>
       <c r="K81" s="8">
-        <f>C81*K3</f>
+        <f>C81*K2</f>
         <v>0</v>
       </c>
       <c r="L81" s="8">
-        <f>C81*L3</f>
-        <v>0</v>
+        <f>C81*L2</f>
+        <v>16</v>
       </c>
       <c r="M81" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>C81*M2</f>
+        <v>32</v>
       </c>
       <c r="N81" s="8"/>
       <c r="O81" s="8"/>
       <c r="P81" s="8">
-        <f t="shared" ref="P81:P145" si="10">SUM(D81:M81)</f>
-        <v>4</v>
-      </c>
-      <c r="Q81" s="8"/>
+        <f>SUM(D81:M81)</f>
+        <v>64</v>
+      </c>
+      <c r="Q81" s="8">
+        <f>SUM(P81:P83)</f>
+        <v>148</v>
+      </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C82" s="8">
-        <f t="shared" si="7"/>
-        <v>16</v>
+        <f>C3*2</f>
+        <v>2</v>
       </c>
       <c r="D82" s="8">
-        <f t="shared" si="8"/>
-        <v>16</v>
+        <f>C82*D3</f>
+        <v>0</v>
       </c>
       <c r="E82" s="8">
-        <f>C82*E4</f>
-        <v>48</v>
+        <f>C82*E3</f>
+        <v>2</v>
       </c>
       <c r="F82" s="8">
-        <f>C82*F4</f>
-        <v>16</v>
+        <f>C82*F3</f>
+        <v>2</v>
       </c>
       <c r="G82" s="8">
-        <f>C82*G4</f>
+        <f>C82*G3</f>
         <v>0</v>
       </c>
       <c r="H82" s="8">
-        <f>C82*H4</f>
+        <f>C82*H3</f>
         <v>0</v>
       </c>
       <c r="I82" s="8">
-        <f>C82*I4</f>
+        <f>C82*I3</f>
         <v>0</v>
       </c>
       <c r="J82" s="8">
-        <f>C82*J4</f>
+        <f>C82*J3</f>
         <v>0</v>
       </c>
       <c r="K82" s="8">
-        <f>C82*K4</f>
+        <f>C82*K3</f>
         <v>0</v>
       </c>
       <c r="L82" s="8">
-        <f>C82*L4</f>
+        <f>C82*L3</f>
         <v>0</v>
       </c>
       <c r="M82" s="8">
-        <f t="shared" si="9"/>
+        <f>C82*M3</f>
         <v>0</v>
       </c>
       <c r="N82" s="8"/>
       <c r="O82" s="8"/>
       <c r="P82" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="P82:P147" si="7">SUM(D82:M82)</f>
+        <v>4</v>
+      </c>
+      <c r="Q82" s="8"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="8">
+        <f>C4*2</f>
+        <v>16</v>
+      </c>
+      <c r="D83" s="8">
+        <f>C83*D4</f>
+        <v>16</v>
+      </c>
+      <c r="E83" s="8">
+        <f>C83*E4</f>
+        <v>48</v>
+      </c>
+      <c r="F83" s="8">
+        <f>C83*F4</f>
+        <v>16</v>
+      </c>
+      <c r="G83" s="8">
+        <f>C83*G4</f>
+        <v>0</v>
+      </c>
+      <c r="H83" s="8">
+        <f>C83*H4</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="8">
+        <f>C83*I4</f>
+        <v>0</v>
+      </c>
+      <c r="J83" s="8">
+        <f>C83*J4</f>
+        <v>0</v>
+      </c>
+      <c r="K83" s="8">
+        <f>C83*K4</f>
+        <v>0</v>
+      </c>
+      <c r="L83" s="8">
+        <f>C83*L4</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="8">
+        <f>C83*M4</f>
+        <v>0</v>
+      </c>
+      <c r="N83" s="8"/>
+      <c r="O83" s="8"/>
+      <c r="P83" s="8">
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="Q82" s="8"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
+      <c r="Q83" s="8"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A84" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B84" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C84" s="6">
+        <f>C5*2</f>
+        <v>564</v>
+      </c>
+      <c r="D84" s="6">
+        <f>C84*D5</f>
+        <v>0</v>
+      </c>
+      <c r="E84" s="6">
+        <f>C84*E5</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="6">
+        <f>C84*F5</f>
+        <v>0</v>
+      </c>
+      <c r="G84" s="6">
+        <f>C84*G5</f>
+        <v>0</v>
+      </c>
+      <c r="H84" s="6">
+        <f>C84*H5</f>
+        <v>0</v>
+      </c>
+      <c r="I84" s="6">
+        <f>C84*I5</f>
+        <v>0</v>
+      </c>
+      <c r="J84" s="6">
+        <f>C84*J5</f>
+        <v>564</v>
+      </c>
+      <c r="K84" s="6">
+        <f>C84*K5</f>
+        <v>0</v>
+      </c>
+      <c r="L84" s="6">
+        <f>C84*L5</f>
+        <v>0</v>
+      </c>
+      <c r="M84" s="14">
+        <f>C84*M5</f>
+        <v>564</v>
+      </c>
+      <c r="N84" s="6"/>
+      <c r="O84" s="14"/>
+      <c r="P84" s="14">
         <f t="shared" si="7"/>
-        <v>564</v>
-      </c>
-      <c r="D83" s="6">
+        <v>1128</v>
+      </c>
+      <c r="Q84" s="6">
+        <f>SUM(P84)</f>
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A85" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C85" s="8">
+        <f>C6*2</f>
+        <v>148</v>
+      </c>
+      <c r="D85" s="8">
+        <f>C85*D6</f>
+        <v>0</v>
+      </c>
+      <c r="E85" s="8">
+        <f t="shared" ref="E85:L85" si="8">D85*E6</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="8">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="E83" s="6">
-        <f>C83*E5</f>
-        <v>0</v>
-      </c>
-      <c r="F83" s="6">
-        <f>C83*F5</f>
-        <v>0</v>
-      </c>
-      <c r="G83" s="6">
-        <f>C83*G5</f>
-        <v>0</v>
-      </c>
-      <c r="H83" s="6">
-        <f>C83*H5</f>
-        <v>0</v>
-      </c>
-      <c r="I83" s="6">
-        <f>C83*I5</f>
-        <v>0</v>
-      </c>
-      <c r="J83" s="6">
-        <f>C83*J5</f>
-        <v>564</v>
-      </c>
-      <c r="K83" s="6">
-        <f>C83*K5</f>
-        <v>0</v>
-      </c>
-      <c r="L83" s="6">
-        <f>C83*L5</f>
-        <v>0</v>
-      </c>
-      <c r="M83" s="14">
-        <f t="shared" si="9"/>
-        <v>564</v>
-      </c>
-      <c r="N83" s="6"/>
-      <c r="O83" s="14"/>
-      <c r="P83" s="14">
-        <f t="shared" si="10"/>
-        <v>1128</v>
-      </c>
-      <c r="Q83" s="6">
-        <f>SUM(P83)</f>
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A84" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C84" s="8">
-        <f t="shared" si="7"/>
+      <c r="G85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M85" s="8">
+        <f>C85*M6</f>
         <v>148</v>
       </c>
-      <c r="D84" s="8">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E84" s="8">
-        <f t="shared" ref="E84:L84" si="11">D84*E6</f>
-        <v>0</v>
-      </c>
-      <c r="F84" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G84" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H84" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J84" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K84" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L84" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M84" s="8">
-        <f t="shared" si="9"/>
+      <c r="N85" s="8"/>
+      <c r="O85" s="8"/>
+      <c r="P85" s="8">
+        <f>SUM(D85:M85)</f>
         <v>148</v>
       </c>
-      <c r="N84" s="8"/>
-      <c r="O84" s="8"/>
-      <c r="P84" s="8">
-        <f>SUM(D84:M84)</f>
+      <c r="Q85" s="8">
+        <f>SUM(P85)</f>
         <v>148</v>
-      </c>
-      <c r="Q84" s="8">
-        <f>SUM(P84)</f>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A85" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="C85" s="14">
-        <f t="shared" si="7"/>
-        <v>278</v>
-      </c>
-      <c r="D85" s="14">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E85" s="14">
-        <f>C85*E7</f>
-        <v>0</v>
-      </c>
-      <c r="F85" s="14">
-        <f>C85*F7</f>
-        <v>0</v>
-      </c>
-      <c r="G85" s="14">
-        <f>C85*G7</f>
-        <v>0</v>
-      </c>
-      <c r="H85" s="14">
-        <f>C85*H7</f>
-        <v>0</v>
-      </c>
-      <c r="I85" s="14">
-        <f>C85*I7</f>
-        <v>0</v>
-      </c>
-      <c r="J85" s="14">
-        <f>C85*J7</f>
-        <v>0</v>
-      </c>
-      <c r="K85" s="14">
-        <f>C85*K7</f>
-        <v>278</v>
-      </c>
-      <c r="L85" s="14">
-        <f t="shared" ref="L85:L93" si="12">C85*L7</f>
-        <v>0</v>
-      </c>
-      <c r="M85" s="14">
-        <f t="shared" si="9"/>
-        <v>834</v>
-      </c>
-      <c r="N85" s="14"/>
-      <c r="O85" s="14"/>
-      <c r="P85" s="14">
-        <f t="shared" si="10"/>
-        <v>1112</v>
-      </c>
-      <c r="Q85" s="14">
-        <f>SUM(P85:P88)</f>
-        <v>1962</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.3">
@@ -4514,116 +4501,119 @@
         <v>19</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C86" s="14">
-        <f t="shared" si="7"/>
-        <v>282</v>
+        <f>C7*2</f>
+        <v>278</v>
       </c>
       <c r="D86" s="14">
-        <f t="shared" si="8"/>
+        <f>C86*D7</f>
         <v>0</v>
       </c>
       <c r="E86" s="14">
-        <f>C86*E8</f>
+        <f>C86*E7</f>
         <v>0</v>
       </c>
       <c r="F86" s="14">
-        <f>C86*F8</f>
+        <f>C86*F7</f>
         <v>0</v>
       </c>
       <c r="G86" s="14">
-        <f>C86*G8</f>
+        <f>C86*G7</f>
         <v>0</v>
       </c>
       <c r="H86" s="14">
-        <f>C86*H8</f>
+        <f>C86*H7</f>
         <v>0</v>
       </c>
       <c r="I86" s="14">
-        <f>C86*I8</f>
-        <v>282</v>
+        <f>C86*I7</f>
+        <v>0</v>
       </c>
       <c r="J86" s="14">
-        <f>C86*J8</f>
+        <f>C86*J7</f>
         <v>0</v>
       </c>
       <c r="K86" s="14">
-        <f>C86*K8</f>
-        <v>0</v>
+        <f>C86*K7</f>
+        <v>278</v>
       </c>
       <c r="L86" s="14">
-        <f t="shared" si="12"/>
+        <f>C86*L7</f>
         <v>0</v>
       </c>
       <c r="M86" s="14">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>C86*M7</f>
+        <v>834</v>
       </c>
       <c r="N86" s="14"/>
       <c r="O86" s="14"/>
       <c r="P86" s="14">
-        <f t="shared" si="10"/>
-        <v>282</v>
-      </c>
-      <c r="Q86" s="14"/>
+        <f t="shared" si="7"/>
+        <v>1112</v>
+      </c>
+      <c r="Q86" s="14">
+        <f>SUM(P86:P89)</f>
+        <v>1962</v>
+      </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="C87" s="14">
-        <f t="shared" si="7"/>
-        <v>276</v>
+        <f>C8*2</f>
+        <v>282</v>
       </c>
       <c r="D87" s="14">
-        <f t="shared" si="8"/>
+        <f>C87*D8</f>
         <v>0</v>
       </c>
       <c r="E87" s="14">
-        <f>C87*E9</f>
+        <f>C87*E8</f>
         <v>0</v>
       </c>
       <c r="F87" s="14">
-        <f>C87*F9</f>
+        <f>C87*F8</f>
         <v>0</v>
       </c>
       <c r="G87" s="14">
-        <f>C87*G9</f>
+        <f>C87*G8</f>
         <v>0</v>
       </c>
       <c r="H87" s="14">
-        <f>C87*H9</f>
+        <f>C87*H8</f>
         <v>0</v>
       </c>
       <c r="I87" s="14">
-        <f>C87*I9</f>
-        <v>0</v>
+        <f>C87*I8</f>
+        <v>282</v>
       </c>
       <c r="J87" s="14">
-        <f>C87*J9</f>
+        <f>C87*J8</f>
         <v>0</v>
       </c>
       <c r="K87" s="14">
-        <f>C87*K9</f>
+        <f>C87*K8</f>
         <v>0</v>
       </c>
       <c r="L87" s="14">
-        <f t="shared" si="12"/>
+        <f>C87*L8</f>
         <v>0</v>
       </c>
       <c r="M87" s="14">
-        <f t="shared" si="9"/>
-        <v>276</v>
+        <f>C87*M8</f>
+        <v>0</v>
       </c>
       <c r="N87" s="14"/>
       <c r="O87" s="14"/>
       <c r="P87" s="14">
-        <f t="shared" si="10"/>
-        <v>276</v>
+        <f t="shared" si="7"/>
+        <v>282</v>
       </c>
       <c r="Q87" s="14"/>
     </row>
@@ -4632,229 +4622,229 @@
         <v>19</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C88" s="14">
-        <f t="shared" si="7"/>
-        <v>292</v>
+        <f>C9*2</f>
+        <v>276</v>
       </c>
       <c r="D88" s="14">
+        <f>C88*D9</f>
         <v>0</v>
       </c>
       <c r="E88" s="14">
+        <f>C88*E9</f>
         <v>0</v>
       </c>
       <c r="F88" s="14">
+        <f>C88*F9</f>
         <v>0</v>
       </c>
       <c r="G88" s="14">
+        <f>C88*G9</f>
         <v>0</v>
       </c>
       <c r="H88" s="14">
+        <f>C88*H9</f>
         <v>0</v>
       </c>
       <c r="I88" s="14">
+        <f>C88*I9</f>
         <v>0</v>
       </c>
       <c r="J88" s="14">
+        <f>C88*J9</f>
         <v>0</v>
       </c>
       <c r="K88" s="14">
+        <f>C88*K9</f>
         <v>0</v>
       </c>
       <c r="L88" s="14">
-        <f t="shared" si="12"/>
-        <v>292</v>
+        <f>C88*L9</f>
+        <v>0</v>
       </c>
       <c r="M88" s="14">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>C88*M9</f>
+        <v>276</v>
       </c>
       <c r="N88" s="14"/>
       <c r="O88" s="14"/>
       <c r="P88" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
+        <v>276</v>
+      </c>
+      <c r="Q88" s="14"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A89" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C89" s="14">
+        <f>C10*2</f>
         <v>292</v>
       </c>
-      <c r="Q88" s="14"/>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A89" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C89" s="8">
+      <c r="D89" s="14">
+        <v>0</v>
+      </c>
+      <c r="E89" s="14">
+        <v>0</v>
+      </c>
+      <c r="F89" s="14">
+        <v>0</v>
+      </c>
+      <c r="G89" s="14">
+        <v>0</v>
+      </c>
+      <c r="H89" s="14">
+        <v>0</v>
+      </c>
+      <c r="I89" s="14">
+        <v>0</v>
+      </c>
+      <c r="J89" s="14">
+        <v>0</v>
+      </c>
+      <c r="K89" s="14">
+        <v>0</v>
+      </c>
+      <c r="L89" s="14">
+        <f>C89*L10</f>
+        <v>292</v>
+      </c>
+      <c r="M89" s="14">
+        <f>C89*M10</f>
+        <v>0</v>
+      </c>
+      <c r="N89" s="14"/>
+      <c r="O89" s="14"/>
+      <c r="P89" s="14">
         <f t="shared" si="7"/>
-        <v>66</v>
-      </c>
-      <c r="D89" s="8">
-        <f>C89*D11</f>
-        <v>0</v>
-      </c>
-      <c r="E89" s="8">
-        <f>C89*E11</f>
-        <v>0</v>
-      </c>
-      <c r="F89" s="8">
-        <f>C89*F11</f>
-        <v>0</v>
-      </c>
-      <c r="G89" s="8">
-        <f>C89*G11</f>
-        <v>0</v>
-      </c>
-      <c r="H89" s="8">
-        <f>C89*H11</f>
-        <v>0</v>
-      </c>
-      <c r="I89" s="8">
-        <f>C89*I11</f>
-        <v>0</v>
-      </c>
-      <c r="J89" s="8">
-        <f>C89*J11</f>
-        <v>0</v>
-      </c>
-      <c r="K89" s="8">
-        <f>C89*K11</f>
-        <v>66</v>
-      </c>
-      <c r="L89" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N89" s="8"/>
-      <c r="O89" s="8"/>
-      <c r="P89" s="8">
-        <f t="shared" si="10"/>
-        <v>66</v>
-      </c>
-      <c r="Q89" s="8">
-        <f>SUM(P89:P93)</f>
-        <v>1288</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="Q89" s="14"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C90" s="8">
-        <f t="shared" si="7"/>
-        <v>92</v>
+        <f>C11*2</f>
+        <v>66</v>
       </c>
       <c r="D90" s="8">
-        <f>C90*D12</f>
+        <f>C90*D11</f>
         <v>0</v>
       </c>
       <c r="E90" s="8">
-        <f>C90*E12</f>
+        <f>C90*E11</f>
         <v>0</v>
       </c>
       <c r="F90" s="8">
-        <f>C90*F12</f>
+        <f>C90*F11</f>
         <v>0</v>
       </c>
       <c r="G90" s="8">
-        <f>C90*G12</f>
-        <v>92</v>
+        <f>C90*G11</f>
+        <v>0</v>
       </c>
       <c r="H90" s="8">
-        <f>C90*H12</f>
+        <f>C90*H11</f>
         <v>0</v>
       </c>
       <c r="I90" s="8">
-        <f>C90*I12</f>
+        <f>C90*I11</f>
         <v>0</v>
       </c>
       <c r="J90" s="8">
-        <f>C90*J12</f>
+        <f>C90*J11</f>
         <v>0</v>
       </c>
       <c r="K90" s="8">
-        <f>C90*K12</f>
-        <v>0</v>
+        <f>C90*K11</f>
+        <v>66</v>
       </c>
       <c r="L90" s="8">
-        <f t="shared" si="12"/>
+        <f>C90*L11</f>
         <v>0</v>
       </c>
       <c r="M90" s="8">
-        <f t="shared" si="9"/>
+        <f>C90*M11</f>
         <v>0</v>
       </c>
       <c r="N90" s="8"/>
       <c r="O90" s="8"/>
       <c r="P90" s="8">
-        <f t="shared" si="10"/>
-        <v>92</v>
-      </c>
-      <c r="Q90" s="8"/>
+        <f t="shared" si="7"/>
+        <v>66</v>
+      </c>
+      <c r="Q90" s="8">
+        <f>SUM(P90:P94)</f>
+        <v>1288</v>
+      </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C91" s="8">
-        <f t="shared" si="7"/>
-        <v>84</v>
+        <f>C12*2</f>
+        <v>92</v>
       </c>
       <c r="D91" s="8">
-        <f>C91*D13</f>
+        <f>C91*D12</f>
         <v>0</v>
       </c>
       <c r="E91" s="8">
-        <f>C91*E13</f>
+        <f>C91*E12</f>
         <v>0</v>
       </c>
       <c r="F91" s="8">
-        <f>C91*F13</f>
+        <f>C91*F12</f>
         <v>0</v>
       </c>
       <c r="G91" s="8">
-        <f>C91*G13</f>
-        <v>0</v>
+        <f>C91*G12</f>
+        <v>92</v>
       </c>
       <c r="H91" s="8">
-        <f>C91*H13</f>
+        <f>C91*H12</f>
         <v>0</v>
       </c>
       <c r="I91" s="8">
-        <f>C91*I13</f>
+        <f>C91*I12</f>
         <v>0</v>
       </c>
       <c r="J91" s="8">
-        <f>C91*J13</f>
+        <f>C91*J12</f>
         <v>0</v>
       </c>
       <c r="K91" s="8">
-        <f>C91*K13</f>
-        <v>84</v>
+        <f>C91*K12</f>
+        <v>0</v>
       </c>
       <c r="L91" s="8">
-        <f t="shared" si="12"/>
+        <f>C91*L12</f>
         <v>0</v>
       </c>
       <c r="M91" s="8">
-        <f t="shared" si="9"/>
-        <v>840</v>
+        <f>C91*M12</f>
+        <v>0</v>
       </c>
       <c r="N91" s="8"/>
       <c r="O91" s="8"/>
       <c r="P91" s="8">
-        <f t="shared" si="10"/>
-        <v>924</v>
+        <f t="shared" si="7"/>
+        <v>92</v>
       </c>
       <c r="Q91" s="8"/>
     </row>
@@ -4863,57 +4853,57 @@
         <v>22</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C92" s="8">
-        <f t="shared" si="7"/>
-        <v>120</v>
+        <f>C13*2</f>
+        <v>84</v>
       </c>
       <c r="D92" s="8">
-        <f>C92*D14</f>
+        <f>C92*D13</f>
         <v>0</v>
       </c>
       <c r="E92" s="8">
-        <f>C92*E14</f>
+        <f>C92*E13</f>
         <v>0</v>
       </c>
       <c r="F92" s="8">
-        <f>C92*F14</f>
+        <f>C92*F13</f>
         <v>0</v>
       </c>
       <c r="G92" s="8">
-        <f>C92*G14</f>
-        <v>120</v>
+        <f>C92*G13</f>
+        <v>0</v>
       </c>
       <c r="H92" s="8">
-        <f>C92*H14</f>
+        <f>C92*H13</f>
         <v>0</v>
       </c>
       <c r="I92" s="8">
-        <f>C92*I14</f>
+        <f>C92*I13</f>
         <v>0</v>
       </c>
       <c r="J92" s="8">
-        <f>C92*J14</f>
+        <f>C92*J13</f>
         <v>0</v>
       </c>
       <c r="K92" s="8">
-        <f>C92*K14</f>
-        <v>0</v>
+        <f>C92*K13</f>
+        <v>84</v>
       </c>
       <c r="L92" s="8">
-        <f t="shared" si="12"/>
+        <f>C92*L13</f>
         <v>0</v>
       </c>
       <c r="M92" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f>C92*M13</f>
+        <v>840</v>
       </c>
       <c r="N92" s="8"/>
       <c r="O92" s="8"/>
       <c r="P92" s="8">
-        <f t="shared" si="10"/>
-        <v>120</v>
+        <f t="shared" si="7"/>
+        <v>924</v>
       </c>
       <c r="Q92" s="8"/>
     </row>
@@ -4922,173 +4912,170 @@
         <v>22</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C93" s="8">
-        <f t="shared" si="7"/>
-        <v>86</v>
+        <f>C14*2</f>
+        <v>120</v>
       </c>
       <c r="D93" s="8">
-        <f>C93*D15</f>
+        <f>C93*D14</f>
         <v>0</v>
       </c>
       <c r="E93" s="8">
-        <f>C93*E15</f>
+        <f>C93*E14</f>
         <v>0</v>
       </c>
       <c r="F93" s="8">
-        <f>C93*F15</f>
-        <v>86</v>
+        <f>C93*F14</f>
+        <v>0</v>
       </c>
       <c r="G93" s="8">
-        <f>C93*G15</f>
-        <v>0</v>
+        <f>C93*G14</f>
+        <v>120</v>
       </c>
       <c r="H93" s="8">
-        <f>C93*H15</f>
+        <f>C93*H14</f>
         <v>0</v>
       </c>
       <c r="I93" s="8">
-        <f>C93*I15</f>
+        <f>C93*I14</f>
         <v>0</v>
       </c>
       <c r="J93" s="8">
-        <f>C93*J15</f>
+        <f>C93*J14</f>
         <v>0</v>
       </c>
       <c r="K93" s="8">
-        <f>C93*K15</f>
+        <f>C93*K14</f>
         <v>0</v>
       </c>
       <c r="L93" s="8">
-        <f t="shared" si="12"/>
+        <f>C93*L14</f>
         <v>0</v>
       </c>
       <c r="M93" s="8">
-        <f t="shared" si="9"/>
+        <f>C93*M14</f>
         <v>0</v>
       </c>
       <c r="N93" s="8"/>
       <c r="O93" s="8"/>
       <c r="P93" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
+        <v>120</v>
+      </c>
+      <c r="Q93" s="8"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A94" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" s="8">
+        <f>C15*2</f>
         <v>86</v>
       </c>
-      <c r="Q93" s="8"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A94" s="14" t="s">
+      <c r="D94" s="8">
+        <f>C94*D15</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="8">
+        <f>C94*E15</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="8">
+        <f>C94*F15</f>
+        <v>86</v>
+      </c>
+      <c r="G94" s="8">
+        <f>C94*G15</f>
+        <v>0</v>
+      </c>
+      <c r="H94" s="8">
+        <f>C94*H15</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="8">
+        <f>C94*I15</f>
+        <v>0</v>
+      </c>
+      <c r="J94" s="8">
+        <f>C94*J15</f>
+        <v>0</v>
+      </c>
+      <c r="K94" s="8">
+        <f>C94*K15</f>
+        <v>0</v>
+      </c>
+      <c r="L94" s="8">
+        <f>C94*L15</f>
+        <v>0</v>
+      </c>
+      <c r="M94" s="8">
+        <f>C94*M15</f>
+        <v>0</v>
+      </c>
+      <c r="N94" s="8"/>
+      <c r="O94" s="8"/>
+      <c r="P94" s="8">
+        <f t="shared" si="7"/>
+        <v>86</v>
+      </c>
+      <c r="Q94" s="8"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A95" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B95" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C94" s="14">
+      <c r="C95" s="14">
+        <f>C16*2</f>
+        <v>364</v>
+      </c>
+      <c r="D95" s="14">
+        <v>0</v>
+      </c>
+      <c r="E95" s="14">
+        <v>0</v>
+      </c>
+      <c r="F95" s="14">
+        <v>0</v>
+      </c>
+      <c r="G95" s="14">
+        <v>0</v>
+      </c>
+      <c r="H95" s="14">
+        <v>0</v>
+      </c>
+      <c r="I95" s="14">
+        <v>0</v>
+      </c>
+      <c r="J95" s="14">
+        <v>0</v>
+      </c>
+      <c r="K95" s="14">
+        <v>0</v>
+      </c>
+      <c r="L95" s="14">
+        <v>0</v>
+      </c>
+      <c r="M95" s="14">
+        <f>C95*M17</f>
+        <v>364</v>
+      </c>
+      <c r="N95" s="14"/>
+      <c r="O95" s="14"/>
+      <c r="P95" s="14">
         <f t="shared" si="7"/>
         <v>364</v>
       </c>
-      <c r="D94" s="14">
-        <v>0</v>
-      </c>
-      <c r="E94" s="14">
-        <v>0</v>
-      </c>
-      <c r="F94" s="14">
-        <v>0</v>
-      </c>
-      <c r="G94" s="14">
-        <v>0</v>
-      </c>
-      <c r="H94" s="14">
-        <v>0</v>
-      </c>
-      <c r="I94" s="14">
-        <v>0</v>
-      </c>
-      <c r="J94" s="14">
-        <v>0</v>
-      </c>
-      <c r="K94" s="14">
-        <v>0</v>
-      </c>
-      <c r="L94" s="14">
-        <v>0</v>
-      </c>
-      <c r="M94" s="14">
-        <f>C94*M17</f>
+      <c r="Q95" s="14">
+        <f>P95</f>
         <v>364</v>
-      </c>
-      <c r="N94" s="14"/>
-      <c r="O94" s="14"/>
-      <c r="P94" s="14">
-        <f t="shared" si="10"/>
-        <v>364</v>
-      </c>
-      <c r="Q94" s="14">
-        <f>P94</f>
-        <v>364</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A95" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C95" s="8">
-        <f t="shared" si="7"/>
-        <v>370</v>
-      </c>
-      <c r="D95" s="8">
-        <f t="shared" ref="D95:D105" si="13">C95*D17</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="8">
-        <f>C95*E17</f>
-        <v>0</v>
-      </c>
-      <c r="F95" s="8">
-        <f>C95*F17</f>
-        <v>0</v>
-      </c>
-      <c r="G95" s="8">
-        <f>C95*G17</f>
-        <v>0</v>
-      </c>
-      <c r="H95" s="8">
-        <f>D95*H17</f>
-        <v>0</v>
-      </c>
-      <c r="I95" s="8">
-        <f>C95*I17</f>
-        <v>0</v>
-      </c>
-      <c r="J95" s="8">
-        <f>C95*J17</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="8">
-        <f>C95*K17</f>
-        <v>0</v>
-      </c>
-      <c r="L95" s="8">
-        <f>C95*L17</f>
-        <v>0</v>
-      </c>
-      <c r="M95" s="8">
-        <f t="shared" ref="M95:M126" si="14">C95*M17</f>
-        <v>370</v>
-      </c>
-      <c r="N95" s="8"/>
-      <c r="O95" s="8"/>
-      <c r="P95" s="8">
-        <f t="shared" si="10"/>
-        <v>370</v>
-      </c>
-      <c r="Q95" s="8">
-        <f>SUM(P95:P96)</f>
-        <v>1202</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.3">
@@ -5099,179 +5086,179 @@
         <v>29</v>
       </c>
       <c r="C96" s="8">
-        <f t="shared" si="7"/>
-        <v>416</v>
+        <f>C17*2</f>
+        <v>370</v>
       </c>
       <c r="D96" s="8">
-        <f t="shared" si="13"/>
+        <f>C96*D17</f>
         <v>0</v>
       </c>
       <c r="E96" s="8">
-        <f>C96*E18</f>
+        <f>C96*E17</f>
         <v>0</v>
       </c>
       <c r="F96" s="8">
-        <f>C96*F18</f>
+        <f>C96*F17</f>
         <v>0</v>
       </c>
       <c r="G96" s="8">
-        <f>C96*G18</f>
+        <f>C96*G17</f>
         <v>0</v>
       </c>
       <c r="H96" s="8">
-        <f>D96*H18</f>
+        <f>D96*H17</f>
         <v>0</v>
       </c>
       <c r="I96" s="8">
-        <f>C96*I18</f>
+        <f>C96*I17</f>
         <v>0</v>
       </c>
       <c r="J96" s="8">
-        <f>C96*J18</f>
-        <v>416</v>
+        <f>C96*J17</f>
+        <v>0</v>
       </c>
       <c r="K96" s="8">
-        <f>C96*K18</f>
+        <f>C96*K17</f>
         <v>0</v>
       </c>
       <c r="L96" s="8">
-        <f>C96*L18</f>
-        <v>416</v>
+        <f>C96*L17</f>
+        <v>0</v>
       </c>
       <c r="M96" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>C96*M17</f>
+        <v>370</v>
       </c>
       <c r="N96" s="8"/>
       <c r="O96" s="8"/>
       <c r="P96" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
+        <v>370</v>
+      </c>
+      <c r="Q96" s="8">
+        <f>SUM(P96:P97)</f>
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A97" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" s="8">
+        <f>C18*2</f>
+        <v>416</v>
+      </c>
+      <c r="D97" s="8">
+        <f>C97*D18</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="8">
+        <f>C97*E18</f>
+        <v>0</v>
+      </c>
+      <c r="F97" s="8">
+        <f>C97*F18</f>
+        <v>0</v>
+      </c>
+      <c r="G97" s="8">
+        <f>C97*G18</f>
+        <v>0</v>
+      </c>
+      <c r="H97" s="8">
+        <f>D97*H18</f>
+        <v>0</v>
+      </c>
+      <c r="I97" s="8">
+        <f>C97*I18</f>
+        <v>0</v>
+      </c>
+      <c r="J97" s="8">
+        <f>C97*J18</f>
+        <v>416</v>
+      </c>
+      <c r="K97" s="8">
+        <f>C97*K18</f>
+        <v>0</v>
+      </c>
+      <c r="L97" s="8">
+        <f>C97*L18</f>
+        <v>416</v>
+      </c>
+      <c r="M97" s="8">
+        <f>C97*M18</f>
+        <v>0</v>
+      </c>
+      <c r="N97" s="8"/>
+      <c r="O97" s="8"/>
+      <c r="P97" s="8">
+        <f t="shared" si="7"/>
         <v>832</v>
       </c>
-      <c r="Q96" s="8"/>
-    </row>
-    <row r="97" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="14" t="s">
+      <c r="Q97" s="8"/>
+    </row>
+    <row r="98" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B98" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C97" s="14">
+      <c r="C98" s="14">
+        <f>C19*2</f>
+        <v>236</v>
+      </c>
+      <c r="D98" s="14">
+        <f>C98*D19</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="14">
+        <f t="shared" ref="E98:L98" si="9">D98*E19</f>
+        <v>0</v>
+      </c>
+      <c r="F98" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G98" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I98" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J98" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K98" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L98" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M98" s="14">
+        <f>C98*M19</f>
+        <v>236</v>
+      </c>
+      <c r="N98" s="14"/>
+      <c r="O98" s="14"/>
+      <c r="P98" s="14">
         <f t="shared" si="7"/>
         <v>236</v>
       </c>
-      <c r="D97" s="14">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E97" s="14">
-        <f t="shared" ref="E97:L97" si="15">D97*E19</f>
-        <v>0</v>
-      </c>
-      <c r="F97" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G97" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I97" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J97" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K97" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="L97" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M97" s="14">
-        <f t="shared" si="14"/>
+      <c r="Q98" s="14">
+        <f>P98</f>
         <v>236</v>
-      </c>
-      <c r="N97" s="14"/>
-      <c r="O97" s="14"/>
-      <c r="P97" s="14">
-        <f t="shared" si="10"/>
-        <v>236</v>
-      </c>
-      <c r="Q97" s="14">
-        <f>P97</f>
-        <v>236</v>
-      </c>
-    </row>
-    <row r="98" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C98" s="8">
-        <f t="shared" si="7"/>
-        <v>110</v>
-      </c>
-      <c r="D98" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E98" s="8">
-        <f t="shared" ref="E98:E105" si="16">C98*E20</f>
-        <v>110</v>
-      </c>
-      <c r="F98" s="8">
-        <f t="shared" ref="F98:F105" si="17">C98*F20</f>
-        <v>110</v>
-      </c>
-      <c r="G98" s="8">
-        <f t="shared" ref="G98:G105" si="18">C98*G20</f>
-        <v>0</v>
-      </c>
-      <c r="H98" s="8">
-        <f t="shared" ref="H98:H105" si="19">C98*H20</f>
-        <v>0</v>
-      </c>
-      <c r="I98" s="8">
-        <f t="shared" ref="I98:I105" si="20">C98*I20</f>
-        <v>0</v>
-      </c>
-      <c r="J98" s="8">
-        <f t="shared" ref="J98:J105" si="21">C98*J20</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="8">
-        <f t="shared" ref="K98:K105" si="22">C98*K20</f>
-        <v>0</v>
-      </c>
-      <c r="L98" s="8">
-        <f t="shared" ref="L98:L105" si="23">C98*L20</f>
-        <v>0</v>
-      </c>
-      <c r="M98" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N98" s="8"/>
-      <c r="O98" s="8"/>
-      <c r="P98" s="8">
-        <f t="shared" si="10"/>
-        <v>220</v>
-      </c>
-      <c r="Q98" s="8">
-        <f>SUM(P98:P102)</f>
-        <v>906</v>
       </c>
     </row>
     <row r="99" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
@@ -5279,116 +5266,119 @@
         <v>30</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C99" s="8">
-        <f t="shared" si="7"/>
-        <v>108</v>
+        <f>C20*2</f>
+        <v>110</v>
       </c>
       <c r="D99" s="8">
-        <f t="shared" si="13"/>
+        <f>C99*D20</f>
         <v>0</v>
       </c>
       <c r="E99" s="8">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>C99*E20</f>
+        <v>110</v>
       </c>
       <c r="F99" s="8">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f>C99*F20</f>
+        <v>110</v>
       </c>
       <c r="G99" s="8">
-        <f t="shared" si="18"/>
-        <v>108</v>
+        <f>C99*G20</f>
+        <v>0</v>
       </c>
       <c r="H99" s="8">
-        <f t="shared" si="19"/>
+        <f>C99*H20</f>
         <v>0</v>
       </c>
       <c r="I99" s="8">
-        <f t="shared" si="20"/>
+        <f>C99*I20</f>
         <v>0</v>
       </c>
       <c r="J99" s="8">
-        <f t="shared" si="21"/>
+        <f>C99*J20</f>
         <v>0</v>
       </c>
       <c r="K99" s="8">
-        <f t="shared" si="22"/>
+        <f>C99*K20</f>
         <v>0</v>
       </c>
       <c r="L99" s="8">
-        <f t="shared" si="23"/>
+        <f>C99*L20</f>
         <v>0</v>
       </c>
       <c r="M99" s="8">
-        <f t="shared" si="14"/>
+        <f>C99*M20</f>
         <v>0</v>
       </c>
       <c r="N99" s="8"/>
       <c r="O99" s="8"/>
       <c r="P99" s="8">
-        <f t="shared" si="10"/>
-        <v>108</v>
-      </c>
-      <c r="Q99" s="8"/>
+        <f t="shared" si="7"/>
+        <v>220</v>
+      </c>
+      <c r="Q99" s="8">
+        <f>SUM(P99:P103)</f>
+        <v>906</v>
+      </c>
     </row>
     <row r="100" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C100" s="8">
-        <f t="shared" si="7"/>
-        <v>110</v>
+        <f>C21*2</f>
+        <v>108</v>
       </c>
       <c r="D100" s="8">
-        <f t="shared" si="13"/>
+        <f>C100*D21</f>
         <v>0</v>
       </c>
       <c r="E100" s="8">
-        <f t="shared" si="16"/>
-        <v>110</v>
+        <f>C100*E21</f>
+        <v>0</v>
       </c>
       <c r="F100" s="8">
-        <f t="shared" si="17"/>
+        <f>C100*F21</f>
         <v>0</v>
       </c>
       <c r="G100" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>C100*G21</f>
+        <v>108</v>
       </c>
       <c r="H100" s="8">
-        <f t="shared" si="19"/>
+        <f>C100*H21</f>
         <v>0</v>
       </c>
       <c r="I100" s="8">
-        <f t="shared" si="20"/>
+        <f>C100*I21</f>
         <v>0</v>
       </c>
       <c r="J100" s="8">
-        <f t="shared" si="21"/>
+        <f>C100*J21</f>
         <v>0</v>
       </c>
       <c r="K100" s="8">
-        <f t="shared" si="22"/>
+        <f>C100*K21</f>
         <v>0</v>
       </c>
       <c r="L100" s="8">
-        <f t="shared" si="23"/>
+        <f>C100*L21</f>
         <v>0</v>
       </c>
       <c r="M100" s="8">
-        <f t="shared" si="14"/>
+        <f>C100*M21</f>
         <v>0</v>
       </c>
       <c r="N100" s="8"/>
       <c r="O100" s="8"/>
       <c r="P100" s="8">
-        <f t="shared" si="10"/>
-        <v>110</v>
+        <f t="shared" si="7"/>
+        <v>108</v>
       </c>
       <c r="Q100" s="8"/>
     </row>
@@ -5397,57 +5387,57 @@
         <v>30</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C101" s="8">
-        <f t="shared" si="7"/>
-        <v>92</v>
+        <f>C22*2</f>
+        <v>110</v>
       </c>
       <c r="D101" s="8">
-        <f t="shared" si="13"/>
+        <f>C101*D22</f>
         <v>0</v>
       </c>
       <c r="E101" s="8">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f>C101*E22</f>
+        <v>110</v>
       </c>
       <c r="F101" s="8">
-        <f t="shared" si="17"/>
+        <f>C101*F22</f>
         <v>0</v>
       </c>
       <c r="G101" s="8">
-        <f t="shared" si="18"/>
+        <f>C101*G22</f>
         <v>0</v>
       </c>
       <c r="H101" s="8">
-        <f t="shared" si="19"/>
+        <f>C101*H22</f>
         <v>0</v>
       </c>
       <c r="I101" s="8">
-        <f t="shared" si="20"/>
+        <f>C101*I22</f>
         <v>0</v>
       </c>
       <c r="J101" s="8">
-        <f t="shared" si="21"/>
-        <v>92</v>
+        <f>C101*J22</f>
+        <v>0</v>
       </c>
       <c r="K101" s="8">
-        <f t="shared" si="22"/>
+        <f>C101*K22</f>
         <v>0</v>
       </c>
       <c r="L101" s="8">
-        <f t="shared" si="23"/>
+        <f>C101*L22</f>
         <v>0</v>
       </c>
       <c r="M101" s="8">
-        <f t="shared" si="14"/>
+        <f>C101*M22</f>
         <v>0</v>
       </c>
       <c r="N101" s="8"/>
       <c r="O101" s="8"/>
       <c r="P101" s="8">
-        <f t="shared" si="10"/>
-        <v>92</v>
+        <f t="shared" si="7"/>
+        <v>110</v>
       </c>
       <c r="Q101" s="8"/>
     </row>
@@ -5456,639 +5446,639 @@
         <v>30</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C102" s="8">
-        <f t="shared" si="7"/>
-        <v>94</v>
+        <f>C23*2</f>
+        <v>92</v>
       </c>
       <c r="D102" s="8">
-        <f t="shared" si="13"/>
+        <f>C102*D23</f>
         <v>0</v>
       </c>
       <c r="E102" s="8">
-        <f t="shared" si="16"/>
+        <f>C102*E23</f>
         <v>0</v>
       </c>
       <c r="F102" s="8">
-        <f t="shared" si="17"/>
+        <f>C102*F23</f>
         <v>0</v>
       </c>
       <c r="G102" s="8">
-        <f t="shared" si="18"/>
+        <f>C102*G23</f>
         <v>0</v>
       </c>
       <c r="H102" s="8">
-        <f t="shared" si="19"/>
-        <v>94</v>
+        <f>C102*H23</f>
+        <v>0</v>
       </c>
       <c r="I102" s="8">
-        <f t="shared" si="20"/>
-        <v>188</v>
+        <f>C102*I23</f>
+        <v>0</v>
       </c>
       <c r="J102" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f>C102*J23</f>
+        <v>92</v>
       </c>
       <c r="K102" s="8">
-        <f t="shared" si="22"/>
-        <v>94</v>
+        <f>C102*K23</f>
+        <v>0</v>
       </c>
       <c r="L102" s="8">
-        <f t="shared" si="23"/>
+        <f>C102*L23</f>
         <v>0</v>
       </c>
       <c r="M102" s="8">
-        <f t="shared" si="14"/>
+        <f>C102*M23</f>
         <v>0</v>
       </c>
       <c r="N102" s="8"/>
       <c r="O102" s="8"/>
       <c r="P102" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
+        <v>92</v>
+      </c>
+      <c r="Q102" s="8"/>
+    </row>
+    <row r="103" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C103" s="8">
+        <f>C24*2</f>
+        <v>94</v>
+      </c>
+      <c r="D103" s="8">
+        <f>C103*D24</f>
+        <v>0</v>
+      </c>
+      <c r="E103" s="8">
+        <f>C103*E24</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="8">
+        <f>C103*F24</f>
+        <v>0</v>
+      </c>
+      <c r="G103" s="8">
+        <f>C103*G24</f>
+        <v>0</v>
+      </c>
+      <c r="H103" s="8">
+        <f>C103*H24</f>
+        <v>94</v>
+      </c>
+      <c r="I103" s="8">
+        <f>C103*I24</f>
+        <v>188</v>
+      </c>
+      <c r="J103" s="8">
+        <f>C103*J24</f>
+        <v>0</v>
+      </c>
+      <c r="K103" s="8">
+        <f>C103*K24</f>
+        <v>94</v>
+      </c>
+      <c r="L103" s="8">
+        <f>C103*L24</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="8">
+        <f>C103*M24</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="8"/>
+      <c r="O103" s="8"/>
+      <c r="P103" s="8">
+        <f t="shared" si="7"/>
         <v>376</v>
       </c>
-      <c r="Q102" s="8"/>
-    </row>
-    <row r="103" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="14" t="s">
+      <c r="Q103" s="8"/>
+    </row>
+    <row r="104" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B104" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C103" s="14">
+      <c r="C104" s="14">
+        <f>C25*2</f>
+        <v>800</v>
+      </c>
+      <c r="D104" s="14">
+        <f>C104*D25</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="14">
+        <f>C104*E25</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="14">
+        <f>C104*F25</f>
+        <v>0</v>
+      </c>
+      <c r="G104" s="14">
+        <f>C104*G25</f>
+        <v>0</v>
+      </c>
+      <c r="H104" s="14">
+        <f>C104*H25</f>
+        <v>0</v>
+      </c>
+      <c r="I104" s="14">
+        <f>C104*I25</f>
+        <v>0</v>
+      </c>
+      <c r="J104" s="14">
+        <f>C104*J25</f>
+        <v>0</v>
+      </c>
+      <c r="K104" s="14">
+        <f>C104*K25</f>
+        <v>0</v>
+      </c>
+      <c r="L104" s="14">
+        <f>C104*L25</f>
+        <v>800</v>
+      </c>
+      <c r="M104" s="14">
+        <f>C104*M25</f>
+        <v>0</v>
+      </c>
+      <c r="N104" s="14"/>
+      <c r="O104" s="14"/>
+      <c r="P104" s="14">
         <f t="shared" si="7"/>
         <v>800</v>
       </c>
-      <c r="D103" s="14">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E103" s="14">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="14">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G103" s="14">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H103" s="14">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I103" s="14">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J103" s="14">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K103" s="14">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L103" s="14">
-        <f t="shared" si="23"/>
+      <c r="Q104" s="14">
+        <f t="shared" ref="Q104:Q109" si="10">P104</f>
         <v>800</v>
       </c>
-      <c r="M103" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N103" s="14"/>
-      <c r="O103" s="14"/>
-      <c r="P103" s="14">
-        <f t="shared" si="10"/>
-        <v>800</v>
-      </c>
-      <c r="Q103" s="14">
-        <f t="shared" ref="Q103:Q108" si="24">P103</f>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="104" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="8" t="s">
+    </row>
+    <row r="105" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B105" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C104" s="8">
+      <c r="C105" s="8">
+        <f>C26*2</f>
+        <v>726</v>
+      </c>
+      <c r="D105" s="8">
+        <f>C105*D26</f>
+        <v>0</v>
+      </c>
+      <c r="E105" s="8">
+        <f>C105*E26</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="8">
+        <f>C105*F26</f>
+        <v>0</v>
+      </c>
+      <c r="G105" s="8">
+        <f>C105*G26</f>
+        <v>0</v>
+      </c>
+      <c r="H105" s="8">
+        <f>C105*H26</f>
+        <v>0</v>
+      </c>
+      <c r="I105" s="8">
+        <f>C105*I26</f>
+        <v>0</v>
+      </c>
+      <c r="J105" s="8">
+        <f>C105*J26</f>
+        <v>0</v>
+      </c>
+      <c r="K105" s="8">
+        <f>C105*K26</f>
+        <v>726</v>
+      </c>
+      <c r="L105" s="8">
+        <f>C105*L26</f>
+        <v>0</v>
+      </c>
+      <c r="M105" s="8">
+        <f>C105*M26</f>
+        <v>0</v>
+      </c>
+      <c r="N105" s="8"/>
+      <c r="O105" s="8"/>
+      <c r="P105" s="8">
         <f t="shared" si="7"/>
         <v>726</v>
       </c>
-      <c r="D104" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E104" s="8">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F104" s="8">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G104" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H104" s="8">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="8">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J104" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K104" s="8">
-        <f t="shared" si="22"/>
-        <v>726</v>
-      </c>
-      <c r="L104" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M104" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N104" s="8"/>
-      <c r="O104" s="8"/>
-      <c r="P104" s="8">
+      <c r="Q105" s="8">
         <f t="shared" si="10"/>
         <v>726</v>
       </c>
-      <c r="Q104" s="8">
-        <f t="shared" si="24"/>
-        <v>726</v>
-      </c>
-      <c r="R104" s="18"/>
-      <c r="S104" s="18"/>
-      <c r="T104" s="18"/>
-      <c r="U104" s="18"/>
-      <c r="V104" s="18"/>
-      <c r="W104" s="18"/>
-      <c r="X104" s="18"/>
-      <c r="Y104" s="18"/>
-      <c r="Z104" s="18"/>
-      <c r="AA104" s="18"/>
-      <c r="AB104" s="18"/>
-      <c r="AC104" s="18"/>
-      <c r="AD104" s="18"/>
-    </row>
-    <row r="105" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="14" t="s">
+      <c r="R105" s="18"/>
+      <c r="S105" s="18"/>
+      <c r="T105" s="18"/>
+      <c r="U105" s="18"/>
+      <c r="V105" s="18"/>
+      <c r="W105" s="18"/>
+      <c r="X105" s="18"/>
+      <c r="Y105" s="18"/>
+      <c r="Z105" s="18"/>
+      <c r="AA105" s="18"/>
+      <c r="AB105" s="18"/>
+      <c r="AC105" s="18"/>
+      <c r="AD105" s="18"/>
+    </row>
+    <row r="106" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B106" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C105" s="14">
+      <c r="C106" s="14">
+        <f>C27*2</f>
+        <v>186</v>
+      </c>
+      <c r="D106" s="14">
+        <f>C106*D27</f>
+        <v>0</v>
+      </c>
+      <c r="E106" s="14">
+        <f>C106*E27</f>
+        <v>0</v>
+      </c>
+      <c r="F106" s="14">
+        <f>C106*F27</f>
+        <v>0</v>
+      </c>
+      <c r="G106" s="14">
+        <f>C106*G27</f>
+        <v>0</v>
+      </c>
+      <c r="H106" s="14">
+        <f>C106*H27</f>
+        <v>0</v>
+      </c>
+      <c r="I106" s="14">
+        <f>C106*I27</f>
+        <v>0</v>
+      </c>
+      <c r="J106" s="14">
+        <f>C106*J27</f>
+        <v>0</v>
+      </c>
+      <c r="K106" s="14">
+        <f>C106*K27</f>
+        <v>0</v>
+      </c>
+      <c r="L106" s="14">
+        <f>C106*L27</f>
+        <v>0</v>
+      </c>
+      <c r="M106" s="14">
+        <f>C106*M27</f>
+        <v>186</v>
+      </c>
+      <c r="N106" s="14"/>
+      <c r="O106" s="14"/>
+      <c r="P106" s="14">
         <f t="shared" si="7"/>
         <v>186</v>
       </c>
-      <c r="D105" s="14">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E105" s="14">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F105" s="14">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G105" s="14">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H105" s="14">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I105" s="14">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J105" s="14">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K105" s="14">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L105" s="14">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="14">
-        <f t="shared" si="14"/>
+      <c r="Q106" s="14">
+        <f>P106</f>
         <v>186</v>
       </c>
-      <c r="N105" s="14"/>
-      <c r="O105" s="14"/>
-      <c r="P105" s="14">
-        <f t="shared" si="10"/>
-        <v>186</v>
-      </c>
-      <c r="Q105" s="14">
-        <f>P105</f>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="106" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="8" t="s">
+    </row>
+    <row r="107" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B107" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C106" s="8">
-        <f t="shared" si="7"/>
+      <c r="C107" s="8">
+        <f>C28*2</f>
         <v>348</v>
       </c>
-      <c r="D106" s="8">
-        <v>0</v>
-      </c>
-      <c r="E106" s="8">
-        <v>0</v>
-      </c>
-      <c r="F106" s="8">
-        <v>0</v>
-      </c>
-      <c r="G106" s="8">
-        <v>0</v>
-      </c>
-      <c r="H106" s="8">
-        <v>0</v>
-      </c>
-      <c r="I106" s="8">
-        <v>0</v>
-      </c>
-      <c r="J106" s="8">
-        <v>0</v>
-      </c>
-      <c r="K106" s="8">
-        <v>0</v>
-      </c>
-      <c r="L106" s="8">
-        <v>0</v>
-      </c>
-      <c r="M106" s="8">
-        <f t="shared" si="14"/>
+      <c r="D107" s="8">
+        <v>0</v>
+      </c>
+      <c r="E107" s="8">
+        <v>0</v>
+      </c>
+      <c r="F107" s="8">
+        <v>0</v>
+      </c>
+      <c r="G107" s="8">
+        <v>0</v>
+      </c>
+      <c r="H107" s="8">
+        <v>0</v>
+      </c>
+      <c r="I107" s="8">
+        <v>0</v>
+      </c>
+      <c r="J107" s="8">
+        <v>0</v>
+      </c>
+      <c r="K107" s="8">
+        <v>0</v>
+      </c>
+      <c r="L107" s="8">
+        <v>0</v>
+      </c>
+      <c r="M107" s="8">
+        <f>C107*M28</f>
         <v>348</v>
       </c>
-      <c r="N106" s="8"/>
-      <c r="O106" s="8"/>
-      <c r="P106" s="8">
-        <f>SUM(D106:M106)</f>
+      <c r="N107" s="8"/>
+      <c r="O107" s="8"/>
+      <c r="P107" s="8">
+        <f>SUM(D107:M107)</f>
         <v>348</v>
       </c>
-      <c r="Q106" s="8">
-        <f>P106</f>
+      <c r="Q107" s="8">
+        <f>P107</f>
         <v>348</v>
       </c>
-      <c r="R106" s="18"/>
-      <c r="S106" s="18"/>
-      <c r="T106" s="18"/>
-      <c r="U106" s="18"/>
-      <c r="V106" s="18"/>
-      <c r="W106" s="18"/>
-      <c r="X106" s="18"/>
-      <c r="Y106" s="18"/>
-      <c r="Z106" s="18"/>
-      <c r="AA106" s="18"/>
-      <c r="AB106" s="18"/>
-      <c r="AC106" s="18"/>
-      <c r="AD106" s="18"/>
-    </row>
-    <row r="107" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="14" t="s">
+      <c r="R107" s="18"/>
+      <c r="S107" s="18"/>
+      <c r="T107" s="18"/>
+      <c r="U107" s="18"/>
+      <c r="V107" s="18"/>
+      <c r="W107" s="18"/>
+      <c r="X107" s="18"/>
+      <c r="Y107" s="18"/>
+      <c r="Z107" s="18"/>
+      <c r="AA107" s="18"/>
+      <c r="AB107" s="18"/>
+      <c r="AC107" s="18"/>
+      <c r="AD107" s="18"/>
+    </row>
+    <row r="108" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="B108" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C107" s="14">
+      <c r="C108" s="14">
+        <f>C29*2</f>
+        <v>418</v>
+      </c>
+      <c r="D108" s="14">
+        <f t="shared" ref="D108:K108" si="11">C108*D30</f>
+        <v>0</v>
+      </c>
+      <c r="E108" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="F108" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G108" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H108" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I108" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J108" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K108" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L108" s="14">
+        <f>C108*L29</f>
+        <v>418</v>
+      </c>
+      <c r="M108" s="14">
+        <f>C108*M29</f>
+        <v>0</v>
+      </c>
+      <c r="N108" s="14"/>
+      <c r="O108" s="14"/>
+      <c r="P108" s="14">
         <f t="shared" si="7"/>
         <v>418</v>
       </c>
-      <c r="D107" s="14">
-        <f t="shared" ref="D107:K107" si="25">C107*D30</f>
-        <v>0</v>
-      </c>
-      <c r="E107" s="14">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="F107" s="14">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="G107" s="14">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H107" s="14">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="I107" s="14">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="J107" s="14">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="K107" s="14">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="L107" s="14">
-        <f>C107*L29</f>
-        <v>418</v>
-      </c>
-      <c r="M107" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N107" s="14"/>
-      <c r="O107" s="14"/>
-      <c r="P107" s="14">
+      <c r="Q108" s="14">
         <f t="shared" si="10"/>
         <v>418</v>
       </c>
-      <c r="Q107" s="14">
-        <f t="shared" si="24"/>
-        <v>418</v>
-      </c>
-    </row>
-    <row r="108" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="8" t="s">
+    </row>
+    <row r="109" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="B109" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C108" s="8">
+      <c r="C109" s="8">
+        <f>C30*2</f>
+        <v>516</v>
+      </c>
+      <c r="D109" s="8">
+        <f>C109*D30</f>
+        <v>0</v>
+      </c>
+      <c r="E109" s="8">
+        <f>C109*E30</f>
+        <v>0</v>
+      </c>
+      <c r="F109" s="8">
+        <f>C109*F30</f>
+        <v>0</v>
+      </c>
+      <c r="G109" s="8">
+        <f>C109*G30</f>
+        <v>0</v>
+      </c>
+      <c r="H109" s="8">
+        <f>C109*H30</f>
+        <v>0</v>
+      </c>
+      <c r="I109" s="8">
+        <f>C109*I30</f>
+        <v>516</v>
+      </c>
+      <c r="J109" s="8">
+        <f>C109*J30</f>
+        <v>0</v>
+      </c>
+      <c r="K109" s="8">
+        <f>C109*K30</f>
+        <v>0</v>
+      </c>
+      <c r="L109" s="8">
+        <f>C109*L30</f>
+        <v>0</v>
+      </c>
+      <c r="M109" s="8">
+        <f>C109*M30</f>
+        <v>0</v>
+      </c>
+      <c r="N109" s="8"/>
+      <c r="O109" s="8"/>
+      <c r="P109" s="8">
         <f t="shared" si="7"/>
         <v>516</v>
       </c>
-      <c r="D108" s="8">
-        <f t="shared" ref="D108:D139" si="26">C108*D30</f>
-        <v>0</v>
-      </c>
-      <c r="E108" s="8">
-        <f>C108*E30</f>
-        <v>0</v>
-      </c>
-      <c r="F108" s="8">
-        <f>C108*F30</f>
-        <v>0</v>
-      </c>
-      <c r="G108" s="8">
-        <f>C108*G30</f>
-        <v>0</v>
-      </c>
-      <c r="H108" s="8">
-        <f t="shared" ref="H108:H139" si="27">C108*H30</f>
-        <v>0</v>
-      </c>
-      <c r="I108" s="8">
-        <f>C108*I30</f>
-        <v>516</v>
-      </c>
-      <c r="J108" s="8">
-        <f>C108*J30</f>
-        <v>0</v>
-      </c>
-      <c r="K108" s="8">
-        <f>C108*K30</f>
-        <v>0</v>
-      </c>
-      <c r="L108" s="8">
-        <f>C108*L30</f>
-        <v>0</v>
-      </c>
-      <c r="M108" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="8"/>
-      <c r="O108" s="8"/>
-      <c r="P108" s="8">
+      <c r="Q109" s="8">
         <f t="shared" si="10"/>
         <v>516</v>
       </c>
-      <c r="Q108" s="8">
-        <f t="shared" si="24"/>
-        <v>516</v>
-      </c>
-      <c r="R108" s="18"/>
-      <c r="S108" s="18"/>
-      <c r="T108" s="18"/>
-      <c r="U108" s="18"/>
-      <c r="V108" s="18"/>
-      <c r="W108" s="18"/>
-      <c r="X108" s="18"/>
-      <c r="Y108" s="18"/>
-      <c r="Z108" s="18"/>
-      <c r="AA108" s="18"/>
-      <c r="AB108" s="18"/>
-      <c r="AC108" s="18"/>
-      <c r="AD108" s="18"/>
-    </row>
-    <row r="109" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="B109" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C109" s="14">
-        <f t="shared" si="7"/>
-        <v>50</v>
-      </c>
-      <c r="D109" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E109" s="14">
-        <f>C109*E31</f>
-        <v>0</v>
-      </c>
-      <c r="F109" s="14">
-        <f>C109*F31</f>
-        <v>0</v>
-      </c>
-      <c r="G109" s="14">
-        <f>C109*G31</f>
-        <v>0</v>
-      </c>
-      <c r="H109" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I109" s="14">
-        <f>C109*I31</f>
-        <v>0</v>
-      </c>
-      <c r="J109" s="14">
-        <f>C109*J31</f>
-        <v>50</v>
-      </c>
-      <c r="K109" s="14">
-        <f>C109*K31</f>
-        <v>50</v>
-      </c>
-      <c r="L109" s="14">
-        <f>C109*L31</f>
-        <v>0</v>
-      </c>
-      <c r="M109" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N109" s="14"/>
-      <c r="O109" s="14"/>
-      <c r="P109" s="14">
-        <f t="shared" ref="P109:P114" si="28">SUM(D109:M109)</f>
-        <v>100</v>
-      </c>
-      <c r="Q109" s="14">
-        <f>SUM(P109:P114)</f>
-        <v>1660</v>
-      </c>
+      <c r="R109" s="18"/>
+      <c r="S109" s="18"/>
+      <c r="T109" s="18"/>
+      <c r="U109" s="18"/>
+      <c r="V109" s="18"/>
+      <c r="W109" s="18"/>
+      <c r="X109" s="18"/>
+      <c r="Y109" s="18"/>
+      <c r="Z109" s="18"/>
+      <c r="AA109" s="18"/>
+      <c r="AB109" s="18"/>
+      <c r="AC109" s="18"/>
+      <c r="AD109" s="18"/>
     </row>
     <row r="110" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="C110" s="14">
-        <f t="shared" si="7"/>
-        <v>38</v>
+        <f>C31*2</f>
+        <v>50</v>
       </c>
       <c r="D110" s="14">
-        <f t="shared" si="26"/>
+        <f>C110*D31</f>
         <v>0</v>
       </c>
       <c r="E110" s="14">
-        <f>D110*E32</f>
+        <f>C110*E31</f>
         <v>0</v>
       </c>
       <c r="F110" s="14">
-        <f>E110*F32</f>
+        <f>C110*F31</f>
         <v>0</v>
       </c>
       <c r="G110" s="14">
-        <f>F110*G32</f>
+        <f>C110*G31</f>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <f t="shared" si="27"/>
+        <f>C110*H31</f>
         <v>0</v>
       </c>
       <c r="I110" s="14">
-        <f>D110*I32</f>
+        <f>C110*I31</f>
         <v>0</v>
       </c>
       <c r="J110" s="14">
-        <f>E110*J32</f>
-        <v>0</v>
+        <f>C110*J31</f>
+        <v>50</v>
       </c>
       <c r="K110" s="14">
-        <f>F110*K32</f>
-        <v>0</v>
+        <f>C110*K31</f>
+        <v>50</v>
       </c>
       <c r="L110" s="14">
-        <f>G110*L32</f>
+        <f>C110*L31</f>
         <v>0</v>
       </c>
       <c r="M110" s="14">
-        <f t="shared" si="14"/>
-        <v>38</v>
+        <f>C110*M31</f>
+        <v>0</v>
       </c>
       <c r="N110" s="14"/>
       <c r="O110" s="14"/>
       <c r="P110" s="14">
-        <f t="shared" si="28"/>
-        <v>38</v>
-      </c>
-      <c r="Q110" s="14"/>
+        <f t="shared" ref="P110:P115" si="12">SUM(D110:M110)</f>
+        <v>100</v>
+      </c>
+      <c r="Q110" s="14">
+        <f>SUM(P110:P115)</f>
+        <v>1660</v>
+      </c>
     </row>
     <row r="111" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="C111" s="14">
-        <f t="shared" si="7"/>
-        <v>54</v>
+        <f>C32*2</f>
+        <v>38</v>
       </c>
       <c r="D111" s="14">
-        <f t="shared" si="26"/>
+        <f>C111*D32</f>
         <v>0</v>
       </c>
       <c r="E111" s="14">
-        <f t="shared" ref="E111:E139" si="29">C111*E33</f>
+        <f>D111*E32</f>
         <v>0</v>
       </c>
       <c r="F111" s="14">
-        <f t="shared" ref="F111:F139" si="30">C111*F33</f>
+        <f>E111*F32</f>
         <v>0</v>
       </c>
       <c r="G111" s="14">
-        <f t="shared" ref="G111:G139" si="31">C111*G33</f>
-        <v>54</v>
+        <f>F111*G32</f>
+        <v>0</v>
       </c>
       <c r="H111" s="14">
-        <f t="shared" si="27"/>
+        <f>C111*H32</f>
         <v>0</v>
       </c>
       <c r="I111" s="14">
-        <f t="shared" ref="I111:I139" si="32">C111*I33</f>
-        <v>54</v>
+        <f>D111*I32</f>
+        <v>0</v>
       </c>
       <c r="J111" s="14">
-        <f t="shared" ref="J111:J139" si="33">C111*J33</f>
-        <v>108</v>
+        <f>E111*J32</f>
+        <v>0</v>
       </c>
       <c r="K111" s="14">
-        <f t="shared" ref="K111:K139" si="34">C111*K33</f>
+        <f>F111*K32</f>
         <v>0</v>
       </c>
       <c r="L111" s="14">
-        <f t="shared" ref="L111:L145" si="35">C111*L33</f>
+        <f>G111*L32</f>
         <v>0</v>
       </c>
       <c r="M111" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N111" s="20"/>
+        <f>C111*M32</f>
+        <v>38</v>
+      </c>
+      <c r="N111" s="14"/>
       <c r="O111" s="14"/>
       <c r="P111" s="14">
-        <f t="shared" si="28"/>
-        <v>216</v>
+        <f t="shared" si="12"/>
+        <v>38</v>
       </c>
       <c r="Q111" s="14"/>
     </row>
@@ -6097,57 +6087,57 @@
         <v>44</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C112" s="14">
-        <f t="shared" ref="C112:C143" si="36">C34*2</f>
+        <f>C33*2</f>
         <v>54</v>
       </c>
       <c r="D112" s="14">
-        <f t="shared" si="26"/>
+        <f>C112*D33</f>
         <v>0</v>
       </c>
       <c r="E112" s="14">
-        <f t="shared" si="29"/>
+        <f>C112*E33</f>
         <v>0</v>
       </c>
       <c r="F112" s="14">
-        <f t="shared" si="30"/>
+        <f>C112*F33</f>
         <v>0</v>
       </c>
       <c r="G112" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f>C112*G33</f>
+        <v>54</v>
       </c>
       <c r="H112" s="14">
-        <f t="shared" si="27"/>
+        <f>C112*H33</f>
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
+        <f>C112*I33</f>
+        <v>54</v>
       </c>
       <c r="J112" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f>C112*J33</f>
+        <v>108</v>
       </c>
       <c r="K112" s="14">
-        <f t="shared" si="34"/>
-        <v>54</v>
+        <f>C112*K33</f>
+        <v>0</v>
       </c>
       <c r="L112" s="14">
-        <f t="shared" si="35"/>
+        <f>C112*L33</f>
         <v>0</v>
       </c>
       <c r="M112" s="14">
-        <f t="shared" si="14"/>
-        <v>378</v>
-      </c>
-      <c r="N112" s="14"/>
+        <f>C112*M33</f>
+        <v>0</v>
+      </c>
+      <c r="N112" s="20"/>
       <c r="O112" s="14"/>
       <c r="P112" s="14">
-        <f t="shared" si="28"/>
-        <v>432</v>
+        <f t="shared" si="12"/>
+        <v>216</v>
       </c>
       <c r="Q112" s="14"/>
     </row>
@@ -6156,57 +6146,57 @@
         <v>44</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C113" s="14">
-        <f t="shared" si="36"/>
+        <f>C34*2</f>
         <v>54</v>
       </c>
       <c r="D113" s="14">
-        <f t="shared" si="26"/>
+        <f>C113*D34</f>
         <v>0</v>
       </c>
       <c r="E113" s="14">
-        <f t="shared" si="29"/>
+        <f>C113*E34</f>
         <v>0</v>
       </c>
       <c r="F113" s="14">
-        <f t="shared" si="30"/>
+        <f>C113*F34</f>
+        <v>0</v>
+      </c>
+      <c r="G113" s="14">
+        <f>C113*G34</f>
+        <v>0</v>
+      </c>
+      <c r="H113" s="14">
+        <f>C113*H34</f>
+        <v>0</v>
+      </c>
+      <c r="I113" s="14">
+        <f>C113*I34</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="14">
+        <f>C113*J34</f>
+        <v>0</v>
+      </c>
+      <c r="K113" s="14">
+        <f>C113*K34</f>
         <v>54</v>
       </c>
-      <c r="G113" s="14">
-        <f t="shared" si="31"/>
-        <v>108</v>
-      </c>
-      <c r="H113" s="14">
-        <f t="shared" si="27"/>
-        <v>54</v>
-      </c>
-      <c r="I113" s="14">
-        <f t="shared" si="32"/>
-        <v>54</v>
-      </c>
-      <c r="J113" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K113" s="14">
-        <f t="shared" si="34"/>
-        <v>54</v>
-      </c>
       <c r="L113" s="14">
-        <f t="shared" si="35"/>
-        <v>54</v>
+        <f>C113*L34</f>
+        <v>0</v>
       </c>
       <c r="M113" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
+        <f>C113*M34</f>
+        <v>378</v>
       </c>
       <c r="N113" s="14"/>
       <c r="O113" s="14"/>
       <c r="P113" s="14">
-        <f t="shared" si="28"/>
-        <v>378</v>
+        <f t="shared" si="12"/>
+        <v>432</v>
       </c>
       <c r="Q113" s="14"/>
     </row>
@@ -6215,193 +6205,180 @@
         <v>44</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C114" s="14">
-        <f t="shared" si="36"/>
-        <v>62</v>
+        <f>C35*2</f>
+        <v>54</v>
       </c>
       <c r="D114" s="14">
-        <f t="shared" si="26"/>
+        <f>C114*D35</f>
         <v>0</v>
       </c>
       <c r="E114" s="14">
-        <f t="shared" si="29"/>
+        <f>C114*E35</f>
         <v>0</v>
       </c>
       <c r="F114" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
+        <f>C114*F35</f>
+        <v>54</v>
       </c>
       <c r="G114" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f>C114*G35</f>
+        <v>108</v>
       </c>
       <c r="H114" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>C114*H35</f>
+        <v>54</v>
       </c>
       <c r="I114" s="14">
-        <f t="shared" si="32"/>
-        <v>62</v>
+        <f>C114*I35</f>
+        <v>54</v>
       </c>
       <c r="J114" s="14">
-        <f t="shared" si="33"/>
+        <f>C114*J35</f>
         <v>0</v>
       </c>
       <c r="K114" s="14">
-        <f t="shared" si="34"/>
-        <v>186</v>
+        <f>C114*K35</f>
+        <v>54</v>
       </c>
       <c r="L114" s="14">
-        <f t="shared" si="35"/>
-        <v>124</v>
+        <f>C114*L35</f>
+        <v>54</v>
       </c>
       <c r="M114" s="14">
-        <f t="shared" si="14"/>
-        <v>124</v>
+        <f>C114*M35</f>
+        <v>0</v>
       </c>
       <c r="N114" s="14"/>
       <c r="O114" s="14"/>
       <c r="P114" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="12"/>
+        <v>378</v>
+      </c>
+      <c r="Q114" s="14"/>
+    </row>
+    <row r="115" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B115" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C115" s="14">
+        <f>C36*2</f>
+        <v>62</v>
+      </c>
+      <c r="D115" s="14">
+        <f>C115*D36</f>
+        <v>0</v>
+      </c>
+      <c r="E115" s="14">
+        <f>C115*E36</f>
+        <v>0</v>
+      </c>
+      <c r="F115" s="14">
+        <f>C115*F36</f>
+        <v>0</v>
+      </c>
+      <c r="G115" s="14">
+        <f>C115*G36</f>
+        <v>0</v>
+      </c>
+      <c r="H115" s="14">
+        <f>C115*H36</f>
+        <v>0</v>
+      </c>
+      <c r="I115" s="14">
+        <f>C115*I36</f>
+        <v>62</v>
+      </c>
+      <c r="J115" s="14">
+        <f>C115*J36</f>
+        <v>0</v>
+      </c>
+      <c r="K115" s="14">
+        <f>C115*K36</f>
+        <v>186</v>
+      </c>
+      <c r="L115" s="14">
+        <f>C115*L36</f>
+        <v>124</v>
+      </c>
+      <c r="M115" s="14">
+        <f>C115*M36</f>
+        <v>124</v>
+      </c>
+      <c r="N115" s="14"/>
+      <c r="O115" s="14"/>
+      <c r="P115" s="14">
+        <f t="shared" si="12"/>
         <v>496</v>
       </c>
-      <c r="Q114" s="14"/>
-    </row>
-    <row r="115" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B115" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C115" s="8">
-        <f t="shared" si="36"/>
-        <v>158</v>
-      </c>
-      <c r="D115" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E115" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F115" s="8">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G115" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H115" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I115" s="8">
-        <f t="shared" si="32"/>
-        <v>158</v>
-      </c>
-      <c r="J115" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K115" s="8">
-        <f t="shared" si="34"/>
-        <v>158</v>
-      </c>
-      <c r="L115" s="8">
-        <f t="shared" si="35"/>
-        <v>158</v>
-      </c>
-      <c r="M115" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N115" s="8"/>
-      <c r="O115" s="8"/>
-      <c r="P115" s="8">
-        <f t="shared" si="10"/>
-        <v>474</v>
-      </c>
-      <c r="Q115" s="8">
-        <f>SUM(P115:P117)</f>
-        <v>1150</v>
-      </c>
-      <c r="R115" s="18"/>
-      <c r="S115" s="18"/>
-      <c r="T115" s="18"/>
-      <c r="U115" s="18"/>
-      <c r="V115" s="18"/>
-      <c r="W115" s="18"/>
-      <c r="X115" s="18"/>
-      <c r="Y115" s="18"/>
-      <c r="Z115" s="18"/>
-      <c r="AA115" s="18"/>
-      <c r="AB115" s="18"/>
-      <c r="AC115" s="18"/>
-      <c r="AD115" s="18"/>
+      <c r="Q115" s="14"/>
     </row>
     <row r="116" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C116" s="8">
-        <f t="shared" si="36"/>
-        <v>140</v>
+        <f>C37*2</f>
+        <v>158</v>
       </c>
       <c r="D116" s="8">
-        <f t="shared" si="26"/>
+        <f>C116*D37</f>
         <v>0</v>
       </c>
       <c r="E116" s="8">
-        <f t="shared" si="29"/>
+        <f>C116*E37</f>
         <v>0</v>
       </c>
       <c r="F116" s="8">
-        <f t="shared" si="30"/>
+        <f>C116*F37</f>
         <v>0</v>
       </c>
       <c r="G116" s="8">
-        <f t="shared" si="31"/>
+        <f>C116*G37</f>
         <v>0</v>
       </c>
       <c r="H116" s="8">
-        <f t="shared" si="27"/>
+        <f>C116*H37</f>
         <v>0</v>
       </c>
       <c r="I116" s="8">
-        <f t="shared" si="32"/>
-        <v>280</v>
+        <f>C116*I37</f>
+        <v>158</v>
       </c>
       <c r="J116" s="8">
-        <f t="shared" si="33"/>
+        <f>C116*J37</f>
         <v>0</v>
       </c>
       <c r="K116" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f>C116*K37</f>
+        <v>158</v>
       </c>
       <c r="L116" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f>C116*L37</f>
+        <v>158</v>
       </c>
       <c r="M116" s="8">
-        <f t="shared" si="14"/>
+        <f>C116*M37</f>
         <v>0</v>
       </c>
       <c r="N116" s="8"/>
       <c r="O116" s="8"/>
       <c r="P116" s="8">
-        <f t="shared" si="10"/>
-        <v>280</v>
-      </c>
-      <c r="Q116" s="8"/>
+        <f t="shared" si="7"/>
+        <v>474</v>
+      </c>
+      <c r="Q116" s="8">
+        <f>SUM(P116:P118)</f>
+        <v>1150</v>
+      </c>
       <c r="R116" s="18"/>
       <c r="S116" s="18"/>
       <c r="T116" s="18"/>
@@ -6421,57 +6398,57 @@
         <v>40</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C117" s="8">
-        <f t="shared" si="36"/>
-        <v>132</v>
+        <f>C38*2</f>
+        <v>140</v>
       </c>
       <c r="D117" s="8">
-        <f t="shared" si="26"/>
+        <f>C117*D38</f>
         <v>0</v>
       </c>
       <c r="E117" s="8">
-        <f t="shared" si="29"/>
+        <f>C117*E38</f>
         <v>0</v>
       </c>
       <c r="F117" s="8">
-        <f t="shared" si="30"/>
+        <f>C117*F38</f>
         <v>0</v>
       </c>
       <c r="G117" s="8">
-        <f t="shared" si="31"/>
+        <f>C117*G38</f>
         <v>0</v>
       </c>
       <c r="H117" s="8">
-        <f t="shared" si="27"/>
+        <f>C117*H38</f>
         <v>0</v>
       </c>
       <c r="I117" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
+        <f>C117*I38</f>
+        <v>280</v>
       </c>
       <c r="J117" s="8">
-        <f t="shared" si="33"/>
-        <v>132</v>
+        <f>C117*J38</f>
+        <v>0</v>
       </c>
       <c r="K117" s="8">
-        <f t="shared" si="34"/>
-        <v>132</v>
+        <f>C117*K38</f>
+        <v>0</v>
       </c>
       <c r="L117" s="8">
-        <f t="shared" si="35"/>
-        <v>132</v>
+        <f>C117*L38</f>
+        <v>0</v>
       </c>
       <c r="M117" s="8">
-        <f t="shared" si="14"/>
+        <f>C117*M38</f>
         <v>0</v>
       </c>
       <c r="N117" s="8"/>
       <c r="O117" s="8"/>
       <c r="P117" s="8">
-        <f t="shared" si="10"/>
-        <v>396</v>
+        <f t="shared" si="7"/>
+        <v>280</v>
       </c>
       <c r="Q117" s="8"/>
       <c r="R117" s="18"/>
@@ -6488,534 +6465,534 @@
       <c r="AC117" s="18"/>
       <c r="AD117" s="18"/>
     </row>
-    <row r="118" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="14" t="s">
+    <row r="118" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C118" s="8">
+        <f>C39*2</f>
+        <v>132</v>
+      </c>
+      <c r="D118" s="8">
+        <f>C118*D39</f>
+        <v>0</v>
+      </c>
+      <c r="E118" s="8">
+        <f>C118*E39</f>
+        <v>0</v>
+      </c>
+      <c r="F118" s="8">
+        <f>C118*F39</f>
+        <v>0</v>
+      </c>
+      <c r="G118" s="8">
+        <f>C118*G39</f>
+        <v>0</v>
+      </c>
+      <c r="H118" s="8">
+        <f>C118*H39</f>
+        <v>0</v>
+      </c>
+      <c r="I118" s="8">
+        <f>C118*I39</f>
+        <v>0</v>
+      </c>
+      <c r="J118" s="8">
+        <f>C118*J39</f>
+        <v>132</v>
+      </c>
+      <c r="K118" s="8">
+        <f>C118*K39</f>
+        <v>132</v>
+      </c>
+      <c r="L118" s="8">
+        <f>C118*L39</f>
+        <v>132</v>
+      </c>
+      <c r="M118" s="8">
+        <f>C118*M39</f>
+        <v>0</v>
+      </c>
+      <c r="N118" s="8"/>
+      <c r="O118" s="8"/>
+      <c r="P118" s="8">
+        <f t="shared" si="7"/>
+        <v>396</v>
+      </c>
+      <c r="Q118" s="8"/>
+      <c r="R118" s="18"/>
+      <c r="S118" s="18"/>
+      <c r="T118" s="18"/>
+      <c r="U118" s="18"/>
+      <c r="V118" s="18"/>
+      <c r="W118" s="18"/>
+      <c r="X118" s="18"/>
+      <c r="Y118" s="18"/>
+      <c r="Z118" s="18"/>
+      <c r="AA118" s="18"/>
+      <c r="AB118" s="18"/>
+      <c r="AC118" s="18"/>
+      <c r="AD118" s="18"/>
+    </row>
+    <row r="119" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B118" s="14" t="s">
+      <c r="B119" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C118" s="14">
-        <f t="shared" si="36"/>
+      <c r="C119" s="14">
+        <f>C40*2</f>
         <v>840</v>
       </c>
-      <c r="D118" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E118" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F118" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G118" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H118" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J118" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K118" s="14">
-        <f t="shared" si="34"/>
+      <c r="D119" s="14">
+        <f>C119*D40</f>
+        <v>0</v>
+      </c>
+      <c r="E119" s="14">
+        <f>C119*E40</f>
+        <v>0</v>
+      </c>
+      <c r="F119" s="14">
+        <f>C119*F40</f>
+        <v>0</v>
+      </c>
+      <c r="G119" s="14">
+        <f>C119*G40</f>
+        <v>0</v>
+      </c>
+      <c r="H119" s="14">
+        <f>C119*H40</f>
+        <v>0</v>
+      </c>
+      <c r="I119" s="14">
+        <f>C119*I40</f>
+        <v>0</v>
+      </c>
+      <c r="J119" s="14">
+        <f>C119*J40</f>
+        <v>0</v>
+      </c>
+      <c r="K119" s="14">
+        <f>C119*K40</f>
         <v>840</v>
       </c>
-      <c r="L118" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M118" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N118" s="14"/>
-      <c r="O118" s="14"/>
-      <c r="P118" s="14">
-        <f t="shared" si="10"/>
+      <c r="L119" s="14">
+        <f>C119*L40</f>
+        <v>0</v>
+      </c>
+      <c r="M119" s="14">
+        <f>C119*M40</f>
+        <v>0</v>
+      </c>
+      <c r="N119" s="14"/>
+      <c r="O119" s="14"/>
+      <c r="P119" s="14">
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
-      <c r="Q118" s="14">
-        <f>P118</f>
+      <c r="Q119" s="14">
+        <f>P119</f>
         <v>840</v>
       </c>
     </row>
-    <row r="119" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="8" t="s">
+    <row r="120" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="B120" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C119" s="8">
-        <f t="shared" si="36"/>
+      <c r="C120" s="8">
+        <f>C41*2</f>
         <v>282</v>
       </c>
-      <c r="D119" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E119" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F119" s="8">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G119" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H119" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I119" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J119" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K119" s="8">
-        <f t="shared" si="34"/>
+      <c r="D120" s="8">
+        <f>C120*D41</f>
+        <v>0</v>
+      </c>
+      <c r="E120" s="8">
+        <f>C120*E41</f>
+        <v>0</v>
+      </c>
+      <c r="F120" s="8">
+        <f>C120*F41</f>
+        <v>0</v>
+      </c>
+      <c r="G120" s="8">
+        <f>C120*G41</f>
+        <v>0</v>
+      </c>
+      <c r="H120" s="8">
+        <f>C120*H41</f>
+        <v>0</v>
+      </c>
+      <c r="I120" s="8">
+        <f>C120*I41</f>
+        <v>0</v>
+      </c>
+      <c r="J120" s="8">
+        <f>C120*J41</f>
+        <v>0</v>
+      </c>
+      <c r="K120" s="8">
+        <f>C120*K41</f>
         <v>282</v>
       </c>
-      <c r="L119" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M119" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N119" s="8"/>
-      <c r="O119" s="8"/>
-      <c r="P119" s="8">
-        <f t="shared" si="10"/>
+      <c r="L120" s="8">
+        <f>C120*L41</f>
+        <v>0</v>
+      </c>
+      <c r="M120" s="8">
+        <f>C120*M41</f>
+        <v>0</v>
+      </c>
+      <c r="N120" s="8"/>
+      <c r="O120" s="8"/>
+      <c r="P120" s="8">
+        <f t="shared" si="7"/>
         <v>282</v>
       </c>
-      <c r="Q119" s="8">
-        <f>P119</f>
+      <c r="Q120" s="8">
+        <f>P120</f>
         <v>282</v>
       </c>
-      <c r="R119" s="18"/>
-      <c r="S119" s="18"/>
-      <c r="T119" s="18"/>
-      <c r="U119" s="18"/>
-      <c r="V119" s="18"/>
-      <c r="W119" s="18"/>
-      <c r="X119" s="18"/>
-      <c r="Y119" s="18"/>
-      <c r="Z119" s="18"/>
-      <c r="AA119" s="18"/>
-      <c r="AB119" s="18"/>
-      <c r="AC119" s="18"/>
-      <c r="AD119" s="18"/>
-    </row>
-    <row r="120" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="14" t="s">
+      <c r="R120" s="18"/>
+      <c r="S120" s="18"/>
+      <c r="T120" s="18"/>
+      <c r="U120" s="18"/>
+      <c r="V120" s="18"/>
+      <c r="W120" s="18"/>
+      <c r="X120" s="18"/>
+      <c r="Y120" s="18"/>
+      <c r="Z120" s="18"/>
+      <c r="AA120" s="18"/>
+      <c r="AB120" s="18"/>
+      <c r="AC120" s="18"/>
+      <c r="AD120" s="18"/>
+    </row>
+    <row r="121" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B120" s="14" t="s">
+      <c r="B121" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C120" s="14">
-        <f t="shared" si="36"/>
+      <c r="C121" s="14">
+        <f>C42*2</f>
         <v>160</v>
       </c>
-      <c r="D120" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E120" s="14">
-        <f t="shared" si="29"/>
+      <c r="D121" s="14">
+        <f>C121*D42</f>
+        <v>0</v>
+      </c>
+      <c r="E121" s="14">
+        <f>C121*E42</f>
         <v>160</v>
       </c>
-      <c r="F120" s="14">
-        <f t="shared" si="30"/>
+      <c r="F121" s="14">
+        <f>C121*F42</f>
         <v>160</v>
       </c>
-      <c r="G120" s="14">
-        <f t="shared" si="31"/>
+      <c r="G121" s="14">
+        <f>C121*G42</f>
         <v>320</v>
       </c>
-      <c r="H120" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I120" s="14">
-        <f t="shared" si="32"/>
+      <c r="H121" s="14">
+        <f>C121*H42</f>
+        <v>0</v>
+      </c>
+      <c r="I121" s="14">
+        <f>C121*I42</f>
         <v>480</v>
       </c>
-      <c r="J120" s="14">
-        <f t="shared" si="33"/>
+      <c r="J121" s="14">
+        <f>C121*J42</f>
         <v>160</v>
       </c>
-      <c r="K120" s="14">
-        <f t="shared" si="34"/>
+      <c r="K121" s="14">
+        <f>C121*K42</f>
         <v>160</v>
       </c>
-      <c r="L120" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M120" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N120" s="14"/>
-      <c r="O120" s="14"/>
-      <c r="P120" s="14">
-        <f t="shared" si="10"/>
+      <c r="L121" s="14">
+        <f>C121*L42</f>
+        <v>0</v>
+      </c>
+      <c r="M121" s="14">
+        <f>C121*M42</f>
+        <v>0</v>
+      </c>
+      <c r="N121" s="14"/>
+      <c r="O121" s="14"/>
+      <c r="P121" s="14">
+        <f t="shared" si="7"/>
         <v>1440</v>
       </c>
-      <c r="Q120" s="14">
-        <f>P120</f>
+      <c r="Q121" s="14">
+        <f>P121</f>
         <v>1440</v>
       </c>
     </row>
-    <row r="121" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="8" t="s">
+    <row r="122" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B121" s="8" t="s">
+      <c r="B122" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C121" s="8">
-        <f t="shared" si="36"/>
+      <c r="C122" s="8">
+        <f>C43*2</f>
         <v>1044</v>
       </c>
-      <c r="D121" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E121" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F121" s="8">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G121" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H121" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I121" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J121" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K121" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L121" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M121" s="8">
-        <f t="shared" si="14"/>
+      <c r="D122" s="8">
+        <f>C122*D43</f>
+        <v>0</v>
+      </c>
+      <c r="E122" s="8">
+        <f>C122*E43</f>
+        <v>0</v>
+      </c>
+      <c r="F122" s="8">
+        <f>C122*F43</f>
+        <v>0</v>
+      </c>
+      <c r="G122" s="8">
+        <f>C122*G43</f>
+        <v>0</v>
+      </c>
+      <c r="H122" s="8">
+        <f>C122*H43</f>
+        <v>0</v>
+      </c>
+      <c r="I122" s="8">
+        <f>C122*I43</f>
+        <v>0</v>
+      </c>
+      <c r="J122" s="8">
+        <f>C122*J43</f>
+        <v>0</v>
+      </c>
+      <c r="K122" s="8">
+        <f>C122*K43</f>
+        <v>0</v>
+      </c>
+      <c r="L122" s="8">
+        <f>C122*L43</f>
+        <v>0</v>
+      </c>
+      <c r="M122" s="8">
+        <f>C122*M43</f>
         <v>2088</v>
       </c>
-      <c r="N121" s="8"/>
-      <c r="O121" s="8"/>
-      <c r="P121" s="8">
-        <f t="shared" si="10"/>
+      <c r="N122" s="8"/>
+      <c r="O122" s="8"/>
+      <c r="P122" s="8">
+        <f t="shared" si="7"/>
         <v>2088</v>
       </c>
-      <c r="Q121" s="8">
-        <f>P121</f>
+      <c r="Q122" s="8">
+        <f>P122</f>
         <v>2088</v>
       </c>
-      <c r="R121" s="18"/>
-      <c r="S121" s="18"/>
-      <c r="T121" s="18"/>
-      <c r="U121" s="18"/>
-      <c r="V121" s="18"/>
-      <c r="W121" s="18"/>
-      <c r="X121" s="18"/>
-      <c r="Y121" s="18"/>
-      <c r="Z121" s="18"/>
-      <c r="AA121" s="18"/>
-      <c r="AB121" s="18"/>
-      <c r="AC121" s="18"/>
-      <c r="AD121" s="18"/>
-    </row>
-    <row r="122" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B122" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C122" s="14">
-        <f t="shared" si="36"/>
-        <v>68</v>
-      </c>
-      <c r="D122" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E122" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F122" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G122" s="14">
-        <f t="shared" si="31"/>
-        <v>68</v>
-      </c>
-      <c r="H122" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I122" s="14">
-        <f t="shared" si="32"/>
-        <v>136</v>
-      </c>
-      <c r="J122" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K122" s="14">
-        <f t="shared" si="34"/>
-        <v>136</v>
-      </c>
-      <c r="L122" s="14">
-        <f t="shared" si="35"/>
-        <v>68</v>
-      </c>
-      <c r="M122" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N122" s="14"/>
-      <c r="O122" s="14"/>
-      <c r="P122" s="14">
-        <f t="shared" si="10"/>
-        <v>408</v>
-      </c>
-      <c r="Q122" s="14">
-        <f>SUM(P122:P123)</f>
-        <v>498</v>
-      </c>
+      <c r="R122" s="18"/>
+      <c r="S122" s="18"/>
+      <c r="T122" s="18"/>
+      <c r="U122" s="18"/>
+      <c r="V122" s="18"/>
+      <c r="W122" s="18"/>
+      <c r="X122" s="18"/>
+      <c r="Y122" s="18"/>
+      <c r="Z122" s="18"/>
+      <c r="AA122" s="18"/>
+      <c r="AB122" s="18"/>
+      <c r="AC122" s="18"/>
+      <c r="AD122" s="18"/>
     </row>
     <row r="123" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="14" t="s">
         <v>56</v>
       </c>
       <c r="B123" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C123" s="14">
-        <f t="shared" si="36"/>
-        <v>90</v>
+        <f>C44*2</f>
+        <v>68</v>
       </c>
       <c r="D123" s="14">
-        <f t="shared" si="26"/>
+        <f>C123*D44</f>
         <v>0</v>
       </c>
       <c r="E123" s="14">
-        <f t="shared" si="29"/>
+        <f>C123*E44</f>
         <v>0</v>
       </c>
       <c r="F123" s="14">
-        <f t="shared" si="30"/>
-        <v>90</v>
+        <f>C123*F44</f>
+        <v>0</v>
       </c>
       <c r="G123" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f>C123*G44</f>
+        <v>68</v>
       </c>
       <c r="H123" s="14">
-        <f t="shared" si="27"/>
+        <f>C123*H44</f>
         <v>0</v>
       </c>
       <c r="I123" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
+        <f>C123*I44</f>
+        <v>136</v>
       </c>
       <c r="J123" s="14">
-        <f t="shared" si="33"/>
+        <f>C123*J44</f>
         <v>0</v>
       </c>
       <c r="K123" s="14">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f>C123*K44</f>
+        <v>136</v>
       </c>
       <c r="L123" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
+        <f>C123*L44</f>
+        <v>68</v>
       </c>
       <c r="M123" s="14">
-        <f t="shared" si="14"/>
+        <f>C123*M44</f>
         <v>0</v>
       </c>
       <c r="N123" s="14"/>
       <c r="O123" s="14"/>
       <c r="P123" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
+        <v>408</v>
+      </c>
+      <c r="Q123" s="14">
+        <f>SUM(P123:P124)</f>
+        <v>498</v>
+      </c>
+    </row>
+    <row r="124" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C124" s="14">
+        <f>C45*2</f>
         <v>90</v>
       </c>
-      <c r="Q123" s="14"/>
-    </row>
-    <row r="124" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B124" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C124" s="8">
-        <f t="shared" si="36"/>
-        <v>264</v>
-      </c>
-      <c r="D124" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E124" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F124" s="8">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G124" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H124" s="8">
-        <f t="shared" si="27"/>
-        <v>264</v>
-      </c>
-      <c r="I124" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J124" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K124" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L124" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M124" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N124" s="8"/>
-      <c r="O124" s="8"/>
-      <c r="P124" s="8">
-        <f t="shared" si="10"/>
-        <v>264</v>
-      </c>
-      <c r="Q124" s="8">
-        <f>SUM(P124:P126)</f>
-        <v>1050</v>
-      </c>
-      <c r="R124" s="18"/>
-      <c r="S124" s="18"/>
-      <c r="T124" s="18"/>
-      <c r="U124" s="18"/>
-      <c r="V124" s="18"/>
-      <c r="W124" s="18"/>
-      <c r="X124" s="18"/>
-      <c r="Y124" s="18"/>
-      <c r="Z124" s="18"/>
-      <c r="AA124" s="18"/>
-      <c r="AB124" s="18"/>
-      <c r="AC124" s="18"/>
-      <c r="AD124" s="18"/>
+      <c r="D124" s="14">
+        <f>C124*D45</f>
+        <v>0</v>
+      </c>
+      <c r="E124" s="14">
+        <f>C124*E45</f>
+        <v>0</v>
+      </c>
+      <c r="F124" s="14">
+        <f>C124*F45</f>
+        <v>90</v>
+      </c>
+      <c r="G124" s="14">
+        <f>C124*G45</f>
+        <v>0</v>
+      </c>
+      <c r="H124" s="14">
+        <f>C124*H45</f>
+        <v>0</v>
+      </c>
+      <c r="I124" s="14">
+        <f>C124*I45</f>
+        <v>0</v>
+      </c>
+      <c r="J124" s="14">
+        <f>C124*J45</f>
+        <v>0</v>
+      </c>
+      <c r="K124" s="14">
+        <f>C124*K45</f>
+        <v>0</v>
+      </c>
+      <c r="L124" s="14">
+        <f>C124*L45</f>
+        <v>0</v>
+      </c>
+      <c r="M124" s="14">
+        <f>C124*M45</f>
+        <v>0</v>
+      </c>
+      <c r="N124" s="14"/>
+      <c r="O124" s="14"/>
+      <c r="P124" s="14">
+        <f t="shared" si="7"/>
+        <v>90</v>
+      </c>
+      <c r="Q124" s="14"/>
     </row>
     <row r="125" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>59</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C125" s="8">
-        <f t="shared" si="36"/>
-        <v>262</v>
+        <f>C46*2</f>
+        <v>264</v>
       </c>
       <c r="D125" s="8">
-        <f t="shared" si="26"/>
+        <f>C125*D46</f>
         <v>0</v>
       </c>
       <c r="E125" s="8">
-        <f t="shared" si="29"/>
+        <f>C125*E46</f>
         <v>0</v>
       </c>
       <c r="F125" s="8">
-        <f t="shared" si="30"/>
-        <v>262</v>
+        <f>C125*F46</f>
+        <v>0</v>
       </c>
       <c r="G125" s="8">
-        <f t="shared" si="31"/>
+        <f>C125*G46</f>
         <v>0</v>
       </c>
       <c r="H125" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>C125*H46</f>
+        <v>264</v>
       </c>
       <c r="I125" s="8">
-        <f t="shared" si="32"/>
+        <f>C125*I46</f>
         <v>0</v>
       </c>
       <c r="J125" s="8">
-        <f t="shared" si="33"/>
+        <f>C125*J46</f>
         <v>0</v>
       </c>
       <c r="K125" s="8">
-        <f t="shared" si="34"/>
+        <f>C125*K46</f>
         <v>0</v>
       </c>
       <c r="L125" s="8">
-        <f t="shared" si="35"/>
+        <f>C125*L46</f>
         <v>0</v>
       </c>
       <c r="M125" s="8">
-        <f t="shared" si="14"/>
+        <f>C125*M46</f>
         <v>0</v>
       </c>
       <c r="N125" s="8"/>
       <c r="O125" s="8"/>
       <c r="P125" s="8">
-        <f t="shared" si="10"/>
-        <v>262</v>
-      </c>
-      <c r="Q125" s="8"/>
+        <f t="shared" si="7"/>
+        <v>264</v>
+      </c>
+      <c r="Q125" s="8">
+        <f>SUM(P125:P127)</f>
+        <v>1050</v>
+      </c>
       <c r="R125" s="18"/>
       <c r="S125" s="18"/>
       <c r="T125" s="18"/>
@@ -7035,57 +7012,57 @@
         <v>59</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C126" s="8">
-        <f t="shared" si="36"/>
+        <f>C47*2</f>
         <v>262</v>
       </c>
       <c r="D126" s="8">
-        <f t="shared" si="26"/>
+        <f>C126*D47</f>
+        <v>0</v>
+      </c>
+      <c r="E126" s="8">
+        <f>C126*E47</f>
+        <v>0</v>
+      </c>
+      <c r="F126" s="8">
+        <f>C126*F47</f>
         <v>262</v>
       </c>
-      <c r="E126" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F126" s="8">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
       <c r="G126" s="8">
-        <f t="shared" si="31"/>
+        <f>C126*G47</f>
         <v>0</v>
       </c>
       <c r="H126" s="8">
-        <f t="shared" si="27"/>
+        <f>C126*H47</f>
         <v>0</v>
       </c>
       <c r="I126" s="8">
-        <f t="shared" si="32"/>
+        <f>C126*I47</f>
         <v>0</v>
       </c>
       <c r="J126" s="8">
-        <f t="shared" si="33"/>
+        <f>C126*J47</f>
         <v>0</v>
       </c>
       <c r="K126" s="8">
-        <f t="shared" si="34"/>
-        <v>262</v>
+        <f>C126*K47</f>
+        <v>0</v>
       </c>
       <c r="L126" s="8">
-        <f t="shared" si="35"/>
+        <f>C126*L47</f>
         <v>0</v>
       </c>
       <c r="M126" s="8">
-        <f t="shared" si="14"/>
+        <f>C126*M47</f>
         <v>0</v>
       </c>
       <c r="N126" s="8"/>
       <c r="O126" s="8"/>
       <c r="P126" s="8">
-        <f t="shared" si="10"/>
-        <v>524</v>
+        <f t="shared" si="7"/>
+        <v>262</v>
       </c>
       <c r="Q126" s="8"/>
       <c r="R126" s="18"/>
@@ -7102,201 +7079,201 @@
       <c r="AC126" s="18"/>
       <c r="AD126" s="18"/>
     </row>
-    <row r="127" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="14" t="s">
+    <row r="127" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C127" s="8">
+        <f>C48*2</f>
+        <v>262</v>
+      </c>
+      <c r="D127" s="8">
+        <f>C127*D48</f>
+        <v>262</v>
+      </c>
+      <c r="E127" s="8">
+        <f>C127*E48</f>
+        <v>0</v>
+      </c>
+      <c r="F127" s="8">
+        <f>C127*F48</f>
+        <v>0</v>
+      </c>
+      <c r="G127" s="8">
+        <f>C127*G48</f>
+        <v>0</v>
+      </c>
+      <c r="H127" s="8">
+        <f>C127*H48</f>
+        <v>0</v>
+      </c>
+      <c r="I127" s="8">
+        <f>C127*I48</f>
+        <v>0</v>
+      </c>
+      <c r="J127" s="8">
+        <f>C127*J48</f>
+        <v>0</v>
+      </c>
+      <c r="K127" s="8">
+        <f>C127*K48</f>
+        <v>262</v>
+      </c>
+      <c r="L127" s="8">
+        <f>C127*L48</f>
+        <v>0</v>
+      </c>
+      <c r="M127" s="8">
+        <f>C127*M48</f>
+        <v>0</v>
+      </c>
+      <c r="N127" s="8"/>
+      <c r="O127" s="8"/>
+      <c r="P127" s="8">
+        <f t="shared" si="7"/>
+        <v>524</v>
+      </c>
+      <c r="Q127" s="8"/>
+      <c r="R127" s="18"/>
+      <c r="S127" s="18"/>
+      <c r="T127" s="18"/>
+      <c r="U127" s="18"/>
+      <c r="V127" s="18"/>
+      <c r="W127" s="18"/>
+      <c r="X127" s="18"/>
+      <c r="Y127" s="18"/>
+      <c r="Z127" s="18"/>
+      <c r="AA127" s="18"/>
+      <c r="AB127" s="18"/>
+      <c r="AC127" s="18"/>
+      <c r="AD127" s="18"/>
+    </row>
+    <row r="128" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B127" s="14" t="s">
+      <c r="B128" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C127" s="14">
-        <f t="shared" si="36"/>
+      <c r="C128" s="14">
+        <f>C49*2</f>
         <v>272</v>
       </c>
-      <c r="D127" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E127" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F127" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G127" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H127" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I127" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J127" s="14">
-        <f t="shared" si="33"/>
+      <c r="D128" s="14">
+        <f>C128*D49</f>
+        <v>0</v>
+      </c>
+      <c r="E128" s="14">
+        <f>C128*E49</f>
+        <v>0</v>
+      </c>
+      <c r="F128" s="14">
+        <f>C128*F49</f>
+        <v>0</v>
+      </c>
+      <c r="G128" s="14">
+        <f>C128*G49</f>
+        <v>0</v>
+      </c>
+      <c r="H128" s="14">
+        <f>C128*H49</f>
+        <v>0</v>
+      </c>
+      <c r="I128" s="14">
+        <f>C128*I49</f>
+        <v>0</v>
+      </c>
+      <c r="J128" s="14">
+        <f>C128*J49</f>
         <v>544</v>
       </c>
-      <c r="K127" s="14">
-        <f t="shared" si="34"/>
+      <c r="K128" s="14">
+        <f>C128*K49</f>
         <v>272</v>
       </c>
-      <c r="L127" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M127" s="14">
-        <f t="shared" ref="M127:M158" si="37">C127*M49</f>
-        <v>0</v>
-      </c>
-      <c r="N127" s="14"/>
-      <c r="O127" s="14"/>
-      <c r="P127" s="14">
-        <f t="shared" si="10"/>
+      <c r="L128" s="14">
+        <f>C128*L49</f>
+        <v>0</v>
+      </c>
+      <c r="M128" s="14">
+        <f>C128*M49</f>
+        <v>0</v>
+      </c>
+      <c r="N128" s="14"/>
+      <c r="O128" s="14"/>
+      <c r="P128" s="14">
+        <f t="shared" si="7"/>
         <v>816</v>
       </c>
-      <c r="Q127" s="14">
-        <f>P127</f>
+      <c r="Q128" s="14">
+        <f>P128</f>
         <v>816</v>
       </c>
-    </row>
-    <row r="128" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C128" s="8">
-        <f t="shared" si="36"/>
-        <v>266</v>
-      </c>
-      <c r="D128" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E128" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F128" s="8">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G128" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H128" s="8">
-        <f t="shared" si="27"/>
-        <v>266</v>
-      </c>
-      <c r="I128" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J128" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K128" s="8">
-        <f t="shared" si="34"/>
-        <v>266</v>
-      </c>
-      <c r="L128" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M128" s="8">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N128" s="8"/>
-      <c r="O128" s="8"/>
-      <c r="P128" s="8">
-        <f t="shared" si="10"/>
-        <v>532</v>
-      </c>
-      <c r="Q128" s="8">
-        <f>SUM(P128:P131)</f>
-        <v>1396</v>
-      </c>
-      <c r="R128" s="18"/>
-      <c r="S128" s="18"/>
-      <c r="T128" s="18"/>
-      <c r="U128" s="18"/>
-      <c r="V128" s="18"/>
-      <c r="W128" s="18"/>
-      <c r="X128" s="18"/>
-      <c r="Y128" s="18"/>
-      <c r="Z128" s="18"/>
-      <c r="AA128" s="18"/>
-      <c r="AB128" s="18"/>
-      <c r="AC128" s="18"/>
-      <c r="AD128" s="18"/>
     </row>
     <row r="129" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C129" s="8">
-        <f t="shared" si="36"/>
-        <v>304</v>
+        <f>C50*2</f>
+        <v>266</v>
       </c>
       <c r="D129" s="8">
-        <f t="shared" si="26"/>
+        <f>C129*D50</f>
         <v>0</v>
       </c>
       <c r="E129" s="8">
-        <f t="shared" si="29"/>
+        <f>C129*E50</f>
         <v>0</v>
       </c>
       <c r="F129" s="8">
-        <f t="shared" si="30"/>
+        <f>C129*F50</f>
         <v>0</v>
       </c>
       <c r="G129" s="8">
-        <f t="shared" si="31"/>
+        <f>C129*G50</f>
         <v>0</v>
       </c>
       <c r="H129" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>C129*H50</f>
+        <v>266</v>
       </c>
       <c r="I129" s="8">
-        <f t="shared" si="32"/>
+        <f>C129*I50</f>
         <v>0</v>
       </c>
       <c r="J129" s="8">
-        <f t="shared" si="33"/>
+        <f>C129*J50</f>
         <v>0</v>
       </c>
       <c r="K129" s="8">
-        <f t="shared" si="34"/>
-        <v>304</v>
+        <f>C129*K50</f>
+        <v>266</v>
       </c>
       <c r="L129" s="8">
-        <f t="shared" si="35"/>
+        <f>C129*L50</f>
         <v>0</v>
       </c>
       <c r="M129" s="8">
-        <f t="shared" si="37"/>
+        <f>C129*M50</f>
         <v>0</v>
       </c>
       <c r="N129" s="8"/>
       <c r="O129" s="8"/>
       <c r="P129" s="8">
-        <f t="shared" si="10"/>
-        <v>304</v>
-      </c>
-      <c r="Q129" s="8"/>
+        <f t="shared" si="7"/>
+        <v>532</v>
+      </c>
+      <c r="Q129" s="8">
+        <f>SUM(P129:P132)</f>
+        <v>1396</v>
+      </c>
       <c r="R129" s="18"/>
       <c r="S129" s="18"/>
       <c r="T129" s="18"/>
@@ -7316,57 +7293,57 @@
         <v>65</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C130" s="8">
-        <f t="shared" si="36"/>
-        <v>254</v>
+        <f>C51*2</f>
+        <v>304</v>
       </c>
       <c r="D130" s="8">
-        <f t="shared" si="26"/>
+        <f>C130*D51</f>
         <v>0</v>
       </c>
       <c r="E130" s="8">
-        <f t="shared" si="29"/>
+        <f>C130*E51</f>
         <v>0</v>
       </c>
       <c r="F130" s="8">
-        <f t="shared" si="30"/>
+        <f>C130*F51</f>
         <v>0</v>
       </c>
       <c r="G130" s="8">
-        <f t="shared" si="31"/>
+        <f>C130*G51</f>
         <v>0</v>
       </c>
       <c r="H130" s="8">
-        <f t="shared" si="27"/>
+        <f>C130*H51</f>
         <v>0</v>
       </c>
       <c r="I130" s="8">
-        <f t="shared" si="32"/>
-        <v>254</v>
+        <f>C130*I51</f>
+        <v>0</v>
       </c>
       <c r="J130" s="8">
-        <f t="shared" si="33"/>
+        <f>C130*J51</f>
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f>C130*K51</f>
+        <v>304</v>
       </c>
       <c r="L130" s="8">
-        <f t="shared" si="35"/>
+        <f>C130*L51</f>
         <v>0</v>
       </c>
       <c r="M130" s="8">
-        <f t="shared" si="37"/>
+        <f>C130*M51</f>
         <v>0</v>
       </c>
       <c r="N130" s="8"/>
       <c r="O130" s="8"/>
       <c r="P130" s="8">
-        <f t="shared" si="10"/>
-        <v>254</v>
+        <f t="shared" si="7"/>
+        <v>304</v>
       </c>
       <c r="Q130" s="8"/>
       <c r="R130" s="18"/>
@@ -7383,62 +7360,62 @@
       <c r="AC130" s="18"/>
       <c r="AD130" s="18"/>
     </row>
-    <row r="131" spans="1:30" s="19" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C131" s="8">
-        <f t="shared" si="36"/>
-        <v>306</v>
+        <f>C52*2</f>
+        <v>254</v>
       </c>
       <c r="D131" s="8">
-        <f t="shared" si="26"/>
+        <f>C131*D52</f>
         <v>0</v>
       </c>
       <c r="E131" s="8">
-        <f t="shared" si="29"/>
+        <f>C131*E52</f>
         <v>0</v>
       </c>
       <c r="F131" s="8">
-        <f t="shared" si="30"/>
+        <f>C131*F52</f>
         <v>0</v>
       </c>
       <c r="G131" s="8">
-        <f t="shared" si="31"/>
+        <f>C131*G52</f>
         <v>0</v>
       </c>
       <c r="H131" s="8">
-        <f t="shared" si="27"/>
+        <f>C131*H52</f>
         <v>0</v>
       </c>
       <c r="I131" s="8">
-        <f t="shared" si="32"/>
-        <v>306</v>
+        <f>C131*I52</f>
+        <v>254</v>
       </c>
       <c r="J131" s="8">
-        <f t="shared" si="33"/>
+        <f>C131*J52</f>
         <v>0</v>
       </c>
       <c r="K131" s="8">
-        <f t="shared" si="34"/>
+        <f>C131*K52</f>
         <v>0</v>
       </c>
       <c r="L131" s="8">
-        <f t="shared" si="35"/>
+        <f>C131*L52</f>
         <v>0</v>
       </c>
       <c r="M131" s="8">
-        <f t="shared" si="37"/>
+        <f>C131*M52</f>
         <v>0</v>
       </c>
       <c r="N131" s="8"/>
       <c r="O131" s="8"/>
       <c r="P131" s="8">
-        <f t="shared" si="10"/>
-        <v>306</v>
+        <f t="shared" si="7"/>
+        <v>254</v>
       </c>
       <c r="Q131" s="8"/>
       <c r="R131" s="18"/>
@@ -7455,319 +7432,319 @@
       <c r="AC131" s="18"/>
       <c r="AD131" s="18"/>
     </row>
-    <row r="132" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B132" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C132" s="14">
-        <f t="shared" si="36"/>
-        <v>124</v>
-      </c>
-      <c r="D132" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E132" s="14">
-        <f t="shared" si="29"/>
-        <v>124</v>
-      </c>
-      <c r="F132" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G132" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H132" s="14">
-        <f t="shared" si="27"/>
-        <v>124</v>
-      </c>
-      <c r="I132" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J132" s="14">
-        <f t="shared" si="33"/>
-        <v>248</v>
-      </c>
-      <c r="K132" s="14">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L132" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M132" s="14">
-        <f t="shared" si="37"/>
-        <v>124</v>
-      </c>
-      <c r="N132" s="14"/>
-      <c r="O132" s="14"/>
-      <c r="P132" s="14">
-        <f t="shared" si="10"/>
-        <v>620</v>
-      </c>
-      <c r="Q132" s="14">
-        <f>SUM(P132:P134)</f>
-        <v>1004</v>
-      </c>
+    <row r="132" spans="1:30" s="19" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C132" s="8">
+        <f>C53*2</f>
+        <v>306</v>
+      </c>
+      <c r="D132" s="8">
+        <f>C132*D53</f>
+        <v>0</v>
+      </c>
+      <c r="E132" s="8">
+        <f>C132*E53</f>
+        <v>0</v>
+      </c>
+      <c r="F132" s="8">
+        <f>C132*F53</f>
+        <v>0</v>
+      </c>
+      <c r="G132" s="8">
+        <f>C132*G53</f>
+        <v>0</v>
+      </c>
+      <c r="H132" s="8">
+        <f>C132*H53</f>
+        <v>0</v>
+      </c>
+      <c r="I132" s="8">
+        <f>C132*I53</f>
+        <v>306</v>
+      </c>
+      <c r="J132" s="8">
+        <f>C132*J53</f>
+        <v>0</v>
+      </c>
+      <c r="K132" s="8">
+        <f>C132*K53</f>
+        <v>0</v>
+      </c>
+      <c r="L132" s="8">
+        <f>C132*L53</f>
+        <v>0</v>
+      </c>
+      <c r="M132" s="8">
+        <f>C132*M53</f>
+        <v>0</v>
+      </c>
+      <c r="N132" s="8"/>
+      <c r="O132" s="8"/>
+      <c r="P132" s="8">
+        <f t="shared" si="7"/>
+        <v>306</v>
+      </c>
+      <c r="Q132" s="8"/>
+      <c r="R132" s="18"/>
+      <c r="S132" s="18"/>
+      <c r="T132" s="18"/>
+      <c r="U132" s="18"/>
+      <c r="V132" s="18"/>
+      <c r="W132" s="18"/>
+      <c r="X132" s="18"/>
+      <c r="Y132" s="18"/>
+      <c r="Z132" s="18"/>
+      <c r="AA132" s="18"/>
+      <c r="AB132" s="18"/>
+      <c r="AC132" s="18"/>
+      <c r="AD132" s="18"/>
     </row>
     <row r="133" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="14" t="s">
         <v>70</v>
       </c>
       <c r="B133" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C133" s="14">
-        <f t="shared" si="36"/>
-        <v>130</v>
+        <f>C54*2</f>
+        <v>124</v>
       </c>
       <c r="D133" s="14">
-        <f t="shared" si="26"/>
+        <f>C133*D54</f>
         <v>0</v>
       </c>
       <c r="E133" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f>C133*E54</f>
+        <v>124</v>
       </c>
       <c r="F133" s="14">
-        <f t="shared" si="30"/>
+        <f>C133*F54</f>
         <v>0</v>
       </c>
       <c r="G133" s="14">
-        <f t="shared" si="31"/>
-        <v>260</v>
+        <f>C133*G54</f>
+        <v>0</v>
       </c>
       <c r="H133" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
+        <f>C133*H54</f>
+        <v>124</v>
       </c>
       <c r="I133" s="14">
-        <f t="shared" si="32"/>
+        <f>C133*I54</f>
         <v>0</v>
       </c>
       <c r="J133" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f>C133*J54</f>
+        <v>248</v>
       </c>
       <c r="K133" s="14">
-        <f t="shared" si="34"/>
+        <f>C133*K54</f>
         <v>0</v>
       </c>
       <c r="L133" s="14">
-        <f t="shared" si="35"/>
+        <f>C133*L54</f>
         <v>0</v>
       </c>
       <c r="M133" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
+        <f>C133*M54</f>
+        <v>124</v>
       </c>
       <c r="N133" s="14"/>
       <c r="O133" s="14"/>
       <c r="P133" s="14">
-        <f t="shared" si="10"/>
-        <v>260</v>
-      </c>
-      <c r="Q133" s="14"/>
+        <f t="shared" si="7"/>
+        <v>620</v>
+      </c>
+      <c r="Q133" s="14">
+        <f>SUM(P133:P135)</f>
+        <v>1004</v>
+      </c>
     </row>
     <row r="134" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="14" t="s">
         <v>70</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C134" s="14">
-        <f t="shared" si="36"/>
-        <v>124</v>
+        <f>C55*2</f>
+        <v>130</v>
       </c>
       <c r="D134" s="14">
-        <f t="shared" si="26"/>
+        <f>C134*D55</f>
         <v>0</v>
       </c>
       <c r="E134" s="14">
-        <f t="shared" si="29"/>
+        <f>C134*E55</f>
         <v>0</v>
       </c>
       <c r="F134" s="14">
-        <f t="shared" si="30"/>
+        <f>C134*F55</f>
         <v>0</v>
       </c>
       <c r="G134" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
+        <f>C134*G55</f>
+        <v>260</v>
       </c>
       <c r="H134" s="14">
-        <f t="shared" si="27"/>
+        <f>C134*H55</f>
         <v>0</v>
       </c>
       <c r="I134" s="14">
-        <f t="shared" si="32"/>
+        <f>C134*I55</f>
         <v>0</v>
       </c>
       <c r="J134" s="14">
-        <f t="shared" si="33"/>
+        <f>C134*J55</f>
         <v>0</v>
       </c>
       <c r="K134" s="14">
-        <f t="shared" si="34"/>
-        <v>124</v>
+        <f>C134*K55</f>
+        <v>0</v>
       </c>
       <c r="L134" s="14">
-        <f t="shared" si="35"/>
+        <f>C134*L55</f>
         <v>0</v>
       </c>
       <c r="M134" s="14">
-        <f t="shared" si="37"/>
+        <f>C134*M55</f>
         <v>0</v>
       </c>
       <c r="N134" s="14"/>
       <c r="O134" s="14"/>
       <c r="P134" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
+        <v>260</v>
+      </c>
+      <c r="Q134" s="14"/>
+    </row>
+    <row r="135" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C135" s="14">
+        <f>C56*2</f>
         <v>124</v>
       </c>
-      <c r="Q134" s="14"/>
-    </row>
-    <row r="135" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B135" s="8" t="s">
+      <c r="D135" s="14">
+        <f>C135*D56</f>
+        <v>0</v>
+      </c>
+      <c r="E135" s="14">
+        <f>C135*E56</f>
+        <v>0</v>
+      </c>
+      <c r="F135" s="14">
+        <f>C135*F56</f>
+        <v>0</v>
+      </c>
+      <c r="G135" s="14">
+        <f>C135*G56</f>
+        <v>0</v>
+      </c>
+      <c r="H135" s="14">
+        <f>C135*H56</f>
+        <v>0</v>
+      </c>
+      <c r="I135" s="14">
+        <f>C135*I56</f>
+        <v>0</v>
+      </c>
+      <c r="J135" s="14">
+        <f>C135*J56</f>
+        <v>0</v>
+      </c>
+      <c r="K135" s="14">
+        <f>C135*K56</f>
         <v>124</v>
       </c>
-      <c r="C135" s="8">
-        <f t="shared" si="36"/>
-        <v>90</v>
-      </c>
-      <c r="D135" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E135" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F135" s="8">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G135" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H135" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I135" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J135" s="8">
-        <f t="shared" si="33"/>
-        <v>90</v>
-      </c>
-      <c r="K135" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L135" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M135" s="8">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N135" s="8"/>
-      <c r="O135" s="8"/>
-      <c r="P135" s="8">
-        <f t="shared" si="10"/>
-        <v>90</v>
-      </c>
-      <c r="Q135" s="8">
-        <f>SUM(P135:P137)</f>
-        <v>286</v>
-      </c>
-      <c r="R135" s="18"/>
-      <c r="S135" s="18"/>
-      <c r="T135" s="18"/>
-      <c r="U135" s="18"/>
-      <c r="V135" s="18"/>
-      <c r="W135" s="18"/>
-      <c r="X135" s="18"/>
-      <c r="Y135" s="18"/>
-      <c r="Z135" s="18"/>
-      <c r="AA135" s="18"/>
-      <c r="AB135" s="18"/>
-      <c r="AC135" s="18"/>
-      <c r="AD135" s="18"/>
+      <c r="L135" s="14">
+        <f>C135*L56</f>
+        <v>0</v>
+      </c>
+      <c r="M135" s="14">
+        <f>C135*M56</f>
+        <v>0</v>
+      </c>
+      <c r="N135" s="14"/>
+      <c r="O135" s="14"/>
+      <c r="P135" s="14">
+        <f t="shared" si="7"/>
+        <v>124</v>
+      </c>
+      <c r="Q135" s="14"/>
     </row>
     <row r="136" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>74</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="C136" s="8">
-        <f t="shared" si="36"/>
-        <v>106</v>
+        <f>C57*2</f>
+        <v>90</v>
       </c>
       <c r="D136" s="8">
-        <f t="shared" si="26"/>
-        <v>106</v>
+        <f>C136*D57</f>
+        <v>0</v>
       </c>
       <c r="E136" s="8">
-        <f t="shared" si="29"/>
+        <f>C136*E57</f>
         <v>0</v>
       </c>
       <c r="F136" s="8">
-        <f t="shared" si="30"/>
+        <f>C136*F57</f>
         <v>0</v>
       </c>
       <c r="G136" s="8">
-        <f t="shared" si="31"/>
+        <f>C136*G57</f>
         <v>0</v>
       </c>
       <c r="H136" s="8">
-        <f t="shared" si="27"/>
+        <f>C136*H57</f>
         <v>0</v>
       </c>
       <c r="I136" s="8">
-        <f t="shared" si="32"/>
+        <f>C136*I57</f>
         <v>0</v>
       </c>
       <c r="J136" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f>C136*J57</f>
+        <v>90</v>
       </c>
       <c r="K136" s="8">
-        <f t="shared" si="34"/>
+        <f>C136*K57</f>
         <v>0</v>
       </c>
       <c r="L136" s="8">
-        <f t="shared" si="35"/>
+        <f>C136*L57</f>
         <v>0</v>
       </c>
       <c r="M136" s="8">
-        <f t="shared" si="37"/>
+        <f>C136*M57</f>
         <v>0</v>
       </c>
       <c r="N136" s="8"/>
       <c r="O136" s="8"/>
       <c r="P136" s="8">
-        <f t="shared" si="10"/>
-        <v>106</v>
-      </c>
-      <c r="Q136" s="8"/>
+        <f t="shared" si="7"/>
+        <v>90</v>
+      </c>
+      <c r="Q136" s="8">
+        <f>SUM(P136:P138)</f>
+        <v>286</v>
+      </c>
       <c r="R136" s="18"/>
       <c r="S136" s="18"/>
       <c r="T136" s="18"/>
@@ -7787,57 +7764,57 @@
         <v>74</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C137" s="8">
-        <f t="shared" si="36"/>
-        <v>90</v>
+        <f>C58*2</f>
+        <v>106</v>
       </c>
       <c r="D137" s="8">
-        <f t="shared" si="26"/>
-        <v>0</v>
+        <f>C137*D58</f>
+        <v>106</v>
       </c>
       <c r="E137" s="8">
-        <f t="shared" si="29"/>
-        <v>90</v>
+        <f>C137*E58</f>
+        <v>0</v>
       </c>
       <c r="F137" s="8">
-        <f t="shared" si="30"/>
+        <f>C137*F58</f>
         <v>0</v>
       </c>
       <c r="G137" s="8">
-        <f t="shared" si="31"/>
+        <f>C137*G58</f>
         <v>0</v>
       </c>
       <c r="H137" s="8">
-        <f t="shared" si="27"/>
+        <f>C137*H58</f>
         <v>0</v>
       </c>
       <c r="I137" s="8">
-        <f t="shared" si="32"/>
+        <f>C137*I58</f>
         <v>0</v>
       </c>
       <c r="J137" s="8">
-        <f t="shared" si="33"/>
+        <f>C137*J58</f>
         <v>0</v>
       </c>
       <c r="K137" s="8">
-        <f t="shared" si="34"/>
+        <f>C137*K58</f>
         <v>0</v>
       </c>
       <c r="L137" s="8">
-        <f t="shared" si="35"/>
+        <f>C137*L58</f>
         <v>0</v>
       </c>
       <c r="M137" s="8">
-        <f t="shared" si="37"/>
+        <f>C137*M58</f>
         <v>0</v>
       </c>
       <c r="N137" s="8"/>
       <c r="O137" s="8"/>
       <c r="P137" s="8">
-        <f t="shared" si="10"/>
-        <v>90</v>
+        <f t="shared" si="7"/>
+        <v>106</v>
       </c>
       <c r="Q137" s="8"/>
       <c r="R137" s="18"/>
@@ -7854,1227 +7831,1372 @@
       <c r="AC137" s="18"/>
       <c r="AD137" s="18"/>
     </row>
-    <row r="138" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B138" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C138" s="14">
-        <f t="shared" si="36"/>
-        <v>40</v>
-      </c>
-      <c r="D138" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E138" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F138" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G138" s="14">
-        <f t="shared" si="31"/>
-        <v>80</v>
-      </c>
-      <c r="H138" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I138" s="14">
-        <f t="shared" si="32"/>
-        <v>160</v>
-      </c>
-      <c r="J138" s="14">
-        <f t="shared" si="33"/>
-        <v>160</v>
-      </c>
-      <c r="K138" s="14">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L138" s="14">
-        <f t="shared" si="35"/>
-        <v>40</v>
-      </c>
-      <c r="M138" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N138" s="14"/>
-      <c r="O138" s="14"/>
-      <c r="P138" s="14">
-        <f t="shared" si="10"/>
-        <v>440</v>
-      </c>
-      <c r="Q138" s="14">
-        <f>SUM(P138:P140)</f>
-        <v>712</v>
-      </c>
+    <row r="138" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C138" s="8">
+        <f>C59*2</f>
+        <v>90</v>
+      </c>
+      <c r="D138" s="8">
+        <f>C138*D59</f>
+        <v>0</v>
+      </c>
+      <c r="E138" s="8">
+        <f>C138*E59</f>
+        <v>90</v>
+      </c>
+      <c r="F138" s="8">
+        <f>C138*F59</f>
+        <v>0</v>
+      </c>
+      <c r="G138" s="8">
+        <f>C138*G59</f>
+        <v>0</v>
+      </c>
+      <c r="H138" s="8">
+        <f>C138*H59</f>
+        <v>0</v>
+      </c>
+      <c r="I138" s="8">
+        <f>C138*I59</f>
+        <v>0</v>
+      </c>
+      <c r="J138" s="8">
+        <f>C138*J59</f>
+        <v>0</v>
+      </c>
+      <c r="K138" s="8">
+        <f>C138*K59</f>
+        <v>0</v>
+      </c>
+      <c r="L138" s="8">
+        <f>C138*L59</f>
+        <v>0</v>
+      </c>
+      <c r="M138" s="8">
+        <f>C138*M59</f>
+        <v>0</v>
+      </c>
+      <c r="N138" s="8"/>
+      <c r="O138" s="8"/>
+      <c r="P138" s="8">
+        <f t="shared" si="7"/>
+        <v>90</v>
+      </c>
+      <c r="Q138" s="8"/>
+      <c r="R138" s="18"/>
+      <c r="S138" s="18"/>
+      <c r="T138" s="18"/>
+      <c r="U138" s="18"/>
+      <c r="V138" s="18"/>
+      <c r="W138" s="18"/>
+      <c r="X138" s="18"/>
+      <c r="Y138" s="18"/>
+      <c r="Z138" s="18"/>
+      <c r="AA138" s="18"/>
+      <c r="AB138" s="18"/>
+      <c r="AC138" s="18"/>
+      <c r="AD138" s="18"/>
     </row>
     <row r="139" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="14" t="s">
         <v>78</v>
       </c>
       <c r="B139" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C139" s="14">
+        <f>C60*2</f>
+        <v>40</v>
+      </c>
+      <c r="D139" s="14">
+        <f>C139*D60</f>
+        <v>0</v>
+      </c>
+      <c r="E139" s="14">
+        <f>C139*E60</f>
+        <v>0</v>
+      </c>
+      <c r="F139" s="14">
+        <f>C139*F60</f>
+        <v>0</v>
+      </c>
+      <c r="G139" s="14">
+        <f>C139*G60</f>
         <v>80</v>
       </c>
-      <c r="C139" s="14">
-        <f t="shared" si="36"/>
-        <v>34</v>
-      </c>
-      <c r="D139" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E139" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F139" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G139" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
       <c r="H139" s="14">
-        <f t="shared" si="27"/>
+        <f>C139*H60</f>
         <v>0</v>
       </c>
       <c r="I139" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
+        <f>C139*I60</f>
+        <v>160</v>
       </c>
       <c r="J139" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
+        <f>C139*J60</f>
+        <v>160</v>
       </c>
       <c r="K139" s="14">
-        <f t="shared" si="34"/>
-        <v>136</v>
+        <f>C139*K60</f>
+        <v>0</v>
       </c>
       <c r="L139" s="14">
-        <f t="shared" si="35"/>
-        <v>68</v>
+        <f>C139*L60</f>
+        <v>40</v>
       </c>
       <c r="M139" s="14">
-        <f t="shared" si="37"/>
+        <f>C139*M60</f>
         <v>0</v>
       </c>
       <c r="N139" s="14"/>
       <c r="O139" s="14"/>
       <c r="P139" s="14">
-        <f t="shared" si="10"/>
-        <v>204</v>
-      </c>
-      <c r="Q139" s="14"/>
+        <f t="shared" si="7"/>
+        <v>440</v>
+      </c>
+      <c r="Q139" s="14">
+        <f>SUM(P139:P141)</f>
+        <v>712</v>
+      </c>
     </row>
     <row r="140" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="14" t="s">
         <v>78</v>
       </c>
       <c r="B140" s="14" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C140" s="14">
-        <f t="shared" si="36"/>
+        <f>C61*2</f>
         <v>34</v>
       </c>
       <c r="D140" s="14">
+        <f>C140*D61</f>
         <v>0</v>
       </c>
       <c r="E140" s="14">
+        <f>C140*E61</f>
         <v>0</v>
       </c>
       <c r="F140" s="14">
+        <f>C140*F61</f>
         <v>0</v>
       </c>
       <c r="G140" s="14">
+        <f>C140*G61</f>
         <v>0</v>
       </c>
       <c r="H140" s="14">
+        <f>C140*H61</f>
         <v>0</v>
       </c>
       <c r="I140" s="14">
+        <f>C140*I61</f>
         <v>0</v>
       </c>
       <c r="J140" s="14">
+        <f>C140*J61</f>
         <v>0</v>
       </c>
       <c r="K140" s="14">
-        <v>0</v>
+        <f>C140*K61</f>
+        <v>136</v>
       </c>
       <c r="L140" s="14">
-        <f t="shared" si="35"/>
+        <f>C140*L61</f>
         <v>68</v>
       </c>
       <c r="M140" s="14">
-        <f t="shared" si="37"/>
+        <f>C140*M61</f>
         <v>0</v>
       </c>
       <c r="N140" s="14"/>
       <c r="O140" s="14"/>
       <c r="P140" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
+        <v>204</v>
+      </c>
+      <c r="Q140" s="14"/>
+    </row>
+    <row r="141" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B141" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C141" s="14">
+        <f>C62*2</f>
+        <v>34</v>
+      </c>
+      <c r="D141" s="14">
+        <v>0</v>
+      </c>
+      <c r="E141" s="14">
+        <v>0</v>
+      </c>
+      <c r="F141" s="14">
+        <v>0</v>
+      </c>
+      <c r="G141" s="14">
+        <v>0</v>
+      </c>
+      <c r="H141" s="14">
+        <v>0</v>
+      </c>
+      <c r="I141" s="14">
+        <v>0</v>
+      </c>
+      <c r="J141" s="14">
+        <v>0</v>
+      </c>
+      <c r="K141" s="14">
+        <v>0</v>
+      </c>
+      <c r="L141" s="14">
+        <f>C141*L62</f>
         <v>68</v>
       </c>
-      <c r="Q140" s="14"/>
-    </row>
-    <row r="141" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="8" t="s">
+      <c r="M141" s="14">
+        <f>C141*M62</f>
+        <v>0</v>
+      </c>
+      <c r="N141" s="14"/>
+      <c r="O141" s="14"/>
+      <c r="P141" s="14">
+        <f t="shared" si="7"/>
+        <v>68</v>
+      </c>
+      <c r="Q141" s="14"/>
+    </row>
+    <row r="142" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B141" s="8" t="s">
+      <c r="B142" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C141" s="8">
-        <f t="shared" si="36"/>
+      <c r="C142" s="8">
+        <f>C63*2</f>
         <v>248</v>
       </c>
-      <c r="D141" s="8">
-        <f>C141*D63</f>
+      <c r="D142" s="8">
+        <f>C142*D63</f>
         <v>248</v>
       </c>
-      <c r="E141" s="8">
-        <f>C141*E63</f>
+      <c r="E142" s="8">
+        <f>C142*E63</f>
         <v>248</v>
       </c>
-      <c r="F141" s="8">
-        <f>C141*F63</f>
+      <c r="F142" s="8">
+        <f>C142*F63</f>
         <v>248</v>
       </c>
-      <c r="G141" s="8">
-        <f>C141*G63</f>
+      <c r="G142" s="8">
+        <f>C142*G63</f>
         <v>496</v>
       </c>
-      <c r="H141" s="8">
-        <f>C141*H63</f>
-        <v>0</v>
-      </c>
-      <c r="I141" s="8">
-        <f>C141*I63</f>
-        <v>0</v>
-      </c>
-      <c r="J141" s="8">
-        <f>C141*J63</f>
-        <v>0</v>
-      </c>
-      <c r="K141" s="8">
-        <f>C141*K63</f>
-        <v>0</v>
-      </c>
-      <c r="L141" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M141" s="8">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N141" s="8"/>
-      <c r="O141" s="8"/>
-      <c r="P141" s="8">
-        <f t="shared" si="10"/>
+      <c r="H142" s="8">
+        <f>C142*H63</f>
+        <v>0</v>
+      </c>
+      <c r="I142" s="8">
+        <f>C142*I63</f>
+        <v>0</v>
+      </c>
+      <c r="J142" s="8">
+        <f>C142*J63</f>
+        <v>0</v>
+      </c>
+      <c r="K142" s="8">
+        <f>C142*K63</f>
+        <v>0</v>
+      </c>
+      <c r="L142" s="8">
+        <f>C142*L63</f>
+        <v>0</v>
+      </c>
+      <c r="M142" s="8">
+        <f>C142*M63</f>
+        <v>0</v>
+      </c>
+      <c r="N142" s="8"/>
+      <c r="O142" s="8"/>
+      <c r="P142" s="8">
+        <f t="shared" si="7"/>
         <v>1240</v>
       </c>
-      <c r="Q141" s="8">
-        <f>SUM(P141)</f>
+      <c r="Q142" s="8">
+        <f>SUM(P142)</f>
         <v>1240</v>
       </c>
-      <c r="R141" s="18"/>
-      <c r="S141" s="18"/>
-      <c r="T141" s="18"/>
-      <c r="U141" s="18"/>
-      <c r="V141" s="18"/>
-      <c r="W141" s="18"/>
-      <c r="X141" s="18"/>
-      <c r="Y141" s="18"/>
-      <c r="Z141" s="18"/>
-      <c r="AA141" s="18"/>
-      <c r="AB141" s="18"/>
-      <c r="AC141" s="18"/>
-      <c r="AD141" s="18"/>
-    </row>
-    <row r="142" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="B142" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C142" s="14">
-        <f t="shared" si="36"/>
-        <v>124</v>
-      </c>
-      <c r="D142" s="14">
-        <f>C142*D64</f>
-        <v>0</v>
-      </c>
-      <c r="E142" s="14">
-        <f>C142*E64</f>
-        <v>0</v>
-      </c>
-      <c r="F142" s="14">
-        <f>C142*F64</f>
-        <v>0</v>
-      </c>
-      <c r="G142" s="14">
-        <f>C142*G64</f>
-        <v>124</v>
-      </c>
-      <c r="H142" s="14">
-        <f>C142*H64</f>
-        <v>0</v>
-      </c>
-      <c r="I142" s="14">
-        <f>C142*I64</f>
-        <v>0</v>
-      </c>
-      <c r="J142" s="14">
-        <f>C142*J64</f>
-        <v>124</v>
-      </c>
-      <c r="K142" s="14">
-        <f>C142*K64</f>
-        <v>0</v>
-      </c>
-      <c r="L142" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M142" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N142" s="14"/>
-      <c r="O142" s="14"/>
-      <c r="P142" s="14">
-        <f t="shared" si="10"/>
-        <v>248</v>
-      </c>
-      <c r="Q142" s="14">
-        <f>SUM(P142:P144)</f>
-        <v>482</v>
-      </c>
+      <c r="R142" s="18"/>
+      <c r="S142" s="18"/>
+      <c r="T142" s="18"/>
+      <c r="U142" s="18"/>
+      <c r="V142" s="18"/>
+      <c r="W142" s="18"/>
+      <c r="X142" s="18"/>
+      <c r="Y142" s="18"/>
+      <c r="Z142" s="18"/>
+      <c r="AA142" s="18"/>
+      <c r="AB142" s="18"/>
+      <c r="AC142" s="18"/>
+      <c r="AD142" s="18"/>
     </row>
     <row r="143" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="14" t="s">
         <v>83</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C143" s="14">
-        <f t="shared" si="36"/>
-        <v>118</v>
+        <f>C64*2</f>
+        <v>124</v>
       </c>
       <c r="D143" s="14">
-        <f>C143*D65</f>
-        <v>118</v>
+        <f>C143*D64</f>
+        <v>0</v>
       </c>
       <c r="E143" s="14">
-        <f>C143*E65</f>
+        <f>C143*E64</f>
         <v>0</v>
       </c>
       <c r="F143" s="14">
-        <f>C143*F65</f>
+        <f>C143*F64</f>
         <v>0</v>
       </c>
       <c r="G143" s="14">
-        <f>C143*G65</f>
-        <v>0</v>
+        <f>C143*G64</f>
+        <v>124</v>
       </c>
       <c r="H143" s="14">
-        <f>C143*H65</f>
+        <f>C143*H64</f>
         <v>0</v>
       </c>
       <c r="I143" s="14">
-        <f>C143*I65</f>
+        <f>C143*I64</f>
         <v>0</v>
       </c>
       <c r="J143" s="14">
-        <f>C143*J65</f>
-        <v>0</v>
+        <f>C143*J64</f>
+        <v>124</v>
       </c>
       <c r="K143" s="14">
-        <f>C143*K65</f>
+        <f>C143*K64</f>
         <v>0</v>
       </c>
       <c r="L143" s="14">
-        <f t="shared" si="35"/>
+        <f>C143*L64</f>
         <v>0</v>
       </c>
       <c r="M143" s="14">
-        <f t="shared" si="37"/>
+        <f>C143*M64</f>
         <v>0</v>
       </c>
       <c r="N143" s="14"/>
       <c r="O143" s="14"/>
       <c r="P143" s="14">
-        <f t="shared" si="10"/>
-        <v>118</v>
-      </c>
-      <c r="Q143" s="14"/>
+        <f t="shared" si="7"/>
+        <v>248</v>
+      </c>
+      <c r="Q143" s="14">
+        <f>SUM(P143:P145)</f>
+        <v>482</v>
+      </c>
     </row>
     <row r="144" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="14" t="s">
         <v>83</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C144" s="14">
-        <f t="shared" ref="C144:C175" si="38">C66*2</f>
-        <v>116</v>
+        <f>C65*2</f>
+        <v>118</v>
       </c>
       <c r="D144" s="14">
-        <f>C144*D66</f>
-        <v>0</v>
+        <f>C144*D65</f>
+        <v>118</v>
       </c>
       <c r="E144" s="14">
-        <f>C144*E66</f>
+        <f>C144*E65</f>
         <v>0</v>
       </c>
       <c r="F144" s="14">
-        <f>C144*F66</f>
+        <f>C144*F65</f>
         <v>0</v>
       </c>
       <c r="G144" s="14">
-        <f>C144*G66</f>
+        <f>C144*G65</f>
         <v>0</v>
       </c>
       <c r="H144" s="14">
-        <f>C144*H66</f>
+        <f>C144*H65</f>
         <v>0</v>
       </c>
       <c r="I144" s="14">
-        <f>C144*I66</f>
-        <v>116</v>
+        <f>C144*I65</f>
+        <v>0</v>
       </c>
       <c r="J144" s="14">
-        <f>C144*J66</f>
+        <f>C144*J65</f>
         <v>0</v>
       </c>
       <c r="K144" s="14">
-        <f>C144*K66</f>
+        <f>C144*K65</f>
         <v>0</v>
       </c>
       <c r="L144" s="14">
-        <f t="shared" si="35"/>
+        <f>C144*L65</f>
         <v>0</v>
       </c>
       <c r="M144" s="14">
-        <f t="shared" si="37"/>
+        <f>C144*M65</f>
         <v>0</v>
       </c>
       <c r="N144" s="14"/>
       <c r="O144" s="14"/>
       <c r="P144" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="7"/>
+        <v>118</v>
+      </c>
+      <c r="Q144" s="14"/>
+    </row>
+    <row r="145" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B145" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C145" s="14">
+        <f>C66*2</f>
         <v>116</v>
       </c>
-      <c r="Q144" s="14"/>
-    </row>
-    <row r="145" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="8" t="s">
+      <c r="D145" s="14">
+        <f>C145*D66</f>
+        <v>0</v>
+      </c>
+      <c r="E145" s="14">
+        <f>C145*E66</f>
+        <v>0</v>
+      </c>
+      <c r="F145" s="14">
+        <f>C145*F66</f>
+        <v>0</v>
+      </c>
+      <c r="G145" s="14">
+        <f>C145*G66</f>
+        <v>0</v>
+      </c>
+      <c r="H145" s="14">
+        <f>C145*H66</f>
+        <v>0</v>
+      </c>
+      <c r="I145" s="14">
+        <f>C145*I66</f>
+        <v>116</v>
+      </c>
+      <c r="J145" s="14">
+        <f>C145*J66</f>
+        <v>0</v>
+      </c>
+      <c r="K145" s="14">
+        <f>C145*K66</f>
+        <v>0</v>
+      </c>
+      <c r="L145" s="14">
+        <f>C145*L66</f>
+        <v>0</v>
+      </c>
+      <c r="M145" s="14">
+        <f>C145*M66</f>
+        <v>0</v>
+      </c>
+      <c r="N145" s="14"/>
+      <c r="O145" s="14"/>
+      <c r="P145" s="14">
+        <f t="shared" si="7"/>
+        <v>116</v>
+      </c>
+      <c r="Q145" s="14"/>
+    </row>
+    <row r="146" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B145" s="8" t="s">
+      <c r="B146" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C145" s="8">
-        <f t="shared" si="38"/>
+      <c r="C146" s="8">
+        <f>C67*2</f>
         <v>138</v>
       </c>
-      <c r="D145" s="8">
-        <f>C145*D67</f>
-        <v>0</v>
-      </c>
-      <c r="E145" s="8">
-        <f>C145*E67</f>
-        <v>0</v>
-      </c>
-      <c r="F145" s="8">
-        <f>C145*F67</f>
+      <c r="D146" s="8">
+        <f>C146*D67</f>
+        <v>0</v>
+      </c>
+      <c r="E146" s="8">
+        <f>C146*E67</f>
+        <v>0</v>
+      </c>
+      <c r="F146" s="8">
+        <f>C146*F67</f>
         <v>138</v>
       </c>
-      <c r="G145" s="8">
-        <f>C145*G67</f>
-        <v>0</v>
-      </c>
-      <c r="H145" s="8">
-        <f>C145*H67</f>
-        <v>0</v>
-      </c>
-      <c r="I145" s="8">
-        <f>C145*I67</f>
-        <v>0</v>
-      </c>
-      <c r="J145" s="8">
-        <f>C145*J67</f>
-        <v>0</v>
-      </c>
-      <c r="K145" s="8">
-        <f>C145*K67</f>
-        <v>0</v>
-      </c>
-      <c r="L145" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M145" s="8">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N145" s="8"/>
-      <c r="O145" s="8"/>
-      <c r="P145" s="8">
-        <f t="shared" si="10"/>
+      <c r="G146" s="8">
+        <f>C146*G67</f>
+        <v>0</v>
+      </c>
+      <c r="H146" s="8">
+        <f>C146*H67</f>
+        <v>0</v>
+      </c>
+      <c r="I146" s="8">
+        <f>C146*I67</f>
+        <v>0</v>
+      </c>
+      <c r="J146" s="8">
+        <f>C146*J67</f>
+        <v>0</v>
+      </c>
+      <c r="K146" s="8">
+        <f>C146*K67</f>
+        <v>0</v>
+      </c>
+      <c r="L146" s="8">
+        <f>C146*L67</f>
+        <v>0</v>
+      </c>
+      <c r="M146" s="8">
+        <f>C146*M67</f>
+        <v>0</v>
+      </c>
+      <c r="N146" s="8"/>
+      <c r="O146" s="8"/>
+      <c r="P146" s="8">
+        <f t="shared" si="7"/>
         <v>138</v>
       </c>
-      <c r="Q145" s="8">
-        <f>P145</f>
+      <c r="Q146" s="8">
+        <f>P146</f>
         <v>138</v>
       </c>
-      <c r="R145" s="18"/>
-      <c r="S145" s="18"/>
-      <c r="T145" s="18"/>
-      <c r="U145" s="18"/>
-      <c r="V145" s="18"/>
-      <c r="W145" s="18"/>
-      <c r="X145" s="18"/>
-      <c r="Y145" s="18"/>
-      <c r="Z145" s="18"/>
-      <c r="AA145" s="18"/>
-      <c r="AB145" s="18"/>
-      <c r="AC145" s="18"/>
-      <c r="AD145" s="18"/>
-    </row>
-    <row r="149" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A149" s="7" t="s">
+      <c r="R146" s="18"/>
+      <c r="S146" s="18"/>
+      <c r="T146" s="18"/>
+      <c r="U146" s="18"/>
+      <c r="V146" s="18"/>
+      <c r="W146" s="18"/>
+      <c r="X146" s="18"/>
+      <c r="Y146" s="18"/>
+      <c r="Z146" s="18"/>
+      <c r="AA146" s="18"/>
+      <c r="AB146" s="18"/>
+      <c r="AC146" s="18"/>
+      <c r="AD146" s="18"/>
+    </row>
+    <row r="147" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A147" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C147" s="14">
+        <f>C68*2</f>
+        <v>376</v>
+      </c>
+      <c r="D147" s="14">
+        <f>C147*D68</f>
+        <v>0</v>
+      </c>
+      <c r="E147" s="14">
+        <f>C147*E68</f>
+        <v>0</v>
+      </c>
+      <c r="F147" s="14">
+        <f>C147*F68</f>
+        <v>0</v>
+      </c>
+      <c r="G147" s="14">
+        <f>C147*G68</f>
+        <v>0</v>
+      </c>
+      <c r="H147" s="14">
+        <f>C147*H68</f>
+        <v>0</v>
+      </c>
+      <c r="I147" s="14">
+        <f>C147*I68</f>
+        <v>0</v>
+      </c>
+      <c r="J147" s="14">
+        <f>C147*J68</f>
+        <v>0</v>
+      </c>
+      <c r="K147" s="14">
+        <f>C147*K68</f>
+        <v>0</v>
+      </c>
+      <c r="L147" s="14">
+        <f>C147*L68</f>
+        <v>0</v>
+      </c>
+      <c r="M147" s="14">
+        <f>C147*M68</f>
+        <v>0</v>
+      </c>
+      <c r="N147" s="6"/>
+      <c r="O147" s="6"/>
+      <c r="P147" s="14">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q147" s="14">
+        <f>P147</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A150" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B149" s="7"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7" t="s">
+      <c r="B150" s="7"/>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E149" s="7" t="s">
+      <c r="E150" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F149" s="7" t="s">
+      <c r="F150" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G149" s="7" t="s">
+      <c r="G150" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="H150" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="I150" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J149" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K149" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L149" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="M149" s="9" t="s">
+      <c r="M150" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="N149" s="9" t="s">
+      <c r="N150" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O149" s="9" t="s">
+      <c r="O150" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="P149" s="7"/>
-      <c r="Q149" s="9"/>
-    </row>
-    <row r="150" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A150" s="8"/>
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="8">
-        <f t="shared" ref="D150:M150" si="39">SUM(D80:D145)</f>
+      <c r="P150" s="7"/>
+      <c r="Q150" s="9"/>
+    </row>
+    <row r="151" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A151" s="8"/>
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="8">
+        <f>SUM(D81:D147)</f>
         <v>750</v>
       </c>
-      <c r="E150" s="8">
-        <f t="shared" si="39"/>
+      <c r="E151" s="8">
+        <f t="shared" ref="E151:M151" si="13">SUM(E81:E147)</f>
         <v>892</v>
       </c>
-      <c r="F150" s="8">
-        <f t="shared" si="39"/>
+      <c r="F151" s="8">
+        <f t="shared" si="13"/>
         <v>1166</v>
       </c>
-      <c r="G150" s="8">
-        <f t="shared" si="39"/>
+      <c r="G151" s="8">
+        <f t="shared" si="13"/>
         <v>1830</v>
       </c>
-      <c r="H150" s="8">
-        <f t="shared" si="39"/>
+      <c r="H151" s="8">
+        <f t="shared" si="13"/>
         <v>802</v>
       </c>
-      <c r="I150" s="8">
-        <f t="shared" si="39"/>
+      <c r="I151" s="8">
+        <f t="shared" si="13"/>
         <v>3046</v>
       </c>
-      <c r="J150" s="8">
-        <f t="shared" si="39"/>
+      <c r="J151" s="8">
+        <f t="shared" si="13"/>
         <v>2704</v>
       </c>
-      <c r="K150" s="8">
-        <f t="shared" si="39"/>
+      <c r="K151" s="8">
+        <f t="shared" si="13"/>
         <v>4664</v>
       </c>
-      <c r="L150" s="8">
-        <f t="shared" si="39"/>
+      <c r="L151" s="8">
+        <f t="shared" si="13"/>
         <v>2654</v>
       </c>
-      <c r="M150" s="8">
-        <f t="shared" si="39"/>
+      <c r="M151" s="8">
+        <f t="shared" si="13"/>
         <v>6950</v>
       </c>
-      <c r="N150" s="8">
-        <f>SUM(D150:M150)</f>
+      <c r="N151" s="8">
+        <f>SUM(D151:M151)</f>
         <v>25458</v>
       </c>
-      <c r="O150" s="15">
-        <f>N150/N69</f>
+      <c r="O151" s="15">
+        <f>N151/N70</f>
         <v>153.36144578313252</v>
       </c>
-      <c r="P150" s="8">
-        <f>SUM(P80:P145)</f>
+      <c r="P151" s="8">
+        <f>SUM(P81:P147)</f>
         <v>25458</v>
       </c>
-      <c r="Q150" s="8">
-        <f>SUM(Q80:Q145)</f>
+      <c r="Q151" s="8">
+        <f>SUM(Q81:Q147)</f>
         <v>25458</v>
       </c>
     </row>
-    <row r="151" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="16">
-        <f t="shared" ref="D151:N151" si="40">D150/D69</f>
+    <row r="152" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A152" s="6"/>
+      <c r="B152" s="6"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="16">
+        <f t="shared" ref="D152:N152" si="14">D151/D70</f>
         <v>150</v>
       </c>
-      <c r="E151" s="16">
-        <f t="shared" si="40"/>
+      <c r="E152" s="16">
+        <f t="shared" si="14"/>
         <v>89.2</v>
       </c>
-      <c r="F151" s="16">
-        <f t="shared" si="40"/>
+      <c r="F152" s="16">
+        <f t="shared" si="14"/>
         <v>116.6</v>
       </c>
-      <c r="G151" s="16">
-        <f t="shared" si="40"/>
+      <c r="G152" s="16">
+        <f t="shared" si="14"/>
         <v>114.375</v>
       </c>
-      <c r="H151" s="16">
-        <f t="shared" si="40"/>
+      <c r="H152" s="16">
+        <f t="shared" si="14"/>
         <v>160.4</v>
       </c>
-      <c r="I151" s="16">
-        <f t="shared" si="40"/>
+      <c r="I152" s="16">
+        <f t="shared" si="14"/>
         <v>138.45454545454547</v>
       </c>
-      <c r="J151" s="16">
-        <f t="shared" si="40"/>
+      <c r="J152" s="16">
+        <f t="shared" si="14"/>
         <v>142.31578947368422</v>
       </c>
-      <c r="K151" s="16">
-        <f t="shared" si="40"/>
+      <c r="K152" s="16">
+        <f t="shared" si="14"/>
         <v>172.74074074074073</v>
       </c>
-      <c r="L151" s="16">
-        <f t="shared" si="40"/>
+      <c r="L152" s="16">
+        <f t="shared" si="14"/>
         <v>165.875</v>
       </c>
-      <c r="M151" s="16">
-        <f t="shared" si="40"/>
+      <c r="M152" s="16">
+        <f t="shared" si="14"/>
         <v>193.05555555555554</v>
       </c>
-      <c r="N151" s="16">
-        <f t="shared" si="40"/>
+      <c r="N152" s="16">
+        <f t="shared" si="14"/>
         <v>153.36144578313252</v>
       </c>
-      <c r="O151" s="6" t="s">
+      <c r="O152" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="P151" s="6"/>
-      <c r="Q151" s="6"/>
-    </row>
-    <row r="154" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A154" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B154" s="7" t="s">
+      <c r="P152" s="6"/>
+      <c r="Q152" s="6"/>
+    </row>
+    <row r="155" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A155" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B155" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C154" s="7" t="s">
+      <c r="C155" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D154" s="7" t="s">
+      <c r="D155" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A155" s="8" t="s">
+    <row r="156" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A156" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B155" s="8">
+      <c r="B156" s="8">
         <f>Q2</f>
         <v>3</v>
       </c>
-      <c r="C155" s="8">
+      <c r="C156" s="8">
         <f>SUM(N2:N4)</f>
         <v>11</v>
       </c>
-      <c r="D155" s="8">
-        <f>Q80</f>
+      <c r="D156" s="8">
+        <f>Q81</f>
         <v>148</v>
       </c>
     </row>
-    <row r="156" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A156" s="14" t="s">
+    <row r="157" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A157" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B156" s="14">
+      <c r="B157" s="14">
         <f>Q5</f>
         <v>1</v>
       </c>
-      <c r="C156" s="14">
+      <c r="C157" s="14">
         <f>N5</f>
         <v>2</v>
       </c>
-      <c r="D156" s="14">
-        <f>Q83</f>
+      <c r="D157" s="14">
+        <f>Q84</f>
         <v>1128</v>
       </c>
     </row>
-    <row r="157" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A157" s="8" t="s">
+    <row r="158" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A158" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B157" s="8">
+      <c r="B158" s="8">
         <f>Q6</f>
         <v>1</v>
       </c>
-      <c r="C157" s="8">
+      <c r="C158" s="8">
         <f>Q6</f>
         <v>1</v>
       </c>
-      <c r="D157" s="8">
-        <f>Q84</f>
+      <c r="D158" s="8">
+        <f>Q85</f>
         <v>148</v>
       </c>
     </row>
-    <row r="158" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A158" s="14" t="s">
+    <row r="159" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A159" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B158" s="14">
+      <c r="B159" s="14">
         <f>Q7</f>
         <v>4</v>
       </c>
-      <c r="C158" s="14">
+      <c r="C159" s="14">
         <f>SUM(N7:N10)</f>
         <v>7</v>
       </c>
-      <c r="D158" s="14">
-        <f>Q85</f>
+      <c r="D159" s="14">
+        <f>Q86</f>
         <v>1962</v>
       </c>
     </row>
-    <row r="159" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A159" s="8" t="s">
+    <row r="160" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A160" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B159" s="8">
+      <c r="B160" s="8">
         <f>Q11</f>
         <v>5</v>
       </c>
-      <c r="C159" s="8">
+      <c r="C160" s="8">
         <f>SUM(N11:N15)</f>
         <v>15</v>
       </c>
-      <c r="D159" s="8">
-        <f>Q89</f>
+      <c r="D160" s="8">
+        <f>Q90</f>
         <v>1288</v>
       </c>
     </row>
-    <row r="160" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A160" s="14" t="s">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B160" s="14">
+      <c r="B161" s="14">
         <f>Q16</f>
         <v>1</v>
       </c>
-      <c r="C160" s="14">
+      <c r="C161" s="14">
         <f>N16</f>
         <v>1</v>
       </c>
-      <c r="D160" s="14">
-        <f>Q94</f>
+      <c r="D161" s="14">
+        <f>Q95</f>
         <v>364</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="8" t="s">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B161" s="8">
+      <c r="B162" s="8">
         <f>Q17</f>
         <v>2</v>
       </c>
-      <c r="C161" s="8">
+      <c r="C162" s="8">
         <f>SUM(N17:N18)</f>
         <v>3</v>
       </c>
-      <c r="D161" s="8">
-        <f>Q95</f>
+      <c r="D162" s="8">
+        <f>Q96</f>
         <v>1202</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="14" t="s">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B162" s="14">
+      <c r="B163" s="14">
         <f>Q19</f>
         <v>1</v>
       </c>
-      <c r="C162" s="14">
+      <c r="C163" s="14">
         <f>N19</f>
         <v>1</v>
       </c>
-      <c r="D162" s="14">
-        <f>Q97</f>
+      <c r="D163" s="14">
+        <f>Q98</f>
         <v>236</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="8" t="s">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B163" s="8">
+      <c r="B164" s="8">
         <f>Q20</f>
         <v>5</v>
       </c>
-      <c r="C163" s="8">
+      <c r="C164" s="8">
         <f>SUM(N20:N24)</f>
         <v>9</v>
       </c>
-      <c r="D163" s="8">
-        <f>Q98</f>
+      <c r="D164" s="8">
+        <f>Q99</f>
         <v>906</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="14" t="s">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="B164" s="14">
+      <c r="B165" s="14">
         <f>Q25</f>
         <v>1</v>
       </c>
-      <c r="C164" s="14">
+      <c r="C165" s="14">
         <f>N25</f>
         <v>1</v>
       </c>
-      <c r="D164" s="14">
-        <f t="shared" ref="D164:D170" si="41">Q103</f>
+      <c r="D165" s="14">
+        <f t="shared" ref="D165:D171" si="15">Q104</f>
         <v>800</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="8" t="s">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B165" s="8">
+      <c r="B166" s="8">
         <f>Q26</f>
         <v>1</v>
       </c>
-      <c r="C165" s="8">
+      <c r="C166" s="8">
         <f>N26</f>
         <v>1</v>
       </c>
-      <c r="D165" s="8">
-        <f t="shared" si="41"/>
+      <c r="D166" s="8">
+        <f t="shared" si="15"/>
         <v>726</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="14" t="s">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B166" s="14">
+      <c r="B167" s="14">
         <f>Q27</f>
         <v>1</v>
       </c>
-      <c r="C166" s="14">
+      <c r="C167" s="14">
         <f>N27</f>
         <v>1</v>
       </c>
-      <c r="D166" s="14">
-        <f t="shared" si="41"/>
+      <c r="D167" s="14">
+        <f t="shared" si="15"/>
         <v>186</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="8" t="s">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B167" s="8">
+      <c r="B168" s="8">
         <f>N28</f>
         <v>1</v>
       </c>
-      <c r="C167" s="8">
+      <c r="C168" s="8">
         <f>Q28</f>
         <v>1</v>
       </c>
-      <c r="D167" s="8">
-        <f t="shared" si="41"/>
+      <c r="D168" s="8">
+        <f t="shared" si="15"/>
         <v>348</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="14" t="s">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B168" s="14">
+      <c r="B169" s="14">
         <f>Q29</f>
         <v>1</v>
       </c>
-      <c r="C168" s="14">
+      <c r="C169" s="14">
         <f>N29</f>
         <v>1</v>
       </c>
-      <c r="D168" s="14">
-        <f t="shared" si="41"/>
+      <c r="D169" s="14">
+        <f t="shared" si="15"/>
         <v>418</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="8" t="s">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B169" s="8">
+      <c r="B170" s="8">
         <f>N30</f>
         <v>1</v>
       </c>
-      <c r="C169" s="8">
+      <c r="C170" s="8">
         <f>Q30</f>
         <v>1</v>
       </c>
-      <c r="D169" s="8">
-        <f t="shared" si="41"/>
+      <c r="D170" s="8">
+        <f t="shared" si="15"/>
         <v>516</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="14" t="s">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B170" s="14">
+      <c r="B171" s="14">
         <f>Q31</f>
         <v>6</v>
       </c>
-      <c r="C170" s="14">
+      <c r="C171" s="14">
         <f>SUM(N31:N36)</f>
         <v>30</v>
       </c>
-      <c r="D170" s="14">
-        <f t="shared" si="41"/>
+      <c r="D171" s="14">
+        <f t="shared" si="15"/>
         <v>1660</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="8" t="s">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B171" s="8">
+      <c r="B172" s="8">
         <f>Q37</f>
         <v>3</v>
       </c>
-      <c r="C171" s="8">
+      <c r="C172" s="8">
         <f>SUM(N37:N39)</f>
         <v>8</v>
       </c>
-      <c r="D171" s="8">
-        <f>Q115</f>
+      <c r="D172" s="8">
+        <f>Q116</f>
         <v>1150</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="14" t="s">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B172" s="14">
+      <c r="B173" s="14">
         <f>Q40</f>
         <v>1</v>
       </c>
-      <c r="C172" s="14">
+      <c r="C173" s="14">
         <f>N40</f>
         <v>1</v>
       </c>
-      <c r="D172" s="14">
-        <f>Q118</f>
+      <c r="D173" s="14">
+        <f>Q119</f>
         <v>840</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="8" t="s">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B173" s="8">
+      <c r="B174" s="8">
         <f>Q41</f>
         <v>1</v>
       </c>
-      <c r="C173" s="8">
+      <c r="C174" s="8">
         <f>N41</f>
         <v>1</v>
       </c>
-      <c r="D173" s="8">
-        <f>Q119</f>
+      <c r="D174" s="8">
+        <f>Q120</f>
         <v>282</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="14" t="s">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B174" s="14">
+      <c r="B175" s="14">
         <f>Q42</f>
         <v>1</v>
       </c>
-      <c r="C174" s="14">
+      <c r="C175" s="14">
         <f>N42</f>
         <v>9</v>
       </c>
-      <c r="D174" s="14">
-        <f>Q120</f>
+      <c r="D175" s="14">
+        <f>Q121</f>
         <v>1440</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="8" t="s">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B175" s="8">
+      <c r="B176" s="8">
         <f>Q43</f>
         <v>1</v>
       </c>
-      <c r="C175" s="8">
+      <c r="C176" s="8">
         <f>M43</f>
         <v>2</v>
       </c>
-      <c r="D175" s="8">
-        <f>Q121</f>
+      <c r="D176" s="8">
+        <f>Q122</f>
         <v>2088</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="14" t="s">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B176" s="14">
+      <c r="B177" s="14">
         <f>Q44</f>
         <v>2</v>
       </c>
-      <c r="C176" s="14">
+      <c r="C177" s="14">
         <f>SUM(N44:N45)</f>
         <v>7</v>
       </c>
-      <c r="D176" s="14">
-        <f>Q122</f>
+      <c r="D177" s="14">
+        <f>Q123</f>
         <v>498</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="8" t="s">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B177" s="8">
+      <c r="B178" s="8">
         <f>Q46</f>
         <v>3</v>
       </c>
-      <c r="C177" s="8">
+      <c r="C178" s="8">
         <f>SUM(N46:N48)</f>
         <v>4</v>
       </c>
-      <c r="D177" s="8">
-        <f>Q124</f>
+      <c r="D178" s="8">
+        <f>Q125</f>
         <v>1050</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="14" t="s">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B178" s="14">
+      <c r="B179" s="14">
         <f>Q49</f>
         <v>1</v>
       </c>
-      <c r="C178" s="14">
+      <c r="C179" s="14">
         <f>N49</f>
         <v>3</v>
       </c>
-      <c r="D178" s="14">
-        <f>Q127</f>
+      <c r="D179" s="14">
+        <f>Q128</f>
         <v>816</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="8" t="s">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B179" s="8">
+      <c r="B180" s="8">
         <f>Q50</f>
         <v>4</v>
       </c>
-      <c r="C179" s="8">
+      <c r="C180" s="8">
         <f>SUM(N50:N53)</f>
         <v>5</v>
       </c>
-      <c r="D179" s="8">
-        <f>Q128</f>
+      <c r="D180" s="8">
+        <f>Q129</f>
         <v>1396</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="14" t="s">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B180" s="14">
+      <c r="B181" s="14">
         <f>Q54</f>
         <v>3</v>
       </c>
-      <c r="C180" s="14">
+      <c r="C181" s="14">
         <f>SUM(N54:N56)</f>
         <v>8</v>
       </c>
-      <c r="D180" s="14">
-        <f>Q132</f>
+      <c r="D181" s="14">
+        <f>Q133</f>
         <v>1004</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="8" t="s">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B181" s="8">
+      <c r="B182" s="8">
         <f>Q57</f>
         <v>3</v>
       </c>
-      <c r="C181" s="8">
+      <c r="C182" s="8">
         <f>SUM(N57:N59)</f>
         <v>3</v>
       </c>
-      <c r="D181" s="8">
-        <f>Q135</f>
+      <c r="D182" s="8">
+        <f>Q136</f>
         <v>286</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="14" t="s">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B182" s="14">
+      <c r="B183" s="14">
         <f>Q60</f>
         <v>3</v>
       </c>
-      <c r="C182" s="14">
+      <c r="C183" s="14">
         <f>SUM(N60:N62)</f>
         <v>19</v>
       </c>
-      <c r="D182" s="14">
-        <f>Q138</f>
+      <c r="D183" s="14">
+        <f>Q139</f>
         <v>712</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="8" t="s">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B183" s="8">
+      <c r="B184" s="8">
         <f>Q63</f>
         <v>1</v>
       </c>
-      <c r="C183" s="8">
+      <c r="C184" s="8">
         <f>N63</f>
         <v>5</v>
       </c>
-      <c r="D183" s="8">
-        <f>Q141</f>
+      <c r="D184" s="8">
+        <f>Q142</f>
         <v>1240</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="14" t="s">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B184" s="14">
+      <c r="B185" s="14">
         <f>Q64</f>
         <v>3</v>
       </c>
-      <c r="C184" s="14">
+      <c r="C185" s="14">
         <f>SUM(N64:N66)</f>
         <v>4</v>
       </c>
-      <c r="D184" s="14">
-        <f>Q142</f>
+      <c r="D185" s="14">
+        <f>Q143</f>
         <v>482</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="8" t="s">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B185" s="8">
+      <c r="B186" s="8">
         <f>Q67</f>
         <v>1</v>
       </c>
-      <c r="C185" s="8">
+      <c r="C186" s="8">
         <f>N67</f>
         <v>1</v>
       </c>
-      <c r="D185" s="8">
+      <c r="D186" s="8">
+        <f>Q146</f>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B187" s="23">
+        <f>Q68</f>
+        <v>0</v>
+      </c>
+      <c r="C187" s="23">
+        <f>N68</f>
+        <v>0</v>
+      </c>
+      <c r="D187" s="14">
         <f>Q145</f>
-        <v>138</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="8"/>
-      <c r="B186" s="8"/>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="22"/>
-      <c r="B187" s="22">
-        <f>SUM(B155:B185)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="22"/>
+      <c r="B188" s="22">
+        <f>SUM(B156:B187)</f>
         <v>66</v>
       </c>
-      <c r="C187" s="22">
-        <f>SUM(C155:C185)</f>
+      <c r="C188" s="22">
+        <f>SUM(C156:C187)</f>
         <v>166</v>
       </c>
-      <c r="D187" s="22">
-        <f>SUM(D155:D185)</f>
+      <c r="D188" s="22">
+        <f>SUM(D156:D187)</f>
         <v>25458</v>
       </c>
     </row>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4E23CC-D3F6-4D5E-833F-F09221F23C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0107D012-01DE-45FB-A913-DD1CC68515F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="20952" windowHeight="12816" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
+    <workbookView xWindow="1920" yWindow="864" windowWidth="20952" windowHeight="12816" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
   <sheets>
     <sheet name="pelipaikat" sheetId="1" r:id="rId1"/>
@@ -577,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -601,7 +601,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3871,21 +3870,23 @@
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
-      <c r="M68" s="6"/>
+      <c r="M68" s="6">
+        <v>1</v>
+      </c>
       <c r="N68" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="P68" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="Q68" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.3">
@@ -3904,15 +3905,15 @@
       <c r="M69" s="6"/>
       <c r="N69" s="6">
         <f>SUM(N2:N68)</f>
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O69" s="6">
         <f>SUM(O2:O68)</f>
-        <v>12729</v>
+        <v>12917</v>
       </c>
       <c r="P69" s="6">
         <f>SUM(P2:P68)</f>
-        <v>25458</v>
+        <v>25834</v>
       </c>
       <c r="Q69" s="6"/>
     </row>
@@ -3969,11 +3970,11 @@
       <c r="O70" s="12"/>
       <c r="P70" s="7">
         <f>SUM(P2:P68)</f>
-        <v>25458</v>
+        <v>25834</v>
       </c>
       <c r="Q70" s="13">
         <f>SUM(Q2:Q68)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.3">
@@ -4200,11 +4201,11 @@
         <v>14</v>
       </c>
       <c r="C81" s="8">
-        <f>C2*2</f>
+        <f t="shared" ref="C81:C112" si="7">C2*2</f>
         <v>16</v>
       </c>
       <c r="D81" s="8">
-        <f>C81*D2</f>
+        <f t="shared" ref="D81:D88" si="8">C81*D2</f>
         <v>0</v>
       </c>
       <c r="E81" s="8">
@@ -4240,7 +4241,7 @@
         <v>16</v>
       </c>
       <c r="M81" s="8">
-        <f>C81*M2</f>
+        <f t="shared" ref="M81:M94" si="9">C81*M2</f>
         <v>32</v>
       </c>
       <c r="N81" s="8"/>
@@ -4262,11 +4263,11 @@
         <v>15</v>
       </c>
       <c r="C82" s="8">
-        <f>C3*2</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="D82" s="8">
-        <f>C82*D3</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E82" s="8">
@@ -4302,13 +4303,13 @@
         <v>0</v>
       </c>
       <c r="M82" s="8">
-        <f>C82*M3</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N82" s="8"/>
       <c r="O82" s="8"/>
       <c r="P82" s="8">
-        <f t="shared" ref="P82:P147" si="7">SUM(D82:M82)</f>
+        <f t="shared" ref="P82:P147" si="10">SUM(D82:M82)</f>
         <v>4</v>
       </c>
       <c r="Q82" s="8"/>
@@ -4321,11 +4322,11 @@
         <v>16</v>
       </c>
       <c r="C83" s="8">
-        <f>C4*2</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="D83" s="8">
-        <f>C83*D4</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="E83" s="8">
@@ -4361,13 +4362,13 @@
         <v>0</v>
       </c>
       <c r="M83" s="8">
-        <f>C83*M4</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N83" s="8"/>
       <c r="O83" s="8"/>
       <c r="P83" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="Q83" s="8"/>
@@ -4380,11 +4381,11 @@
         <v>18</v>
       </c>
       <c r="C84" s="6">
-        <f>C5*2</f>
+        <f t="shared" si="7"/>
         <v>564</v>
       </c>
       <c r="D84" s="6">
-        <f>C84*D5</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E84" s="6">
@@ -4420,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="M84" s="14">
-        <f>C84*M5</f>
+        <f t="shared" si="9"/>
         <v>564</v>
       </c>
       <c r="N84" s="6"/>
       <c r="O84" s="14"/>
       <c r="P84" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1128</v>
       </c>
       <c r="Q84" s="6">
@@ -4442,47 +4443,47 @@
         <v>130</v>
       </c>
       <c r="C85" s="8">
-        <f>C6*2</f>
+        <f t="shared" si="7"/>
         <v>148</v>
       </c>
       <c r="D85" s="8">
-        <f>C85*D6</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E85" s="8">
-        <f t="shared" ref="E85:L85" si="8">D85*E6</f>
+        <f t="shared" ref="E85:L85" si="11">D85*E6</f>
         <v>0</v>
       </c>
       <c r="F85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L85" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M85" s="8">
-        <f>C85*M6</f>
+        <f t="shared" si="9"/>
         <v>148</v>
       </c>
       <c r="N85" s="8"/>
@@ -4504,11 +4505,11 @@
         <v>20</v>
       </c>
       <c r="C86" s="14">
-        <f>C7*2</f>
+        <f t="shared" si="7"/>
         <v>278</v>
       </c>
       <c r="D86" s="14">
-        <f>C86*D7</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E86" s="14">
@@ -4540,17 +4541,17 @@
         <v>278</v>
       </c>
       <c r="L86" s="14">
-        <f>C86*L7</f>
+        <f t="shared" ref="L86:L94" si="12">C86*L7</f>
         <v>0</v>
       </c>
       <c r="M86" s="14">
-        <f>C86*M7</f>
+        <f t="shared" si="9"/>
         <v>834</v>
       </c>
       <c r="N86" s="14"/>
       <c r="O86" s="14"/>
       <c r="P86" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1112</v>
       </c>
       <c r="Q86" s="14">
@@ -4566,11 +4567,11 @@
         <v>21</v>
       </c>
       <c r="C87" s="14">
-        <f>C8*2</f>
+        <f t="shared" si="7"/>
         <v>282</v>
       </c>
       <c r="D87" s="14">
-        <f>C87*D8</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E87" s="14">
@@ -4602,17 +4603,17 @@
         <v>0</v>
       </c>
       <c r="L87" s="14">
-        <f>C87*L8</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M87" s="14">
-        <f>C87*M8</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N87" s="14"/>
       <c r="O87" s="14"/>
       <c r="P87" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>282</v>
       </c>
       <c r="Q87" s="14"/>
@@ -4625,11 +4626,11 @@
         <v>135</v>
       </c>
       <c r="C88" s="14">
-        <f>C9*2</f>
+        <f t="shared" si="7"/>
         <v>276</v>
       </c>
       <c r="D88" s="14">
-        <f>C88*D9</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E88" s="14">
@@ -4661,17 +4662,17 @@
         <v>0</v>
       </c>
       <c r="L88" s="14">
-        <f>C88*L9</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M88" s="14">
-        <f>C88*M9</f>
+        <f t="shared" si="9"/>
         <v>276</v>
       </c>
       <c r="N88" s="14"/>
       <c r="O88" s="14"/>
       <c r="P88" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>276</v>
       </c>
       <c r="Q88" s="14"/>
@@ -4684,7 +4685,7 @@
         <v>133</v>
       </c>
       <c r="C89" s="14">
-        <f>C10*2</f>
+        <f t="shared" si="7"/>
         <v>292</v>
       </c>
       <c r="D89" s="14">
@@ -4712,17 +4713,17 @@
         <v>0</v>
       </c>
       <c r="L89" s="14">
-        <f>C89*L10</f>
+        <f t="shared" si="12"/>
         <v>292</v>
       </c>
       <c r="M89" s="14">
-        <f>C89*M10</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N89" s="14"/>
       <c r="O89" s="14"/>
       <c r="P89" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>292</v>
       </c>
       <c r="Q89" s="14"/>
@@ -4735,7 +4736,7 @@
         <v>23</v>
       </c>
       <c r="C90" s="8">
-        <f>C11*2</f>
+        <f t="shared" si="7"/>
         <v>66</v>
       </c>
       <c r="D90" s="8">
@@ -4771,17 +4772,17 @@
         <v>66</v>
       </c>
       <c r="L90" s="8">
-        <f>C90*L11</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M90" s="8">
-        <f>C90*M11</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N90" s="8"/>
       <c r="O90" s="8"/>
       <c r="P90" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>66</v>
       </c>
       <c r="Q90" s="8">
@@ -4797,7 +4798,7 @@
         <v>24</v>
       </c>
       <c r="C91" s="8">
-        <f>C12*2</f>
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
       <c r="D91" s="8">
@@ -4833,17 +4834,17 @@
         <v>0</v>
       </c>
       <c r="L91" s="8">
-        <f>C91*L12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M91" s="8">
-        <f>C91*M12</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N91" s="8"/>
       <c r="O91" s="8"/>
       <c r="P91" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>92</v>
       </c>
       <c r="Q91" s="8"/>
@@ -4856,7 +4857,7 @@
         <v>25</v>
       </c>
       <c r="C92" s="8">
-        <f>C13*2</f>
+        <f t="shared" si="7"/>
         <v>84</v>
       </c>
       <c r="D92" s="8">
@@ -4892,17 +4893,17 @@
         <v>84</v>
       </c>
       <c r="L92" s="8">
-        <f>C92*L13</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M92" s="8">
-        <f>C92*M13</f>
+        <f t="shared" si="9"/>
         <v>840</v>
       </c>
       <c r="N92" s="8"/>
       <c r="O92" s="8"/>
       <c r="P92" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>924</v>
       </c>
       <c r="Q92" s="8"/>
@@ -4915,7 +4916,7 @@
         <v>26</v>
       </c>
       <c r="C93" s="8">
-        <f>C14*2</f>
+        <f t="shared" si="7"/>
         <v>120</v>
       </c>
       <c r="D93" s="8">
@@ -4951,17 +4952,17 @@
         <v>0</v>
       </c>
       <c r="L93" s="8">
-        <f>C93*L14</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M93" s="8">
-        <f>C93*M14</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N93" s="8"/>
       <c r="O93" s="8"/>
       <c r="P93" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>120</v>
       </c>
       <c r="Q93" s="8"/>
@@ -4974,7 +4975,7 @@
         <v>27</v>
       </c>
       <c r="C94" s="8">
-        <f>C15*2</f>
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
       <c r="D94" s="8">
@@ -5010,17 +5011,17 @@
         <v>0</v>
       </c>
       <c r="L94" s="8">
-        <f>C94*L15</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M94" s="8">
-        <f>C94*M15</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="N94" s="8"/>
       <c r="O94" s="8"/>
       <c r="P94" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>86</v>
       </c>
       <c r="Q94" s="8"/>
@@ -5033,7 +5034,7 @@
         <v>126</v>
       </c>
       <c r="C95" s="14">
-        <f>C16*2</f>
+        <f t="shared" si="7"/>
         <v>364</v>
       </c>
       <c r="D95" s="14">
@@ -5070,7 +5071,7 @@
       <c r="N95" s="14"/>
       <c r="O95" s="14"/>
       <c r="P95" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>364</v>
       </c>
       <c r="Q95" s="14">
@@ -5086,11 +5087,11 @@
         <v>29</v>
       </c>
       <c r="C96" s="8">
-        <f>C17*2</f>
+        <f t="shared" si="7"/>
         <v>370</v>
       </c>
       <c r="D96" s="8">
-        <f>C96*D17</f>
+        <f t="shared" ref="D96:D106" si="13">C96*D17</f>
         <v>0</v>
       </c>
       <c r="E96" s="8">
@@ -5126,13 +5127,13 @@
         <v>0</v>
       </c>
       <c r="M96" s="8">
-        <f>C96*M17</f>
+        <f t="shared" ref="M96:M127" si="14">C96*M17</f>
         <v>370</v>
       </c>
       <c r="N96" s="8"/>
       <c r="O96" s="8"/>
       <c r="P96" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>370</v>
       </c>
       <c r="Q96" s="8">
@@ -5148,11 +5149,11 @@
         <v>29</v>
       </c>
       <c r="C97" s="8">
-        <f>C18*2</f>
+        <f t="shared" si="7"/>
         <v>416</v>
       </c>
       <c r="D97" s="8">
-        <f>C97*D18</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E97" s="8">
@@ -5188,13 +5189,13 @@
         <v>416</v>
       </c>
       <c r="M97" s="8">
-        <f>C97*M18</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N97" s="8"/>
       <c r="O97" s="8"/>
       <c r="P97" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>832</v>
       </c>
       <c r="Q97" s="8"/>
@@ -5207,53 +5208,53 @@
         <v>132</v>
       </c>
       <c r="C98" s="14">
-        <f>C19*2</f>
+        <f t="shared" si="7"/>
         <v>236</v>
       </c>
       <c r="D98" s="14">
-        <f>C98*D19</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E98" s="14">
-        <f t="shared" ref="E98:L98" si="9">D98*E19</f>
+        <f t="shared" ref="E98:L98" si="15">D98*E19</f>
         <v>0</v>
       </c>
       <c r="F98" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G98" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="I98" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J98" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="K98" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="L98" s="14">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="M98" s="14">
-        <f>C98*M19</f>
+        <f t="shared" si="14"/>
         <v>236</v>
       </c>
       <c r="N98" s="14"/>
       <c r="O98" s="14"/>
       <c r="P98" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>236</v>
       </c>
       <c r="Q98" s="14">
@@ -5269,53 +5270,53 @@
         <v>31</v>
       </c>
       <c r="C99" s="8">
-        <f>C20*2</f>
+        <f t="shared" si="7"/>
         <v>110</v>
       </c>
       <c r="D99" s="8">
-        <f>C99*D20</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E99" s="8">
-        <f>C99*E20</f>
+        <f t="shared" ref="E99:E106" si="16">C99*E20</f>
         <v>110</v>
       </c>
       <c r="F99" s="8">
-        <f>C99*F20</f>
+        <f t="shared" ref="F99:F106" si="17">C99*F20</f>
         <v>110</v>
       </c>
       <c r="G99" s="8">
-        <f>C99*G20</f>
+        <f t="shared" ref="G99:G106" si="18">C99*G20</f>
         <v>0</v>
       </c>
       <c r="H99" s="8">
-        <f>C99*H20</f>
+        <f t="shared" ref="H99:H106" si="19">C99*H20</f>
         <v>0</v>
       </c>
       <c r="I99" s="8">
-        <f>C99*I20</f>
+        <f t="shared" ref="I99:I106" si="20">C99*I20</f>
         <v>0</v>
       </c>
       <c r="J99" s="8">
-        <f>C99*J20</f>
+        <f t="shared" ref="J99:J106" si="21">C99*J20</f>
         <v>0</v>
       </c>
       <c r="K99" s="8">
-        <f>C99*K20</f>
+        <f t="shared" ref="K99:K106" si="22">C99*K20</f>
         <v>0</v>
       </c>
       <c r="L99" s="8">
-        <f>C99*L20</f>
+        <f t="shared" ref="L99:L106" si="23">C99*L20</f>
         <v>0</v>
       </c>
       <c r="M99" s="8">
-        <f>C99*M20</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N99" s="8"/>
       <c r="O99" s="8"/>
       <c r="P99" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>220</v>
       </c>
       <c r="Q99" s="8">
@@ -5331,53 +5332,53 @@
         <v>32</v>
       </c>
       <c r="C100" s="8">
-        <f>C21*2</f>
+        <f t="shared" si="7"/>
         <v>108</v>
       </c>
       <c r="D100" s="8">
-        <f>C100*D21</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E100" s="8">
-        <f>C100*E21</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F100" s="8">
-        <f>C100*F21</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G100" s="8">
-        <f>C100*G21</f>
+        <f t="shared" si="18"/>
         <v>108</v>
       </c>
       <c r="H100" s="8">
-        <f>C100*H21</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I100" s="8">
-        <f>C100*I21</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J100" s="8">
-        <f>C100*J21</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K100" s="8">
-        <f>C100*K21</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L100" s="8">
-        <f>C100*L21</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M100" s="8">
-        <f>C100*M21</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N100" s="8"/>
       <c r="O100" s="8"/>
       <c r="P100" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>108</v>
       </c>
       <c r="Q100" s="8"/>
@@ -5390,53 +5391,53 @@
         <v>33</v>
       </c>
       <c r="C101" s="8">
-        <f>C22*2</f>
+        <f t="shared" si="7"/>
         <v>110</v>
       </c>
       <c r="D101" s="8">
-        <f>C101*D22</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E101" s="8">
-        <f>C101*E22</f>
+        <f t="shared" si="16"/>
         <v>110</v>
       </c>
       <c r="F101" s="8">
-        <f>C101*F22</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G101" s="8">
-        <f>C101*G22</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H101" s="8">
-        <f>C101*H22</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I101" s="8">
-        <f>C101*I22</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J101" s="8">
-        <f>C101*J22</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K101" s="8">
-        <f>C101*K22</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L101" s="8">
-        <f>C101*L22</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M101" s="8">
-        <f>C101*M22</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N101" s="8"/>
       <c r="O101" s="8"/>
       <c r="P101" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>110</v>
       </c>
       <c r="Q101" s="8"/>
@@ -5449,53 +5450,53 @@
         <v>34</v>
       </c>
       <c r="C102" s="8">
-        <f>C23*2</f>
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
       <c r="D102" s="8">
-        <f>C102*D23</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E102" s="8">
-        <f>C102*E23</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F102" s="8">
-        <f>C102*F23</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G102" s="8">
-        <f>C102*G23</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H102" s="8">
-        <f>C102*H23</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I102" s="8">
-        <f>C102*I23</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J102" s="8">
-        <f>C102*J23</f>
+        <f t="shared" si="21"/>
         <v>92</v>
       </c>
       <c r="K102" s="8">
-        <f>C102*K23</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L102" s="8">
-        <f>C102*L23</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M102" s="8">
-        <f>C102*M23</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N102" s="8"/>
       <c r="O102" s="8"/>
       <c r="P102" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>92</v>
       </c>
       <c r="Q102" s="8"/>
@@ -5508,53 +5509,53 @@
         <v>35</v>
       </c>
       <c r="C103" s="8">
-        <f>C24*2</f>
+        <f t="shared" si="7"/>
         <v>94</v>
       </c>
       <c r="D103" s="8">
-        <f>C103*D24</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E103" s="8">
-        <f>C103*E24</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F103" s="8">
-        <f>C103*F24</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G103" s="8">
-        <f>C103*G24</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H103" s="8">
-        <f>C103*H24</f>
+        <f t="shared" si="19"/>
         <v>94</v>
       </c>
       <c r="I103" s="8">
-        <f>C103*I24</f>
+        <f t="shared" si="20"/>
         <v>188</v>
       </c>
       <c r="J103" s="8">
-        <f>C103*J24</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K103" s="8">
-        <f>C103*K24</f>
+        <f t="shared" si="22"/>
         <v>94</v>
       </c>
       <c r="L103" s="8">
-        <f>C103*L24</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M103" s="8">
-        <f>C103*M24</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N103" s="8"/>
       <c r="O103" s="8"/>
       <c r="P103" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>376</v>
       </c>
       <c r="Q103" s="8"/>
@@ -5567,57 +5568,57 @@
         <v>101</v>
       </c>
       <c r="C104" s="14">
-        <f>C25*2</f>
+        <f t="shared" si="7"/>
         <v>800</v>
       </c>
       <c r="D104" s="14">
-        <f>C104*D25</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E104" s="14">
-        <f>C104*E25</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F104" s="14">
-        <f>C104*F25</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G104" s="14">
-        <f>C104*G25</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H104" s="14">
-        <f>C104*H25</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I104" s="14">
-        <f>C104*I25</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J104" s="14">
-        <f>C104*J25</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K104" s="14">
-        <f>C104*K25</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L104" s="14">
-        <f>C104*L25</f>
+        <f t="shared" si="23"/>
         <v>800</v>
       </c>
       <c r="M104" s="14">
-        <f>C104*M25</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N104" s="14"/>
       <c r="O104" s="14"/>
       <c r="P104" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>800</v>
       </c>
       <c r="Q104" s="14">
-        <f t="shared" ref="Q104:Q109" si="10">P104</f>
+        <f t="shared" ref="Q104:Q109" si="24">P104</f>
         <v>800</v>
       </c>
     </row>
@@ -5629,57 +5630,57 @@
         <v>37</v>
       </c>
       <c r="C105" s="8">
-        <f>C26*2</f>
+        <f t="shared" si="7"/>
         <v>726</v>
       </c>
       <c r="D105" s="8">
-        <f>C105*D26</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E105" s="8">
-        <f>C105*E26</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F105" s="8">
-        <f>C105*F26</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G105" s="8">
-        <f>C105*G26</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H105" s="8">
-        <f>C105*H26</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I105" s="8">
-        <f>C105*I26</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J105" s="8">
-        <f>C105*J26</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K105" s="8">
-        <f>C105*K26</f>
+        <f t="shared" si="22"/>
         <v>726</v>
       </c>
       <c r="L105" s="8">
-        <f>C105*L26</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M105" s="8">
-        <f>C105*M26</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N105" s="8"/>
       <c r="O105" s="8"/>
       <c r="P105" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>726</v>
       </c>
       <c r="Q105" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>726</v>
       </c>
       <c r="R105" s="18"/>
@@ -5704,53 +5705,53 @@
         <v>95</v>
       </c>
       <c r="C106" s="14">
-        <f>C27*2</f>
+        <f t="shared" si="7"/>
         <v>186</v>
       </c>
       <c r="D106" s="14">
-        <f>C106*D27</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E106" s="14">
-        <f>C106*E27</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F106" s="14">
-        <f>C106*F27</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G106" s="14">
-        <f>C106*G27</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H106" s="14">
-        <f>C106*H27</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="I106" s="14">
-        <f>C106*I27</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="J106" s="14">
-        <f>C106*J27</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K106" s="14">
-        <f>C106*K27</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L106" s="14">
-        <f>C106*L27</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M106" s="14">
-        <f>C106*M27</f>
+        <f t="shared" si="14"/>
         <v>186</v>
       </c>
       <c r="N106" s="14"/>
       <c r="O106" s="14"/>
       <c r="P106" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>186</v>
       </c>
       <c r="Q106" s="14">
@@ -5766,7 +5767,7 @@
         <v>123</v>
       </c>
       <c r="C107" s="8">
-        <f>C28*2</f>
+        <f t="shared" si="7"/>
         <v>348</v>
       </c>
       <c r="D107" s="8">
@@ -5797,7 +5798,7 @@
         <v>0</v>
       </c>
       <c r="M107" s="8">
-        <f>C107*M28</f>
+        <f t="shared" si="14"/>
         <v>348</v>
       </c>
       <c r="N107" s="8"/>
@@ -5832,39 +5833,39 @@
         <v>100</v>
       </c>
       <c r="C108" s="14">
-        <f>C29*2</f>
+        <f t="shared" si="7"/>
         <v>418</v>
       </c>
       <c r="D108" s="14">
-        <f t="shared" ref="D108:K108" si="11">C108*D30</f>
+        <f t="shared" ref="D108:K108" si="25">C108*D30</f>
         <v>0</v>
       </c>
       <c r="E108" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="F108" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="G108" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H108" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="J108" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="K108" s="14">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="L108" s="14">
@@ -5872,17 +5873,17 @@
         <v>418</v>
       </c>
       <c r="M108" s="14">
-        <f>C108*M29</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N108" s="14"/>
       <c r="O108" s="14"/>
       <c r="P108" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>418</v>
       </c>
       <c r="Q108" s="14">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>418</v>
       </c>
     </row>
@@ -5894,11 +5895,11 @@
         <v>39</v>
       </c>
       <c r="C109" s="8">
-        <f>C30*2</f>
+        <f t="shared" si="7"/>
         <v>516</v>
       </c>
       <c r="D109" s="8">
-        <f>C109*D30</f>
+        <f t="shared" ref="D109:D140" si="26">C109*D30</f>
         <v>0</v>
       </c>
       <c r="E109" s="8">
@@ -5914,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="8">
-        <f>C109*H30</f>
+        <f t="shared" ref="H109:H140" si="27">C109*H30</f>
         <v>0</v>
       </c>
       <c r="I109" s="8">
@@ -5934,17 +5935,17 @@
         <v>0</v>
       </c>
       <c r="M109" s="8">
-        <f>C109*M30</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N109" s="8"/>
       <c r="O109" s="8"/>
       <c r="P109" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>516</v>
       </c>
       <c r="Q109" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="24"/>
         <v>516</v>
       </c>
       <c r="R109" s="18"/>
@@ -5969,11 +5970,11 @@
         <v>45</v>
       </c>
       <c r="C110" s="14">
-        <f>C31*2</f>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="D110" s="14">
-        <f>C110*D31</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E110" s="14">
@@ -5989,7 +5990,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <f>C110*H31</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I110" s="14">
@@ -6009,13 +6010,13 @@
         <v>0</v>
       </c>
       <c r="M110" s="14">
-        <f>C110*M31</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N110" s="14"/>
       <c r="O110" s="14"/>
       <c r="P110" s="14">
-        <f t="shared" ref="P110:P115" si="12">SUM(D110:M110)</f>
+        <f t="shared" ref="P110:P115" si="28">SUM(D110:M110)</f>
         <v>100</v>
       </c>
       <c r="Q110" s="14">
@@ -6031,11 +6032,11 @@
         <v>128</v>
       </c>
       <c r="C111" s="14">
-        <f>C32*2</f>
+        <f t="shared" si="7"/>
         <v>38</v>
       </c>
       <c r="D111" s="14">
-        <f>C111*D32</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E111" s="14">
@@ -6051,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <f>C111*H32</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I111" s="14">
@@ -6071,13 +6072,13 @@
         <v>0</v>
       </c>
       <c r="M111" s="14">
-        <f>C111*M32</f>
+        <f t="shared" si="14"/>
         <v>38</v>
       </c>
       <c r="N111" s="14"/>
       <c r="O111" s="14"/>
       <c r="P111" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>38</v>
       </c>
       <c r="Q111" s="14"/>
@@ -6090,53 +6091,53 @@
         <v>46</v>
       </c>
       <c r="C112" s="14">
-        <f>C33*2</f>
+        <f t="shared" si="7"/>
         <v>54</v>
       </c>
       <c r="D112" s="14">
-        <f>C112*D33</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E112" s="14">
-        <f>C112*E33</f>
+        <f t="shared" ref="E112:E140" si="29">C112*E33</f>
         <v>0</v>
       </c>
       <c r="F112" s="14">
-        <f>C112*F33</f>
+        <f t="shared" ref="F112:F140" si="30">C112*F33</f>
         <v>0</v>
       </c>
       <c r="G112" s="14">
-        <f>C112*G33</f>
+        <f t="shared" ref="G112:G140" si="31">C112*G33</f>
         <v>54</v>
       </c>
       <c r="H112" s="14">
-        <f>C112*H33</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I112" s="14">
-        <f>C112*I33</f>
+        <f t="shared" ref="I112:I140" si="32">C112*I33</f>
         <v>54</v>
       </c>
       <c r="J112" s="14">
-        <f>C112*J33</f>
+        <f t="shared" ref="J112:J140" si="33">C112*J33</f>
         <v>108</v>
       </c>
       <c r="K112" s="14">
-        <f>C112*K33</f>
+        <f t="shared" ref="K112:K140" si="34">C112*K33</f>
         <v>0</v>
       </c>
       <c r="L112" s="14">
-        <f>C112*L33</f>
+        <f t="shared" ref="L112:L147" si="35">C112*L33</f>
         <v>0</v>
       </c>
       <c r="M112" s="14">
-        <f>C112*M33</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N112" s="20"/>
       <c r="O112" s="14"/>
       <c r="P112" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>216</v>
       </c>
       <c r="Q112" s="14"/>
@@ -6149,53 +6150,53 @@
         <v>47</v>
       </c>
       <c r="C113" s="14">
-        <f>C34*2</f>
+        <f t="shared" ref="C113:C144" si="36">C34*2</f>
         <v>54</v>
       </c>
       <c r="D113" s="14">
-        <f>C113*D34</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E113" s="14">
-        <f>C113*E34</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F113" s="14">
-        <f>C113*F34</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G113" s="14">
-        <f>C113*G34</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <f>C113*H34</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I113" s="14">
-        <f>C113*I34</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J113" s="14">
-        <f>C113*J34</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K113" s="14">
-        <f>C113*K34</f>
+        <f t="shared" si="34"/>
         <v>54</v>
       </c>
       <c r="L113" s="14">
-        <f>C113*L34</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M113" s="14">
-        <f>C113*M34</f>
+        <f t="shared" si="14"/>
         <v>378</v>
       </c>
       <c r="N113" s="14"/>
       <c r="O113" s="14"/>
       <c r="P113" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>432</v>
       </c>
       <c r="Q113" s="14"/>
@@ -6208,53 +6209,53 @@
         <v>48</v>
       </c>
       <c r="C114" s="14">
-        <f>C35*2</f>
+        <f t="shared" si="36"/>
         <v>54</v>
       </c>
       <c r="D114" s="14">
-        <f>C114*D35</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E114" s="14">
-        <f>C114*E35</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F114" s="14">
-        <f>C114*F35</f>
+        <f t="shared" si="30"/>
         <v>54</v>
       </c>
       <c r="G114" s="14">
-        <f>C114*G35</f>
+        <f t="shared" si="31"/>
         <v>108</v>
       </c>
       <c r="H114" s="14">
-        <f>C114*H35</f>
+        <f t="shared" si="27"/>
         <v>54</v>
       </c>
       <c r="I114" s="14">
-        <f>C114*I35</f>
+        <f t="shared" si="32"/>
         <v>54</v>
       </c>
       <c r="J114" s="14">
-        <f>C114*J35</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K114" s="14">
-        <f>C114*K35</f>
+        <f t="shared" si="34"/>
         <v>54</v>
       </c>
       <c r="L114" s="14">
-        <f>C114*L35</f>
+        <f t="shared" si="35"/>
         <v>54</v>
       </c>
       <c r="M114" s="14">
-        <f>C114*M35</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N114" s="14"/>
       <c r="O114" s="14"/>
       <c r="P114" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>378</v>
       </c>
       <c r="Q114" s="14"/>
@@ -6267,53 +6268,53 @@
         <v>49</v>
       </c>
       <c r="C115" s="14">
-        <f>C36*2</f>
+        <f t="shared" si="36"/>
         <v>62</v>
       </c>
       <c r="D115" s="14">
-        <f>C115*D36</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E115" s="14">
-        <f>C115*E36</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F115" s="14">
-        <f>C115*F36</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G115" s="14">
-        <f>C115*G36</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <f>C115*H36</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I115" s="14">
-        <f>C115*I36</f>
+        <f t="shared" si="32"/>
         <v>62</v>
       </c>
       <c r="J115" s="14">
-        <f>C115*J36</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K115" s="14">
-        <f>C115*K36</f>
+        <f t="shared" si="34"/>
         <v>186</v>
       </c>
       <c r="L115" s="14">
-        <f>C115*L36</f>
+        <f t="shared" si="35"/>
         <v>124</v>
       </c>
       <c r="M115" s="14">
-        <f>C115*M36</f>
+        <f t="shared" si="14"/>
         <v>124</v>
       </c>
       <c r="N115" s="14"/>
       <c r="O115" s="14"/>
       <c r="P115" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="28"/>
         <v>496</v>
       </c>
       <c r="Q115" s="14"/>
@@ -6326,53 +6327,53 @@
         <v>41</v>
       </c>
       <c r="C116" s="8">
-        <f>C37*2</f>
+        <f t="shared" si="36"/>
         <v>158</v>
       </c>
       <c r="D116" s="8">
-        <f>C116*D37</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E116" s="8">
-        <f>C116*E37</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F116" s="8">
-        <f>C116*F37</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G116" s="8">
-        <f>C116*G37</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H116" s="8">
-        <f>C116*H37</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I116" s="8">
-        <f>C116*I37</f>
+        <f t="shared" si="32"/>
         <v>158</v>
       </c>
       <c r="J116" s="8">
-        <f>C116*J37</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K116" s="8">
-        <f>C116*K37</f>
+        <f t="shared" si="34"/>
         <v>158</v>
       </c>
       <c r="L116" s="8">
-        <f>C116*L37</f>
+        <f t="shared" si="35"/>
         <v>158</v>
       </c>
       <c r="M116" s="8">
-        <f>C116*M37</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N116" s="8"/>
       <c r="O116" s="8"/>
       <c r="P116" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>474</v>
       </c>
       <c r="Q116" s="8">
@@ -6401,53 +6402,53 @@
         <v>42</v>
       </c>
       <c r="C117" s="8">
-        <f>C38*2</f>
+        <f t="shared" si="36"/>
         <v>140</v>
       </c>
       <c r="D117" s="8">
-        <f>C117*D38</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E117" s="8">
-        <f>C117*E38</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F117" s="8">
-        <f>C117*F38</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G117" s="8">
-        <f>C117*G38</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H117" s="8">
-        <f>C117*H38</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I117" s="8">
-        <f>C117*I38</f>
+        <f t="shared" si="32"/>
         <v>280</v>
       </c>
       <c r="J117" s="8">
-        <f>C117*J38</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K117" s="8">
-        <f>C117*K38</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L117" s="8">
-        <f>C117*L38</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M117" s="8">
-        <f>C117*M38</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N117" s="8"/>
       <c r="O117" s="8"/>
       <c r="P117" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>280</v>
       </c>
       <c r="Q117" s="8"/>
@@ -6473,53 +6474,53 @@
         <v>43</v>
       </c>
       <c r="C118" s="8">
-        <f>C39*2</f>
+        <f t="shared" si="36"/>
         <v>132</v>
       </c>
       <c r="D118" s="8">
-        <f>C118*D39</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E118" s="8">
-        <f>C118*E39</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F118" s="8">
-        <f>C118*F39</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G118" s="8">
-        <f>C118*G39</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H118" s="8">
-        <f>C118*H39</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I118" s="8">
-        <f>C118*I39</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J118" s="8">
-        <f>C118*J39</f>
+        <f t="shared" si="33"/>
         <v>132</v>
       </c>
       <c r="K118" s="8">
-        <f>C118*K39</f>
+        <f t="shared" si="34"/>
         <v>132</v>
       </c>
       <c r="L118" s="8">
-        <f>C118*L39</f>
+        <f t="shared" si="35"/>
         <v>132</v>
       </c>
       <c r="M118" s="8">
-        <f>C118*M39</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N118" s="8"/>
       <c r="O118" s="8"/>
       <c r="P118" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>396</v>
       </c>
       <c r="Q118" s="8"/>
@@ -6545,53 +6546,53 @@
         <v>51</v>
       </c>
       <c r="C119" s="14">
-        <f>C40*2</f>
+        <f t="shared" si="36"/>
         <v>840</v>
       </c>
       <c r="D119" s="14">
-        <f>C119*D40</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E119" s="14">
-        <f>C119*E40</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F119" s="14">
-        <f>C119*F40</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G119" s="14">
-        <f>C119*G40</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <f>C119*H40</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I119" s="14">
-        <f>C119*I40</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J119" s="14">
-        <f>C119*J40</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K119" s="14">
-        <f>C119*K40</f>
+        <f t="shared" si="34"/>
         <v>840</v>
       </c>
       <c r="L119" s="14">
-        <f>C119*L40</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M119" s="14">
-        <f>C119*M40</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N119" s="14"/>
       <c r="O119" s="14"/>
       <c r="P119" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>840</v>
       </c>
       <c r="Q119" s="14">
@@ -6607,53 +6608,53 @@
         <v>53</v>
       </c>
       <c r="C120" s="8">
-        <f>C41*2</f>
+        <f t="shared" si="36"/>
         <v>282</v>
       </c>
       <c r="D120" s="8">
-        <f>C120*D41</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E120" s="8">
-        <f>C120*E41</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F120" s="8">
-        <f>C120*F41</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G120" s="8">
-        <f>C120*G41</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H120" s="8">
-        <f>C120*H41</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I120" s="8">
-        <f>C120*I41</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J120" s="8">
-        <f>C120*J41</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K120" s="8">
-        <f>C120*K41</f>
+        <f t="shared" si="34"/>
         <v>282</v>
       </c>
       <c r="L120" s="8">
-        <f>C120*L41</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M120" s="8">
-        <f>C120*M41</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N120" s="8"/>
       <c r="O120" s="8"/>
       <c r="P120" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>282</v>
       </c>
       <c r="Q120" s="8">
@@ -6682,53 +6683,53 @@
         <v>55</v>
       </c>
       <c r="C121" s="14">
-        <f>C42*2</f>
+        <f t="shared" si="36"/>
         <v>160</v>
       </c>
       <c r="D121" s="14">
-        <f>C121*D42</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E121" s="14">
-        <f>C121*E42</f>
+        <f t="shared" si="29"/>
         <v>160</v>
       </c>
       <c r="F121" s="14">
-        <f>C121*F42</f>
+        <f t="shared" si="30"/>
         <v>160</v>
       </c>
       <c r="G121" s="14">
-        <f>C121*G42</f>
+        <f t="shared" si="31"/>
         <v>320</v>
       </c>
       <c r="H121" s="14">
-        <f>C121*H42</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I121" s="14">
-        <f>C121*I42</f>
+        <f t="shared" si="32"/>
         <v>480</v>
       </c>
       <c r="J121" s="14">
-        <f>C121*J42</f>
+        <f t="shared" si="33"/>
         <v>160</v>
       </c>
       <c r="K121" s="14">
-        <f>C121*K42</f>
+        <f t="shared" si="34"/>
         <v>160</v>
       </c>
       <c r="L121" s="14">
-        <f>C121*L42</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M121" s="14">
-        <f>C121*M42</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N121" s="14"/>
       <c r="O121" s="14"/>
       <c r="P121" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1440</v>
       </c>
       <c r="Q121" s="14">
@@ -6744,53 +6745,53 @@
         <v>119</v>
       </c>
       <c r="C122" s="8">
-        <f>C43*2</f>
+        <f t="shared" si="36"/>
         <v>1044</v>
       </c>
       <c r="D122" s="8">
-        <f>C122*D43</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E122" s="8">
-        <f>C122*E43</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F122" s="8">
-        <f>C122*F43</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G122" s="8">
-        <f>C122*G43</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H122" s="8">
-        <f>C122*H43</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I122" s="8">
-        <f>C122*I43</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J122" s="8">
-        <f>C122*J43</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K122" s="8">
-        <f>C122*K43</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L122" s="8">
-        <f>C122*L43</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M122" s="8">
-        <f>C122*M43</f>
+        <f t="shared" si="14"/>
         <v>2088</v>
       </c>
       <c r="N122" s="8"/>
       <c r="O122" s="8"/>
       <c r="P122" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>2088</v>
       </c>
       <c r="Q122" s="8">
@@ -6819,53 +6820,53 @@
         <v>57</v>
       </c>
       <c r="C123" s="14">
-        <f>C44*2</f>
+        <f t="shared" si="36"/>
         <v>68</v>
       </c>
       <c r="D123" s="14">
-        <f>C123*D44</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E123" s="14">
-        <f>C123*E44</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F123" s="14">
-        <f>C123*F44</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G123" s="14">
-        <f>C123*G44</f>
+        <f t="shared" si="31"/>
         <v>68</v>
       </c>
       <c r="H123" s="14">
-        <f>C123*H44</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I123" s="14">
-        <f>C123*I44</f>
+        <f t="shared" si="32"/>
         <v>136</v>
       </c>
       <c r="J123" s="14">
-        <f>C123*J44</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K123" s="14">
-        <f>C123*K44</f>
+        <f t="shared" si="34"/>
         <v>136</v>
       </c>
       <c r="L123" s="14">
-        <f>C123*L44</f>
+        <f t="shared" si="35"/>
         <v>68</v>
       </c>
       <c r="M123" s="14">
-        <f>C123*M44</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N123" s="14"/>
       <c r="O123" s="14"/>
       <c r="P123" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>408</v>
       </c>
       <c r="Q123" s="14">
@@ -6881,53 +6882,53 @@
         <v>58</v>
       </c>
       <c r="C124" s="14">
-        <f>C45*2</f>
+        <f t="shared" si="36"/>
         <v>90</v>
       </c>
       <c r="D124" s="14">
-        <f>C124*D45</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E124" s="14">
-        <f>C124*E45</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F124" s="14">
-        <f>C124*F45</f>
+        <f t="shared" si="30"/>
         <v>90</v>
       </c>
       <c r="G124" s="14">
-        <f>C124*G45</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <f>C124*H45</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I124" s="14">
-        <f>C124*I45</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J124" s="14">
-        <f>C124*J45</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K124" s="14">
-        <f>C124*K45</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L124" s="14">
-        <f>C124*L45</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M124" s="14">
-        <f>C124*M45</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N124" s="14"/>
       <c r="O124" s="14"/>
       <c r="P124" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>90</v>
       </c>
       <c r="Q124" s="14"/>
@@ -6940,53 +6941,53 @@
         <v>60</v>
       </c>
       <c r="C125" s="8">
-        <f>C46*2</f>
+        <f t="shared" si="36"/>
         <v>264</v>
       </c>
       <c r="D125" s="8">
-        <f>C125*D46</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E125" s="8">
-        <f>C125*E46</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F125" s="8">
-        <f>C125*F46</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G125" s="8">
-        <f>C125*G46</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H125" s="8">
-        <f>C125*H46</f>
+        <f t="shared" si="27"/>
         <v>264</v>
       </c>
       <c r="I125" s="8">
-        <f>C125*I46</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J125" s="8">
-        <f>C125*J46</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K125" s="8">
-        <f>C125*K46</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L125" s="8">
-        <f>C125*L46</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M125" s="8">
-        <f>C125*M46</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N125" s="8"/>
       <c r="O125" s="8"/>
       <c r="P125" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>264</v>
       </c>
       <c r="Q125" s="8">
@@ -7015,53 +7016,53 @@
         <v>61</v>
       </c>
       <c r="C126" s="8">
-        <f>C47*2</f>
+        <f t="shared" si="36"/>
         <v>262</v>
       </c>
       <c r="D126" s="8">
-        <f>C126*D47</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E126" s="8">
-        <f>C126*E47</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F126" s="8">
-        <f>C126*F47</f>
+        <f t="shared" si="30"/>
         <v>262</v>
       </c>
       <c r="G126" s="8">
-        <f>C126*G47</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H126" s="8">
-        <f>C126*H47</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I126" s="8">
-        <f>C126*I47</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J126" s="8">
-        <f>C126*J47</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K126" s="8">
-        <f>C126*K47</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L126" s="8">
-        <f>C126*L47</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M126" s="8">
-        <f>C126*M47</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N126" s="8"/>
       <c r="O126" s="8"/>
       <c r="P126" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>262</v>
       </c>
       <c r="Q126" s="8"/>
@@ -7087,53 +7088,53 @@
         <v>62</v>
       </c>
       <c r="C127" s="8">
-        <f>C48*2</f>
+        <f t="shared" si="36"/>
         <v>262</v>
       </c>
       <c r="D127" s="8">
-        <f>C127*D48</f>
+        <f t="shared" si="26"/>
         <v>262</v>
       </c>
       <c r="E127" s="8">
-        <f>C127*E48</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F127" s="8">
-        <f>C127*F48</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G127" s="8">
-        <f>C127*G48</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H127" s="8">
-        <f>C127*H48</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I127" s="8">
-        <f>C127*I48</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J127" s="8">
-        <f>C127*J48</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K127" s="8">
-        <f>C127*K48</f>
+        <f t="shared" si="34"/>
         <v>262</v>
       </c>
       <c r="L127" s="8">
-        <f>C127*L48</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M127" s="8">
-        <f>C127*M48</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N127" s="8"/>
       <c r="O127" s="8"/>
       <c r="P127" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>524</v>
       </c>
       <c r="Q127" s="8"/>
@@ -7159,53 +7160,53 @@
         <v>64</v>
       </c>
       <c r="C128" s="14">
-        <f>C49*2</f>
+        <f t="shared" si="36"/>
         <v>272</v>
       </c>
       <c r="D128" s="14">
-        <f>C128*D49</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E128" s="14">
-        <f>C128*E49</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F128" s="14">
-        <f>C128*F49</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G128" s="14">
-        <f>C128*G49</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <f>C128*H49</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I128" s="14">
-        <f>C128*I49</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J128" s="14">
-        <f>C128*J49</f>
+        <f t="shared" si="33"/>
         <v>544</v>
       </c>
       <c r="K128" s="14">
-        <f>C128*K49</f>
+        <f t="shared" si="34"/>
         <v>272</v>
       </c>
       <c r="L128" s="14">
-        <f>C128*L49</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M128" s="14">
-        <f>C128*M49</f>
+        <f t="shared" ref="M128:M159" si="37">C128*M49</f>
         <v>0</v>
       </c>
       <c r="N128" s="14"/>
       <c r="O128" s="14"/>
       <c r="P128" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>816</v>
       </c>
       <c r="Q128" s="14">
@@ -7221,53 +7222,53 @@
         <v>66</v>
       </c>
       <c r="C129" s="8">
-        <f>C50*2</f>
+        <f t="shared" si="36"/>
         <v>266</v>
       </c>
       <c r="D129" s="8">
-        <f>C129*D50</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E129" s="8">
-        <f>C129*E50</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F129" s="8">
-        <f>C129*F50</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G129" s="8">
-        <f>C129*G50</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H129" s="8">
-        <f>C129*H50</f>
+        <f t="shared" si="27"/>
         <v>266</v>
       </c>
       <c r="I129" s="8">
-        <f>C129*I50</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J129" s="8">
-        <f>C129*J50</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K129" s="8">
-        <f>C129*K50</f>
+        <f t="shared" si="34"/>
         <v>266</v>
       </c>
       <c r="L129" s="8">
-        <f>C129*L50</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M129" s="8">
-        <f>C129*M50</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N129" s="8"/>
       <c r="O129" s="8"/>
       <c r="P129" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>532</v>
       </c>
       <c r="Q129" s="8">
@@ -7296,53 +7297,53 @@
         <v>67</v>
       </c>
       <c r="C130" s="8">
-        <f>C51*2</f>
+        <f t="shared" si="36"/>
         <v>304</v>
       </c>
       <c r="D130" s="8">
-        <f>C130*D51</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E130" s="8">
-        <f>C130*E51</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F130" s="8">
-        <f>C130*F51</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G130" s="8">
-        <f>C130*G51</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H130" s="8">
-        <f>C130*H51</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I130" s="8">
-        <f>C130*I51</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J130" s="8">
-        <f>C130*J51</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K130" s="8">
-        <f>C130*K51</f>
+        <f t="shared" si="34"/>
         <v>304</v>
       </c>
       <c r="L130" s="8">
-        <f>C130*L51</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M130" s="8">
-        <f>C130*M51</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N130" s="8"/>
       <c r="O130" s="8"/>
       <c r="P130" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>304</v>
       </c>
       <c r="Q130" s="8"/>
@@ -7368,53 +7369,53 @@
         <v>68</v>
       </c>
       <c r="C131" s="8">
-        <f>C52*2</f>
+        <f t="shared" si="36"/>
         <v>254</v>
       </c>
       <c r="D131" s="8">
-        <f>C131*D52</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E131" s="8">
-        <f>C131*E52</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F131" s="8">
-        <f>C131*F52</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G131" s="8">
-        <f>C131*G52</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H131" s="8">
-        <f>C131*H52</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I131" s="8">
-        <f>C131*I52</f>
+        <f t="shared" si="32"/>
         <v>254</v>
       </c>
       <c r="J131" s="8">
-        <f>C131*J52</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K131" s="8">
-        <f>C131*K52</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L131" s="8">
-        <f>C131*L52</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M131" s="8">
-        <f>C131*M52</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N131" s="8"/>
       <c r="O131" s="8"/>
       <c r="P131" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>254</v>
       </c>
       <c r="Q131" s="8"/>
@@ -7440,53 +7441,53 @@
         <v>69</v>
       </c>
       <c r="C132" s="8">
-        <f>C53*2</f>
+        <f t="shared" si="36"/>
         <v>306</v>
       </c>
       <c r="D132" s="8">
-        <f>C132*D53</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E132" s="8">
-        <f>C132*E53</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F132" s="8">
-        <f>C132*F53</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G132" s="8">
-        <f>C132*G53</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H132" s="8">
-        <f>C132*H53</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I132" s="8">
-        <f>C132*I53</f>
+        <f t="shared" si="32"/>
         <v>306</v>
       </c>
       <c r="J132" s="8">
-        <f>C132*J53</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K132" s="8">
-        <f>C132*K53</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L132" s="8">
-        <f>C132*L53</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M132" s="8">
-        <f>C132*M53</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N132" s="8"/>
       <c r="O132" s="8"/>
       <c r="P132" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>306</v>
       </c>
       <c r="Q132" s="8"/>
@@ -7512,53 +7513,53 @@
         <v>71</v>
       </c>
       <c r="C133" s="14">
-        <f>C54*2</f>
+        <f t="shared" si="36"/>
         <v>124</v>
       </c>
       <c r="D133" s="14">
-        <f>C133*D54</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E133" s="14">
-        <f>C133*E54</f>
+        <f t="shared" si="29"/>
         <v>124</v>
       </c>
       <c r="F133" s="14">
-        <f>C133*F54</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G133" s="14">
-        <f>C133*G54</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H133" s="14">
-        <f>C133*H54</f>
+        <f t="shared" si="27"/>
         <v>124</v>
       </c>
       <c r="I133" s="14">
-        <f>C133*I54</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J133" s="14">
-        <f>C133*J54</f>
+        <f t="shared" si="33"/>
         <v>248</v>
       </c>
       <c r="K133" s="14">
-        <f>C133*K54</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L133" s="14">
-        <f>C133*L54</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M133" s="14">
-        <f>C133*M54</f>
+        <f t="shared" si="37"/>
         <v>124</v>
       </c>
       <c r="N133" s="14"/>
       <c r="O133" s="14"/>
       <c r="P133" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>620</v>
       </c>
       <c r="Q133" s="14">
@@ -7574,53 +7575,53 @@
         <v>72</v>
       </c>
       <c r="C134" s="14">
-        <f>C55*2</f>
+        <f t="shared" si="36"/>
         <v>130</v>
       </c>
       <c r="D134" s="14">
-        <f>C134*D55</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E134" s="14">
-        <f>C134*E55</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F134" s="14">
-        <f>C134*F55</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G134" s="14">
-        <f>C134*G55</f>
+        <f t="shared" si="31"/>
         <v>260</v>
       </c>
       <c r="H134" s="14">
-        <f>C134*H55</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I134" s="14">
-        <f>C134*I55</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J134" s="14">
-        <f>C134*J55</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K134" s="14">
-        <f>C134*K55</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L134" s="14">
-        <f>C134*L55</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M134" s="14">
-        <f>C134*M55</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N134" s="14"/>
       <c r="O134" s="14"/>
       <c r="P134" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>260</v>
       </c>
       <c r="Q134" s="14"/>
@@ -7633,53 +7634,53 @@
         <v>73</v>
       </c>
       <c r="C135" s="14">
-        <f>C56*2</f>
+        <f t="shared" si="36"/>
         <v>124</v>
       </c>
       <c r="D135" s="14">
-        <f>C135*D56</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E135" s="14">
-        <f>C135*E56</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F135" s="14">
-        <f>C135*F56</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G135" s="14">
-        <f>C135*G56</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H135" s="14">
-        <f>C135*H56</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I135" s="14">
-        <f>C135*I56</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J135" s="14">
-        <f>C135*J56</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K135" s="14">
-        <f>C135*K56</f>
+        <f t="shared" si="34"/>
         <v>124</v>
       </c>
       <c r="L135" s="14">
-        <f>C135*L56</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M135" s="14">
-        <f>C135*M56</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N135" s="14"/>
       <c r="O135" s="14"/>
       <c r="P135" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>124</v>
       </c>
       <c r="Q135" s="14"/>
@@ -7692,53 +7693,53 @@
         <v>124</v>
       </c>
       <c r="C136" s="8">
-        <f>C57*2</f>
+        <f t="shared" si="36"/>
         <v>90</v>
       </c>
       <c r="D136" s="8">
-        <f>C136*D57</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E136" s="8">
-        <f>C136*E57</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F136" s="8">
-        <f>C136*F57</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G136" s="8">
-        <f>C136*G57</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H136" s="8">
-        <f>C136*H57</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I136" s="8">
-        <f>C136*I57</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J136" s="8">
-        <f>C136*J57</f>
+        <f t="shared" si="33"/>
         <v>90</v>
       </c>
       <c r="K136" s="8">
-        <f>C136*K57</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L136" s="8">
-        <f>C136*L57</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M136" s="8">
-        <f>C136*M57</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N136" s="8"/>
       <c r="O136" s="8"/>
       <c r="P136" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>90</v>
       </c>
       <c r="Q136" s="8">
@@ -7767,53 +7768,53 @@
         <v>76</v>
       </c>
       <c r="C137" s="8">
-        <f>C58*2</f>
+        <f t="shared" si="36"/>
         <v>106</v>
       </c>
       <c r="D137" s="8">
-        <f>C137*D58</f>
+        <f t="shared" si="26"/>
         <v>106</v>
       </c>
       <c r="E137" s="8">
-        <f>C137*E58</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F137" s="8">
-        <f>C137*F58</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G137" s="8">
-        <f>C137*G58</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H137" s="8">
-        <f>C137*H58</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I137" s="8">
-        <f>C137*I58</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J137" s="8">
-        <f>C137*J58</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K137" s="8">
-        <f>C137*K58</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L137" s="8">
-        <f>C137*L58</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M137" s="8">
-        <f>C137*M58</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N137" s="8"/>
       <c r="O137" s="8"/>
       <c r="P137" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>106</v>
       </c>
       <c r="Q137" s="8"/>
@@ -7839,53 +7840,53 @@
         <v>77</v>
       </c>
       <c r="C138" s="8">
-        <f>C59*2</f>
+        <f t="shared" si="36"/>
         <v>90</v>
       </c>
       <c r="D138" s="8">
-        <f>C138*D59</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E138" s="8">
-        <f>C138*E59</f>
+        <f t="shared" si="29"/>
         <v>90</v>
       </c>
       <c r="F138" s="8">
-        <f>C138*F59</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G138" s="8">
-        <f>C138*G59</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H138" s="8">
-        <f>C138*H59</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I138" s="8">
-        <f>C138*I59</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J138" s="8">
-        <f>C138*J59</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K138" s="8">
-        <f>C138*K59</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L138" s="8">
-        <f>C138*L59</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M138" s="8">
-        <f>C138*M59</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N138" s="8"/>
       <c r="O138" s="8"/>
       <c r="P138" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>90</v>
       </c>
       <c r="Q138" s="8"/>
@@ -7911,53 +7912,53 @@
         <v>79</v>
       </c>
       <c r="C139" s="14">
-        <f>C60*2</f>
+        <f t="shared" si="36"/>
         <v>40</v>
       </c>
       <c r="D139" s="14">
-        <f>C139*D60</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E139" s="14">
-        <f>C139*E60</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F139" s="14">
-        <f>C139*F60</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G139" s="14">
-        <f>C139*G60</f>
+        <f t="shared" si="31"/>
         <v>80</v>
       </c>
       <c r="H139" s="14">
-        <f>C139*H60</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I139" s="14">
-        <f>C139*I60</f>
+        <f t="shared" si="32"/>
         <v>160</v>
       </c>
       <c r="J139" s="14">
-        <f>C139*J60</f>
+        <f t="shared" si="33"/>
         <v>160</v>
       </c>
       <c r="K139" s="14">
-        <f>C139*K60</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L139" s="14">
-        <f>C139*L60</f>
+        <f t="shared" si="35"/>
         <v>40</v>
       </c>
       <c r="M139" s="14">
-        <f>C139*M60</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N139" s="14"/>
       <c r="O139" s="14"/>
       <c r="P139" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>440</v>
       </c>
       <c r="Q139" s="14">
@@ -7973,53 +7974,53 @@
         <v>80</v>
       </c>
       <c r="C140" s="14">
-        <f>C61*2</f>
+        <f t="shared" si="36"/>
         <v>34</v>
       </c>
       <c r="D140" s="14">
-        <f>C140*D61</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="E140" s="14">
-        <f>C140*E61</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="F140" s="14">
-        <f>C140*F61</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="G140" s="14">
-        <f>C140*G61</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H140" s="14">
-        <f>C140*H61</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="I140" s="14">
-        <f>C140*I61</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="J140" s="14">
-        <f>C140*J61</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K140" s="14">
-        <f>C140*K61</f>
+        <f t="shared" si="34"/>
         <v>136</v>
       </c>
       <c r="L140" s="14">
-        <f>C140*L61</f>
+        <f t="shared" si="35"/>
         <v>68</v>
       </c>
       <c r="M140" s="14">
-        <f>C140*M61</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N140" s="14"/>
       <c r="O140" s="14"/>
       <c r="P140" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>204</v>
       </c>
       <c r="Q140" s="14"/>
@@ -8032,7 +8033,7 @@
         <v>102</v>
       </c>
       <c r="C141" s="14">
-        <f>C62*2</f>
+        <f t="shared" si="36"/>
         <v>34</v>
       </c>
       <c r="D141" s="14">
@@ -8060,17 +8061,17 @@
         <v>0</v>
       </c>
       <c r="L141" s="14">
-        <f>C141*L62</f>
+        <f t="shared" si="35"/>
         <v>68</v>
       </c>
       <c r="M141" s="14">
-        <f>C141*M62</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N141" s="14"/>
       <c r="O141" s="14"/>
       <c r="P141" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>68</v>
       </c>
       <c r="Q141" s="14"/>
@@ -8083,53 +8084,53 @@
         <v>82</v>
       </c>
       <c r="C142" s="8">
-        <f>C63*2</f>
+        <f t="shared" si="36"/>
         <v>248</v>
       </c>
       <c r="D142" s="8">
-        <f>C142*D63</f>
+        <f t="shared" ref="D142:D147" si="38">C142*D63</f>
         <v>248</v>
       </c>
       <c r="E142" s="8">
-        <f>C142*E63</f>
+        <f t="shared" ref="E142:E147" si="39">C142*E63</f>
         <v>248</v>
       </c>
       <c r="F142" s="8">
-        <f>C142*F63</f>
+        <f t="shared" ref="F142:F147" si="40">C142*F63</f>
         <v>248</v>
       </c>
       <c r="G142" s="8">
-        <f>C142*G63</f>
+        <f t="shared" ref="G142:G147" si="41">C142*G63</f>
         <v>496</v>
       </c>
       <c r="H142" s="8">
-        <f>C142*H63</f>
+        <f t="shared" ref="H142:H147" si="42">C142*H63</f>
         <v>0</v>
       </c>
       <c r="I142" s="8">
-        <f>C142*I63</f>
+        <f t="shared" ref="I142:I147" si="43">C142*I63</f>
         <v>0</v>
       </c>
       <c r="J142" s="8">
-        <f>C142*J63</f>
+        <f t="shared" ref="J142:J147" si="44">C142*J63</f>
         <v>0</v>
       </c>
       <c r="K142" s="8">
-        <f>C142*K63</f>
+        <f t="shared" ref="K142:K147" si="45">C142*K63</f>
         <v>0</v>
       </c>
       <c r="L142" s="8">
-        <f>C142*L63</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M142" s="8">
-        <f>C142*M63</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N142" s="8"/>
       <c r="O142" s="8"/>
       <c r="P142" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>1240</v>
       </c>
       <c r="Q142" s="8">
@@ -8158,53 +8159,53 @@
         <v>84</v>
       </c>
       <c r="C143" s="14">
-        <f>C64*2</f>
+        <f t="shared" si="36"/>
         <v>124</v>
       </c>
       <c r="D143" s="14">
-        <f>C143*D64</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="E143" s="14">
-        <f>C143*E64</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="F143" s="14">
-        <f>C143*F64</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="G143" s="14">
-        <f>C143*G64</f>
+        <f t="shared" si="41"/>
         <v>124</v>
       </c>
       <c r="H143" s="14">
-        <f>C143*H64</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="I143" s="14">
-        <f>C143*I64</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J143" s="14">
-        <f>C143*J64</f>
+        <f t="shared" si="44"/>
         <v>124</v>
       </c>
       <c r="K143" s="14">
-        <f>C143*K64</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L143" s="14">
-        <f>C143*L64</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M143" s="14">
-        <f>C143*M64</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N143" s="14"/>
       <c r="O143" s="14"/>
       <c r="P143" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>248</v>
       </c>
       <c r="Q143" s="14">
@@ -8220,53 +8221,53 @@
         <v>85</v>
       </c>
       <c r="C144" s="14">
-        <f>C65*2</f>
+        <f t="shared" si="36"/>
         <v>118</v>
       </c>
       <c r="D144" s="14">
-        <f>C144*D65</f>
+        <f t="shared" si="38"/>
         <v>118</v>
       </c>
       <c r="E144" s="14">
-        <f>C144*E65</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="F144" s="14">
-        <f>C144*F65</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="G144" s="14">
-        <f>C144*G65</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="H144" s="14">
-        <f>C144*H65</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="I144" s="14">
-        <f>C144*I65</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J144" s="14">
-        <f>C144*J65</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K144" s="14">
-        <f>C144*K65</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L144" s="14">
-        <f>C144*L65</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M144" s="14">
-        <f>C144*M65</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N144" s="14"/>
       <c r="O144" s="14"/>
       <c r="P144" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>118</v>
       </c>
       <c r="Q144" s="14"/>
@@ -8279,53 +8280,53 @@
         <v>86</v>
       </c>
       <c r="C145" s="14">
-        <f>C66*2</f>
+        <f t="shared" ref="C145:C176" si="46">C66*2</f>
         <v>116</v>
       </c>
       <c r="D145" s="14">
-        <f>C145*D66</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="E145" s="14">
-        <f>C145*E66</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="F145" s="14">
-        <f>C145*F66</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="G145" s="14">
-        <f>C145*G66</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="H145" s="14">
-        <f>C145*H66</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="I145" s="14">
-        <f>C145*I66</f>
+        <f t="shared" si="43"/>
         <v>116</v>
       </c>
       <c r="J145" s="14">
-        <f>C145*J66</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K145" s="14">
-        <f>C145*K66</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L145" s="14">
-        <f>C145*L66</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M145" s="14">
-        <f>C145*M66</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N145" s="14"/>
       <c r="O145" s="14"/>
       <c r="P145" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>116</v>
       </c>
       <c r="Q145" s="14"/>
@@ -8338,53 +8339,53 @@
         <v>88</v>
       </c>
       <c r="C146" s="8">
-        <f>C67*2</f>
+        <f t="shared" si="46"/>
         <v>138</v>
       </c>
       <c r="D146" s="8">
-        <f>C146*D67</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="E146" s="8">
-        <f>C146*E67</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="F146" s="8">
-        <f>C146*F67</f>
+        <f t="shared" si="40"/>
         <v>138</v>
       </c>
       <c r="G146" s="8">
-        <f>C146*G67</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="H146" s="8">
-        <f>C146*H67</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="I146" s="8">
-        <f>C146*I67</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J146" s="8">
-        <f>C146*J67</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K146" s="8">
-        <f>C146*K67</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L146" s="8">
-        <f>C146*L67</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M146" s="8">
-        <f>C146*M67</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="N146" s="8"/>
       <c r="O146" s="8"/>
       <c r="P146" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>138</v>
       </c>
       <c r="Q146" s="8">
@@ -8413,58 +8414,58 @@
         <v>137</v>
       </c>
       <c r="C147" s="14">
-        <f>C68*2</f>
+        <f t="shared" si="46"/>
         <v>376</v>
       </c>
       <c r="D147" s="14">
-        <f>C147*D68</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="E147" s="14">
-        <f>C147*E68</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="F147" s="14">
-        <f>C147*F68</f>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="G147" s="14">
-        <f>C147*G68</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="H147" s="14">
-        <f>C147*H68</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="I147" s="14">
-        <f>C147*I68</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J147" s="14">
-        <f>C147*J68</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K147" s="14">
-        <f>C147*K68</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="L147" s="14">
-        <f>C147*L68</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M147" s="14">
-        <f>C147*M68</f>
-        <v>0</v>
+        <f t="shared" si="37"/>
+        <v>376</v>
       </c>
       <c r="N147" s="6"/>
       <c r="O147" s="6"/>
       <c r="P147" s="14">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>376</v>
       </c>
       <c r="Q147" s="14">
         <f>P147</f>
-        <v>0</v>
+        <v>376</v>
       </c>
     </row>
     <row r="150" spans="1:30" x14ac:dyDescent="0.3">
@@ -8521,56 +8522,56 @@
         <v>750</v>
       </c>
       <c r="E151" s="8">
-        <f t="shared" ref="E151:M151" si="13">SUM(E81:E147)</f>
+        <f t="shared" ref="E151:M151" si="47">SUM(E81:E147)</f>
         <v>892</v>
       </c>
       <c r="F151" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="47"/>
         <v>1166</v>
       </c>
       <c r="G151" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="47"/>
         <v>1830</v>
       </c>
       <c r="H151" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="47"/>
         <v>802</v>
       </c>
       <c r="I151" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="47"/>
         <v>3046</v>
       </c>
       <c r="J151" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="47"/>
         <v>2704</v>
       </c>
       <c r="K151" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="47"/>
         <v>4664</v>
       </c>
       <c r="L151" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="47"/>
         <v>2654</v>
       </c>
       <c r="M151" s="8">
-        <f t="shared" si="13"/>
-        <v>6950</v>
+        <f t="shared" si="47"/>
+        <v>7326</v>
       </c>
       <c r="N151" s="8">
         <f>SUM(D151:M151)</f>
-        <v>25458</v>
+        <v>25834</v>
       </c>
       <c r="O151" s="15">
         <f>N151/N70</f>
-        <v>153.36144578313252</v>
+        <v>155.62650602409639</v>
       </c>
       <c r="P151" s="8">
         <f>SUM(P81:P147)</f>
-        <v>25458</v>
+        <v>25834</v>
       </c>
       <c r="Q151" s="8">
         <f>SUM(Q81:Q147)</f>
-        <v>25458</v>
+        <v>25834</v>
       </c>
     </row>
     <row r="152" spans="1:30" x14ac:dyDescent="0.3">
@@ -8578,48 +8579,48 @@
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
       <c r="D152" s="16">
-        <f t="shared" ref="D152:N152" si="14">D151/D70</f>
+        <f t="shared" ref="D152:N152" si="48">D151/D70</f>
         <v>150</v>
       </c>
       <c r="E152" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="48"/>
         <v>89.2</v>
       </c>
       <c r="F152" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="48"/>
         <v>116.6</v>
       </c>
       <c r="G152" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="48"/>
         <v>114.375</v>
       </c>
       <c r="H152" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="48"/>
         <v>160.4</v>
       </c>
       <c r="I152" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="48"/>
         <v>138.45454545454547</v>
       </c>
       <c r="J152" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="48"/>
         <v>142.31578947368422</v>
       </c>
       <c r="K152" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="48"/>
         <v>172.74074074074073</v>
       </c>
       <c r="L152" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="48"/>
         <v>165.875</v>
       </c>
       <c r="M152" s="16">
-        <f t="shared" si="14"/>
-        <v>193.05555555555554</v>
+        <f t="shared" si="48"/>
+        <v>203.5</v>
       </c>
       <c r="N152" s="16">
-        <f t="shared" si="14"/>
-        <v>153.36144578313252</v>
+        <f t="shared" si="48"/>
+        <v>155.62650602409639</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>97</v>
@@ -8807,7 +8808,7 @@
         <v>1</v>
       </c>
       <c r="D165" s="14">
-        <f t="shared" ref="D165:D171" si="15">Q104</f>
+        <f t="shared" ref="D165:D171" si="49">Q104</f>
         <v>800</v>
       </c>
     </row>
@@ -8824,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="D166" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="49"/>
         <v>726</v>
       </c>
     </row>
@@ -8841,7 +8842,7 @@
         <v>1</v>
       </c>
       <c r="D167" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="49"/>
         <v>186</v>
       </c>
     </row>
@@ -8858,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="D168" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="49"/>
         <v>348</v>
       </c>
     </row>
@@ -8875,7 +8876,7 @@
         <v>1</v>
       </c>
       <c r="D169" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="49"/>
         <v>418</v>
       </c>
     </row>
@@ -8892,7 +8893,7 @@
         <v>1</v>
       </c>
       <c r="D170" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="49"/>
         <v>516</v>
       </c>
     </row>
@@ -8909,7 +8910,7 @@
         <v>30</v>
       </c>
       <c r="D171" s="14">
-        <f t="shared" si="15"/>
+        <f t="shared" si="49"/>
         <v>1660</v>
       </c>
     </row>
@@ -9169,16 +9170,16 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="23" t="s">
+      <c r="A187" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="B187" s="23">
+      <c r="B187" s="14">
         <f>Q68</f>
-        <v>0</v>
-      </c>
-      <c r="C187" s="23">
+        <v>1</v>
+      </c>
+      <c r="C187" s="14">
         <f>N68</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D187" s="14">
         <f>Q145</f>
@@ -9189,11 +9190,11 @@
       <c r="A188" s="22"/>
       <c r="B188" s="22">
         <f>SUM(B156:B187)</f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C188" s="22">
         <f>SUM(C156:C187)</f>
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D188" s="22">
         <f>SUM(D156:D187)</f>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0107D012-01DE-45FB-A913-DD1CC68515F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22368C8A-8607-4D06-8E45-C0925CBD1444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="864" windowWidth="20952" windowHeight="12816" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
+    <workbookView xWindow="0" yWindow="876" windowWidth="23040" windowHeight="12804" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
   <sheets>
     <sheet name="pelipaikat" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="139">
   <si>
     <t>Paikkakunta</t>
   </si>
@@ -451,6 +451,9 @@
   </si>
   <si>
     <t>Ähtärin liikuntahalli</t>
+  </si>
+  <si>
+    <t>Hattelmalan kylä</t>
   </si>
 </sst>
 </file>
@@ -577,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -595,12 +598,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -923,8 +927,8 @@
     <col min="3" max="11" width="9.77734375" customWidth="1"/>
     <col min="12" max="12" width="10.5546875" customWidth="1"/>
     <col min="13" max="16" width="9.77734375" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="8.88671875" style="18"/>
+    <col min="18" max="18" width="9.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="30" width="8.88671875" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -979,7 +983,7 @@
       <c r="Q1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="R1" s="21">
+      <c r="R1" s="20">
         <v>46137</v>
       </c>
     </row>
@@ -1629,7 +1633,7 @@
       </c>
       <c r="Q18" s="8"/>
     </row>
-    <row r="19" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>131</v>
       </c>
@@ -1667,7 +1671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>30</v>
       </c>
@@ -1706,21 +1710,21 @@
       <c r="Q20" s="8">
         <v>5</v>
       </c>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="18"/>
-      <c r="AA20" s="18"/>
-      <c r="AB20" s="18"/>
-      <c r="AC20" s="18"/>
-      <c r="AD20" s="18"/>
-    </row>
-    <row r="21" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+    </row>
+    <row r="21" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>30</v>
       </c>
@@ -1755,21 +1759,21 @@
         <v>108</v>
       </c>
       <c r="Q21" s="8"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="18"/>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="18"/>
-      <c r="AC21" s="18"/>
-      <c r="AD21" s="18"/>
-    </row>
-    <row r="22" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+    </row>
+    <row r="22" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>30</v>
       </c>
@@ -1804,21 +1808,21 @@
         <v>110</v>
       </c>
       <c r="Q22" s="8"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="18"/>
-      <c r="AA22" s="18"/>
-      <c r="AB22" s="18"/>
-      <c r="AC22" s="18"/>
-      <c r="AD22" s="18"/>
-    </row>
-    <row r="23" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="17"/>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+    </row>
+    <row r="23" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>30</v>
       </c>
@@ -1853,21 +1857,21 @@
         <v>92</v>
       </c>
       <c r="Q23" s="8"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
-      <c r="T23" s="18"/>
-      <c r="U23" s="18"/>
-      <c r="V23" s="18"/>
-      <c r="W23" s="18"/>
-      <c r="X23" s="18"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="18"/>
-      <c r="AA23" s="18"/>
-      <c r="AB23" s="18"/>
-      <c r="AC23" s="18"/>
-      <c r="AD23" s="18"/>
-    </row>
-    <row r="24" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Y23" s="17"/>
+      <c r="Z23" s="17"/>
+      <c r="AA23" s="17"/>
+      <c r="AB23" s="17"/>
+      <c r="AC23" s="17"/>
+      <c r="AD23" s="17"/>
+    </row>
+    <row r="24" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>30</v>
       </c>
@@ -1906,21 +1910,21 @@
         <v>376</v>
       </c>
       <c r="Q24" s="8"/>
-      <c r="R24" s="18"/>
-      <c r="S24" s="18"/>
-      <c r="T24" s="18"/>
-      <c r="U24" s="18"/>
-      <c r="V24" s="18"/>
-      <c r="W24" s="18"/>
-      <c r="X24" s="18"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="18"/>
-      <c r="AA24" s="18"/>
-      <c r="AB24" s="18"/>
-      <c r="AC24" s="18"/>
-      <c r="AD24" s="18"/>
-    </row>
-    <row r="25" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R24" s="17"/>
+      <c r="S24" s="17"/>
+      <c r="T24" s="17"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="17"/>
+      <c r="W24" s="17"/>
+      <c r="X24" s="17"/>
+      <c r="Y24" s="17"/>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="17"/>
+      <c r="AB24" s="17"/>
+      <c r="AC24" s="17"/>
+      <c r="AD24" s="17"/>
+    </row>
+    <row r="25" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>98</v>
       </c>
@@ -1958,7 +1962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>36</v>
       </c>
@@ -1995,21 +1999,21 @@
       <c r="Q26" s="8">
         <v>1</v>
       </c>
-      <c r="R26" s="18"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="18"/>
-      <c r="U26" s="18"/>
-      <c r="V26" s="18"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="18"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="18"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="18"/>
-      <c r="AC26" s="18"/>
-      <c r="AD26" s="18"/>
-    </row>
-    <row r="27" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="17"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="17"/>
+      <c r="W26" s="17"/>
+      <c r="X26" s="17"/>
+      <c r="Y26" s="17"/>
+      <c r="Z26" s="17"/>
+      <c r="AA26" s="17"/>
+      <c r="AB26" s="17"/>
+      <c r="AC26" s="17"/>
+      <c r="AD26" s="17"/>
+    </row>
+    <row r="27" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>94</v>
       </c>
@@ -2047,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>122</v>
       </c>
@@ -2084,21 +2088,21 @@
       <c r="Q28" s="8">
         <v>1</v>
       </c>
-      <c r="R28" s="18"/>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="18"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="18"/>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="18"/>
-      <c r="AA28" s="18"/>
-      <c r="AB28" s="18"/>
-      <c r="AC28" s="18"/>
-      <c r="AD28" s="18"/>
-    </row>
-    <row r="29" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R28" s="17"/>
+      <c r="S28" s="17"/>
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+    </row>
+    <row r="29" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>99</v>
       </c>
@@ -2136,7 +2140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>38</v>
       </c>
@@ -2173,21 +2177,21 @@
       <c r="Q30" s="8">
         <v>1</v>
       </c>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18"/>
-      <c r="W30" s="18"/>
-      <c r="X30" s="18"/>
-      <c r="Y30" s="18"/>
-      <c r="Z30" s="18"/>
-      <c r="AA30" s="18"/>
-      <c r="AB30" s="18"/>
-      <c r="AC30" s="18"/>
-      <c r="AD30" s="18"/>
-    </row>
-    <row r="31" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R30" s="17"/>
+      <c r="S30" s="17"/>
+      <c r="T30" s="17"/>
+      <c r="U30" s="17"/>
+      <c r="V30" s="17"/>
+      <c r="W30" s="17"/>
+      <c r="X30" s="17"/>
+      <c r="Y30" s="17"/>
+      <c r="Z30" s="17"/>
+      <c r="AA30" s="17"/>
+      <c r="AB30" s="17"/>
+      <c r="AC30" s="17"/>
+      <c r="AD30" s="17"/>
+    </row>
+    <row r="31" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>44</v>
       </c>
@@ -2227,7 +2231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>44</v>
       </c>
@@ -2263,7 +2267,7 @@
       </c>
       <c r="Q32" s="14"/>
     </row>
-    <row r="33" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>44</v>
       </c>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="Q33" s="14"/>
     </row>
-    <row r="34" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>44</v>
       </c>
@@ -2341,7 +2345,7 @@
       </c>
       <c r="Q34" s="14"/>
     </row>
-    <row r="35" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>44</v>
       </c>
@@ -2387,7 +2391,7 @@
       </c>
       <c r="Q35" s="14"/>
     </row>
-    <row r="36" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>44</v>
       </c>
@@ -2429,7 +2433,7 @@
       </c>
       <c r="Q36" s="14"/>
     </row>
-    <row r="37" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>40</v>
       </c>
@@ -2470,21 +2474,21 @@
       <c r="Q37" s="8">
         <v>3</v>
       </c>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18"/>
-      <c r="AB37" s="18"/>
-      <c r="AC37" s="18"/>
-      <c r="AD37" s="18"/>
-    </row>
-    <row r="38" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R37" s="17"/>
+      <c r="S37" s="17"/>
+      <c r="T37" s="17"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="17"/>
+      <c r="W37" s="17"/>
+      <c r="X37" s="17"/>
+      <c r="Y37" s="17"/>
+      <c r="Z37" s="17"/>
+      <c r="AA37" s="17"/>
+      <c r="AB37" s="17"/>
+      <c r="AC37" s="17"/>
+      <c r="AD37" s="17"/>
+    </row>
+    <row r="38" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>40</v>
       </c>
@@ -2519,21 +2523,21 @@
         <v>280</v>
       </c>
       <c r="Q38" s="8"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="18"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="18"/>
-      <c r="Z38" s="18"/>
-      <c r="AA38" s="18"/>
-      <c r="AB38" s="18"/>
-      <c r="AC38" s="18"/>
-      <c r="AD38" s="18"/>
-    </row>
-    <row r="39" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R38" s="17"/>
+      <c r="S38" s="17"/>
+      <c r="T38" s="17"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="17"/>
+      <c r="W38" s="17"/>
+      <c r="X38" s="17"/>
+      <c r="Y38" s="17"/>
+      <c r="Z38" s="17"/>
+      <c r="AA38" s="17"/>
+      <c r="AB38" s="17"/>
+      <c r="AC38" s="17"/>
+      <c r="AD38" s="17"/>
+    </row>
+    <row r="39" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>40</v>
       </c>
@@ -2572,21 +2576,21 @@
         <v>396</v>
       </c>
       <c r="Q39" s="8"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="18"/>
-      <c r="T39" s="18"/>
-      <c r="U39" s="18"/>
-      <c r="V39" s="18"/>
-      <c r="W39" s="18"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="18"/>
-      <c r="Z39" s="18"/>
-      <c r="AA39" s="18"/>
-      <c r="AB39" s="18"/>
-      <c r="AC39" s="18"/>
-      <c r="AD39" s="18"/>
-    </row>
-    <row r="40" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R39" s="17"/>
+      <c r="S39" s="17"/>
+      <c r="T39" s="17"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="17"/>
+      <c r="W39" s="17"/>
+      <c r="X39" s="17"/>
+      <c r="Y39" s="17"/>
+      <c r="Z39" s="17"/>
+      <c r="AA39" s="17"/>
+      <c r="AB39" s="17"/>
+      <c r="AC39" s="17"/>
+      <c r="AD39" s="17"/>
+    </row>
+    <row r="40" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>50</v>
       </c>
@@ -2624,7 +2628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>52</v>
       </c>
@@ -2661,21 +2665,21 @@
       <c r="Q41" s="8">
         <v>1</v>
       </c>
-      <c r="R41" s="18"/>
-      <c r="S41" s="18"/>
-      <c r="T41" s="18"/>
-      <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="18"/>
-      <c r="X41" s="18"/>
-      <c r="Y41" s="18"/>
-      <c r="Z41" s="18"/>
-      <c r="AA41" s="18"/>
-      <c r="AB41" s="18"/>
-      <c r="AC41" s="18"/>
-      <c r="AD41" s="18"/>
-    </row>
-    <row r="42" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+      <c r="W41" s="17"/>
+      <c r="X41" s="17"/>
+      <c r="Y41" s="17"/>
+      <c r="Z41" s="17"/>
+      <c r="AA41" s="17"/>
+      <c r="AB41" s="17"/>
+      <c r="AC41" s="17"/>
+      <c r="AD41" s="17"/>
+    </row>
+    <row r="42" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>54</v>
       </c>
@@ -2723,7 +2727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>120</v>
       </c>
@@ -2760,21 +2764,21 @@
       <c r="Q43" s="8">
         <v>1</v>
       </c>
-      <c r="R43" s="18"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="18"/>
-      <c r="U43" s="18"/>
-      <c r="V43" s="18"/>
-      <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="18"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="18"/>
-      <c r="AB43" s="18"/>
-      <c r="AC43" s="18"/>
-      <c r="AD43" s="18"/>
-    </row>
-    <row r="44" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R43" s="17"/>
+      <c r="S43" s="17"/>
+      <c r="T43" s="17"/>
+      <c r="U43" s="17"/>
+      <c r="V43" s="17"/>
+      <c r="W43" s="17"/>
+      <c r="X43" s="17"/>
+      <c r="Y43" s="17"/>
+      <c r="Z43" s="17"/>
+      <c r="AA43" s="17"/>
+      <c r="AB43" s="17"/>
+      <c r="AC43" s="17"/>
+      <c r="AD43" s="17"/>
+    </row>
+    <row r="44" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>56</v>
       </c>
@@ -2818,7 +2822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>56</v>
       </c>
@@ -2854,7 +2858,7 @@
       </c>
       <c r="Q45" s="14"/>
     </row>
-    <row r="46" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>59</v>
       </c>
@@ -2891,21 +2895,21 @@
       <c r="Q46" s="8">
         <v>3</v>
       </c>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18"/>
-      <c r="U46" s="18"/>
-      <c r="V46" s="18"/>
-      <c r="W46" s="18"/>
-      <c r="X46" s="18"/>
-      <c r="Y46" s="18"/>
-      <c r="Z46" s="18"/>
-      <c r="AA46" s="18"/>
-      <c r="AB46" s="18"/>
-      <c r="AC46" s="18"/>
-      <c r="AD46" s="18"/>
-    </row>
-    <row r="47" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
+      <c r="Z46" s="17"/>
+      <c r="AA46" s="17"/>
+      <c r="AB46" s="17"/>
+      <c r="AC46" s="17"/>
+      <c r="AD46" s="17"/>
+    </row>
+    <row r="47" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>59</v>
       </c>
@@ -2940,21 +2944,21 @@
         <v>262</v>
       </c>
       <c r="Q47" s="8"/>
-      <c r="R47" s="18"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="18"/>
-      <c r="U47" s="18"/>
-      <c r="V47" s="18"/>
-      <c r="W47" s="18"/>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
-      <c r="Z47" s="18"/>
-      <c r="AA47" s="18"/>
-      <c r="AB47" s="18"/>
-      <c r="AC47" s="18"/>
-      <c r="AD47" s="18"/>
-    </row>
-    <row r="48" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R47" s="17"/>
+      <c r="S47" s="17"/>
+      <c r="T47" s="17"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="17"/>
+      <c r="W47" s="17"/>
+      <c r="X47" s="17"/>
+      <c r="Y47" s="17"/>
+      <c r="Z47" s="17"/>
+      <c r="AA47" s="17"/>
+      <c r="AB47" s="17"/>
+      <c r="AC47" s="17"/>
+      <c r="AD47" s="17"/>
+    </row>
+    <row r="48" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>59</v>
       </c>
@@ -2991,21 +2995,21 @@
         <v>524</v>
       </c>
       <c r="Q48" s="8"/>
-      <c r="R48" s="18"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="18"/>
-      <c r="U48" s="18"/>
-      <c r="V48" s="18"/>
-      <c r="W48" s="18"/>
-      <c r="X48" s="18"/>
-      <c r="Y48" s="18"/>
-      <c r="Z48" s="18"/>
-      <c r="AA48" s="18"/>
-      <c r="AB48" s="18"/>
-      <c r="AC48" s="18"/>
-      <c r="AD48" s="18"/>
-    </row>
-    <row r="49" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+      <c r="W48" s="17"/>
+      <c r="X48" s="17"/>
+      <c r="Y48" s="17"/>
+      <c r="Z48" s="17"/>
+      <c r="AA48" s="17"/>
+      <c r="AB48" s="17"/>
+      <c r="AC48" s="17"/>
+      <c r="AD48" s="17"/>
+    </row>
+    <row r="49" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>63</v>
       </c>
@@ -3045,7 +3049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>65</v>
       </c>
@@ -3084,21 +3088,21 @@
       <c r="Q50" s="8">
         <v>4</v>
       </c>
-      <c r="R50" s="18"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="18"/>
-      <c r="U50" s="18"/>
-      <c r="V50" s="18"/>
-      <c r="W50" s="18"/>
-      <c r="X50" s="18"/>
-      <c r="Y50" s="18"/>
-      <c r="Z50" s="18"/>
-      <c r="AA50" s="18"/>
-      <c r="AB50" s="18"/>
-      <c r="AC50" s="18"/>
-      <c r="AD50" s="18"/>
-    </row>
-    <row r="51" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R50" s="17"/>
+      <c r="S50" s="17"/>
+      <c r="T50" s="17"/>
+      <c r="U50" s="17"/>
+      <c r="V50" s="17"/>
+      <c r="W50" s="17"/>
+      <c r="X50" s="17"/>
+      <c r="Y50" s="17"/>
+      <c r="Z50" s="17"/>
+      <c r="AA50" s="17"/>
+      <c r="AB50" s="17"/>
+      <c r="AC50" s="17"/>
+      <c r="AD50" s="17"/>
+    </row>
+    <row r="51" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>65</v>
       </c>
@@ -3133,21 +3137,21 @@
         <v>304</v>
       </c>
       <c r="Q51" s="8"/>
-      <c r="R51" s="18"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="18"/>
-      <c r="U51" s="18"/>
-      <c r="V51" s="18"/>
-      <c r="W51" s="18"/>
-      <c r="X51" s="18"/>
-      <c r="Y51" s="18"/>
-      <c r="Z51" s="18"/>
-      <c r="AA51" s="18"/>
-      <c r="AB51" s="18"/>
-      <c r="AC51" s="18"/>
-      <c r="AD51" s="18"/>
-    </row>
-    <row r="52" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R51" s="17"/>
+      <c r="S51" s="17"/>
+      <c r="T51" s="17"/>
+      <c r="U51" s="17"/>
+      <c r="V51" s="17"/>
+      <c r="W51" s="17"/>
+      <c r="X51" s="17"/>
+      <c r="Y51" s="17"/>
+      <c r="Z51" s="17"/>
+      <c r="AA51" s="17"/>
+      <c r="AB51" s="17"/>
+      <c r="AC51" s="17"/>
+      <c r="AD51" s="17"/>
+    </row>
+    <row r="52" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>65</v>
       </c>
@@ -3182,21 +3186,21 @@
         <v>254</v>
       </c>
       <c r="Q52" s="8"/>
-      <c r="R52" s="18"/>
-      <c r="S52" s="18"/>
-      <c r="T52" s="18"/>
-      <c r="U52" s="18"/>
-      <c r="V52" s="18"/>
-      <c r="W52" s="18"/>
-      <c r="X52" s="18"/>
-      <c r="Y52" s="18"/>
-      <c r="Z52" s="18"/>
-      <c r="AA52" s="18"/>
-      <c r="AB52" s="18"/>
-      <c r="AC52" s="18"/>
-      <c r="AD52" s="18"/>
-    </row>
-    <row r="53" spans="1:30" s="19" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="17"/>
+      <c r="W52" s="17"/>
+      <c r="X52" s="17"/>
+      <c r="Y52" s="17"/>
+      <c r="Z52" s="17"/>
+      <c r="AA52" s="17"/>
+      <c r="AB52" s="17"/>
+      <c r="AC52" s="17"/>
+      <c r="AD52" s="17"/>
+    </row>
+    <row r="53" spans="1:30" s="18" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>65</v>
       </c>
@@ -3231,21 +3235,21 @@
         <v>306</v>
       </c>
       <c r="Q53" s="8"/>
-      <c r="R53" s="18"/>
-      <c r="S53" s="18"/>
-      <c r="T53" s="18"/>
-      <c r="U53" s="18"/>
-      <c r="V53" s="18"/>
-      <c r="W53" s="18"/>
-      <c r="X53" s="18"/>
-      <c r="Y53" s="18"/>
-      <c r="Z53" s="18"/>
-      <c r="AA53" s="18"/>
-      <c r="AB53" s="18"/>
-      <c r="AC53" s="18"/>
-      <c r="AD53" s="18"/>
-    </row>
-    <row r="54" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R53" s="17"/>
+      <c r="S53" s="17"/>
+      <c r="T53" s="17"/>
+      <c r="U53" s="17"/>
+      <c r="V53" s="17"/>
+      <c r="W53" s="17"/>
+      <c r="X53" s="17"/>
+      <c r="Y53" s="17"/>
+      <c r="Z53" s="17"/>
+      <c r="AA53" s="17"/>
+      <c r="AB53" s="17"/>
+      <c r="AC53" s="17"/>
+      <c r="AD53" s="17"/>
+    </row>
+    <row r="54" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
         <v>70</v>
       </c>
@@ -3289,7 +3293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>70</v>
       </c>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="Q55" s="14"/>
     </row>
-    <row r="56" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
         <v>70</v>
       </c>
@@ -3361,7 +3365,7 @@
       </c>
       <c r="Q56" s="14"/>
     </row>
-    <row r="57" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>74</v>
       </c>
@@ -3398,21 +3402,21 @@
       <c r="Q57" s="8">
         <v>3</v>
       </c>
-      <c r="R57" s="18"/>
-      <c r="S57" s="18"/>
-      <c r="T57" s="18"/>
-      <c r="U57" s="18"/>
-      <c r="V57" s="18"/>
-      <c r="W57" s="18"/>
-      <c r="X57" s="18"/>
-      <c r="Y57" s="18"/>
-      <c r="Z57" s="18"/>
-      <c r="AA57" s="18"/>
-      <c r="AB57" s="18"/>
-      <c r="AC57" s="18"/>
-      <c r="AD57" s="18"/>
-    </row>
-    <row r="58" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R57" s="17"/>
+      <c r="S57" s="17"/>
+      <c r="T57" s="17"/>
+      <c r="U57" s="17"/>
+      <c r="V57" s="17"/>
+      <c r="W57" s="17"/>
+      <c r="X57" s="17"/>
+      <c r="Y57" s="17"/>
+      <c r="Z57" s="17"/>
+      <c r="AA57" s="17"/>
+      <c r="AB57" s="17"/>
+      <c r="AC57" s="17"/>
+      <c r="AD57" s="17"/>
+    </row>
+    <row r="58" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>74</v>
       </c>
@@ -3447,21 +3451,21 @@
         <v>106</v>
       </c>
       <c r="Q58" s="8"/>
-      <c r="R58" s="18"/>
-      <c r="S58" s="18"/>
-      <c r="T58" s="18"/>
-      <c r="U58" s="18"/>
-      <c r="V58" s="18"/>
-      <c r="W58" s="18"/>
-      <c r="X58" s="18"/>
-      <c r="Y58" s="18"/>
-      <c r="Z58" s="18"/>
-      <c r="AA58" s="18"/>
-      <c r="AB58" s="18"/>
-      <c r="AC58" s="18"/>
-      <c r="AD58" s="18"/>
-    </row>
-    <row r="59" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
+      <c r="W58" s="17"/>
+      <c r="X58" s="17"/>
+      <c r="Y58" s="17"/>
+      <c r="Z58" s="17"/>
+      <c r="AA58" s="17"/>
+      <c r="AB58" s="17"/>
+      <c r="AC58" s="17"/>
+      <c r="AD58" s="17"/>
+    </row>
+    <row r="59" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>74</v>
       </c>
@@ -3496,21 +3500,21 @@
         <v>90</v>
       </c>
       <c r="Q59" s="8"/>
-      <c r="R59" s="18"/>
-      <c r="S59" s="18"/>
-      <c r="T59" s="18"/>
-      <c r="U59" s="18"/>
-      <c r="V59" s="18"/>
-      <c r="W59" s="18"/>
-      <c r="X59" s="18"/>
-      <c r="Y59" s="18"/>
-      <c r="Z59" s="18"/>
-      <c r="AA59" s="18"/>
-      <c r="AB59" s="18"/>
-      <c r="AC59" s="18"/>
-      <c r="AD59" s="18"/>
-    </row>
-    <row r="60" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R59" s="17"/>
+      <c r="S59" s="17"/>
+      <c r="T59" s="17"/>
+      <c r="U59" s="17"/>
+      <c r="V59" s="17"/>
+      <c r="W59" s="17"/>
+      <c r="X59" s="17"/>
+      <c r="Y59" s="17"/>
+      <c r="Z59" s="17"/>
+      <c r="AA59" s="17"/>
+      <c r="AB59" s="17"/>
+      <c r="AC59" s="17"/>
+      <c r="AD59" s="17"/>
+    </row>
+    <row r="60" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
         <v>78</v>
       </c>
@@ -3554,7 +3558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
         <v>78</v>
       </c>
@@ -3592,7 +3596,7 @@
       </c>
       <c r="Q61" s="14"/>
     </row>
-    <row r="62" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
         <v>78</v>
       </c>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="Q62" s="14"/>
     </row>
-    <row r="63" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
         <v>81</v>
       </c>
@@ -3671,21 +3675,21 @@
       <c r="Q63" s="8">
         <v>1</v>
       </c>
-      <c r="R63" s="18"/>
-      <c r="S63" s="18"/>
-      <c r="T63" s="18"/>
-      <c r="U63" s="18"/>
-      <c r="V63" s="18"/>
-      <c r="W63" s="18"/>
-      <c r="X63" s="18"/>
-      <c r="Y63" s="18"/>
-      <c r="Z63" s="18"/>
-      <c r="AA63" s="18"/>
-      <c r="AB63" s="18"/>
-      <c r="AC63" s="18"/>
-      <c r="AD63" s="18"/>
-    </row>
-    <row r="64" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R63" s="17"/>
+      <c r="S63" s="17"/>
+      <c r="T63" s="17"/>
+      <c r="U63" s="17"/>
+      <c r="V63" s="17"/>
+      <c r="W63" s="17"/>
+      <c r="X63" s="17"/>
+      <c r="Y63" s="17"/>
+      <c r="Z63" s="17"/>
+      <c r="AA63" s="17"/>
+      <c r="AB63" s="17"/>
+      <c r="AC63" s="17"/>
+      <c r="AD63" s="17"/>
+    </row>
+    <row r="64" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
         <v>83</v>
       </c>
@@ -3725,7 +3729,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
         <v>83</v>
       </c>
@@ -3761,7 +3765,7 @@
       </c>
       <c r="Q65" s="14"/>
     </row>
-    <row r="66" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
         <v>83</v>
       </c>
@@ -3797,7 +3801,7 @@
       </c>
       <c r="Q66" s="14"/>
     </row>
-    <row r="67" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>87</v>
       </c>
@@ -3837,19 +3841,19 @@
       <c r="Q67" s="8">
         <v>1</v>
       </c>
-      <c r="R67" s="18"/>
-      <c r="S67" s="18"/>
-      <c r="T67" s="18"/>
-      <c r="U67" s="18"/>
-      <c r="V67" s="18"/>
-      <c r="W67" s="18"/>
-      <c r="X67" s="18"/>
-      <c r="Y67" s="18"/>
-      <c r="Z67" s="18"/>
-      <c r="AA67" s="18"/>
-      <c r="AB67" s="18"/>
-      <c r="AC67" s="18"/>
-      <c r="AD67" s="18"/>
+      <c r="R67" s="17"/>
+      <c r="S67" s="17"/>
+      <c r="T67" s="17"/>
+      <c r="U67" s="17"/>
+      <c r="V67" s="17"/>
+      <c r="W67" s="17"/>
+      <c r="X67" s="17"/>
+      <c r="Y67" s="17"/>
+      <c r="Z67" s="17"/>
+      <c r="AA67" s="17"/>
+      <c r="AB67" s="17"/>
+      <c r="AC67" s="17"/>
+      <c r="AD67" s="17"/>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
@@ -5200,7 +5204,7 @@
       </c>
       <c r="Q97" s="8"/>
     </row>
-    <row r="98" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="14" t="s">
         <v>131</v>
       </c>
@@ -5262,7 +5266,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="99" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
         <v>30</v>
       </c>
@@ -5324,7 +5328,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="100" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
         <v>30</v>
       </c>
@@ -5383,7 +5387,7 @@
       </c>
       <c r="Q100" s="8"/>
     </row>
-    <row r="101" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
         <v>30</v>
       </c>
@@ -5442,7 +5446,7 @@
       </c>
       <c r="Q101" s="8"/>
     </row>
-    <row r="102" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
         <v>30</v>
       </c>
@@ -5501,7 +5505,7 @@
       </c>
       <c r="Q102" s="8"/>
     </row>
-    <row r="103" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>30</v>
       </c>
@@ -5560,7 +5564,7 @@
       </c>
       <c r="Q103" s="8"/>
     </row>
-    <row r="104" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="14" t="s">
         <v>98</v>
       </c>
@@ -5622,7 +5626,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="105" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>36</v>
       </c>
@@ -5683,21 +5687,21 @@
         <f t="shared" si="24"/>
         <v>726</v>
       </c>
-      <c r="R105" s="18"/>
-      <c r="S105" s="18"/>
-      <c r="T105" s="18"/>
-      <c r="U105" s="18"/>
-      <c r="V105" s="18"/>
-      <c r="W105" s="18"/>
-      <c r="X105" s="18"/>
-      <c r="Y105" s="18"/>
-      <c r="Z105" s="18"/>
-      <c r="AA105" s="18"/>
-      <c r="AB105" s="18"/>
-      <c r="AC105" s="18"/>
-      <c r="AD105" s="18"/>
-    </row>
-    <row r="106" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R105" s="17"/>
+      <c r="S105" s="17"/>
+      <c r="T105" s="17"/>
+      <c r="U105" s="17"/>
+      <c r="V105" s="17"/>
+      <c r="W105" s="17"/>
+      <c r="X105" s="17"/>
+      <c r="Y105" s="17"/>
+      <c r="Z105" s="17"/>
+      <c r="AA105" s="17"/>
+      <c r="AB105" s="17"/>
+      <c r="AC105" s="17"/>
+      <c r="AD105" s="17"/>
+    </row>
+    <row r="106" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="14" t="s">
         <v>96</v>
       </c>
@@ -5759,7 +5763,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="107" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>122</v>
       </c>
@@ -5811,21 +5815,21 @@
         <f>P107</f>
         <v>348</v>
       </c>
-      <c r="R107" s="18"/>
-      <c r="S107" s="18"/>
-      <c r="T107" s="18"/>
-      <c r="U107" s="18"/>
-      <c r="V107" s="18"/>
-      <c r="W107" s="18"/>
-      <c r="X107" s="18"/>
-      <c r="Y107" s="18"/>
-      <c r="Z107" s="18"/>
-      <c r="AA107" s="18"/>
-      <c r="AB107" s="18"/>
-      <c r="AC107" s="18"/>
-      <c r="AD107" s="18"/>
-    </row>
-    <row r="108" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R107" s="17"/>
+      <c r="S107" s="17"/>
+      <c r="T107" s="17"/>
+      <c r="U107" s="17"/>
+      <c r="V107" s="17"/>
+      <c r="W107" s="17"/>
+      <c r="X107" s="17"/>
+      <c r="Y107" s="17"/>
+      <c r="Z107" s="17"/>
+      <c r="AA107" s="17"/>
+      <c r="AB107" s="17"/>
+      <c r="AC107" s="17"/>
+      <c r="AD107" s="17"/>
+    </row>
+    <row r="108" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="14" t="s">
         <v>99</v>
       </c>
@@ -5887,7 +5891,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="109" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>38</v>
       </c>
@@ -5948,21 +5952,21 @@
         <f t="shared" si="24"/>
         <v>516</v>
       </c>
-      <c r="R109" s="18"/>
-      <c r="S109" s="18"/>
-      <c r="T109" s="18"/>
-      <c r="U109" s="18"/>
-      <c r="V109" s="18"/>
-      <c r="W109" s="18"/>
-      <c r="X109" s="18"/>
-      <c r="Y109" s="18"/>
-      <c r="Z109" s="18"/>
-      <c r="AA109" s="18"/>
-      <c r="AB109" s="18"/>
-      <c r="AC109" s="18"/>
-      <c r="AD109" s="18"/>
-    </row>
-    <row r="110" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R109" s="17"/>
+      <c r="S109" s="17"/>
+      <c r="T109" s="17"/>
+      <c r="U109" s="17"/>
+      <c r="V109" s="17"/>
+      <c r="W109" s="17"/>
+      <c r="X109" s="17"/>
+      <c r="Y109" s="17"/>
+      <c r="Z109" s="17"/>
+      <c r="AA109" s="17"/>
+      <c r="AB109" s="17"/>
+      <c r="AC109" s="17"/>
+      <c r="AD109" s="17"/>
+    </row>
+    <row r="110" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="14" t="s">
         <v>44</v>
       </c>
@@ -6024,7 +6028,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="111" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="14" t="s">
         <v>44</v>
       </c>
@@ -6083,7 +6087,7 @@
       </c>
       <c r="Q111" s="14"/>
     </row>
-    <row r="112" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
         <v>44</v>
       </c>
@@ -6134,7 +6138,7 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="N112" s="20"/>
+      <c r="N112" s="19"/>
       <c r="O112" s="14"/>
       <c r="P112" s="14">
         <f t="shared" si="28"/>
@@ -6142,7 +6146,7 @@
       </c>
       <c r="Q112" s="14"/>
     </row>
-    <row r="113" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="14" t="s">
         <v>44</v>
       </c>
@@ -6201,7 +6205,7 @@
       </c>
       <c r="Q113" s="14"/>
     </row>
-    <row r="114" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="14" t="s">
         <v>44</v>
       </c>
@@ -6260,7 +6264,7 @@
       </c>
       <c r="Q114" s="14"/>
     </row>
-    <row r="115" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="14" t="s">
         <v>44</v>
       </c>
@@ -6319,7 +6323,7 @@
       </c>
       <c r="Q115" s="14"/>
     </row>
-    <row r="116" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>40</v>
       </c>
@@ -6380,21 +6384,21 @@
         <f>SUM(P116:P118)</f>
         <v>1150</v>
       </c>
-      <c r="R116" s="18"/>
-      <c r="S116" s="18"/>
-      <c r="T116" s="18"/>
-      <c r="U116" s="18"/>
-      <c r="V116" s="18"/>
-      <c r="W116" s="18"/>
-      <c r="X116" s="18"/>
-      <c r="Y116" s="18"/>
-      <c r="Z116" s="18"/>
-      <c r="AA116" s="18"/>
-      <c r="AB116" s="18"/>
-      <c r="AC116" s="18"/>
-      <c r="AD116" s="18"/>
-    </row>
-    <row r="117" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R116" s="17"/>
+      <c r="S116" s="17"/>
+      <c r="T116" s="17"/>
+      <c r="U116" s="17"/>
+      <c r="V116" s="17"/>
+      <c r="W116" s="17"/>
+      <c r="X116" s="17"/>
+      <c r="Y116" s="17"/>
+      <c r="Z116" s="17"/>
+      <c r="AA116" s="17"/>
+      <c r="AB116" s="17"/>
+      <c r="AC116" s="17"/>
+      <c r="AD116" s="17"/>
+    </row>
+    <row r="117" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>40</v>
       </c>
@@ -6452,21 +6456,21 @@
         <v>280</v>
       </c>
       <c r="Q117" s="8"/>
-      <c r="R117" s="18"/>
-      <c r="S117" s="18"/>
-      <c r="T117" s="18"/>
-      <c r="U117" s="18"/>
-      <c r="V117" s="18"/>
-      <c r="W117" s="18"/>
-      <c r="X117" s="18"/>
-      <c r="Y117" s="18"/>
-      <c r="Z117" s="18"/>
-      <c r="AA117" s="18"/>
-      <c r="AB117" s="18"/>
-      <c r="AC117" s="18"/>
-      <c r="AD117" s="18"/>
-    </row>
-    <row r="118" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R117" s="17"/>
+      <c r="S117" s="17"/>
+      <c r="T117" s="17"/>
+      <c r="U117" s="17"/>
+      <c r="V117" s="17"/>
+      <c r="W117" s="17"/>
+      <c r="X117" s="17"/>
+      <c r="Y117" s="17"/>
+      <c r="Z117" s="17"/>
+      <c r="AA117" s="17"/>
+      <c r="AB117" s="17"/>
+      <c r="AC117" s="17"/>
+      <c r="AD117" s="17"/>
+    </row>
+    <row r="118" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>40</v>
       </c>
@@ -6524,21 +6528,21 @@
         <v>396</v>
       </c>
       <c r="Q118" s="8"/>
-      <c r="R118" s="18"/>
-      <c r="S118" s="18"/>
-      <c r="T118" s="18"/>
-      <c r="U118" s="18"/>
-      <c r="V118" s="18"/>
-      <c r="W118" s="18"/>
-      <c r="X118" s="18"/>
-      <c r="Y118" s="18"/>
-      <c r="Z118" s="18"/>
-      <c r="AA118" s="18"/>
-      <c r="AB118" s="18"/>
-      <c r="AC118" s="18"/>
-      <c r="AD118" s="18"/>
-    </row>
-    <row r="119" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R118" s="17"/>
+      <c r="S118" s="17"/>
+      <c r="T118" s="17"/>
+      <c r="U118" s="17"/>
+      <c r="V118" s="17"/>
+      <c r="W118" s="17"/>
+      <c r="X118" s="17"/>
+      <c r="Y118" s="17"/>
+      <c r="Z118" s="17"/>
+      <c r="AA118" s="17"/>
+      <c r="AB118" s="17"/>
+      <c r="AC118" s="17"/>
+      <c r="AD118" s="17"/>
+    </row>
+    <row r="119" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="14" t="s">
         <v>50</v>
       </c>
@@ -6600,7 +6604,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="120" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>52</v>
       </c>
@@ -6661,21 +6665,21 @@
         <f>P120</f>
         <v>282</v>
       </c>
-      <c r="R120" s="18"/>
-      <c r="S120" s="18"/>
-      <c r="T120" s="18"/>
-      <c r="U120" s="18"/>
-      <c r="V120" s="18"/>
-      <c r="W120" s="18"/>
-      <c r="X120" s="18"/>
-      <c r="Y120" s="18"/>
-      <c r="Z120" s="18"/>
-      <c r="AA120" s="18"/>
-      <c r="AB120" s="18"/>
-      <c r="AC120" s="18"/>
-      <c r="AD120" s="18"/>
-    </row>
-    <row r="121" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R120" s="17"/>
+      <c r="S120" s="17"/>
+      <c r="T120" s="17"/>
+      <c r="U120" s="17"/>
+      <c r="V120" s="17"/>
+      <c r="W120" s="17"/>
+      <c r="X120" s="17"/>
+      <c r="Y120" s="17"/>
+      <c r="Z120" s="17"/>
+      <c r="AA120" s="17"/>
+      <c r="AB120" s="17"/>
+      <c r="AC120" s="17"/>
+      <c r="AD120" s="17"/>
+    </row>
+    <row r="121" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="14" t="s">
         <v>54</v>
       </c>
@@ -6737,7 +6741,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="122" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>120</v>
       </c>
@@ -6798,21 +6802,21 @@
         <f>P122</f>
         <v>2088</v>
       </c>
-      <c r="R122" s="18"/>
-      <c r="S122" s="18"/>
-      <c r="T122" s="18"/>
-      <c r="U122" s="18"/>
-      <c r="V122" s="18"/>
-      <c r="W122" s="18"/>
-      <c r="X122" s="18"/>
-      <c r="Y122" s="18"/>
-      <c r="Z122" s="18"/>
-      <c r="AA122" s="18"/>
-      <c r="AB122" s="18"/>
-      <c r="AC122" s="18"/>
-      <c r="AD122" s="18"/>
-    </row>
-    <row r="123" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R122" s="17"/>
+      <c r="S122" s="17"/>
+      <c r="T122" s="17"/>
+      <c r="U122" s="17"/>
+      <c r="V122" s="17"/>
+      <c r="W122" s="17"/>
+      <c r="X122" s="17"/>
+      <c r="Y122" s="17"/>
+      <c r="Z122" s="17"/>
+      <c r="AA122" s="17"/>
+      <c r="AB122" s="17"/>
+      <c r="AC122" s="17"/>
+      <c r="AD122" s="17"/>
+    </row>
+    <row r="123" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="14" t="s">
         <v>56</v>
       </c>
@@ -6874,7 +6878,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="124" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="14" t="s">
         <v>56</v>
       </c>
@@ -6933,7 +6937,7 @@
       </c>
       <c r="Q124" s="14"/>
     </row>
-    <row r="125" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>59</v>
       </c>
@@ -6994,21 +6998,21 @@
         <f>SUM(P125:P127)</f>
         <v>1050</v>
       </c>
-      <c r="R125" s="18"/>
-      <c r="S125" s="18"/>
-      <c r="T125" s="18"/>
-      <c r="U125" s="18"/>
-      <c r="V125" s="18"/>
-      <c r="W125" s="18"/>
-      <c r="X125" s="18"/>
-      <c r="Y125" s="18"/>
-      <c r="Z125" s="18"/>
-      <c r="AA125" s="18"/>
-      <c r="AB125" s="18"/>
-      <c r="AC125" s="18"/>
-      <c r="AD125" s="18"/>
-    </row>
-    <row r="126" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R125" s="17"/>
+      <c r="S125" s="17"/>
+      <c r="T125" s="17"/>
+      <c r="U125" s="17"/>
+      <c r="V125" s="17"/>
+      <c r="W125" s="17"/>
+      <c r="X125" s="17"/>
+      <c r="Y125" s="17"/>
+      <c r="Z125" s="17"/>
+      <c r="AA125" s="17"/>
+      <c r="AB125" s="17"/>
+      <c r="AC125" s="17"/>
+      <c r="AD125" s="17"/>
+    </row>
+    <row r="126" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>59</v>
       </c>
@@ -7066,21 +7070,21 @@
         <v>262</v>
       </c>
       <c r="Q126" s="8"/>
-      <c r="R126" s="18"/>
-      <c r="S126" s="18"/>
-      <c r="T126" s="18"/>
-      <c r="U126" s="18"/>
-      <c r="V126" s="18"/>
-      <c r="W126" s="18"/>
-      <c r="X126" s="18"/>
-      <c r="Y126" s="18"/>
-      <c r="Z126" s="18"/>
-      <c r="AA126" s="18"/>
-      <c r="AB126" s="18"/>
-      <c r="AC126" s="18"/>
-      <c r="AD126" s="18"/>
-    </row>
-    <row r="127" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R126" s="17"/>
+      <c r="S126" s="17"/>
+      <c r="T126" s="17"/>
+      <c r="U126" s="17"/>
+      <c r="V126" s="17"/>
+      <c r="W126" s="17"/>
+      <c r="X126" s="17"/>
+      <c r="Y126" s="17"/>
+      <c r="Z126" s="17"/>
+      <c r="AA126" s="17"/>
+      <c r="AB126" s="17"/>
+      <c r="AC126" s="17"/>
+      <c r="AD126" s="17"/>
+    </row>
+    <row r="127" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>59</v>
       </c>
@@ -7138,21 +7142,21 @@
         <v>524</v>
       </c>
       <c r="Q127" s="8"/>
-      <c r="R127" s="18"/>
-      <c r="S127" s="18"/>
-      <c r="T127" s="18"/>
-      <c r="U127" s="18"/>
-      <c r="V127" s="18"/>
-      <c r="W127" s="18"/>
-      <c r="X127" s="18"/>
-      <c r="Y127" s="18"/>
-      <c r="Z127" s="18"/>
-      <c r="AA127" s="18"/>
-      <c r="AB127" s="18"/>
-      <c r="AC127" s="18"/>
-      <c r="AD127" s="18"/>
-    </row>
-    <row r="128" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R127" s="17"/>
+      <c r="S127" s="17"/>
+      <c r="T127" s="17"/>
+      <c r="U127" s="17"/>
+      <c r="V127" s="17"/>
+      <c r="W127" s="17"/>
+      <c r="X127" s="17"/>
+      <c r="Y127" s="17"/>
+      <c r="Z127" s="17"/>
+      <c r="AA127" s="17"/>
+      <c r="AB127" s="17"/>
+      <c r="AC127" s="17"/>
+      <c r="AD127" s="17"/>
+    </row>
+    <row r="128" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="14" t="s">
         <v>63</v>
       </c>
@@ -7200,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="14">
-        <f t="shared" ref="M128:M159" si="37">C128*M49</f>
+        <f t="shared" ref="M128:M147" si="37">C128*M49</f>
         <v>0</v>
       </c>
       <c r="N128" s="14"/>
@@ -7214,7 +7218,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="129" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>65</v>
       </c>
@@ -7275,21 +7279,21 @@
         <f>SUM(P129:P132)</f>
         <v>1396</v>
       </c>
-      <c r="R129" s="18"/>
-      <c r="S129" s="18"/>
-      <c r="T129" s="18"/>
-      <c r="U129" s="18"/>
-      <c r="V129" s="18"/>
-      <c r="W129" s="18"/>
-      <c r="X129" s="18"/>
-      <c r="Y129" s="18"/>
-      <c r="Z129" s="18"/>
-      <c r="AA129" s="18"/>
-      <c r="AB129" s="18"/>
-      <c r="AC129" s="18"/>
-      <c r="AD129" s="18"/>
-    </row>
-    <row r="130" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R129" s="17"/>
+      <c r="S129" s="17"/>
+      <c r="T129" s="17"/>
+      <c r="U129" s="17"/>
+      <c r="V129" s="17"/>
+      <c r="W129" s="17"/>
+      <c r="X129" s="17"/>
+      <c r="Y129" s="17"/>
+      <c r="Z129" s="17"/>
+      <c r="AA129" s="17"/>
+      <c r="AB129" s="17"/>
+      <c r="AC129" s="17"/>
+      <c r="AD129" s="17"/>
+    </row>
+    <row r="130" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>65</v>
       </c>
@@ -7347,21 +7351,21 @@
         <v>304</v>
       </c>
       <c r="Q130" s="8"/>
-      <c r="R130" s="18"/>
-      <c r="S130" s="18"/>
-      <c r="T130" s="18"/>
-      <c r="U130" s="18"/>
-      <c r="V130" s="18"/>
-      <c r="W130" s="18"/>
-      <c r="X130" s="18"/>
-      <c r="Y130" s="18"/>
-      <c r="Z130" s="18"/>
-      <c r="AA130" s="18"/>
-      <c r="AB130" s="18"/>
-      <c r="AC130" s="18"/>
-      <c r="AD130" s="18"/>
-    </row>
-    <row r="131" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R130" s="17"/>
+      <c r="S130" s="17"/>
+      <c r="T130" s="17"/>
+      <c r="U130" s="17"/>
+      <c r="V130" s="17"/>
+      <c r="W130" s="17"/>
+      <c r="X130" s="17"/>
+      <c r="Y130" s="17"/>
+      <c r="Z130" s="17"/>
+      <c r="AA130" s="17"/>
+      <c r="AB130" s="17"/>
+      <c r="AC130" s="17"/>
+      <c r="AD130" s="17"/>
+    </row>
+    <row r="131" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>65</v>
       </c>
@@ -7419,21 +7423,21 @@
         <v>254</v>
       </c>
       <c r="Q131" s="8"/>
-      <c r="R131" s="18"/>
-      <c r="S131" s="18"/>
-      <c r="T131" s="18"/>
-      <c r="U131" s="18"/>
-      <c r="V131" s="18"/>
-      <c r="W131" s="18"/>
-      <c r="X131" s="18"/>
-      <c r="Y131" s="18"/>
-      <c r="Z131" s="18"/>
-      <c r="AA131" s="18"/>
-      <c r="AB131" s="18"/>
-      <c r="AC131" s="18"/>
-      <c r="AD131" s="18"/>
-    </row>
-    <row r="132" spans="1:30" s="19" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R131" s="17"/>
+      <c r="S131" s="17"/>
+      <c r="T131" s="17"/>
+      <c r="U131" s="17"/>
+      <c r="V131" s="17"/>
+      <c r="W131" s="17"/>
+      <c r="X131" s="17"/>
+      <c r="Y131" s="17"/>
+      <c r="Z131" s="17"/>
+      <c r="AA131" s="17"/>
+      <c r="AB131" s="17"/>
+      <c r="AC131" s="17"/>
+      <c r="AD131" s="17"/>
+    </row>
+    <row r="132" spans="1:30" s="18" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>65</v>
       </c>
@@ -7491,21 +7495,21 @@
         <v>306</v>
       </c>
       <c r="Q132" s="8"/>
-      <c r="R132" s="18"/>
-      <c r="S132" s="18"/>
-      <c r="T132" s="18"/>
-      <c r="U132" s="18"/>
-      <c r="V132" s="18"/>
-      <c r="W132" s="18"/>
-      <c r="X132" s="18"/>
-      <c r="Y132" s="18"/>
-      <c r="Z132" s="18"/>
-      <c r="AA132" s="18"/>
-      <c r="AB132" s="18"/>
-      <c r="AC132" s="18"/>
-      <c r="AD132" s="18"/>
-    </row>
-    <row r="133" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R132" s="17"/>
+      <c r="S132" s="17"/>
+      <c r="T132" s="17"/>
+      <c r="U132" s="17"/>
+      <c r="V132" s="17"/>
+      <c r="W132" s="17"/>
+      <c r="X132" s="17"/>
+      <c r="Y132" s="17"/>
+      <c r="Z132" s="17"/>
+      <c r="AA132" s="17"/>
+      <c r="AB132" s="17"/>
+      <c r="AC132" s="17"/>
+      <c r="AD132" s="17"/>
+    </row>
+    <row r="133" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="14" t="s">
         <v>70</v>
       </c>
@@ -7567,7 +7571,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="134" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="14" t="s">
         <v>70</v>
       </c>
@@ -7626,7 +7630,7 @@
       </c>
       <c r="Q134" s="14"/>
     </row>
-    <row r="135" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="14" t="s">
         <v>70</v>
       </c>
@@ -7685,7 +7689,7 @@
       </c>
       <c r="Q135" s="14"/>
     </row>
-    <row r="136" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>74</v>
       </c>
@@ -7746,21 +7750,21 @@
         <f>SUM(P136:P138)</f>
         <v>286</v>
       </c>
-      <c r="R136" s="18"/>
-      <c r="S136" s="18"/>
-      <c r="T136" s="18"/>
-      <c r="U136" s="18"/>
-      <c r="V136" s="18"/>
-      <c r="W136" s="18"/>
-      <c r="X136" s="18"/>
-      <c r="Y136" s="18"/>
-      <c r="Z136" s="18"/>
-      <c r="AA136" s="18"/>
-      <c r="AB136" s="18"/>
-      <c r="AC136" s="18"/>
-      <c r="AD136" s="18"/>
-    </row>
-    <row r="137" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R136" s="17"/>
+      <c r="S136" s="17"/>
+      <c r="T136" s="17"/>
+      <c r="U136" s="17"/>
+      <c r="V136" s="17"/>
+      <c r="W136" s="17"/>
+      <c r="X136" s="17"/>
+      <c r="Y136" s="17"/>
+      <c r="Z136" s="17"/>
+      <c r="AA136" s="17"/>
+      <c r="AB136" s="17"/>
+      <c r="AC136" s="17"/>
+      <c r="AD136" s="17"/>
+    </row>
+    <row r="137" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>74</v>
       </c>
@@ -7818,21 +7822,21 @@
         <v>106</v>
       </c>
       <c r="Q137" s="8"/>
-      <c r="R137" s="18"/>
-      <c r="S137" s="18"/>
-      <c r="T137" s="18"/>
-      <c r="U137" s="18"/>
-      <c r="V137" s="18"/>
-      <c r="W137" s="18"/>
-      <c r="X137" s="18"/>
-      <c r="Y137" s="18"/>
-      <c r="Z137" s="18"/>
-      <c r="AA137" s="18"/>
-      <c r="AB137" s="18"/>
-      <c r="AC137" s="18"/>
-      <c r="AD137" s="18"/>
-    </row>
-    <row r="138" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R137" s="17"/>
+      <c r="S137" s="17"/>
+      <c r="T137" s="17"/>
+      <c r="U137" s="17"/>
+      <c r="V137" s="17"/>
+      <c r="W137" s="17"/>
+      <c r="X137" s="17"/>
+      <c r="Y137" s="17"/>
+      <c r="Z137" s="17"/>
+      <c r="AA137" s="17"/>
+      <c r="AB137" s="17"/>
+      <c r="AC137" s="17"/>
+      <c r="AD137" s="17"/>
+    </row>
+    <row r="138" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>74</v>
       </c>
@@ -7890,21 +7894,21 @@
         <v>90</v>
       </c>
       <c r="Q138" s="8"/>
-      <c r="R138" s="18"/>
-      <c r="S138" s="18"/>
-      <c r="T138" s="18"/>
-      <c r="U138" s="18"/>
-      <c r="V138" s="18"/>
-      <c r="W138" s="18"/>
-      <c r="X138" s="18"/>
-      <c r="Y138" s="18"/>
-      <c r="Z138" s="18"/>
-      <c r="AA138" s="18"/>
-      <c r="AB138" s="18"/>
-      <c r="AC138" s="18"/>
-      <c r="AD138" s="18"/>
-    </row>
-    <row r="139" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R138" s="17"/>
+      <c r="S138" s="17"/>
+      <c r="T138" s="17"/>
+      <c r="U138" s="17"/>
+      <c r="V138" s="17"/>
+      <c r="W138" s="17"/>
+      <c r="X138" s="17"/>
+      <c r="Y138" s="17"/>
+      <c r="Z138" s="17"/>
+      <c r="AA138" s="17"/>
+      <c r="AB138" s="17"/>
+      <c r="AC138" s="17"/>
+      <c r="AD138" s="17"/>
+    </row>
+    <row r="139" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="14" t="s">
         <v>78</v>
       </c>
@@ -7966,7 +7970,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="140" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="14" t="s">
         <v>78</v>
       </c>
@@ -8025,7 +8029,7 @@
       </c>
       <c r="Q140" s="14"/>
     </row>
-    <row r="141" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="14" t="s">
         <v>78</v>
       </c>
@@ -8076,7 +8080,7 @@
       </c>
       <c r="Q141" s="14"/>
     </row>
-    <row r="142" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>81</v>
       </c>
@@ -8137,21 +8141,21 @@
         <f>SUM(P142)</f>
         <v>1240</v>
       </c>
-      <c r="R142" s="18"/>
-      <c r="S142" s="18"/>
-      <c r="T142" s="18"/>
-      <c r="U142" s="18"/>
-      <c r="V142" s="18"/>
-      <c r="W142" s="18"/>
-      <c r="X142" s="18"/>
-      <c r="Y142" s="18"/>
-      <c r="Z142" s="18"/>
-      <c r="AA142" s="18"/>
-      <c r="AB142" s="18"/>
-      <c r="AC142" s="18"/>
-      <c r="AD142" s="18"/>
-    </row>
-    <row r="143" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R142" s="17"/>
+      <c r="S142" s="17"/>
+      <c r="T142" s="17"/>
+      <c r="U142" s="17"/>
+      <c r="V142" s="17"/>
+      <c r="W142" s="17"/>
+      <c r="X142" s="17"/>
+      <c r="Y142" s="17"/>
+      <c r="Z142" s="17"/>
+      <c r="AA142" s="17"/>
+      <c r="AB142" s="17"/>
+      <c r="AC142" s="17"/>
+      <c r="AD142" s="17"/>
+    </row>
+    <row r="143" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="14" t="s">
         <v>83</v>
       </c>
@@ -8213,7 +8217,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="144" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="14" t="s">
         <v>83</v>
       </c>
@@ -8272,7 +8276,7 @@
       </c>
       <c r="Q144" s="14"/>
     </row>
-    <row r="145" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="14" t="s">
         <v>83</v>
       </c>
@@ -8280,7 +8284,7 @@
         <v>86</v>
       </c>
       <c r="C145" s="14">
-        <f t="shared" ref="C145:C176" si="46">C66*2</f>
+        <f t="shared" ref="C145:C147" si="46">C66*2</f>
         <v>116</v>
       </c>
       <c r="D145" s="14">
@@ -8331,7 +8335,7 @@
       </c>
       <c r="Q145" s="14"/>
     </row>
-    <row r="146" spans="1:30" s="19" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>87</v>
       </c>
@@ -8392,19 +8396,19 @@
         <f>P146</f>
         <v>138</v>
       </c>
-      <c r="R146" s="18"/>
-      <c r="S146" s="18"/>
-      <c r="T146" s="18"/>
-      <c r="U146" s="18"/>
-      <c r="V146" s="18"/>
-      <c r="W146" s="18"/>
-      <c r="X146" s="18"/>
-      <c r="Y146" s="18"/>
-      <c r="Z146" s="18"/>
-      <c r="AA146" s="18"/>
-      <c r="AB146" s="18"/>
-      <c r="AC146" s="18"/>
-      <c r="AD146" s="18"/>
+      <c r="R146" s="17"/>
+      <c r="S146" s="17"/>
+      <c r="T146" s="17"/>
+      <c r="U146" s="17"/>
+      <c r="V146" s="17"/>
+      <c r="W146" s="17"/>
+      <c r="X146" s="17"/>
+      <c r="Y146" s="17"/>
+      <c r="Z146" s="17"/>
+      <c r="AA146" s="17"/>
+      <c r="AB146" s="17"/>
+      <c r="AC146" s="17"/>
+      <c r="AD146" s="17"/>
     </row>
     <row r="147" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A147" s="14" t="s">
@@ -9187,16 +9191,16 @@
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="22"/>
-      <c r="B188" s="22">
+      <c r="A188" s="21"/>
+      <c r="B188" s="21">
         <f>SUM(B156:B187)</f>
         <v>67</v>
       </c>
-      <c r="C188" s="22">
+      <c r="C188" s="21">
         <f>SUM(C156:C187)</f>
         <v>167</v>
       </c>
-      <c r="D188" s="22">
+      <c r="D188" s="21">
         <f>SUM(D156:D187)</f>
         <v>25458</v>
       </c>
@@ -9209,15 +9213,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB3AEAB-3835-4342-9FF8-FBE02F12A238}">
-  <dimension ref="A1:I234"/>
+  <dimension ref="A1:J236"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" customWidth="1"/>
     <col min="2" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="10" width="9.77734375" customWidth="1"/>
+    <col min="3" max="11" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -9236,17 +9240,20 @@
       <c r="F1" s="7">
         <v>2025</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>104</v>
       </c>
@@ -9265,20 +9272,21 @@
       <c r="F2" s="8">
         <v>1</v>
       </c>
-      <c r="G2" s="8">
-        <f>SUM(D2:F2)</f>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8">
+        <f>SUM(D2:G2)</f>
         <v>3</v>
       </c>
-      <c r="H2" s="8">
-        <f t="shared" ref="H2:H5" si="0">C2*G2</f>
+      <c r="I2" s="8">
+        <f t="shared" ref="I2:I6" si="0">C2*H2</f>
         <v>360</v>
       </c>
-      <c r="I2" s="8">
-        <f t="shared" ref="I2:I5" si="1">2*H2</f>
+      <c r="J2" s="8">
+        <f t="shared" ref="J2:J6" si="1">2*I2</f>
         <v>720</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>112</v>
       </c>
@@ -9293,20 +9301,21 @@
       <c r="F3" s="6">
         <v>1</v>
       </c>
-      <c r="G3" s="6">
-        <f t="shared" ref="G3:G10" si="2">SUM(D3:F3)</f>
-        <v>1</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="G3" s="6"/>
+      <c r="H3" s="14">
+        <f t="shared" ref="H3:H11" si="2">SUM(D3:G3)</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
         <f t="shared" si="0"/>
         <v>234</v>
       </c>
-      <c r="I3" s="6">
+      <c r="J3" s="6">
         <f t="shared" si="1"/>
         <v>468</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
@@ -9323,801 +9332,883 @@
       <c r="F4" s="8">
         <v>1</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H4" s="8">
+      <c r="I4" s="8">
         <f t="shared" si="0"/>
         <v>284</v>
       </c>
-      <c r="I4" s="8">
+      <c r="J4" s="8">
         <f t="shared" si="1"/>
         <v>568</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="14">
+        <v>47</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14">
+        <v>1</v>
+      </c>
+      <c r="H5" s="14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I5" s="14">
+        <f>C5*H5</f>
+        <v>47</v>
+      </c>
+      <c r="J5" s="14">
+        <f t="shared" ref="J5:J11" si="3">2*I5</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C6" s="8">
         <v>182</v>
       </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H5" s="6">
+      <c r="I6" s="8">
         <f t="shared" si="0"/>
         <v>364</v>
       </c>
-      <c r="I5" s="6">
+      <c r="J6" s="8">
         <f t="shared" si="1"/>
         <v>728</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C7" s="14">
         <v>42</v>
       </c>
-      <c r="D6" s="8">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
+      <c r="D7" s="14">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="F7" s="14">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="H6" s="8">
-        <f>C6*G6</f>
-        <v>126</v>
-      </c>
-      <c r="I6" s="8">
-        <f t="shared" ref="I6:I10" si="3">2*H6</f>
-        <v>252</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="14">
+        <f>C7*H7</f>
+        <v>168</v>
+      </c>
+      <c r="J7" s="14">
+        <f t="shared" si="3"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B8" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C8" s="8">
         <v>131</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H7" s="6">
-        <f>C7*G7</f>
+      <c r="I8" s="8">
+        <f>C8*H8</f>
         <v>131</v>
       </c>
-      <c r="I7" s="6">
+      <c r="J8" s="8">
         <f t="shared" si="3"/>
         <v>262</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B9" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C9" s="14">
         <v>286</v>
       </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="D9" s="14">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="H8" s="8">
-        <f>C8*G8</f>
+      <c r="I9" s="14">
+        <f>C9*H9</f>
         <v>572</v>
       </c>
-      <c r="I8" s="8">
+      <c r="J9" s="14">
         <f t="shared" si="3"/>
         <v>1144</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C10" s="8">
         <v>133</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H9" s="6">
-        <f>C9*G9</f>
+      <c r="I10" s="8">
+        <f>C10*H10</f>
         <v>133</v>
       </c>
-      <c r="I9" s="6">
+      <c r="J10" s="8">
         <f t="shared" si="3"/>
         <v>266</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B11" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C11" s="14">
         <v>131</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="H10" s="8">
-        <f>C10*G10</f>
+      <c r="I11" s="14">
+        <f>C11*H11</f>
         <v>131</v>
       </c>
-      <c r="I10" s="8">
+      <c r="J11" s="14">
         <f t="shared" si="3"/>
         <v>262</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="9">
-        <f>SUM(D2:D13)</f>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9">
+        <f>SUM(D2:D14)</f>
         <v>5</v>
       </c>
-      <c r="E14" s="9">
-        <f>SUM(E2:E13)</f>
+      <c r="E15" s="9">
+        <f>SUM(E2:E14)</f>
         <v>3</v>
       </c>
-      <c r="F14" s="9">
-        <f>SUM(F2:F13)</f>
+      <c r="F15" s="9">
+        <f>SUM(F2:F14)</f>
         <v>8</v>
       </c>
-      <c r="G14" s="9">
-        <f>SUM(D14:F14)</f>
-        <v>16</v>
-      </c>
-      <c r="H14" s="9">
-        <f>SUM(H2:H10)</f>
-        <v>2335</v>
-      </c>
-      <c r="I14" s="9">
-        <f>SUM(I2:I10)</f>
-        <v>4670</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="G15" s="9">
+        <f>SUM(G2:G14)</f>
+        <v>2</v>
+      </c>
+      <c r="H15" s="9">
+        <f>SUM(D15:G15)</f>
+        <v>18</v>
+      </c>
+      <c r="I15" s="9">
+        <f>SUM(I2:I11)</f>
+        <v>2424</v>
+      </c>
+      <c r="J15" s="9">
+        <f>SUM(J2:J11)</f>
+        <v>4848</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8">
-        <f>H14/G14</f>
-        <v>145.9375</v>
-      </c>
-      <c r="I15" s="8">
-        <f>I14/G14</f>
-        <v>291.875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8">
+        <f>I15/H15</f>
+        <v>134.66666666666666</v>
+      </c>
+      <c r="J16" s="8">
+        <f>J15/H15</f>
+        <v>269.33333333333331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D19" s="7">
         <v>2023</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E19" s="7">
         <v>2024</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F19" s="7">
         <v>2025</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7" t="s">
+      <c r="G19" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B20" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="8">
-        <f t="shared" ref="C19:C27" si="4">2*C2</f>
+      <c r="C20" s="8">
+        <f>2*C2</f>
         <v>240</v>
       </c>
-      <c r="D19" s="8">
-        <f>D2*C19</f>
+      <c r="D20" s="8">
+        <f>D2*C20</f>
         <v>240</v>
       </c>
-      <c r="E19" s="8">
-        <f>E2*C19</f>
+      <c r="E20" s="8">
+        <f>E2*C20</f>
         <v>240</v>
       </c>
-      <c r="F19" s="8">
-        <f>F2*C19</f>
+      <c r="F20" s="8">
+        <f>F2*C20</f>
         <v>240</v>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8">
-        <f t="shared" ref="I19:I27" si="5">SUM(D19:F19)</f>
+      <c r="G20" s="8">
+        <f>G2*D20</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8">
+        <f>SUM(D20:G20)</f>
         <v>720</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B21" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="6">
-        <f t="shared" si="4"/>
+      <c r="C21" s="6">
+        <f>2*C3</f>
         <v>468</v>
       </c>
-      <c r="D20" s="6">
-        <f t="shared" ref="D20" si="6">D3*C20</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="6">
-        <f t="shared" ref="E20:E27" si="7">E3*C20</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
-        <f t="shared" ref="F20:F27" si="8">F3*C20</f>
+      <c r="D21" s="6">
+        <f t="shared" ref="D21" si="4">D3*C21</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="6">
+        <f>E3*C21</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
+        <f>F3*C21</f>
         <v>468</v>
       </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6">
-        <f t="shared" si="5"/>
+      <c r="G21" s="6">
+        <f>G3*D21</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="14">
+        <f t="shared" ref="J21:J29" si="5">SUM(D21:G21)</f>
         <v>468</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C21" s="8">
-        <f t="shared" si="4"/>
+      <c r="C22" s="8">
+        <f>2*C4</f>
         <v>284</v>
       </c>
-      <c r="D21" s="8">
-        <f t="shared" ref="D21" si="9">D4*C21</f>
+      <c r="D22" s="8">
+        <f t="shared" ref="D22" si="6">D4*C22</f>
         <v>284</v>
       </c>
-      <c r="E21" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="8"/>
+      <c r="E22" s="8">
+        <f>E4*C22</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="8">
+        <f>F4*C22</f>
         <v>284</v>
       </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8">
+      <c r="G22" s="8">
+        <f>G4*D22</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8">
         <f t="shared" si="5"/>
         <v>568</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="14">
+        <f>2*C5</f>
+        <v>94</v>
+      </c>
+      <c r="D23" s="14">
+        <f>2*D5</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <f>2*E5</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <f>2*F5</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <f>2*D23</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B24" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C22" s="6">
-        <f t="shared" si="4"/>
+      <c r="C24" s="8">
+        <f>2*C6</f>
         <v>364</v>
       </c>
-      <c r="D22" s="6">
-        <f t="shared" ref="D22" si="10">D5*C22</f>
+      <c r="D24" s="8">
+        <f t="shared" ref="D24" si="7">D6*C24</f>
         <v>364</v>
       </c>
-      <c r="E22" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
-        <f t="shared" si="8"/>
+      <c r="E24" s="8">
+        <f>E6*C24</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="8">
+        <f>F6*C24</f>
         <v>364</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6">
+      <c r="G24" s="8">
+        <f>G6*D24</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8">
         <f t="shared" si="5"/>
         <v>728</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B25" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="8">
-        <f t="shared" si="4"/>
+      <c r="C25" s="14">
+        <f>2*C7</f>
         <v>84</v>
       </c>
-      <c r="D23" s="8">
-        <f t="shared" ref="D23" si="11">D6*C23</f>
+      <c r="D25" s="14">
+        <f t="shared" ref="D25" si="8">D7*C25</f>
         <v>84</v>
       </c>
-      <c r="E23" s="8">
-        <f t="shared" si="7"/>
+      <c r="E25" s="14">
+        <f>E7*C25</f>
         <v>84</v>
       </c>
-      <c r="F23" s="8">
-        <f t="shared" si="8"/>
+      <c r="F25" s="14">
+        <f>F7*C25</f>
         <v>84</v>
       </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8">
+      <c r="G25" s="14">
+        <f>G7*D25</f>
+        <v>84</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14">
         <f t="shared" si="5"/>
-        <v>252</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B26" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="C24" s="6">
-        <f t="shared" si="4"/>
+      <c r="C26" s="8">
+        <f>2*C8</f>
         <v>262</v>
       </c>
-      <c r="D24" s="6">
-        <f t="shared" ref="D24" si="12">D7*C24</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="6">
-        <f t="shared" si="8"/>
+      <c r="D26" s="8">
+        <f t="shared" ref="D26" si="9">D8*C26</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <f>E8*C26</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <f>F8*C26</f>
         <v>262</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6">
+      <c r="G26" s="8">
+        <f>G8*D26</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8">
         <f t="shared" si="5"/>
         <v>262</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B27" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="8">
-        <f t="shared" si="4"/>
+      <c r="C27" s="14">
+        <f>2*C9</f>
         <v>572</v>
       </c>
-      <c r="D25" s="8">
-        <f t="shared" ref="D25" si="13">D8*C25</f>
+      <c r="D27" s="14">
+        <f t="shared" ref="D27" si="10">D9*C27</f>
         <v>572</v>
       </c>
-      <c r="E25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F25" s="8">
-        <f t="shared" si="8"/>
+      <c r="E27" s="14">
+        <f>E9*C27</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <f>F9*C27</f>
         <v>572</v>
       </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8">
+      <c r="G27" s="14">
+        <f>G9*D27</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14">
         <f t="shared" si="5"/>
         <v>1144</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B28" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="6">
-        <f t="shared" si="4"/>
+      <c r="C28" s="8">
+        <f>2*C10</f>
         <v>266</v>
       </c>
-      <c r="D26" s="6">
-        <f t="shared" ref="D26" si="14">D9*C26</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="6">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="6">
-        <f t="shared" si="8"/>
+      <c r="D28" s="8">
+        <f t="shared" ref="D28" si="11">D10*C28</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
+        <f>E10*C28</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="8">
+        <f>F10*C28</f>
         <v>266</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6">
+      <c r="G28" s="8">
+        <f>G10*D28</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8">
         <f t="shared" si="5"/>
         <v>266</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B29" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="8">
-        <f t="shared" si="4"/>
+      <c r="C29" s="14">
+        <f>2*C11</f>
         <v>262</v>
       </c>
-      <c r="D27" s="8">
-        <f t="shared" ref="D27" si="15">D10*C27</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="8">
-        <f t="shared" si="7"/>
+      <c r="D29" s="14">
+        <f t="shared" ref="D29" si="12">D11*C29</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="14">
+        <f>E11*C29</f>
         <v>262</v>
       </c>
-      <c r="F27" s="8">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8">
+      <c r="F29" s="14">
+        <f>F11*C29</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <f>G11*D29</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14">
         <f t="shared" si="5"/>
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9">
-        <f>SUM(D19:D27)</f>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9">
+        <f>SUM(D20:D29)</f>
         <v>1544</v>
       </c>
-      <c r="E29" s="9">
-        <f>SUM(E19:E27)</f>
+      <c r="E31" s="9">
+        <f>SUM(E20:E29)</f>
         <v>586</v>
       </c>
-      <c r="F29" s="9">
-        <f>SUM(F19:F27)</f>
+      <c r="F31" s="9">
+        <f>SUM(F20:F29)</f>
         <v>2540</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9">
-        <f>SUM(D29:F29)</f>
-        <v>4670</v>
-      </c>
-      <c r="I29" s="9">
-        <f>SUM(I19:I27)</f>
-        <v>4670</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="G60" t="s">
+      <c r="G31" s="9">
+        <f t="shared" ref="G31" si="13">SUM(G20:G29)</f>
+        <v>84</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9">
+        <f>SUM(D31:G31)</f>
+        <v>4754</v>
+      </c>
+      <c r="J31" s="9">
+        <f>SUM(J20:J29)</f>
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H62" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="4">
-        <f>SUM(I2:I59)</f>
-        <v>18971.875</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="I68">
-        <f>SUM(I2:I59)</f>
-        <v>18971.875</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D69">
-        <f>SUM(D2:D59)</f>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="4">
+        <f>SUM(J2:J61)</f>
+        <v>19473.333333333336</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J70">
+        <f>SUM(J2:J61)</f>
+        <v>19473.333333333336</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D71">
+        <f>SUM(D2:D61)</f>
         <v>5121</v>
       </c>
-      <c r="E69">
-        <f>SUM(E2:E59)</f>
+      <c r="E71">
+        <f>SUM(E2:E61)</f>
         <v>3202</v>
       </c>
-      <c r="F69">
-        <f>SUM(D69:E69)</f>
+      <c r="F71">
+        <f>SUM(D71:E71)</f>
         <v>8323</v>
       </c>
-      <c r="G69">
-        <f>SUM(G2:G59)</f>
-        <v>32</v>
-      </c>
-      <c r="H69">
-        <f>SUM(H2:H59)</f>
-        <v>9485.9375</v>
-      </c>
-      <c r="I69">
-        <f>2*H69</f>
-        <v>18971.875</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C72" s="1" t="s">
+      <c r="H71">
+        <f>SUM(H2:H61)</f>
+        <v>36</v>
+      </c>
+      <c r="I71">
+        <f>SUM(I2:I61)</f>
+        <v>9736.6666666666679</v>
+      </c>
+      <c r="J71">
+        <f>2*I71</f>
+        <v>19473.333333333336</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C74" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D74" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
         <v>13</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B75" t="s">
         <v>14</v>
       </c>
-      <c r="C73">
+      <c r="C75">
         <f>C2*2</f>
         <v>240</v>
       </c>
-      <c r="D73">
-        <f>C73*D2</f>
+      <c r="D75">
+        <f>C75*D2</f>
         <v>240</v>
       </c>
-      <c r="E73">
-        <f>C73*E2</f>
+      <c r="E75">
+        <f>C75*E2</f>
         <v>240</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>13</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B76" t="s">
         <v>15</v>
       </c>
-      <c r="C74">
+      <c r="C76">
         <f>C4*2</f>
         <v>284</v>
       </c>
-      <c r="D74">
-        <f>C74*D4</f>
+      <c r="D76">
+        <f>C76*D4</f>
         <v>284</v>
       </c>
-      <c r="E74">
-        <f>C74*E4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+      <c r="E76">
+        <f>C76*E4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>13</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B77" t="s">
         <v>16</v>
       </c>
-      <c r="C75">
-        <f>C5*2</f>
+      <c r="C77">
+        <f>C6*2</f>
         <v>364</v>
       </c>
-      <c r="D75">
-        <f>C75*D5</f>
+      <c r="D77">
+        <f>C77*D6</f>
         <v>364</v>
       </c>
-      <c r="E75">
-        <f>C75*E5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="E77">
+        <f>C77*E6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>17</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B78" t="s">
         <v>18</v>
       </c>
-      <c r="C76" t="e">
+      <c r="C78" t="e">
         <f>#REF!*2</f>
         <v>#REF!</v>
       </c>
-      <c r="D76" t="e">
-        <f>C76*#REF!</f>
+      <c r="D78" t="e">
+        <f>C78*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E76" t="e">
-        <f>C76*#REF!</f>
+      <c r="E78" t="e">
+        <f>C78*#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>19</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B79" t="s">
         <v>20</v>
       </c>
-      <c r="C77">
-        <f>C6*2</f>
+      <c r="C79">
+        <f>C7*2</f>
         <v>84</v>
       </c>
-      <c r="D77">
-        <f>C77*D6</f>
+      <c r="D79">
+        <f>C79*D7</f>
         <v>84</v>
       </c>
-      <c r="E77">
-        <f>C77*E6</f>
+      <c r="E79">
+        <f>C79*E7</f>
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>19</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B80" t="s">
         <v>21</v>
       </c>
-      <c r="C78">
-        <f>C8*2</f>
+      <c r="C80">
+        <f>C9*2</f>
         <v>572</v>
       </c>
-      <c r="D78">
-        <f>C78*D8</f>
+      <c r="D80">
+        <f>C80*D9</f>
         <v>572</v>
       </c>
-      <c r="E78">
-        <f>C78*E8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>22</v>
-      </c>
-      <c r="B79" t="s">
-        <v>23</v>
-      </c>
-      <c r="C79">
-        <f>C10*2</f>
-        <v>262</v>
-      </c>
-      <c r="D79">
-        <f>C79*D10</f>
-        <v>0</v>
-      </c>
-      <c r="E79">
-        <f>C79*E10</f>
-        <v>262</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>22</v>
-      </c>
-      <c r="B80" t="s">
-        <v>24</v>
-      </c>
-      <c r="C80" t="e">
-        <f>#REF!*2</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D80" t="e">
-        <f>C80*#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E80" t="e">
-        <f>C80*#REF!</f>
-        <v>#REF!</v>
+      <c r="E80">
+        <f>C80*E9</f>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -10125,19 +10216,19 @@
         <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C81">
-        <f t="shared" ref="C81:C92" si="16">C11*2</f>
-        <v>0</v>
+        <f>C11*2</f>
+        <v>262</v>
       </c>
       <c r="D81">
-        <f t="shared" ref="D81:D92" si="17">C81*D11</f>
+        <f>C81*D11</f>
         <v>0</v>
       </c>
       <c r="E81">
-        <f t="shared" ref="E81:E92" si="18">C81*E11</f>
-        <v>0</v>
+        <f>C81*E11</f>
+        <v>262</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -10145,19 +10236,19 @@
         <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
-      </c>
-      <c r="C82">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="D82">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="E82">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="C82" t="e">
+        <f>#REF!*2</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D82" t="e">
+        <f>C82*#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E82" t="e">
+        <f>C82*#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -10165,78 +10256,78 @@
         <v>22</v>
       </c>
       <c r="B83" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C83">
-        <f t="shared" si="16"/>
+        <f>C12*2</f>
         <v>0</v>
       </c>
       <c r="D83">
-        <f t="shared" si="17"/>
+        <f>C83*D12</f>
         <v>0</v>
       </c>
       <c r="E83">
-        <f t="shared" si="18"/>
+        <f>C83*E12</f>
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C84">
-        <f t="shared" si="16"/>
+        <f>C13*2</f>
         <v>0</v>
       </c>
       <c r="D84">
-        <f t="shared" si="17"/>
+        <f>C84*D13</f>
         <v>0</v>
       </c>
       <c r="E84">
-        <f t="shared" si="18"/>
+        <f>C84*E13</f>
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C85">
-        <f t="shared" si="16"/>
+        <f>C14*2</f>
         <v>0</v>
       </c>
       <c r="D85">
-        <f t="shared" si="17"/>
+        <f>C85*D14</f>
         <v>0</v>
       </c>
       <c r="E85">
-        <f t="shared" si="18"/>
+        <f>C85*E14</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B86" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C86">
-        <f t="shared" si="16"/>
+        <f>C15*2</f>
         <v>0</v>
       </c>
       <c r="D86">
-        <f t="shared" si="17"/>
+        <f>C86*D15</f>
         <v>0</v>
       </c>
       <c r="E86">
-        <f t="shared" si="18"/>
+        <f>C86*E15</f>
         <v>0</v>
       </c>
     </row>
@@ -10245,18 +10336,18 @@
         <v>30</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C87">
-        <f t="shared" si="16"/>
+        <f>C16*2</f>
         <v>0</v>
       </c>
       <c r="D87">
-        <f t="shared" si="17"/>
+        <f>C87*D16</f>
         <v>0</v>
       </c>
       <c r="E87">
-        <f t="shared" si="18"/>
+        <f>C87*E16</f>
         <v>0</v>
       </c>
     </row>
@@ -10265,19 +10356,19 @@
         <v>30</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
-      </c>
-      <c r="C88" t="e">
-        <f t="shared" si="16"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D88" t="e">
-        <f t="shared" si="17"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E88" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
+        <v>32</v>
+      </c>
+      <c r="C88">
+        <f>C17*2</f>
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <f>C88*D17</f>
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <f>C88*E17</f>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -10285,501 +10376,502 @@
         <v>30</v>
       </c>
       <c r="B89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C89">
-        <f t="shared" si="16"/>
-        <v>480</v>
+        <f>C18*2</f>
+        <v>0</v>
       </c>
       <c r="D89">
-        <f t="shared" si="17"/>
-        <v>115200</v>
+        <f>C89*D18</f>
+        <v>0</v>
       </c>
       <c r="E89">
-        <f t="shared" si="18"/>
-        <v>115200</v>
+        <f>C89*E18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>101</v>
-      </c>
-      <c r="C90">
-        <f t="shared" si="16"/>
-        <v>936</v>
-      </c>
-      <c r="D90">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="E90">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="C90" t="e">
+        <f>C19*2</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D90" t="e">
+        <f>C90*D19</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E90" t="e">
+        <f>C90*E19</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C91">
-        <f t="shared" si="16"/>
-        <v>568</v>
+        <f>C20*2</f>
+        <v>480</v>
       </c>
       <c r="D91">
-        <f t="shared" si="17"/>
-        <v>161312</v>
+        <f>C91*D20</f>
+        <v>115200</v>
       </c>
       <c r="E91">
-        <f t="shared" si="18"/>
-        <v>0</v>
+        <f>C91*E20</f>
+        <v>115200</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C92">
-        <f t="shared" si="16"/>
-        <v>728</v>
+        <f>C21*2</f>
+        <v>936</v>
       </c>
       <c r="D92">
-        <f t="shared" si="17"/>
-        <v>264992</v>
+        <f>C92*D21</f>
+        <v>0</v>
       </c>
       <c r="E92">
-        <f t="shared" si="18"/>
+        <f>C92*E21</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="C93">
-        <v>209</v>
-      </c>
-      <c r="D93" t="e">
-        <f>#REF!*D24</f>
-        <v>#REF!</v>
+        <f>C22*2</f>
+        <v>568</v>
+      </c>
+      <c r="D93">
+        <f>C93*D22</f>
+        <v>161312</v>
       </c>
       <c r="E93">
-        <f>C93*E24</f>
+        <f>C93*E22</f>
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C94">
-        <f t="shared" ref="C94:C129" si="19">C24*2</f>
-        <v>524</v>
+        <f t="shared" ref="C94" si="14">C24*2</f>
+        <v>728</v>
       </c>
       <c r="D94">
-        <f t="shared" ref="D94:D123" si="20">C94*D24</f>
-        <v>0</v>
+        <f t="shared" ref="D94" si="15">C94*D24</f>
+        <v>264992</v>
       </c>
       <c r="E94">
-        <f t="shared" ref="E94:E129" si="21">C94*E24</f>
+        <f t="shared" ref="E94" si="16">C94*E24</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="B95" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="C95">
-        <f t="shared" si="19"/>
-        <v>1144</v>
-      </c>
-      <c r="D95">
-        <f t="shared" si="20"/>
-        <v>654368</v>
+        <v>209</v>
+      </c>
+      <c r="D95" t="e">
+        <f>#REF!*D26</f>
+        <v>#REF!</v>
       </c>
       <c r="E95">
-        <f t="shared" si="21"/>
+        <f>C95*E26</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C96">
-        <f t="shared" si="19"/>
-        <v>532</v>
+        <f t="shared" ref="C96:C131" si="17">C26*2</f>
+        <v>524</v>
       </c>
       <c r="D96">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D96:D125" si="18">C96*D26</f>
         <v>0</v>
       </c>
       <c r="E96">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+        <f t="shared" ref="E96:E131" si="19">C96*E26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>40</v>
       </c>
       <c r="B97" t="s">
+        <v>41</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="17"/>
+        <v>1144</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="18"/>
+        <v>654368</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" t="s">
+        <v>42</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="17"/>
+        <v>532</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>40</v>
+      </c>
+      <c r="B99" t="s">
         <v>43</v>
       </c>
-      <c r="C97">
+      <c r="C99">
+        <f t="shared" si="17"/>
+        <v>524</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E99">
         <f t="shared" si="19"/>
-        <v>524</v>
-      </c>
-      <c r="D97">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E97">
-        <f t="shared" si="21"/>
         <v>137288</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>44</v>
-      </c>
-      <c r="B98" t="s">
-        <v>45</v>
-      </c>
-      <c r="C98">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D98">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E98">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>44</v>
-      </c>
-      <c r="B99" t="s">
-        <v>46</v>
-      </c>
-      <c r="C99">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D99">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E99">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>44</v>
       </c>
       <c r="B100" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C100">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E100">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D100">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E100">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>44</v>
       </c>
       <c r="B101" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C101">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E101">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D101">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E101">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>44</v>
       </c>
       <c r="B102" t="s">
+        <v>47</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>44</v>
+      </c>
+      <c r="B103" t="s">
+        <v>48</v>
+      </c>
+      <c r="C103">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>44</v>
+      </c>
+      <c r="B104" t="s">
         <v>49</v>
       </c>
-      <c r="C102">
+      <c r="C104">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E104">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D102">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E102">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
         <v>50</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B105" t="s">
         <v>51</v>
       </c>
-      <c r="C103">
+      <c r="C105">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E105">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D103">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E103">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
         <v>52</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B106" t="s">
         <v>53</v>
       </c>
-      <c r="C104">
+      <c r="C106">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E106">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D104">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E104">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>54</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B107" t="s">
         <v>55</v>
       </c>
-      <c r="C105">
+      <c r="C107">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E107">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D105">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E105">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
         <v>56</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B108" t="s">
         <v>57</v>
       </c>
-      <c r="C106">
+      <c r="C108">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E108">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D106">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E106">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
         <v>56</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B109" t="s">
         <v>58</v>
       </c>
-      <c r="C107">
+      <c r="C109">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E109">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="D107">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E107">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>59</v>
-      </c>
-      <c r="B108" t="s">
-        <v>60</v>
-      </c>
-      <c r="C108">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D108">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E108">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>59</v>
-      </c>
-      <c r="B109" t="s">
-        <v>61</v>
-      </c>
-      <c r="C109">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D109">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E109">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>59</v>
       </c>
       <c r="B110" t="s">
+        <v>60</v>
+      </c>
+      <c r="C110">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>59</v>
+      </c>
+      <c r="B111" t="s">
+        <v>61</v>
+      </c>
+      <c r="C111">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>59</v>
+      </c>
+      <c r="B112" t="s">
         <v>62</v>
       </c>
-      <c r="C110">
+      <c r="C112">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E112">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D110">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E110">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>63</v>
-      </c>
-      <c r="B111" t="s">
-        <v>64</v>
-      </c>
-      <c r="C111">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D111">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E111">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>65</v>
-      </c>
-      <c r="B112" t="s">
-        <v>66</v>
-      </c>
-      <c r="C112">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D112">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E112">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B113" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C113">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E113">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D113">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E113">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10788,18 +10880,18 @@
         <v>65</v>
       </c>
       <c r="B114" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C114">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E114">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D114">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E114">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10808,58 +10900,58 @@
         <v>65</v>
       </c>
       <c r="B115" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C115">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E115">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D115">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E115">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B116" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C116">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E116">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D116">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E116">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C117">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E117">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D117">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E117">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10868,58 +10960,58 @@
         <v>70</v>
       </c>
       <c r="B118" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C118">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E118">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D118">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E118">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B119" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C119">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E119">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D119">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E119">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C120">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E120">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D120">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E120">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10928,58 +11020,58 @@
         <v>74</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C121">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E121">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D121">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E121">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B122" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C122">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E122">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D122">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E122">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B123" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C123">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E123">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D123">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E123">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10988,69 +11080,69 @@
         <v>78</v>
       </c>
       <c r="B124" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C124">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E124">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-      <c r="E124">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B125" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C125">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="E125">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D125">
-        <f>C125*D55</f>
-        <v>0</v>
-      </c>
-      <c r="E125">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B126" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C126">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
         <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D126">
-        <f>C126*D56</f>
-        <v>0</v>
-      </c>
-      <c r="E126">
-        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B127" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C127">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="D127">
@@ -11058,7 +11150,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -11067,10 +11159,10 @@
         <v>83</v>
       </c>
       <c r="B128" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="D128">
@@ -11078,19 +11170,19 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B129" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C129">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="D129">
@@ -11098,105 +11190,129 @@
         <v>0</v>
       </c>
       <c r="E129">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>83</v>
+      </c>
+      <c r="B130" t="s">
+        <v>86</v>
+      </c>
+      <c r="C130">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <f>C130*D60</f>
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>87</v>
+      </c>
+      <c r="B131" t="s">
+        <v>88</v>
+      </c>
+      <c r="C131">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <f>C131*D61</f>
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D139" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D140" t="e">
+        <f t="shared" ref="D140:E140" si="20">SUM(D75:D131)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E140" t="e">
+        <f t="shared" si="20"/>
+        <v>#REF!</v>
+      </c>
+      <c r="H140" t="e">
+        <f>SUM(D140:E140)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I140" s="3" t="e">
+        <f>H140/H71</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D141" s="3" t="e">
+        <f t="shared" ref="D141:E141" si="21">D140/D71</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E141" s="3" t="e">
         <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D137" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D138" t="e">
-        <f t="shared" ref="D138:E138" si="22">SUM(D73:D129)</f>
         <v>#REF!</v>
       </c>
-      <c r="E138" t="e">
-        <f t="shared" si="22"/>
+      <c r="H141" s="3" t="e">
+        <f>H140/F71</f>
         <v>#REF!</v>
       </c>
-      <c r="G138" t="e">
-        <f>SUM(D138:E138)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H138" s="3" t="e">
-        <f>G138/G69</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="D139" s="3" t="e">
-        <f t="shared" ref="D139:E139" si="23">D138/D69</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E139" s="3" t="e">
-        <f t="shared" si="23"/>
-        <v>#REF!</v>
-      </c>
-      <c r="G139" s="3" t="e">
-        <f>G138/F69</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H139" t="s">
+      <c r="I141" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B209" s="1" t="s">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B211" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C209" s="1"/>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>13</v>
-      </c>
-      <c r="B210">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>17</v>
-      </c>
-      <c r="B211">
-        <v>1</v>
-      </c>
+      <c r="C211" s="1"/>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B212">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B213">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B214">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B215">
         <v>5</v>
@@ -11204,7 +11320,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -11212,47 +11328,47 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B217">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B218">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B219">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B220">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B221">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -11260,91 +11376,107 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B223">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="B224">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B225">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B226">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B227">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B229">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B230">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B231">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
+        <v>81</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>83</v>
+      </c>
+      <c r="B233">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
         <v>87</v>
       </c>
-      <c r="B232">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A234" s="1"/>
-      <c r="B234" s="1">
-        <f>SUM(B210:B232)</f>
+      <c r="B234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1">
+        <f>SUM(B212:B234)</f>
         <v>53</v>
       </c>
-      <c r="C234" s="1"/>
+      <c r="C236" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22368C8A-8607-4D06-8E45-C0925CBD1444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94FFF9F-AB9E-471B-A1D4-0EEACEB0E822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="876" windowWidth="23040" windowHeight="12804" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
   <sheets>
     <sheet name="pelipaikat" sheetId="1" r:id="rId1"/>
@@ -9392,18 +9392,20 @@
       <c r="F6" s="8">
         <v>1</v>
       </c>
-      <c r="G6" s="8"/>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
       <c r="H6" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="8">
         <f t="shared" si="0"/>
-        <v>364</v>
+        <v>546</v>
       </c>
       <c r="J6" s="8">
         <f t="shared" si="1"/>
-        <v>728</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -9577,19 +9579,19 @@
       </c>
       <c r="G15" s="9">
         <f>SUM(G2:G14)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="9">
         <f>SUM(D15:G15)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" s="9">
         <f>SUM(I2:I11)</f>
-        <v>2424</v>
+        <v>2606</v>
       </c>
       <c r="J15" s="9">
         <f>SUM(J2:J11)</f>
-        <v>4848</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -9605,11 +9607,11 @@
       <c r="H16" s="8"/>
       <c r="I16" s="8">
         <f>I15/H15</f>
-        <v>134.66666666666666</v>
+        <v>137.15789473684211</v>
       </c>
       <c r="J16" s="8">
         <f>J15/H15</f>
-        <v>269.33333333333331</v>
+        <v>274.31578947368422</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -9648,7 +9650,7 @@
         <v>106</v>
       </c>
       <c r="C20" s="8">
-        <f>2*C2</f>
+        <f t="shared" ref="C20:C29" si="4">2*C2</f>
         <v>240</v>
       </c>
       <c r="D20" s="8">
@@ -9660,11 +9662,11 @@
         <v>240</v>
       </c>
       <c r="F20" s="8">
-        <f>F2*C20</f>
+        <f t="shared" ref="F20:G22" si="5">F2*C20</f>
         <v>240</v>
       </c>
       <c r="G20" s="8">
-        <f>G2*D20</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H20" s="8"/>
@@ -9682,11 +9684,11 @@
         <v>113</v>
       </c>
       <c r="C21" s="6">
-        <f>2*C3</f>
+        <f t="shared" si="4"/>
         <v>468</v>
       </c>
       <c r="D21" s="6">
-        <f t="shared" ref="D21" si="4">D3*C21</f>
+        <f t="shared" ref="D21" si="6">D3*C21</f>
         <v>0</v>
       </c>
       <c r="E21" s="6">
@@ -9694,17 +9696,17 @@
         <v>0</v>
       </c>
       <c r="F21" s="6">
-        <f>F3*C21</f>
+        <f t="shared" si="5"/>
         <v>468</v>
       </c>
       <c r="G21" s="6">
-        <f>G3*D21</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="14">
-        <f t="shared" ref="J21:J29" si="5">SUM(D21:G21)</f>
+        <f t="shared" ref="J21:J29" si="7">SUM(D21:G21)</f>
         <v>468</v>
       </c>
     </row>
@@ -9716,11 +9718,11 @@
         <v>107</v>
       </c>
       <c r="C22" s="8">
-        <f>2*C4</f>
+        <f t="shared" si="4"/>
         <v>284</v>
       </c>
       <c r="D22" s="8">
-        <f t="shared" ref="D22" si="6">D4*C22</f>
+        <f t="shared" ref="D22" si="8">D4*C22</f>
         <v>284</v>
       </c>
       <c r="E22" s="8">
@@ -9728,17 +9730,17 @@
         <v>0</v>
       </c>
       <c r="F22" s="8">
-        <f>F4*C22</f>
+        <f t="shared" si="5"/>
         <v>284</v>
       </c>
       <c r="G22" s="8">
-        <f>G4*D22</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H22" s="8"/>
       <c r="I22" s="8"/>
       <c r="J22" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>568</v>
       </c>
     </row>
@@ -9750,7 +9752,7 @@
         <v>138</v>
       </c>
       <c r="C23" s="14">
-        <f>2*C5</f>
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
       <c r="D23" s="14">
@@ -9772,7 +9774,7 @@
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
       <c r="J23" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -9784,30 +9786,30 @@
         <v>105</v>
       </c>
       <c r="C24" s="8">
-        <f>2*C6</f>
+        <f t="shared" si="4"/>
         <v>364</v>
       </c>
       <c r="D24" s="8">
-        <f t="shared" ref="D24" si="7">D6*C24</f>
+        <f t="shared" ref="D24" si="9">D6*C24</f>
         <v>364</v>
       </c>
       <c r="E24" s="8">
-        <f>E6*C24</f>
+        <f t="shared" ref="E24:E29" si="10">E6*C24</f>
         <v>0</v>
       </c>
       <c r="F24" s="8">
-        <f>F6*C24</f>
+        <f t="shared" ref="F24:G29" si="11">F6*C24</f>
         <v>364</v>
       </c>
       <c r="G24" s="8">
-        <f>G6*D24</f>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>364</v>
       </c>
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8">
-        <f t="shared" si="5"/>
-        <v>728</v>
+        <f t="shared" si="7"/>
+        <v>1092</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -9818,29 +9820,29 @@
         <v>103</v>
       </c>
       <c r="C25" s="14">
-        <f>2*C7</f>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="D25" s="14">
-        <f t="shared" ref="D25" si="8">D7*C25</f>
+        <f t="shared" ref="D25" si="12">D7*C25</f>
         <v>84</v>
       </c>
       <c r="E25" s="14">
-        <f>E7*C25</f>
+        <f t="shared" si="10"/>
         <v>84</v>
       </c>
       <c r="F25" s="14">
-        <f>F7*C25</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="G25" s="14">
-        <f>G7*D25</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>336</v>
       </c>
     </row>
@@ -9852,29 +9854,29 @@
         <v>115</v>
       </c>
       <c r="C26" s="8">
-        <f>2*C8</f>
+        <f t="shared" si="4"/>
         <v>262</v>
       </c>
       <c r="D26" s="8">
-        <f t="shared" ref="D26" si="9">D8*C26</f>
+        <f t="shared" ref="D26" si="13">D8*C26</f>
         <v>0</v>
       </c>
       <c r="E26" s="8">
-        <f>E8*C26</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F26" s="8">
-        <f>F8*C26</f>
+        <f t="shared" si="11"/>
         <v>262</v>
       </c>
       <c r="G26" s="8">
-        <f>G8*D26</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>262</v>
       </c>
     </row>
@@ -9886,29 +9888,29 @@
         <v>109</v>
       </c>
       <c r="C27" s="14">
-        <f>2*C9</f>
+        <f t="shared" si="4"/>
         <v>572</v>
       </c>
       <c r="D27" s="14">
-        <f t="shared" ref="D27" si="10">D9*C27</f>
+        <f t="shared" ref="D27" si="14">D9*C27</f>
         <v>572</v>
       </c>
       <c r="E27" s="14">
-        <f>E9*C27</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <f>F9*C27</f>
+        <f t="shared" si="11"/>
         <v>572</v>
       </c>
       <c r="G27" s="14">
-        <f>G9*D27</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1144</v>
       </c>
     </row>
@@ -9920,29 +9922,29 @@
         <v>116</v>
       </c>
       <c r="C28" s="8">
-        <f>2*C10</f>
+        <f t="shared" si="4"/>
         <v>266</v>
       </c>
       <c r="D28" s="8">
-        <f t="shared" ref="D28" si="11">D10*C28</f>
+        <f t="shared" ref="D28" si="15">D10*C28</f>
         <v>0</v>
       </c>
       <c r="E28" s="8">
-        <f>E10*C28</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F28" s="8">
-        <f>F10*C28</f>
+        <f t="shared" si="11"/>
         <v>266</v>
       </c>
       <c r="G28" s="8">
-        <f>G10*D28</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>266</v>
       </c>
     </row>
@@ -9954,29 +9956,29 @@
         <v>111</v>
       </c>
       <c r="C29" s="14">
-        <f>2*C11</f>
+        <f t="shared" si="4"/>
         <v>262</v>
       </c>
       <c r="D29" s="14">
-        <f t="shared" ref="D29" si="12">D11*C29</f>
+        <f t="shared" ref="D29" si="16">D11*C29</f>
         <v>0</v>
       </c>
       <c r="E29" s="14">
-        <f>E11*C29</f>
+        <f t="shared" si="10"/>
         <v>262</v>
       </c>
       <c r="F29" s="14">
-        <f>F11*C29</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G29" s="14">
-        <f>G11*D29</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>262</v>
       </c>
     </row>
@@ -9997,17 +9999,17 @@
         <v>2540</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" ref="G31" si="13">SUM(G20:G29)</f>
-        <v>84</v>
+        <f t="shared" ref="G31" si="17">SUM(G20:G29)</f>
+        <v>448</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9">
         <f>SUM(D31:G31)</f>
-        <v>4754</v>
+        <v>5118</v>
       </c>
       <c r="J31" s="9">
         <f>SUM(J20:J29)</f>
-        <v>4754</v>
+        <v>5118</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
@@ -10027,13 +10029,13 @@
       <c r="I63" s="2"/>
       <c r="J63" s="4">
         <f>SUM(J2:J61)</f>
-        <v>19473.333333333336</v>
+        <v>20934.315789473687</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J70">
         <f>SUM(J2:J61)</f>
-        <v>19473.333333333336</v>
+        <v>20934.315789473687</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
@@ -10051,15 +10053,15 @@
       </c>
       <c r="H71">
         <f>SUM(H2:H61)</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I71">
         <f>SUM(I2:I61)</f>
-        <v>9736.6666666666679</v>
+        <v>10467.157894736843</v>
       </c>
       <c r="J71">
         <f>2*I71</f>
-        <v>19473.333333333336</v>
+        <v>20934.315789473687</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -10259,15 +10261,15 @@
         <v>25</v>
       </c>
       <c r="C83">
-        <f>C12*2</f>
+        <f t="shared" ref="C83:C93" si="18">C12*2</f>
         <v>0</v>
       </c>
       <c r="D83">
-        <f>C83*D12</f>
+        <f t="shared" ref="D83:D93" si="19">C83*D12</f>
         <v>0</v>
       </c>
       <c r="E83">
-        <f>C83*E12</f>
+        <f t="shared" ref="E83:E93" si="20">C83*E12</f>
         <v>0</v>
       </c>
     </row>
@@ -10279,15 +10281,15 @@
         <v>26</v>
       </c>
       <c r="C84">
-        <f>C13*2</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D84">
-        <f>C84*D13</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E84">
-        <f>C84*E13</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -10299,15 +10301,15 @@
         <v>27</v>
       </c>
       <c r="C85">
-        <f>C14*2</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D85">
-        <f>C85*D14</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E85">
-        <f>C85*E14</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -10319,15 +10321,15 @@
         <v>29</v>
       </c>
       <c r="C86">
-        <f>C15*2</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D86">
-        <f>C86*D15</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E86">
-        <f>C86*E15</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -10339,15 +10341,15 @@
         <v>31</v>
       </c>
       <c r="C87">
-        <f>C16*2</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D87">
-        <f>C87*D16</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E87">
-        <f>C87*E16</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -10359,15 +10361,15 @@
         <v>32</v>
       </c>
       <c r="C88">
-        <f>C17*2</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D88">
-        <f>C88*D17</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E88">
-        <f>C88*E17</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -10379,15 +10381,15 @@
         <v>33</v>
       </c>
       <c r="C89">
-        <f>C18*2</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="D89">
-        <f>C89*D18</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E89">
-        <f>C89*E18</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -10399,15 +10401,15 @@
         <v>34</v>
       </c>
       <c r="C90" t="e">
-        <f>C19*2</f>
+        <f t="shared" si="18"/>
         <v>#VALUE!</v>
       </c>
       <c r="D90" t="e">
-        <f>C90*D19</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="E90" t="e">
-        <f>C90*E19</f>
+        <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10419,15 +10421,15 @@
         <v>35</v>
       </c>
       <c r="C91">
-        <f>C20*2</f>
+        <f t="shared" si="18"/>
         <v>480</v>
       </c>
       <c r="D91">
-        <f>C91*D20</f>
+        <f t="shared" si="19"/>
         <v>115200</v>
       </c>
       <c r="E91">
-        <f>C91*E20</f>
+        <f t="shared" si="20"/>
         <v>115200</v>
       </c>
     </row>
@@ -10439,15 +10441,15 @@
         <v>101</v>
       </c>
       <c r="C92">
-        <f>C21*2</f>
+        <f t="shared" si="18"/>
         <v>936</v>
       </c>
       <c r="D92">
-        <f>C92*D21</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="E92">
-        <f>C92*E21</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -10459,15 +10461,15 @@
         <v>37</v>
       </c>
       <c r="C93">
-        <f>C22*2</f>
+        <f t="shared" si="18"/>
         <v>568</v>
       </c>
       <c r="D93">
-        <f>C93*D22</f>
+        <f t="shared" si="19"/>
         <v>161312</v>
       </c>
       <c r="E93">
-        <f>C93*E22</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -10479,15 +10481,15 @@
         <v>95</v>
       </c>
       <c r="C94">
-        <f t="shared" ref="C94" si="14">C24*2</f>
+        <f t="shared" ref="C94" si="21">C24*2</f>
         <v>728</v>
       </c>
       <c r="D94">
-        <f t="shared" ref="D94" si="15">C94*D24</f>
+        <f t="shared" ref="D94" si="22">C94*D24</f>
         <v>264992</v>
       </c>
       <c r="E94">
-        <f t="shared" ref="E94" si="16">C94*E24</f>
+        <f t="shared" ref="E94" si="23">C94*E24</f>
         <v>0</v>
       </c>
     </row>
@@ -10518,15 +10520,15 @@
         <v>39</v>
       </c>
       <c r="C96">
-        <f t="shared" ref="C96:C131" si="17">C26*2</f>
+        <f t="shared" ref="C96:C131" si="24">C26*2</f>
         <v>524</v>
       </c>
       <c r="D96">
-        <f t="shared" ref="D96:D125" si="18">C96*D26</f>
+        <f t="shared" ref="D96:D125" si="25">C96*D26</f>
         <v>0</v>
       </c>
       <c r="E96">
-        <f t="shared" ref="E96:E131" si="19">C96*E26</f>
+        <f t="shared" ref="E96:E131" si="26">C96*E26</f>
         <v>0</v>
       </c>
     </row>
@@ -10538,15 +10540,15 @@
         <v>41</v>
       </c>
       <c r="C97">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>1144</v>
       </c>
       <c r="D97">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>654368</v>
       </c>
       <c r="E97">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10558,15 +10560,15 @@
         <v>42</v>
       </c>
       <c r="C98">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>532</v>
       </c>
       <c r="D98">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E98">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10578,15 +10580,15 @@
         <v>43</v>
       </c>
       <c r="C99">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>524</v>
       </c>
       <c r="D99">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E99">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>137288</v>
       </c>
     </row>
@@ -10598,15 +10600,15 @@
         <v>45</v>
       </c>
       <c r="C100">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D100">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E100">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10618,15 +10620,15 @@
         <v>46</v>
       </c>
       <c r="C101">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D101">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E101">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="F101" s="1"/>
@@ -10643,15 +10645,15 @@
         <v>47</v>
       </c>
       <c r="C102">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D102">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E102">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10663,15 +10665,15 @@
         <v>48</v>
       </c>
       <c r="C103">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D103">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E103">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10683,15 +10685,15 @@
         <v>49</v>
       </c>
       <c r="C104">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D104">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E104">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10703,15 +10705,15 @@
         <v>51</v>
       </c>
       <c r="C105">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D105">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E105">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10723,15 +10725,15 @@
         <v>53</v>
       </c>
       <c r="C106">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D106">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E106">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10743,15 +10745,15 @@
         <v>55</v>
       </c>
       <c r="C107">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D107">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E107">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10763,15 +10765,15 @@
         <v>57</v>
       </c>
       <c r="C108">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D108">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E108">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10783,15 +10785,15 @@
         <v>58</v>
       </c>
       <c r="C109">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D109">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E109">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10803,15 +10805,15 @@
         <v>60</v>
       </c>
       <c r="C110">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D110">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E110">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10823,15 +10825,15 @@
         <v>61</v>
       </c>
       <c r="C111">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D111">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E111">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10843,15 +10845,15 @@
         <v>62</v>
       </c>
       <c r="C112">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D112">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E112">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10863,15 +10865,15 @@
         <v>64</v>
       </c>
       <c r="C113">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D113">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E113">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10883,15 +10885,15 @@
         <v>66</v>
       </c>
       <c r="C114">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D114">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E114">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10903,15 +10905,15 @@
         <v>67</v>
       </c>
       <c r="C115">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D115">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E115">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10923,15 +10925,15 @@
         <v>68</v>
       </c>
       <c r="C116">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D116">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E116">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10943,15 +10945,15 @@
         <v>69</v>
       </c>
       <c r="C117">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D117">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E117">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10963,15 +10965,15 @@
         <v>71</v>
       </c>
       <c r="C118">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D118">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E118">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -10983,15 +10985,15 @@
         <v>72</v>
       </c>
       <c r="C119">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D119">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E119">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11003,15 +11005,15 @@
         <v>73</v>
       </c>
       <c r="C120">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D120">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E120">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11023,15 +11025,15 @@
         <v>75</v>
       </c>
       <c r="C121">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D121">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E121">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11043,15 +11045,15 @@
         <v>76</v>
       </c>
       <c r="C122">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D122">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E122">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11063,15 +11065,15 @@
         <v>77</v>
       </c>
       <c r="C123">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D123">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E123">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11083,15 +11085,15 @@
         <v>79</v>
       </c>
       <c r="C124">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D124">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E124">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11103,15 +11105,15 @@
         <v>80</v>
       </c>
       <c r="C125">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D125">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="E125">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11123,14 +11125,14 @@
         <v>102</v>
       </c>
       <c r="C126">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11142,7 +11144,7 @@
         <v>82</v>
       </c>
       <c r="C127">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D127">
@@ -11150,7 +11152,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11162,7 +11164,7 @@
         <v>84</v>
       </c>
       <c r="C128">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D128">
@@ -11170,7 +11172,7 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11182,7 +11184,7 @@
         <v>85</v>
       </c>
       <c r="C129">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D129">
@@ -11190,7 +11192,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11202,7 +11204,7 @@
         <v>86</v>
       </c>
       <c r="C130">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D130">
@@ -11210,7 +11212,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11222,7 +11224,7 @@
         <v>88</v>
       </c>
       <c r="C131">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="D131">
@@ -11230,7 +11232,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
     </row>
@@ -11244,11 +11246,11 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D140" t="e">
-        <f t="shared" ref="D140:E140" si="20">SUM(D75:D131)</f>
+        <f t="shared" ref="D140:E140" si="27">SUM(D75:D131)</f>
         <v>#REF!</v>
       </c>
       <c r="E140" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="27"/>
         <v>#REF!</v>
       </c>
       <c r="H140" t="e">
@@ -11262,11 +11264,11 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D141" s="3" t="e">
-        <f t="shared" ref="D141:E141" si="21">D140/D71</f>
+        <f t="shared" ref="D141:E141" si="28">D140/D71</f>
         <v>#REF!</v>
       </c>
       <c r="E141" s="3" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>#REF!</v>
       </c>
       <c r="H141" s="3" t="e">

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94FFF9F-AB9E-471B-A1D4-0EEACEB0E822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8923E057-B6B0-469A-86F0-5955307FA83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="140">
   <si>
     <t>Paikkakunta</t>
   </si>
@@ -454,6 +454,9 @@
   </si>
   <si>
     <t>Hattelmalan kylä</t>
+  </si>
+  <si>
+    <t>Beachbox</t>
   </si>
 </sst>
 </file>
@@ -603,8 +606,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9213,7 +9216,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB3AEAB-3835-4342-9FF8-FBE02F12A238}">
-  <dimension ref="A1:J236"/>
+  <dimension ref="A1:J238"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" customWidth="1"/>
@@ -9278,11 +9281,11 @@
         <v>3</v>
       </c>
       <c r="I2" s="8">
-        <f t="shared" ref="I2:I6" si="0">C2*H2</f>
+        <f t="shared" ref="I2:I7" si="0">C2*H2</f>
         <v>360</v>
       </c>
       <c r="J2" s="8">
-        <f t="shared" ref="J2:J6" si="1">2*I2</f>
+        <f t="shared" ref="J2:J7" si="1">2*I2</f>
         <v>720</v>
       </c>
     </row>
@@ -9303,7 +9306,7 @@
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="14">
-        <f t="shared" ref="H3:H11" si="2">SUM(D3:G3)</f>
+        <f t="shared" ref="H3:H12" si="2">SUM(D3:G3)</f>
         <v>1</v>
       </c>
       <c r="I3" s="6">
@@ -9320,171 +9323,167 @@
         <v>19</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="C4" s="8">
         <v>142</v>
       </c>
-      <c r="D4" s="8">
-        <v>1</v>
-      </c>
+      <c r="D4" s="8"/>
       <c r="E4" s="8"/>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
+      <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8">
+        <f>SUM(D4:G4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="14">
+        <v>142</v>
+      </c>
+      <c r="D5" s="14">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14">
+        <v>1</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I5" s="14">
         <f t="shared" si="0"/>
         <v>284</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J5" s="14">
         <f t="shared" si="1"/>
         <v>568</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="14">
-        <v>47</v>
-      </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14">
-        <v>1</v>
-      </c>
-      <c r="H5" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="I5" s="14">
-        <f>C5*H5</f>
-        <v>47</v>
-      </c>
-      <c r="J5" s="14">
-        <f t="shared" ref="J5:J11" si="3">2*I5</f>
-        <v>94</v>
-      </c>
-    </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>105</v>
+        <v>22</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>138</v>
       </c>
       <c r="C6" s="8">
-        <v>182</v>
-      </c>
-      <c r="D6" s="8">
-        <v>1</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D6" s="8"/>
       <c r="E6" s="8"/>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="8">
         <v>1</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I6" s="8">
+        <f>C6*H6</f>
+        <v>47</v>
+      </c>
+      <c r="J6" s="8">
+        <f t="shared" ref="J6:J12" si="3">2*I6</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="14">
+        <v>182</v>
+      </c>
+      <c r="D7" s="14">
+        <v>1</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I7" s="14">
         <f t="shared" si="0"/>
         <v>546</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J7" s="14">
         <f t="shared" si="1"/>
         <v>1092</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B8" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C8" s="8">
         <v>42</v>
       </c>
-      <c r="D7" s="14">
-        <v>1</v>
-      </c>
-      <c r="E7" s="14">
-        <v>1</v>
-      </c>
-      <c r="F7" s="14">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14">
-        <v>1</v>
-      </c>
-      <c r="H7" s="14">
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="I7" s="14">
-        <f>C7*H7</f>
+      <c r="I8" s="8">
+        <f>C8*H8</f>
         <v>168</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J8" s="8">
         <f t="shared" si="3"/>
         <v>336</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="8">
-        <v>131</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="I8" s="8">
-        <f>C8*H8</f>
-        <v>131</v>
-      </c>
-      <c r="J8" s="8">
-        <f t="shared" si="3"/>
-        <v>262</v>
-      </c>
-    </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>109</v>
+        <v>114</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>115</v>
       </c>
       <c r="C9" s="14">
-        <v>286</v>
-      </c>
-      <c r="D9" s="14">
-        <v>1</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14">
         <v>1</v>
@@ -9492,28 +9491,30 @@
       <c r="G9" s="14"/>
       <c r="H9" s="14">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="14">
         <f>C9*H9</f>
-        <v>572</v>
+        <v>131</v>
       </c>
       <c r="J9" s="14">
         <f t="shared" si="3"/>
-        <v>1144</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C10" s="8">
-        <v>133</v>
-      </c>
-      <c r="D10" s="8"/>
+        <v>286</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>1</v>
@@ -9521,15 +9522,15 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="8">
         <f>C10*H10</f>
-        <v>133</v>
+        <v>572</v>
       </c>
       <c r="J10" s="8">
         <f t="shared" si="3"/>
-        <v>266</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -9537,16 +9538,16 @@
         <v>110</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C11" s="14">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="14">
-        <v>1</v>
-      </c>
-      <c r="F11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14">
+        <v>1</v>
+      </c>
       <c r="G11" s="14"/>
       <c r="H11" s="14">
         <f t="shared" si="2"/>
@@ -9554,583 +9555,606 @@
       </c>
       <c r="I11" s="14">
         <f>C11*H11</f>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="3"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C12" s="8">
+        <v>131</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I12" s="8">
+        <f>C12*H12</f>
+        <v>131</v>
+      </c>
+      <c r="J12" s="8">
+        <f t="shared" si="3"/>
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="9">
-        <f>SUM(D2:D14)</f>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9">
+        <f>SUM(D2:D15)</f>
         <v>5</v>
       </c>
-      <c r="E15" s="9">
-        <f>SUM(E2:E14)</f>
+      <c r="E16" s="9">
+        <f>SUM(E2:E15)</f>
         <v>3</v>
       </c>
-      <c r="F15" s="9">
-        <f>SUM(F2:F14)</f>
+      <c r="F16" s="9">
+        <f>SUM(F2:F15)</f>
         <v>8</v>
       </c>
-      <c r="G15" s="9">
-        <f>SUM(G2:G14)</f>
+      <c r="G16" s="9">
+        <f>SUM(G2:G15)</f>
         <v>3</v>
       </c>
-      <c r="H15" s="9">
-        <f>SUM(D15:G15)</f>
+      <c r="H16" s="9">
+        <f>SUM(D16:G16)</f>
         <v>19</v>
       </c>
-      <c r="I15" s="9">
-        <f>SUM(I2:I11)</f>
+      <c r="I16" s="9">
+        <f>SUM(I2:I12)</f>
         <v>2606</v>
       </c>
-      <c r="J15" s="9">
-        <f>SUM(J2:J11)</f>
+      <c r="J16" s="9">
+        <f>SUM(J2:J12)</f>
         <v>5212</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8">
-        <f>I15/H15</f>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8">
+        <f>I16/H16</f>
         <v>137.15789473684211</v>
       </c>
-      <c r="J16" s="8">
-        <f>J15/H15</f>
+      <c r="J17" s="8">
+        <f>J16/H16</f>
         <v>274.31578947368422</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="7" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D20" s="7">
         <v>2023</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E20" s="7">
         <v>2024</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F20" s="7">
         <v>2025</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G20" s="7">
         <v>2026</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7" t="s">
+      <c r="H20" s="9"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B21" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="8">
-        <f t="shared" ref="C20:C29" si="4">2*C2</f>
+      <c r="C21" s="8">
+        <f>2*C2</f>
         <v>240</v>
       </c>
-      <c r="D20" s="8">
-        <f>D2*C20</f>
+      <c r="D21" s="8">
+        <f>D2*C21</f>
         <v>240</v>
       </c>
-      <c r="E20" s="8">
-        <f>E2*C20</f>
+      <c r="E21" s="8">
+        <f>E2*C21</f>
         <v>240</v>
       </c>
-      <c r="F20" s="8">
-        <f t="shared" ref="F20:G22" si="5">F2*C20</f>
+      <c r="F21" s="8">
+        <f>F2*C21</f>
         <v>240</v>
       </c>
-      <c r="G20" s="8">
+      <c r="G21" s="8">
+        <f>G2*D21</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8">
+        <f>SUM(D21:G21)</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="6">
+        <f>2*C3</f>
+        <v>468</v>
+      </c>
+      <c r="D22" s="6">
+        <f t="shared" ref="D22" si="4">D3*C22</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="6">
+        <f>E3*C22</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="6">
+        <f>F3*C22</f>
+        <v>468</v>
+      </c>
+      <c r="G22" s="6">
+        <f>G3*D22</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="14">
+        <f t="shared" ref="J22:J31" si="5">SUM(D22:G22)</f>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="8">
+        <f>2*C4</f>
+        <v>284</v>
+      </c>
+      <c r="D23" s="8">
+        <f>D4*C23</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="8">
+        <f>E4*C23</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="8">
+        <f>F4*C23</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="8">
+        <f>G4*D23</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
+        <f>SUM(D23:G23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="14">
+        <f>2*C5</f>
+        <v>284</v>
+      </c>
+      <c r="D24" s="14">
+        <f t="shared" ref="D24" si="6">D5*C24</f>
+        <v>284</v>
+      </c>
+      <c r="E24" s="14">
+        <f>E5*C24</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <f t="shared" ref="F24:G24" si="7">F5*C24</f>
+        <v>284</v>
+      </c>
+      <c r="G24" s="14">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8">
-        <f>SUM(D20:G20)</f>
-        <v>720</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="6">
-        <f t="shared" si="4"/>
-        <v>468</v>
-      </c>
-      <c r="D21" s="6">
-        <f t="shared" ref="D21" si="6">D3*C21</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="6">
-        <f>E3*C21</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="6">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="8">
+        <f>2*C6</f>
+        <v>94</v>
+      </c>
+      <c r="D25" s="8">
+        <f>2*D6</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
+        <f>2*E6</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <f>2*F6</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <f>2*D25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8">
         <f t="shared" si="5"/>
-        <v>468</v>
-      </c>
-      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="14">
+        <f>2*C7</f>
+        <v>364</v>
+      </c>
+      <c r="D26" s="14">
+        <f t="shared" ref="D26" si="8">D7*C26</f>
+        <v>364</v>
+      </c>
+      <c r="E26" s="14">
+        <f>E7*C26</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <f>F7*C26</f>
+        <v>364</v>
+      </c>
+      <c r="G26" s="14">
+        <f>G7*D26</f>
+        <v>364</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="14">
-        <f t="shared" ref="J21:J29" si="7">SUM(D21:G21)</f>
-        <v>468</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="8">
-        <f t="shared" si="4"/>
-        <v>284</v>
-      </c>
-      <c r="D22" s="8">
-        <f t="shared" ref="D22" si="8">D4*C22</f>
-        <v>284</v>
-      </c>
-      <c r="E22" s="8">
-        <f>E4*C22</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="8">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="8">
+        <f>2*C8</f>
+        <v>84</v>
+      </c>
+      <c r="D27" s="8">
+        <f t="shared" ref="D27" si="9">D8*C27</f>
+        <v>84</v>
+      </c>
+      <c r="E27" s="8">
+        <f>E8*C27</f>
+        <v>84</v>
+      </c>
+      <c r="F27" s="8">
+        <f>F8*C27</f>
+        <v>84</v>
+      </c>
+      <c r="G27" s="8">
+        <f>G8*D27</f>
+        <v>84</v>
+      </c>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8">
         <f t="shared" si="5"/>
-        <v>284</v>
-      </c>
-      <c r="G22" s="8">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="14">
+        <f>2*C9</f>
+        <v>262</v>
+      </c>
+      <c r="D28" s="14">
+        <f t="shared" ref="D28" si="10">D9*C28</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="14">
+        <f>E9*C28</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <f>F9*C28</f>
+        <v>262</v>
+      </c>
+      <c r="G28" s="14">
+        <f>G9*D28</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8">
-        <f t="shared" si="7"/>
-        <v>568</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C23" s="14">
-        <f t="shared" si="4"/>
-        <v>94</v>
-      </c>
-      <c r="D23" s="14">
-        <f>2*D5</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="14">
-        <f>2*E5</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="14">
-        <f>2*F5</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="14">
-        <f>2*D23</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="8">
-        <f t="shared" si="4"/>
-        <v>364</v>
-      </c>
-      <c r="D24" s="8">
-        <f t="shared" ref="D24" si="9">D6*C24</f>
-        <v>364</v>
-      </c>
-      <c r="E24" s="8">
-        <f t="shared" ref="E24:E29" si="10">E6*C24</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="8">
-        <f t="shared" ref="F24:G29" si="11">F6*C24</f>
-        <v>364</v>
-      </c>
-      <c r="G24" s="8">
-        <f t="shared" si="11"/>
-        <v>364</v>
-      </c>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8">
-        <f t="shared" si="7"/>
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="14">
-        <f t="shared" si="4"/>
-        <v>84</v>
-      </c>
-      <c r="D25" s="14">
-        <f t="shared" ref="D25" si="12">D7*C25</f>
-        <v>84</v>
-      </c>
-      <c r="E25" s="14">
-        <f t="shared" si="10"/>
-        <v>84</v>
-      </c>
-      <c r="F25" s="14">
-        <f t="shared" si="11"/>
-        <v>84</v>
-      </c>
-      <c r="G25" s="14">
-        <f t="shared" si="11"/>
-        <v>84</v>
-      </c>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14">
-        <f t="shared" si="7"/>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C26" s="8">
-        <f t="shared" si="4"/>
         <v>262</v>
       </c>
-      <c r="D26" s="8">
-        <f t="shared" ref="D26" si="13">D8*C26</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="8">
-        <f t="shared" si="11"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="8">
+        <f>2*C10</f>
+        <v>572</v>
+      </c>
+      <c r="D29" s="8">
+        <f t="shared" ref="D29" si="11">D10*C29</f>
+        <v>572</v>
+      </c>
+      <c r="E29" s="8">
+        <f>E10*C29</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="8">
+        <f>F10*C29</f>
+        <v>572</v>
+      </c>
+      <c r="G29" s="8">
+        <f>G10*D29</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8">
+        <f t="shared" si="5"/>
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="14">
+        <f>2*C11</f>
+        <v>266</v>
+      </c>
+      <c r="D30" s="14">
+        <f t="shared" ref="D30" si="12">D11*C30</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="14">
+        <f>E11*C30</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <f>F11*C30</f>
+        <v>266</v>
+      </c>
+      <c r="G30" s="14">
+        <f>G11*D30</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14">
+        <f t="shared" si="5"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31" s="8">
+        <f>2*C12</f>
         <v>262</v>
       </c>
-      <c r="G26" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8">
-        <f t="shared" si="7"/>
+      <c r="D31" s="8">
+        <f t="shared" ref="D31" si="13">D12*C31</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="8">
+        <f>E12*C31</f>
         <v>262</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C27" s="14">
-        <f t="shared" si="4"/>
-        <v>572</v>
-      </c>
-      <c r="D27" s="14">
-        <f t="shared" ref="D27" si="14">D9*C27</f>
-        <v>572</v>
-      </c>
-      <c r="E27" s="14">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="14">
-        <f t="shared" si="11"/>
-        <v>572</v>
-      </c>
-      <c r="G27" s="14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14">
-        <f t="shared" si="7"/>
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="8">
-        <f t="shared" si="4"/>
-        <v>266</v>
-      </c>
-      <c r="D28" s="8">
-        <f t="shared" ref="D28" si="15">D10*C28</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="8">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="8">
-        <f t="shared" si="11"/>
-        <v>266</v>
-      </c>
-      <c r="G28" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8">
-        <f t="shared" si="7"/>
-        <v>266</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="14">
-        <f t="shared" si="4"/>
+      <c r="F31" s="8">
+        <f>F12*C31</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <f>G12*D31</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8">
+        <f t="shared" si="5"/>
         <v>262</v>
       </c>
-      <c r="D29" s="14">
-        <f t="shared" ref="D29" si="16">D11*C29</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="14">
-        <f t="shared" si="10"/>
-        <v>262</v>
-      </c>
-      <c r="F29" s="14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G29" s="14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14">
-        <f t="shared" si="7"/>
-        <v>262</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9">
-        <f>SUM(D20:D29)</f>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9">
+        <f>SUM(D21:D31)</f>
         <v>1544</v>
       </c>
-      <c r="E31" s="9">
-        <f>SUM(E20:E29)</f>
+      <c r="E33" s="9">
+        <f>SUM(E21:E31)</f>
         <v>586</v>
       </c>
-      <c r="F31" s="9">
-        <f>SUM(F20:F29)</f>
+      <c r="F33" s="9">
+        <f>SUM(F21:F31)</f>
         <v>2540</v>
       </c>
-      <c r="G31" s="9">
-        <f t="shared" ref="G31" si="17">SUM(G20:G29)</f>
+      <c r="G33" s="9">
+        <f t="shared" ref="G33" si="14">SUM(G21:G31)</f>
         <v>448</v>
       </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9">
-        <f>SUM(D31:G31)</f>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9">
+        <f>SUM(D33:G33)</f>
         <v>5118</v>
       </c>
-      <c r="J31" s="9">
-        <f>SUM(J20:J29)</f>
+      <c r="J33" s="9">
+        <f>SUM(J21:J31)</f>
         <v>5118</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H62" t="s">
+    <row r="64" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H64" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="4">
-        <f>SUM(J2:J61)</f>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="4">
+        <f>SUM(J2:J63)</f>
         <v>20934.315789473687</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J70">
-        <f>SUM(J2:J61)</f>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J72">
+        <f>SUM(J2:J63)</f>
         <v>20934.315789473687</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D71">
-        <f>SUM(D2:D61)</f>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D73">
+        <f>SUM(D2:D63)</f>
         <v>5121</v>
       </c>
-      <c r="E71">
-        <f>SUM(E2:E61)</f>
+      <c r="E73">
+        <f>SUM(E2:E63)</f>
         <v>3202</v>
       </c>
-      <c r="F71">
-        <f>SUM(D71:E71)</f>
+      <c r="F73">
+        <f>SUM(D73:E73)</f>
         <v>8323</v>
       </c>
-      <c r="H71">
-        <f>SUM(H2:H61)</f>
+      <c r="H73">
+        <f>SUM(H2:H63)</f>
         <v>38</v>
       </c>
-      <c r="I71">
-        <f>SUM(I2:I61)</f>
+      <c r="I73">
+        <f>SUM(I2:I63)</f>
         <v>10467.157894736843</v>
       </c>
-      <c r="J71">
-        <f>2*I71</f>
+      <c r="J73">
+        <f>2*I73</f>
         <v>20934.315789473687</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A74" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="1" t="s">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>13</v>
-      </c>
-      <c r="B75" t="s">
-        <v>14</v>
-      </c>
-      <c r="C75">
-        <f>C2*2</f>
-        <v>240</v>
-      </c>
-      <c r="D75">
-        <f>C75*D2</f>
-        <v>240</v>
-      </c>
-      <c r="E75">
-        <f>C75*E2</f>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>13</v>
-      </c>
-      <c r="B76" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76">
-        <f>C4*2</f>
-        <v>284</v>
-      </c>
-      <c r="D76">
-        <f>C76*D4</f>
-        <v>284</v>
-      </c>
-      <c r="E76">
-        <f>C76*E4</f>
-        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
@@ -10138,119 +10162,119 @@
         <v>13</v>
       </c>
       <c r="B77" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C77">
-        <f>C6*2</f>
-        <v>364</v>
+        <f>C2*2</f>
+        <v>240</v>
       </c>
       <c r="D77">
-        <f>C77*D6</f>
-        <v>364</v>
+        <f>C77*D2</f>
+        <v>240</v>
       </c>
       <c r="E77">
-        <f>C77*E6</f>
-        <v>0</v>
+        <f>C77*E2</f>
+        <v>240</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78">
+        <f>C5*2</f>
+        <v>284</v>
+      </c>
+      <c r="D78">
+        <f>C78*D5</f>
+        <v>284</v>
+      </c>
+      <c r="E78">
+        <f>C78*E5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>13</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79">
+        <f>C7*2</f>
+        <v>364</v>
+      </c>
+      <c r="D79">
+        <f>C79*D7</f>
+        <v>364</v>
+      </c>
+      <c r="E79">
+        <f>C79*E7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>17</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B80" t="s">
         <v>18</v>
       </c>
-      <c r="C78" t="e">
+      <c r="C80" t="e">
         <f>#REF!*2</f>
         <v>#REF!</v>
       </c>
-      <c r="D78" t="e">
-        <f>C78*#REF!</f>
+      <c r="D80" t="e">
+        <f>C80*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E78" t="e">
-        <f>C78*#REF!</f>
+      <c r="E80" t="e">
+        <f>C80*#REF!</f>
         <v>#REF!</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>19</v>
-      </c>
-      <c r="B79" t="s">
-        <v>20</v>
-      </c>
-      <c r="C79">
-        <f>C7*2</f>
-        <v>84</v>
-      </c>
-      <c r="D79">
-        <f>C79*D7</f>
-        <v>84</v>
-      </c>
-      <c r="E79">
-        <f>C79*E7</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>19</v>
-      </c>
-      <c r="B80" t="s">
-        <v>21</v>
-      </c>
-      <c r="C80">
-        <f>C9*2</f>
-        <v>572</v>
-      </c>
-      <c r="D80">
-        <f>C80*D9</f>
-        <v>572</v>
-      </c>
-      <c r="E80">
-        <f>C80*E9</f>
-        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B81" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C81">
-        <f>C11*2</f>
-        <v>262</v>
+        <f>C8*2</f>
+        <v>84</v>
       </c>
       <c r="D81">
-        <f>C81*D11</f>
-        <v>0</v>
+        <f>C81*D8</f>
+        <v>84</v>
       </c>
       <c r="E81">
-        <f>C81*E11</f>
-        <v>262</v>
+        <f>C81*E8</f>
+        <v>84</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
-      </c>
-      <c r="C82" t="e">
-        <f>#REF!*2</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D82" t="e">
-        <f>C82*#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E82" t="e">
-        <f>C82*#REF!</f>
-        <v>#REF!</v>
+        <v>21</v>
+      </c>
+      <c r="C82">
+        <f>C10*2</f>
+        <v>572</v>
+      </c>
+      <c r="D82">
+        <f>C82*D10</f>
+        <v>572</v>
+      </c>
+      <c r="E82">
+        <f>C82*E10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -10258,19 +10282,19 @@
         <v>22</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C83">
-        <f t="shared" ref="C83:C93" si="18">C12*2</f>
-        <v>0</v>
+        <f>C12*2</f>
+        <v>262</v>
       </c>
       <c r="D83">
-        <f t="shared" ref="D83:D93" si="19">C83*D12</f>
+        <f>C83*D12</f>
         <v>0</v>
       </c>
       <c r="E83">
-        <f t="shared" ref="E83:E93" si="20">C83*E12</f>
-        <v>0</v>
+        <f>C83*E12</f>
+        <v>262</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -10278,19 +10302,19 @@
         <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
-      </c>
-      <c r="C84">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="D84">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="C84" t="e">
+        <f>#REF!*2</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D84" t="e">
+        <f>C84*#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E84" t="e">
+        <f>C84*#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -10298,78 +10322,78 @@
         <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C85">
-        <f t="shared" si="18"/>
+        <f>C13*2</f>
         <v>0</v>
       </c>
       <c r="D85">
-        <f t="shared" si="19"/>
+        <f>C85*D13</f>
         <v>0</v>
       </c>
       <c r="E85">
-        <f t="shared" si="20"/>
+        <f>C85*E13</f>
         <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C86">
-        <f t="shared" si="18"/>
+        <f>C14*2</f>
         <v>0</v>
       </c>
       <c r="D86">
-        <f t="shared" si="19"/>
+        <f>C86*D14</f>
         <v>0</v>
       </c>
       <c r="E86">
-        <f t="shared" si="20"/>
+        <f>C86*E14</f>
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C87">
-        <f t="shared" si="18"/>
+        <f>C15*2</f>
         <v>0</v>
       </c>
       <c r="D87">
-        <f t="shared" si="19"/>
+        <f>C87*D15</f>
         <v>0</v>
       </c>
       <c r="E87">
-        <f t="shared" si="20"/>
+        <f>C87*E15</f>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B88" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C88">
-        <f t="shared" si="18"/>
+        <f>C16*2</f>
         <v>0</v>
       </c>
       <c r="D88">
-        <f t="shared" si="19"/>
+        <f>C88*D16</f>
         <v>0</v>
       </c>
       <c r="E88">
-        <f t="shared" si="20"/>
+        <f>C88*E16</f>
         <v>0</v>
       </c>
     </row>
@@ -10378,18 +10402,18 @@
         <v>30</v>
       </c>
       <c r="B89" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C89">
-        <f t="shared" si="18"/>
+        <f>C17*2</f>
         <v>0</v>
       </c>
       <c r="D89">
-        <f t="shared" si="19"/>
+        <f>C89*D17</f>
         <v>0</v>
       </c>
       <c r="E89">
-        <f t="shared" si="20"/>
+        <f>C89*E17</f>
         <v>0</v>
       </c>
     </row>
@@ -10398,19 +10422,19 @@
         <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
-      </c>
-      <c r="C90" t="e">
-        <f t="shared" si="18"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D90" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E90" t="e">
-        <f t="shared" si="20"/>
-        <v>#VALUE!</v>
+        <v>32</v>
+      </c>
+      <c r="C90">
+        <f>C18*2</f>
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <f>C90*D18</f>
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <f>C90*E18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -10418,157 +10442,157 @@
         <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C91">
-        <f t="shared" si="18"/>
-        <v>480</v>
+        <f>C19*2</f>
+        <v>0</v>
       </c>
       <c r="D91">
-        <f t="shared" si="19"/>
-        <v>115200</v>
+        <f>C91*D19</f>
+        <v>0</v>
       </c>
       <c r="E91">
-        <f t="shared" si="20"/>
-        <v>115200</v>
+        <f>C91*E19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="B92" t="s">
-        <v>101</v>
-      </c>
-      <c r="C92">
-        <f t="shared" si="18"/>
-        <v>936</v>
-      </c>
-      <c r="D92">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="E92">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="C92" t="e">
+        <f>C20*2</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D92" t="e">
+        <f>C92*D20</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E92" t="e">
+        <f>C92*E20</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B93" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C93">
-        <f t="shared" si="18"/>
-        <v>568</v>
+        <f>C21*2</f>
+        <v>480</v>
       </c>
       <c r="D93">
-        <f t="shared" si="19"/>
-        <v>161312</v>
+        <f>C93*D21</f>
+        <v>115200</v>
       </c>
       <c r="E93">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>C93*E21</f>
+        <v>115200</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C94">
-        <f t="shared" ref="C94" si="21">C24*2</f>
-        <v>728</v>
+        <f>C22*2</f>
+        <v>936</v>
       </c>
       <c r="D94">
-        <f t="shared" ref="D94" si="22">C94*D24</f>
-        <v>264992</v>
+        <f>C94*D22</f>
+        <v>0</v>
       </c>
       <c r="E94">
-        <f t="shared" ref="E94" si="23">C94*E24</f>
+        <f>C94*E22</f>
         <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="C95">
-        <v>209</v>
-      </c>
-      <c r="D95" t="e">
-        <f>#REF!*D26</f>
-        <v>#REF!</v>
+        <f t="shared" ref="C95" si="15">C24*2</f>
+        <v>568</v>
+      </c>
+      <c r="D95">
+        <f t="shared" ref="D95" si="16">C95*D24</f>
+        <v>161312</v>
       </c>
       <c r="E95">
-        <f>C95*E26</f>
+        <f t="shared" ref="E95" si="17">C95*E24</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C96">
-        <f t="shared" ref="C96:C131" si="24">C26*2</f>
-        <v>524</v>
+        <f t="shared" ref="C96" si="18">C26*2</f>
+        <v>728</v>
       </c>
       <c r="D96">
-        <f t="shared" ref="D96:D125" si="25">C96*D26</f>
-        <v>0</v>
+        <f t="shared" ref="D96" si="19">C96*D26</f>
+        <v>264992</v>
       </c>
       <c r="E96">
-        <f t="shared" ref="E96:E131" si="26">C96*E26</f>
+        <f t="shared" ref="E96" si="20">C96*E26</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="B97" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="C97">
-        <f t="shared" si="24"/>
-        <v>1144</v>
-      </c>
-      <c r="D97">
-        <f t="shared" si="25"/>
-        <v>654368</v>
+        <v>209</v>
+      </c>
+      <c r="D97" t="e">
+        <f>#REF!*D28</f>
+        <v>#REF!</v>
       </c>
       <c r="E97">
-        <f t="shared" si="26"/>
+        <f>C97*E28</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B98" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C98">
-        <f t="shared" si="24"/>
-        <v>532</v>
+        <f t="shared" ref="C98:C133" si="21">C28*2</f>
+        <v>524</v>
       </c>
       <c r="D98">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="D98:D127" si="22">C98*D28</f>
         <v>0</v>
       </c>
       <c r="E98">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="E98:E133" si="23">C98*E28</f>
         <v>0</v>
       </c>
     </row>
@@ -10577,83 +10601,78 @@
         <v>40</v>
       </c>
       <c r="B99" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C99">
-        <f t="shared" si="24"/>
-        <v>524</v>
+        <f t="shared" si="21"/>
+        <v>1144</v>
       </c>
       <c r="D99">
-        <f t="shared" si="25"/>
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>654368</v>
       </c>
       <c r="E99">
-        <f t="shared" si="26"/>
-        <v>137288</v>
+        <f t="shared" si="23"/>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B100" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C100">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>532</v>
       </c>
       <c r="D100">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E100">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B101" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C101">
-        <f t="shared" si="24"/>
-        <v>0</v>
+        <f t="shared" si="21"/>
+        <v>524</v>
       </c>
       <c r="D101">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E101">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
+        <f t="shared" si="23"/>
+        <v>137288</v>
+      </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>44</v>
       </c>
       <c r="B102" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C102">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D102">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E102">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -10662,178 +10681,183 @@
         <v>44</v>
       </c>
       <c r="B103" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C103">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D103">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E103">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>44</v>
       </c>
       <c r="B104" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C104">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D104">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E104">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B105" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C105">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D105">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E105">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B106" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C106">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D106">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E106">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B107" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C107">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D107">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E107">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B108" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C108">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D108">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E108">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B109" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C109">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D109">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E109">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B110" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C110">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D110">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E110">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B111" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C111">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D111">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E111">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -10842,78 +10866,78 @@
         <v>59</v>
       </c>
       <c r="B112" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C112">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D112">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E112">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B113" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C113">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D113">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E113">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B114" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C114">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D114">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E114">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B115" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C115">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D115">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E115">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -10922,18 +10946,18 @@
         <v>65</v>
       </c>
       <c r="B116" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C116">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D116">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E116">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -10942,58 +10966,58 @@
         <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C117">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D117">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E117">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C118">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D118">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E118">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B119" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C119">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D119">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E119">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -11002,58 +11026,58 @@
         <v>70</v>
       </c>
       <c r="B120" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C120">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D120">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E120">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C121">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D121">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E121">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C122">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D122">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E122">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -11062,58 +11086,58 @@
         <v>74</v>
       </c>
       <c r="B123" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C123">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D123">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E123">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B124" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C124">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D124">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E124">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B125" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C125">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D125">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E125">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -11122,69 +11146,69 @@
         <v>78</v>
       </c>
       <c r="B126" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C126">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D126">
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E126">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B127" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C127">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D127">
-        <f>C127*D57</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E127">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B128" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C128">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D128">
-        <f>C128*D58</f>
         <v>0</v>
       </c>
       <c r="E128">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B129" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C129">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D129">
@@ -11192,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
@@ -11201,10 +11225,10 @@
         <v>83</v>
       </c>
       <c r="B130" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C130">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D130">
@@ -11212,19 +11236,19 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <f t="shared" si="26"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B131" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C131">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D131">
@@ -11232,105 +11256,129 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D139" s="1" t="s">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>83</v>
+      </c>
+      <c r="B132" t="s">
+        <v>86</v>
+      </c>
+      <c r="C132">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <f>C132*D62</f>
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>87</v>
+      </c>
+      <c r="B133" t="s">
+        <v>88</v>
+      </c>
+      <c r="C133">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <f>C133*D63</f>
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D141" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D140" t="e">
-        <f t="shared" ref="D140:E140" si="27">SUM(D75:D131)</f>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D142" t="e">
+        <f t="shared" ref="D142:E142" si="24">SUM(D77:D133)</f>
         <v>#REF!</v>
       </c>
-      <c r="E140" t="e">
-        <f t="shared" si="27"/>
+      <c r="E142" t="e">
+        <f t="shared" si="24"/>
         <v>#REF!</v>
       </c>
-      <c r="H140" t="e">
-        <f>SUM(D140:E140)</f>
+      <c r="H142" t="e">
+        <f>SUM(D142:E142)</f>
         <v>#REF!</v>
       </c>
-      <c r="I140" s="3" t="e">
-        <f>H140/H71</f>
+      <c r="I142" s="3" t="e">
+        <f>H142/H73</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D141" s="3" t="e">
-        <f t="shared" ref="D141:E141" si="28">D140/D71</f>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D143" s="3" t="e">
+        <f t="shared" ref="D143:E143" si="25">D142/D73</f>
         <v>#REF!</v>
       </c>
-      <c r="E141" s="3" t="e">
-        <f t="shared" si="28"/>
+      <c r="E143" s="3" t="e">
+        <f t="shared" si="25"/>
         <v>#REF!</v>
       </c>
-      <c r="H141" s="3" t="e">
-        <f>H140/F71</f>
+      <c r="H143" s="3" t="e">
+        <f>H142/F73</f>
         <v>#REF!</v>
       </c>
-      <c r="I141" t="s">
+      <c r="I143" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B211" s="1" t="s">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C211" s="1"/>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>13</v>
-      </c>
-      <c r="B212">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>17</v>
-      </c>
-      <c r="B213">
-        <v>1</v>
-      </c>
+      <c r="C213" s="1"/>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B214">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B215">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B216">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B217">
         <v>5</v>
@@ -11338,7 +11386,7 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -11346,47 +11394,47 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B219">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B220">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B221">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B222">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B223">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -11394,91 +11442,107 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B225">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="B226">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B227">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B228">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B229">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B230">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B231">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B232">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B233">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
+        <v>81</v>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>83</v>
+      </c>
+      <c r="B235">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
         <v>87</v>
       </c>
-      <c r="B234">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A236" s="1"/>
-      <c r="B236" s="1">
-        <f>SUM(B212:B234)</f>
+      <c r="B236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1">
+        <f>SUM(B214:B236)</f>
         <v>53</v>
       </c>
-      <c r="C236" s="1"/>
+      <c r="C238" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8923E057-B6B0-469A-86F0-5955307FA83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02039C90-BB46-4529-8FA0-E59AB49330E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
+    <workbookView xWindow="1764" yWindow="1848" windowWidth="21276" windowHeight="9960" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
   <sheets>
     <sheet name="pelipaikat" sheetId="1" r:id="rId1"/>
@@ -9362,18 +9362,20 @@
       <c r="F5" s="14">
         <v>1</v>
       </c>
-      <c r="G5" s="14"/>
+      <c r="G5" s="14">
+        <v>2</v>
+      </c>
       <c r="H5" s="14">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="14">
         <f t="shared" si="0"/>
-        <v>284</v>
+        <v>568</v>
       </c>
       <c r="J5" s="14">
         <f t="shared" si="1"/>
-        <v>568</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -9609,19 +9611,19 @@
       </c>
       <c r="G16" s="9">
         <f>SUM(G2:G15)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H16" s="9">
         <f>SUM(D16:G16)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I16" s="9">
         <f>SUM(I2:I12)</f>
-        <v>2606</v>
+        <v>2890</v>
       </c>
       <c r="J16" s="9">
         <f>SUM(J2:J12)</f>
-        <v>5212</v>
+        <v>5780</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -9637,11 +9639,11 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8">
         <f>I16/H16</f>
-        <v>137.15789473684211</v>
+        <v>137.61904761904762</v>
       </c>
       <c r="J17" s="8">
         <f>J16/H16</f>
-        <v>274.31578947368422</v>
+        <v>275.23809523809524</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -9680,7 +9682,7 @@
         <v>106</v>
       </c>
       <c r="C21" s="8">
-        <f>2*C2</f>
+        <f t="shared" ref="C21:C31" si="4">2*C2</f>
         <v>240</v>
       </c>
       <c r="D21" s="8">
@@ -9692,11 +9694,11 @@
         <v>240</v>
       </c>
       <c r="F21" s="8">
-        <f>F2*C21</f>
+        <f t="shared" ref="F21:G23" si="5">F2*C21</f>
         <v>240</v>
       </c>
       <c r="G21" s="8">
-        <f>G2*D21</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H21" s="8"/>
@@ -9714,11 +9716,11 @@
         <v>113</v>
       </c>
       <c r="C22" s="6">
-        <f>2*C3</f>
+        <f t="shared" si="4"/>
         <v>468</v>
       </c>
       <c r="D22" s="6">
-        <f t="shared" ref="D22" si="4">D3*C22</f>
+        <f t="shared" ref="D22" si="6">D3*C22</f>
         <v>0</v>
       </c>
       <c r="E22" s="6">
@@ -9726,17 +9728,17 @@
         <v>0</v>
       </c>
       <c r="F22" s="6">
-        <f>F3*C22</f>
+        <f t="shared" si="5"/>
         <v>468</v>
       </c>
       <c r="G22" s="6">
-        <f>G3*D22</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="14">
-        <f t="shared" ref="J22:J31" si="5">SUM(D22:G22)</f>
+        <f t="shared" ref="J22:J31" si="7">SUM(D22:G22)</f>
         <v>468</v>
       </c>
     </row>
@@ -9748,7 +9750,7 @@
         <v>139</v>
       </c>
       <c r="C23" s="8">
-        <f>2*C4</f>
+        <f t="shared" si="4"/>
         <v>284</v>
       </c>
       <c r="D23" s="8">
@@ -9760,11 +9762,11 @@
         <v>0</v>
       </c>
       <c r="F23" s="8">
-        <f>F4*C23</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G23" s="8">
-        <f>G4*D23</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H23" s="8"/>
@@ -9782,11 +9784,11 @@
         <v>107</v>
       </c>
       <c r="C24" s="14">
-        <f>2*C5</f>
+        <f t="shared" si="4"/>
         <v>284</v>
       </c>
       <c r="D24" s="14">
-        <f t="shared" ref="D24" si="6">D5*C24</f>
+        <f t="shared" ref="D24" si="8">D5*C24</f>
         <v>284</v>
       </c>
       <c r="E24" s="14">
@@ -9794,18 +9796,18 @@
         <v>0</v>
       </c>
       <c r="F24" s="14">
-        <f t="shared" ref="F24:G24" si="7">F5*C24</f>
+        <f t="shared" ref="F24:G24" si="9">F5*C24</f>
         <v>284</v>
       </c>
       <c r="G24" s="14">
-        <f t="shared" si="7"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>568</v>
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="14">
-        <f t="shared" si="5"/>
-        <v>568</v>
+        <f t="shared" si="7"/>
+        <v>1136</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -9816,7 +9818,7 @@
         <v>138</v>
       </c>
       <c r="C25" s="8">
-        <f>2*C6</f>
+        <f t="shared" si="4"/>
         <v>94</v>
       </c>
       <c r="D25" s="8">
@@ -9838,7 +9840,7 @@
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -9850,29 +9852,29 @@
         <v>105</v>
       </c>
       <c r="C26" s="14">
-        <f>2*C7</f>
+        <f t="shared" si="4"/>
         <v>364</v>
       </c>
       <c r="D26" s="14">
-        <f t="shared" ref="D26" si="8">D7*C26</f>
+        <f t="shared" ref="D26" si="10">D7*C26</f>
         <v>364</v>
       </c>
       <c r="E26" s="14">
-        <f>E7*C26</f>
+        <f t="shared" ref="E26:E31" si="11">E7*C26</f>
         <v>0</v>
       </c>
       <c r="F26" s="14">
-        <f>F7*C26</f>
+        <f t="shared" ref="F26:G31" si="12">F7*C26</f>
         <v>364</v>
       </c>
       <c r="G26" s="14">
-        <f>G7*D26</f>
+        <f t="shared" si="12"/>
         <v>364</v>
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1092</v>
       </c>
     </row>
@@ -9884,29 +9886,29 @@
         <v>103</v>
       </c>
       <c r="C27" s="8">
-        <f>2*C8</f>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="D27" s="8">
-        <f t="shared" ref="D27" si="9">D8*C27</f>
+        <f t="shared" ref="D27" si="13">D8*C27</f>
         <v>84</v>
       </c>
       <c r="E27" s="8">
-        <f>E8*C27</f>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="F27" s="8">
-        <f>F8*C27</f>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="G27" s="8">
-        <f>G8*D27</f>
+        <f t="shared" si="12"/>
         <v>84</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
       <c r="J27" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>336</v>
       </c>
     </row>
@@ -9918,29 +9920,29 @@
         <v>115</v>
       </c>
       <c r="C28" s="14">
-        <f>2*C9</f>
+        <f t="shared" si="4"/>
         <v>262</v>
       </c>
       <c r="D28" s="14">
-        <f t="shared" ref="D28" si="10">D9*C28</f>
+        <f t="shared" ref="D28" si="14">D9*C28</f>
         <v>0</v>
       </c>
       <c r="E28" s="14">
-        <f>E9*C28</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <f>F9*C28</f>
+        <f t="shared" si="12"/>
         <v>262</v>
       </c>
       <c r="G28" s="14">
-        <f>G9*D28</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="14"/>
       <c r="J28" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>262</v>
       </c>
     </row>
@@ -9952,29 +9954,29 @@
         <v>109</v>
       </c>
       <c r="C29" s="8">
-        <f>2*C10</f>
+        <f t="shared" si="4"/>
         <v>572</v>
       </c>
       <c r="D29" s="8">
-        <f t="shared" ref="D29" si="11">D10*C29</f>
+        <f t="shared" ref="D29" si="15">D10*C29</f>
         <v>572</v>
       </c>
       <c r="E29" s="8">
-        <f>E10*C29</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F29" s="8">
-        <f>F10*C29</f>
+        <f t="shared" si="12"/>
         <v>572</v>
       </c>
       <c r="G29" s="8">
-        <f>G10*D29</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
       <c r="J29" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1144</v>
       </c>
     </row>
@@ -9986,29 +9988,29 @@
         <v>116</v>
       </c>
       <c r="C30" s="14">
-        <f>2*C11</f>
+        <f t="shared" si="4"/>
         <v>266</v>
       </c>
       <c r="D30" s="14">
-        <f t="shared" ref="D30" si="12">D11*C30</f>
+        <f t="shared" ref="D30" si="16">D11*C30</f>
         <v>0</v>
       </c>
       <c r="E30" s="14">
-        <f>E11*C30</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="F30" s="14">
-        <f>F11*C30</f>
+        <f t="shared" si="12"/>
         <v>266</v>
       </c>
       <c r="G30" s="14">
-        <f>G11*D30</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>266</v>
       </c>
     </row>
@@ -10020,29 +10022,29 @@
         <v>111</v>
       </c>
       <c r="C31" s="8">
-        <f>2*C12</f>
+        <f t="shared" si="4"/>
         <v>262</v>
       </c>
       <c r="D31" s="8">
-        <f t="shared" ref="D31" si="13">D12*C31</f>
+        <f t="shared" ref="D31" si="17">D12*C31</f>
         <v>0</v>
       </c>
       <c r="E31" s="8">
-        <f>E12*C31</f>
+        <f t="shared" si="11"/>
         <v>262</v>
       </c>
       <c r="F31" s="8">
-        <f>F12*C31</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G31" s="8">
-        <f>G12*D31</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
       <c r="J31" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>262</v>
       </c>
     </row>
@@ -10063,17 +10065,17 @@
         <v>2540</v>
       </c>
       <c r="G33" s="9">
-        <f t="shared" ref="G33" si="14">SUM(G21:G31)</f>
-        <v>448</v>
+        <f t="shared" ref="G33" si="18">SUM(G21:G31)</f>
+        <v>1016</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9">
         <f>SUM(D33:G33)</f>
-        <v>5118</v>
+        <v>5686</v>
       </c>
       <c r="J33" s="9">
         <f>SUM(J21:J31)</f>
-        <v>5118</v>
+        <v>5686</v>
       </c>
     </row>
     <row r="64" spans="8:8" x14ac:dyDescent="0.3">
@@ -10093,13 +10095,13 @@
       <c r="I65" s="2"/>
       <c r="J65" s="4">
         <f>SUM(J2:J63)</f>
-        <v>20934.315789473687</v>
+        <v>23207.238095238095</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J72">
         <f>SUM(J2:J63)</f>
-        <v>20934.315789473687</v>
+        <v>23207.238095238095</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -10117,15 +10119,15 @@
       </c>
       <c r="H73">
         <f>SUM(H2:H63)</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I73">
         <f>SUM(I2:I63)</f>
-        <v>10467.157894736843</v>
+        <v>11603.619047619048</v>
       </c>
       <c r="J73">
         <f>2*I73</f>
-        <v>20934.315789473687</v>
+        <v>23207.238095238095</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -10325,15 +10327,15 @@
         <v>25</v>
       </c>
       <c r="C85">
-        <f>C13*2</f>
+        <f t="shared" ref="C85:C94" si="19">C13*2</f>
         <v>0</v>
       </c>
       <c r="D85">
-        <f>C85*D13</f>
+        <f t="shared" ref="D85:D94" si="20">C85*D13</f>
         <v>0</v>
       </c>
       <c r="E85">
-        <f>C85*E13</f>
+        <f t="shared" ref="E85:E94" si="21">C85*E13</f>
         <v>0</v>
       </c>
     </row>
@@ -10345,15 +10347,15 @@
         <v>26</v>
       </c>
       <c r="C86">
-        <f>C14*2</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D86">
-        <f>C86*D14</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E86">
-        <f>C86*E14</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10365,15 +10367,15 @@
         <v>27</v>
       </c>
       <c r="C87">
-        <f>C15*2</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D87">
-        <f>C87*D15</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E87">
-        <f>C87*E15</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10385,15 +10387,15 @@
         <v>29</v>
       </c>
       <c r="C88">
-        <f>C16*2</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D88">
-        <f>C88*D16</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E88">
-        <f>C88*E16</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10405,15 +10407,15 @@
         <v>31</v>
       </c>
       <c r="C89">
-        <f>C17*2</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D89">
-        <f>C89*D17</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E89">
-        <f>C89*E17</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10425,15 +10427,15 @@
         <v>32</v>
       </c>
       <c r="C90">
-        <f>C18*2</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D90">
-        <f>C90*D18</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E90">
-        <f>C90*E18</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10445,15 +10447,15 @@
         <v>33</v>
       </c>
       <c r="C91">
-        <f>C19*2</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="D91">
-        <f>C91*D19</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E91">
-        <f>C91*E19</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10465,15 +10467,15 @@
         <v>34</v>
       </c>
       <c r="C92" t="e">
-        <f>C20*2</f>
+        <f t="shared" si="19"/>
         <v>#VALUE!</v>
       </c>
       <c r="D92" t="e">
-        <f>C92*D20</f>
+        <f t="shared" si="20"/>
         <v>#VALUE!</v>
       </c>
       <c r="E92" t="e">
-        <f>C92*E20</f>
+        <f t="shared" si="21"/>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -10485,15 +10487,15 @@
         <v>35</v>
       </c>
       <c r="C93">
-        <f>C21*2</f>
+        <f t="shared" si="19"/>
         <v>480</v>
       </c>
       <c r="D93">
-        <f>C93*D21</f>
+        <f t="shared" si="20"/>
         <v>115200</v>
       </c>
       <c r="E93">
-        <f>C93*E21</f>
+        <f t="shared" si="21"/>
         <v>115200</v>
       </c>
     </row>
@@ -10505,15 +10507,15 @@
         <v>101</v>
       </c>
       <c r="C94">
-        <f>C22*2</f>
+        <f t="shared" si="19"/>
         <v>936</v>
       </c>
       <c r="D94">
-        <f>C94*D22</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E94">
-        <f>C94*E22</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -10525,15 +10527,15 @@
         <v>37</v>
       </c>
       <c r="C95">
-        <f t="shared" ref="C95" si="15">C24*2</f>
+        <f t="shared" ref="C95" si="22">C24*2</f>
         <v>568</v>
       </c>
       <c r="D95">
-        <f t="shared" ref="D95" si="16">C95*D24</f>
+        <f t="shared" ref="D95" si="23">C95*D24</f>
         <v>161312</v>
       </c>
       <c r="E95">
-        <f t="shared" ref="E95" si="17">C95*E24</f>
+        <f t="shared" ref="E95" si="24">C95*E24</f>
         <v>0</v>
       </c>
     </row>
@@ -10545,15 +10547,15 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <f t="shared" ref="C96" si="18">C26*2</f>
+        <f t="shared" ref="C96" si="25">C26*2</f>
         <v>728</v>
       </c>
       <c r="D96">
-        <f t="shared" ref="D96" si="19">C96*D26</f>
+        <f t="shared" ref="D96" si="26">C96*D26</f>
         <v>264992</v>
       </c>
       <c r="E96">
-        <f t="shared" ref="E96" si="20">C96*E26</f>
+        <f t="shared" ref="E96" si="27">C96*E26</f>
         <v>0</v>
       </c>
     </row>
@@ -10584,15 +10586,15 @@
         <v>39</v>
       </c>
       <c r="C98">
-        <f t="shared" ref="C98:C133" si="21">C28*2</f>
+        <f t="shared" ref="C98:C133" si="28">C28*2</f>
         <v>524</v>
       </c>
       <c r="D98">
-        <f t="shared" ref="D98:D127" si="22">C98*D28</f>
+        <f t="shared" ref="D98:D127" si="29">C98*D28</f>
         <v>0</v>
       </c>
       <c r="E98">
-        <f t="shared" ref="E98:E133" si="23">C98*E28</f>
+        <f t="shared" ref="E98:E133" si="30">C98*E28</f>
         <v>0</v>
       </c>
     </row>
@@ -10604,15 +10606,15 @@
         <v>41</v>
       </c>
       <c r="C99">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>1144</v>
       </c>
       <c r="D99">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>654368</v>
       </c>
       <c r="E99">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10624,15 +10626,15 @@
         <v>42</v>
       </c>
       <c r="C100">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>532</v>
       </c>
       <c r="D100">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E100">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10644,15 +10646,15 @@
         <v>43</v>
       </c>
       <c r="C101">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>524</v>
       </c>
       <c r="D101">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E101">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>137288</v>
       </c>
     </row>
@@ -10664,15 +10666,15 @@
         <v>45</v>
       </c>
       <c r="C102">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D102">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E102">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10684,15 +10686,15 @@
         <v>46</v>
       </c>
       <c r="C103">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D103">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E103">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="F103" s="1"/>
@@ -10709,15 +10711,15 @@
         <v>47</v>
       </c>
       <c r="C104">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D104">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E104">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10729,15 +10731,15 @@
         <v>48</v>
       </c>
       <c r="C105">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D105">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E105">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10749,15 +10751,15 @@
         <v>49</v>
       </c>
       <c r="C106">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D106">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E106">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10769,15 +10771,15 @@
         <v>51</v>
       </c>
       <c r="C107">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D107">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E107">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10789,15 +10791,15 @@
         <v>53</v>
       </c>
       <c r="C108">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D108">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E108">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10809,15 +10811,15 @@
         <v>55</v>
       </c>
       <c r="C109">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D109">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E109">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10829,15 +10831,15 @@
         <v>57</v>
       </c>
       <c r="C110">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D110">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E110">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10849,15 +10851,15 @@
         <v>58</v>
       </c>
       <c r="C111">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D111">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E111">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10869,15 +10871,15 @@
         <v>60</v>
       </c>
       <c r="C112">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D112">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E112">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10889,15 +10891,15 @@
         <v>61</v>
       </c>
       <c r="C113">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D113">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E113">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10909,15 +10911,15 @@
         <v>62</v>
       </c>
       <c r="C114">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D114">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E114">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10929,15 +10931,15 @@
         <v>64</v>
       </c>
       <c r="C115">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D115">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E115">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10949,15 +10951,15 @@
         <v>66</v>
       </c>
       <c r="C116">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D116">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E116">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10969,15 +10971,15 @@
         <v>67</v>
       </c>
       <c r="C117">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D117">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E117">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -10989,15 +10991,15 @@
         <v>68</v>
       </c>
       <c r="C118">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D118">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E118">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11009,15 +11011,15 @@
         <v>69</v>
       </c>
       <c r="C119">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D119">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E119">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11029,15 +11031,15 @@
         <v>71</v>
       </c>
       <c r="C120">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D120">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E120">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11049,15 +11051,15 @@
         <v>72</v>
       </c>
       <c r="C121">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D121">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E121">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11069,15 +11071,15 @@
         <v>73</v>
       </c>
       <c r="C122">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D122">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E122">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11089,15 +11091,15 @@
         <v>75</v>
       </c>
       <c r="C123">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D123">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E123">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11109,15 +11111,15 @@
         <v>76</v>
       </c>
       <c r="C124">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D124">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E124">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11129,15 +11131,15 @@
         <v>77</v>
       </c>
       <c r="C125">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D125">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E125">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11149,15 +11151,15 @@
         <v>79</v>
       </c>
       <c r="C126">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D126">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E126">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11169,15 +11171,15 @@
         <v>80</v>
       </c>
       <c r="C127">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D127">
-        <f t="shared" si="22"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="E127">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11189,14 +11191,14 @@
         <v>102</v>
       </c>
       <c r="C128">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11208,7 +11210,7 @@
         <v>82</v>
       </c>
       <c r="C129">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D129">
@@ -11216,7 +11218,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11228,7 +11230,7 @@
         <v>84</v>
       </c>
       <c r="C130">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D130">
@@ -11236,7 +11238,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11248,7 +11250,7 @@
         <v>85</v>
       </c>
       <c r="C131">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D131">
@@ -11256,7 +11258,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11268,7 +11270,7 @@
         <v>86</v>
       </c>
       <c r="C132">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D132">
@@ -11276,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11288,7 +11290,7 @@
         <v>88</v>
       </c>
       <c r="C133">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="D133">
@@ -11296,7 +11298,7 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <f t="shared" si="23"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
@@ -11310,11 +11312,11 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D142" t="e">
-        <f t="shared" ref="D142:E142" si="24">SUM(D77:D133)</f>
+        <f t="shared" ref="D142:E142" si="31">SUM(D77:D133)</f>
         <v>#REF!</v>
       </c>
       <c r="E142" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="31"/>
         <v>#REF!</v>
       </c>
       <c r="H142" t="e">
@@ -11328,11 +11330,11 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D143" s="3" t="e">
-        <f t="shared" ref="D143:E143" si="25">D142/D73</f>
+        <f t="shared" ref="D143:E143" si="32">D142/D73</f>
         <v>#REF!</v>
       </c>
       <c r="E143" s="3" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>#REF!</v>
       </c>
       <c r="H143" s="3" t="e">

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02039C90-BB46-4529-8FA0-E59AB49330E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F18B872-D874-4698-AE15-464ACFDADE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1764" yWindow="1848" windowWidth="21276" windowHeight="9960" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
   <sheets>
     <sheet name="pelipaikat" sheetId="1" r:id="rId1"/>
@@ -9392,19 +9392,19 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="8">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="8">
         <f>C6*H6</f>
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="J6" s="8">
         <f t="shared" ref="J6:J12" si="3">2*I6</f>
-        <v>94</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -9611,19 +9611,19 @@
       </c>
       <c r="G16" s="9">
         <f>SUM(G2:G15)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="9">
         <f>SUM(D16:G16)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I16" s="9">
         <f>SUM(I2:I12)</f>
-        <v>2890</v>
+        <v>2937</v>
       </c>
       <c r="J16" s="9">
         <f>SUM(J2:J12)</f>
-        <v>5780</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -9639,11 +9639,11 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8">
         <f>I16/H16</f>
-        <v>137.61904761904762</v>
+        <v>133.5</v>
       </c>
       <c r="J17" s="8">
         <f>J16/H16</f>
-        <v>275.23809523809524</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -9796,7 +9796,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="14">
-        <f t="shared" ref="F24:G24" si="9">F5*C24</f>
+        <f t="shared" ref="F24:G25" si="9">F5*C24</f>
         <v>284</v>
       </c>
       <c r="G24" s="14">
@@ -9834,14 +9834,14 @@
         <v>0</v>
       </c>
       <c r="G25" s="8">
-        <f>2*D25</f>
-        <v>0</v>
+        <f>G6*C25</f>
+        <v>188</v>
       </c>
       <c r="H25" s="8"/>
       <c r="I25" s="8"/>
       <c r="J25" s="8">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -10066,16 +10066,16 @@
       </c>
       <c r="G33" s="9">
         <f t="shared" ref="G33" si="18">SUM(G21:G31)</f>
-        <v>1016</v>
+        <v>1204</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9">
         <f>SUM(D33:G33)</f>
-        <v>5686</v>
+        <v>5874</v>
       </c>
       <c r="J33" s="9">
         <f>SUM(J21:J31)</f>
-        <v>5686</v>
+        <v>5874</v>
       </c>
     </row>
     <row r="64" spans="8:8" x14ac:dyDescent="0.3">
@@ -10095,13 +10095,13 @@
       <c r="I65" s="2"/>
       <c r="J65" s="4">
         <f>SUM(J2:J63)</f>
-        <v>23207.238095238095</v>
+        <v>23763</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J72">
         <f>SUM(J2:J63)</f>
-        <v>23207.238095238095</v>
+        <v>23763</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
@@ -10119,15 +10119,15 @@
       </c>
       <c r="H73">
         <f>SUM(H2:H63)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I73">
         <f>SUM(I2:I63)</f>
-        <v>11603.619047619048</v>
+        <v>11881.5</v>
       </c>
       <c r="J73">
         <f>2*I73</f>
-        <v>23207.238095238095</v>
+        <v>23763</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F18B872-D874-4698-AE15-464ACFDADE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B658DCD6-F21E-4822-9645-9087D5E25010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="142">
   <si>
     <t>Paikkakunta</t>
   </si>
@@ -457,6 +457,12 @@
   </si>
   <si>
     <t>Beachbox</t>
+  </si>
+  <si>
+    <t>Karkkila</t>
+  </si>
+  <si>
+    <t>Karkkilan Beach Volley Areena</t>
   </si>
 </sst>
 </file>
@@ -606,8 +612,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9216,7 +9222,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB3AEAB-3835-4342-9FF8-FBE02F12A238}">
-  <dimension ref="A1:J238"/>
+  <dimension ref="A1:J240"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" customWidth="1"/>
@@ -9306,7 +9312,7 @@
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="14">
-        <f t="shared" ref="H3:H12" si="2">SUM(D3:G3)</f>
+        <f t="shared" ref="H3:H13" si="2">SUM(D3:G3)</f>
         <v>1</v>
       </c>
       <c r="I3" s="6">
@@ -9363,26 +9369,26 @@
         <v>1</v>
       </c>
       <c r="G5" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" s="14">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="14">
         <f t="shared" si="0"/>
-        <v>568</v>
+        <v>710</v>
       </c>
       <c r="J5" s="14">
         <f t="shared" si="1"/>
-        <v>1136</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>138</v>
       </c>
       <c r="C6" s="8">
@@ -9403,7 +9409,7 @@
         <v>94</v>
       </c>
       <c r="J6" s="8">
-        <f t="shared" ref="J6:J12" si="3">2*I6</f>
+        <f t="shared" ref="J6:J13" si="3">2*I6</f>
         <v>188</v>
       </c>
     </row>
@@ -9442,81 +9448,77 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>103</v>
+        <v>140</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>141</v>
       </c>
       <c r="C8" s="8">
-        <v>42</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
       <c r="H8" s="8">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I8" s="8">
-        <f>C8*H8</f>
-        <v>168</v>
+        <f t="shared" ref="I8:I13" si="4">C8*H8</f>
+        <v>0</v>
       </c>
       <c r="J8" s="8">
         <f t="shared" si="3"/>
-        <v>336</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>115</v>
+        <v>74</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>103</v>
       </c>
       <c r="C9" s="14">
-        <v>131</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="D9" s="14">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14">
+        <v>1</v>
+      </c>
       <c r="F9" s="14">
         <v>1</v>
       </c>
-      <c r="G9" s="14"/>
+      <c r="G9" s="14">
+        <v>1</v>
+      </c>
       <c r="H9" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" s="14">
-        <f>C9*H9</f>
-        <v>131</v>
+        <f t="shared" si="4"/>
+        <v>168</v>
       </c>
       <c r="J9" s="14">
         <f t="shared" si="3"/>
-        <v>262</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>115</v>
       </c>
       <c r="C10" s="8">
-        <v>286</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8">
         <v>1</v>
@@ -9524,28 +9526,30 @@
       <c r="G10" s="8"/>
       <c r="H10" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" s="8">
-        <f>C10*H10</f>
-        <v>572</v>
+        <f t="shared" si="4"/>
+        <v>131</v>
       </c>
       <c r="J10" s="8">
         <f t="shared" si="3"/>
-        <v>1144</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C11" s="14">
-        <v>133</v>
-      </c>
-      <c r="D11" s="14"/>
+        <v>286</v>
+      </c>
+      <c r="D11" s="14">
+        <v>1</v>
+      </c>
       <c r="E11" s="14"/>
       <c r="F11" s="14">
         <v>1</v>
@@ -9553,15 +9557,15 @@
       <c r="G11" s="14"/>
       <c r="H11" s="14">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="14">
-        <f>C11*H11</f>
-        <v>133</v>
+        <f t="shared" si="4"/>
+        <v>572</v>
       </c>
       <c r="J11" s="14">
         <f t="shared" si="3"/>
-        <v>266</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -9569,634 +9573,657 @@
         <v>110</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C12" s="8">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="8">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
       <c r="G12" s="8"/>
       <c r="H12" s="8">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I12" s="8">
-        <f>C12*H12</f>
-        <v>131</v>
+        <f t="shared" si="4"/>
+        <v>133</v>
       </c>
       <c r="J12" s="8">
         <f t="shared" si="3"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="14">
+        <v>131</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="I13" s="14">
+        <f t="shared" si="4"/>
+        <v>131</v>
+      </c>
+      <c r="J13" s="14">
+        <f t="shared" si="3"/>
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="9">
-        <f>SUM(D2:D15)</f>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9">
+        <f>SUM(D2:D16)</f>
         <v>5</v>
       </c>
-      <c r="E16" s="9">
-        <f>SUM(E2:E15)</f>
+      <c r="E17" s="9">
+        <f>SUM(E2:E16)</f>
         <v>3</v>
       </c>
-      <c r="F16" s="9">
-        <f>SUM(F2:F15)</f>
+      <c r="F17" s="9">
+        <f>SUM(F2:F16)</f>
         <v>8</v>
       </c>
-      <c r="G16" s="9">
-        <f>SUM(G2:G15)</f>
-        <v>6</v>
-      </c>
-      <c r="H16" s="9">
-        <f>SUM(D16:G16)</f>
-        <v>22</v>
-      </c>
-      <c r="I16" s="9">
-        <f>SUM(I2:I12)</f>
-        <v>2937</v>
-      </c>
-      <c r="J16" s="9">
-        <f>SUM(J2:J12)</f>
-        <v>5874</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+      <c r="G17" s="9">
+        <f>SUM(G2:G16)</f>
+        <v>7</v>
+      </c>
+      <c r="H17" s="9">
+        <f>SUM(D17:G17)</f>
+        <v>23</v>
+      </c>
+      <c r="I17" s="9">
+        <f>SUM(I2:I13)</f>
+        <v>3079</v>
+      </c>
+      <c r="J17" s="9">
+        <f>SUM(J2:J13)</f>
+        <v>6158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8">
-        <f>I16/H16</f>
-        <v>133.5</v>
-      </c>
-      <c r="J17" s="8">
-        <f>J16/H16</f>
-        <v>267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="7" t="s">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8">
+        <f>I17/H17</f>
+        <v>133.86956521739131</v>
+      </c>
+      <c r="J18" s="8">
+        <f>J17/H17</f>
+        <v>267.73913043478262</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D21" s="7">
         <v>2023</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E21" s="7">
         <v>2024</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F21" s="7">
         <v>2025</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G21" s="7">
         <v>2026</v>
       </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7" t="s">
+      <c r="H21" s="9"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="8">
-        <f t="shared" ref="C21:C31" si="4">2*C2</f>
+      <c r="C22" s="8">
+        <f t="shared" ref="C22:C33" si="5">2*C2</f>
         <v>240</v>
       </c>
-      <c r="D21" s="8">
-        <f>D2*C21</f>
+      <c r="D22" s="8">
+        <f>D2*C22</f>
         <v>240</v>
       </c>
-      <c r="E21" s="8">
-        <f>E2*C21</f>
+      <c r="E22" s="8">
+        <f>E2*C22</f>
         <v>240</v>
       </c>
-      <c r="F21" s="8">
-        <f t="shared" ref="F21:G23" si="5">F2*C21</f>
+      <c r="F22" s="8">
+        <f t="shared" ref="F22:G24" si="6">F2*C22</f>
         <v>240</v>
       </c>
-      <c r="G21" s="8">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8">
-        <f>SUM(D21:G21)</f>
+      <c r="G22" s="8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8">
+        <f>SUM(D22:G22)</f>
         <v>720</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B23" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="6">
-        <f t="shared" si="4"/>
-        <v>468</v>
-      </c>
-      <c r="D22" s="6">
-        <f t="shared" ref="D22" si="6">D3*C22</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="6">
-        <f>E3*C22</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="6">
+      <c r="C23" s="6">
         <f t="shared" si="5"/>
         <v>468</v>
       </c>
-      <c r="G22" s="6">
+      <c r="D23" s="6">
+        <f t="shared" ref="D23" si="7">D3*C23</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <f>E3*C23</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="6"/>
+        <v>468</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="14">
+        <f t="shared" ref="J23:J33" si="8">SUM(D23:G23)</f>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="14">
-        <f t="shared" ref="J22:J31" si="7">SUM(D22:G22)</f>
-        <v>468</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D24" s="8">
+        <f>D4*C24</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
+        <f>E4*C24</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8">
+        <f>SUM(D24:G24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" s="8">
-        <f t="shared" si="4"/>
+      <c r="B25" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="14">
+        <f t="shared" si="5"/>
         <v>284</v>
       </c>
-      <c r="D23" s="8">
-        <f>D4*C23</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="8">
-        <f>E4*C23</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="8">
+      <c r="D25" s="14">
+        <f t="shared" ref="D25" si="9">D5*C25</f>
+        <v>284</v>
+      </c>
+      <c r="E25" s="14">
+        <f>E5*C25</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <f t="shared" ref="F25:G25" si="10">F5*C25</f>
+        <v>284</v>
+      </c>
+      <c r="G25" s="14">
+        <f t="shared" si="10"/>
+        <v>852</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14">
+        <f t="shared" si="8"/>
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="8">
+        <v>94</v>
+      </c>
+      <c r="D26" s="8">
+        <f>2*D6</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <f>2*E6</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <f>2*F6</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="8">
+        <f>G6*C26</f>
+        <v>188</v>
+      </c>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8">
+        <f t="shared" si="8"/>
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="14">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8">
-        <f>SUM(D23:G23)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="C24" s="14">
-        <f t="shared" si="4"/>
-        <v>284</v>
-      </c>
-      <c r="D24" s="14">
-        <f t="shared" ref="D24" si="8">D5*C24</f>
-        <v>284</v>
-      </c>
-      <c r="E24" s="14">
-        <f>E5*C24</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="14">
-        <f t="shared" ref="F24:G25" si="9">F5*C24</f>
-        <v>284</v>
-      </c>
-      <c r="G24" s="14">
-        <f t="shared" si="9"/>
-        <v>568</v>
-      </c>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14">
-        <f t="shared" si="7"/>
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="8">
-        <f t="shared" si="4"/>
-        <v>94</v>
-      </c>
-      <c r="D25" s="8">
-        <f>2*D6</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="8">
-        <f>2*E6</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="8">
-        <f>2*F6</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="8">
-        <f>G6*C25</f>
-        <v>188</v>
-      </c>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8">
-        <f t="shared" si="7"/>
-        <v>188</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="14">
-        <f t="shared" si="4"/>
         <v>364</v>
       </c>
-      <c r="D26" s="14">
-        <f t="shared" ref="D26" si="10">D7*C26</f>
+      <c r="D27" s="14">
+        <f t="shared" ref="D27" si="11">D7*C27</f>
         <v>364</v>
       </c>
-      <c r="E26" s="14">
-        <f t="shared" ref="E26:E31" si="11">E7*C26</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="14">
-        <f t="shared" ref="F26:G31" si="12">F7*C26</f>
+      <c r="E27" s="14">
+        <f t="shared" ref="E27:E33" si="12">E7*C27</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <f>F7*C27</f>
         <v>364</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G27" s="14">
+        <f>G7*D27</f>
+        <v>364</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14">
+        <f t="shared" si="8"/>
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="8">
+        <f t="shared" si="5"/>
+        <v>232</v>
+      </c>
+      <c r="D28" s="8">
+        <f>D8*C28</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="8">
         <f t="shared" si="12"/>
-        <v>364</v>
-      </c>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14">
-        <f t="shared" si="7"/>
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8">
+        <f t="shared" ref="F28:F33" si="13">F8*C28</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <f>G8*C28</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B29" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C27" s="8">
-        <f t="shared" si="4"/>
+      <c r="C29" s="14">
+        <f t="shared" si="5"/>
         <v>84</v>
       </c>
-      <c r="D27" s="8">
-        <f t="shared" ref="D27" si="13">D8*C27</f>
+      <c r="D29" s="14">
+        <f t="shared" ref="D29" si="14">D9*C29</f>
         <v>84</v>
       </c>
-      <c r="E27" s="8">
-        <f t="shared" si="11"/>
-        <v>84</v>
-      </c>
-      <c r="F27" s="8">
+      <c r="E29" s="14">
         <f t="shared" si="12"/>
         <v>84</v>
       </c>
-      <c r="G27" s="8">
+      <c r="F29" s="14">
+        <f t="shared" si="13"/>
+        <v>84</v>
+      </c>
+      <c r="G29" s="14">
+        <f>G9*D29</f>
+        <v>84</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14">
+        <f t="shared" si="8"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" s="8">
+        <f t="shared" si="5"/>
+        <v>262</v>
+      </c>
+      <c r="D30" s="8">
+        <f t="shared" ref="D30" si="15">D10*C30</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="8">
         <f t="shared" si="12"/>
-        <v>84</v>
-      </c>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8">
-        <f t="shared" si="7"/>
-        <v>336</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B28" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" s="14">
-        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="8">
+        <f t="shared" si="13"/>
         <v>262</v>
       </c>
-      <c r="D28" s="14">
-        <f t="shared" ref="D28" si="14">D9*C28</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F28" s="14">
+      <c r="G30" s="8">
+        <f>G10*D30</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8">
+        <f t="shared" si="8"/>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="14">
+        <f t="shared" si="5"/>
+        <v>572</v>
+      </c>
+      <c r="D31" s="14">
+        <f t="shared" ref="D31" si="16">D11*C31</f>
+        <v>572</v>
+      </c>
+      <c r="E31" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <f t="shared" si="13"/>
+        <v>572</v>
+      </c>
+      <c r="G31" s="14">
+        <f>G11*D31</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14">
+        <f t="shared" si="8"/>
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="8">
+        <f t="shared" si="5"/>
+        <v>266</v>
+      </c>
+      <c r="D32" s="8">
+        <f t="shared" ref="D32" si="17">D12*C32</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="8">
+        <f t="shared" si="13"/>
+        <v>266</v>
+      </c>
+      <c r="G32" s="8">
+        <f>G12*D32</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8">
+        <f t="shared" si="8"/>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="14">
+        <f t="shared" si="5"/>
+        <v>262</v>
+      </c>
+      <c r="D33" s="14">
+        <f t="shared" ref="D33" si="18">D13*C33</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="14">
         <f t="shared" si="12"/>
         <v>262</v>
       </c>
-      <c r="G28" s="14">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14">
-        <f t="shared" si="7"/>
+      <c r="F33" s="14">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <f>G13*D33</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14">
+        <f t="shared" si="8"/>
         <v>262</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="C29" s="8">
-        <f t="shared" si="4"/>
-        <v>572</v>
-      </c>
-      <c r="D29" s="8">
-        <f t="shared" ref="D29" si="15">D10*C29</f>
-        <v>572</v>
-      </c>
-      <c r="E29" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F29" s="8">
-        <f t="shared" si="12"/>
-        <v>572</v>
-      </c>
-      <c r="G29" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8">
-        <f t="shared" si="7"/>
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="14">
-        <f t="shared" si="4"/>
-        <v>266</v>
-      </c>
-      <c r="D30" s="14">
-        <f t="shared" ref="D30" si="16">D11*C30</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="14">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <f t="shared" si="12"/>
-        <v>266</v>
-      </c>
-      <c r="G30" s="14">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14">
-        <f t="shared" si="7"/>
-        <v>266</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" s="8">
-        <f t="shared" si="4"/>
-        <v>262</v>
-      </c>
-      <c r="D31" s="8">
-        <f t="shared" ref="D31" si="17">D12*C31</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="8">
-        <f t="shared" si="11"/>
-        <v>262</v>
-      </c>
-      <c r="F31" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="G31" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8">
-        <f t="shared" si="7"/>
-        <v>262</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9">
-        <f>SUM(D21:D31)</f>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9">
+        <f>SUM(D22:D33)</f>
         <v>1544</v>
       </c>
-      <c r="E33" s="9">
-        <f>SUM(E21:E31)</f>
+      <c r="E35" s="9">
+        <f>SUM(E22:E33)</f>
         <v>586</v>
       </c>
-      <c r="F33" s="9">
-        <f>SUM(F21:F31)</f>
+      <c r="F35" s="9">
+        <f>SUM(F22:F33)</f>
         <v>2540</v>
       </c>
-      <c r="G33" s="9">
-        <f t="shared" ref="G33" si="18">SUM(G21:G31)</f>
-        <v>1204</v>
-      </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9">
-        <f>SUM(D33:G33)</f>
-        <v>5874</v>
-      </c>
-      <c r="J33" s="9">
-        <f>SUM(J21:J31)</f>
-        <v>5874</v>
-      </c>
-    </row>
-    <row r="64" spans="8:8" x14ac:dyDescent="0.3">
-      <c r="H64" t="s">
+      <c r="G35" s="9">
+        <f t="shared" ref="G35" si="19">SUM(G22:G33)</f>
+        <v>1488</v>
+      </c>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9">
+        <f>SUM(D35:G35)</f>
+        <v>6158</v>
+      </c>
+      <c r="J35" s="9">
+        <f>SUM(J22:J33)</f>
+        <v>6158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H66" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="4">
-        <f>SUM(J2:J63)</f>
-        <v>23763</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J72">
-        <f>SUM(J2:J63)</f>
-        <v>23763</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D73">
-        <f>SUM(D2:D63)</f>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="4">
+        <f>SUM(J2:J65)</f>
+        <v>24899.739130434784</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J74">
+        <f>SUM(J2:J65)</f>
+        <v>24899.739130434784</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D75">
+        <f>SUM(D2:D65)</f>
         <v>5121</v>
       </c>
-      <c r="E73">
-        <f>SUM(E2:E63)</f>
+      <c r="E75">
+        <f>SUM(E2:E65)</f>
         <v>3202</v>
       </c>
-      <c r="F73">
-        <f>SUM(D73:E73)</f>
+      <c r="F75">
+        <f>SUM(D75:E75)</f>
         <v>8323</v>
       </c>
-      <c r="H73">
-        <f>SUM(H2:H63)</f>
-        <v>44</v>
-      </c>
-      <c r="I73">
-        <f>SUM(I2:I63)</f>
-        <v>11881.5</v>
-      </c>
-      <c r="J73">
-        <f>2*I73</f>
-        <v>23763</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A76" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="1" t="s">
+      <c r="H75">
+        <f>SUM(H2:H65)</f>
+        <v>46</v>
+      </c>
+      <c r="I75">
+        <f>SUM(I2:I65)</f>
+        <v>12449.869565217392</v>
+      </c>
+      <c r="J75">
+        <f>2*I75</f>
+        <v>24899.739130434784</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D78" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E78" s="1" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>13</v>
-      </c>
-      <c r="B77" t="s">
-        <v>14</v>
-      </c>
-      <c r="C77">
-        <f>C2*2</f>
-        <v>240</v>
-      </c>
-      <c r="D77">
-        <f>C77*D2</f>
-        <v>240</v>
-      </c>
-      <c r="E77">
-        <f>C77*E2</f>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>13</v>
-      </c>
-      <c r="B78" t="s">
-        <v>15</v>
-      </c>
-      <c r="C78">
-        <f>C5*2</f>
-        <v>284</v>
-      </c>
-      <c r="D78">
-        <f>C78*D5</f>
-        <v>284</v>
-      </c>
-      <c r="E78">
-        <f>C78*E5</f>
-        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
@@ -10204,119 +10231,119 @@
         <v>13</v>
       </c>
       <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79">
+        <f>C2*2</f>
+        <v>240</v>
+      </c>
+      <c r="D79">
+        <f>C79*D2</f>
+        <v>240</v>
+      </c>
+      <c r="E79">
+        <f>C79*E2</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80">
+        <f>C5*2</f>
+        <v>284</v>
+      </c>
+      <c r="D80">
+        <f>C80*D5</f>
+        <v>284</v>
+      </c>
+      <c r="E80">
+        <f>C80*E5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>13</v>
+      </c>
+      <c r="B81" t="s">
         <v>16</v>
       </c>
-      <c r="C79">
+      <c r="C81">
         <f>C7*2</f>
         <v>364</v>
       </c>
-      <c r="D79">
-        <f>C79*D7</f>
+      <c r="D81">
+        <f>C81*D7</f>
         <v>364</v>
       </c>
-      <c r="E79">
-        <f>C79*E7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="E81">
+        <f>C81*E7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
         <v>17</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B82" t="s">
         <v>18</v>
       </c>
-      <c r="C80" t="e">
+      <c r="C82" t="e">
         <f>#REF!*2</f>
         <v>#REF!</v>
       </c>
-      <c r="D80" t="e">
-        <f>C80*#REF!</f>
+      <c r="D82" t="e">
+        <f>C82*#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E80" t="e">
-        <f>C80*#REF!</f>
+      <c r="E82" t="e">
+        <f>C82*#REF!</f>
         <v>#REF!</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>19</v>
-      </c>
-      <c r="B81" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81">
-        <f>C8*2</f>
-        <v>84</v>
-      </c>
-      <c r="D81">
-        <f>C81*D8</f>
-        <v>84</v>
-      </c>
-      <c r="E81">
-        <f>C81*E8</f>
-        <v>84</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>19</v>
-      </c>
-      <c r="B82" t="s">
-        <v>21</v>
-      </c>
-      <c r="C82">
-        <f>C10*2</f>
-        <v>572</v>
-      </c>
-      <c r="D82">
-        <f>C82*D10</f>
-        <v>572</v>
-      </c>
-      <c r="E82">
-        <f>C82*E10</f>
-        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C83">
-        <f>C12*2</f>
-        <v>262</v>
+        <f>C9*2</f>
+        <v>84</v>
       </c>
       <c r="D83">
-        <f>C83*D12</f>
-        <v>0</v>
+        <f>C83*D9</f>
+        <v>84</v>
       </c>
       <c r="E83">
-        <f>C83*E12</f>
-        <v>262</v>
+        <f>C83*E9</f>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
-      </c>
-      <c r="C84" t="e">
-        <f>#REF!*2</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D84" t="e">
-        <f>C84*#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E84" t="e">
-        <f>C84*#REF!</f>
-        <v>#REF!</v>
+        <v>21</v>
+      </c>
+      <c r="C84">
+        <f>C11*2</f>
+        <v>572</v>
+      </c>
+      <c r="D84">
+        <f>C84*D11</f>
+        <v>572</v>
+      </c>
+      <c r="E84">
+        <f>C84*E11</f>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -10324,19 +10351,19 @@
         <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C85">
-        <f t="shared" ref="C85:C94" si="19">C13*2</f>
-        <v>0</v>
+        <f>C13*2</f>
+        <v>262</v>
       </c>
       <c r="D85">
-        <f t="shared" ref="D85:D94" si="20">C85*D13</f>
+        <f>C85*D13</f>
         <v>0</v>
       </c>
       <c r="E85">
-        <f t="shared" ref="E85:E94" si="21">C85*E13</f>
-        <v>0</v>
+        <f>C85*E13</f>
+        <v>262</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -10344,19 +10371,19 @@
         <v>22</v>
       </c>
       <c r="B86" t="s">
-        <v>26</v>
-      </c>
-      <c r="C86">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="D86">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E86">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="C86" t="e">
+        <f>#REF!*2</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D86" t="e">
+        <f>C86*#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E86" t="e">
+        <f>C86*#REF!</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -10364,78 +10391,78 @@
         <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C87">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="C87:C96" si="20">C14*2</f>
         <v>0</v>
       </c>
       <c r="D87">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D87:D96" si="21">C87*D14</f>
         <v>0</v>
       </c>
       <c r="E87">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="E87:E96" si="22">C87*E14</f>
         <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C88">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D88">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E88">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C89">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D89">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E89">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C90">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D90">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E90">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10444,18 +10471,18 @@
         <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C91">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="D91">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="E91">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10464,19 +10491,19 @@
         <v>30</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
-      </c>
-      <c r="C92" t="e">
-        <f t="shared" si="19"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D92" t="e">
+        <v>32</v>
+      </c>
+      <c r="C92">
         <f t="shared" si="20"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E92" t="e">
+        <v>0</v>
+      </c>
+      <c r="D92">
         <f t="shared" si="21"/>
-        <v>#VALUE!</v>
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -10484,157 +10511,157 @@
         <v>30</v>
       </c>
       <c r="B93" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" t="e">
+        <f t="shared" si="20"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D94" t="e">
+        <f t="shared" si="21"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E94" t="e">
+        <f t="shared" si="22"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" t="s">
         <v>35</v>
       </c>
-      <c r="C93">
-        <f t="shared" si="19"/>
+      <c r="C95">
+        <f t="shared" si="20"/>
         <v>480</v>
       </c>
-      <c r="D93">
-        <f t="shared" si="20"/>
-        <v>115200</v>
-      </c>
-      <c r="E93">
+      <c r="D95">
         <f t="shared" si="21"/>
         <v>115200</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>98</v>
-      </c>
-      <c r="B94" t="s">
-        <v>101</v>
-      </c>
-      <c r="C94">
-        <f t="shared" si="19"/>
-        <v>936</v>
-      </c>
-      <c r="D94">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="E94">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>36</v>
-      </c>
-      <c r="B95" t="s">
-        <v>37</v>
-      </c>
-      <c r="C95">
-        <f t="shared" ref="C95" si="22">C24*2</f>
-        <v>568</v>
-      </c>
-      <c r="D95">
-        <f t="shared" ref="D95" si="23">C95*D24</f>
-        <v>161312</v>
-      </c>
       <c r="E95">
-        <f t="shared" ref="E95" si="24">C95*E24</f>
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>115200</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C96">
-        <f t="shared" ref="C96" si="25">C26*2</f>
-        <v>728</v>
+        <f t="shared" si="20"/>
+        <v>936</v>
       </c>
       <c r="D96">
-        <f t="shared" ref="D96" si="26">C96*D26</f>
-        <v>264992</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="E96">
-        <f t="shared" ref="E96" si="27">C96*E26</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="C97">
-        <v>209</v>
-      </c>
-      <c r="D97" t="e">
-        <f>#REF!*D28</f>
-        <v>#REF!</v>
+        <f t="shared" ref="C97" si="23">C25*2</f>
+        <v>568</v>
+      </c>
+      <c r="D97">
+        <f t="shared" ref="D97" si="24">C97*D25</f>
+        <v>161312</v>
       </c>
       <c r="E97">
-        <f>C97*E28</f>
+        <f t="shared" ref="E97" si="25">C97*E25</f>
         <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="C98">
-        <f t="shared" ref="C98:C133" si="28">C28*2</f>
-        <v>524</v>
+        <f t="shared" ref="C98" si="26">C27*2</f>
+        <v>728</v>
       </c>
       <c r="D98">
-        <f t="shared" ref="D98:D127" si="29">C98*D28</f>
-        <v>0</v>
+        <f t="shared" ref="D98" si="27">C98*D27</f>
+        <v>264992</v>
       </c>
       <c r="E98">
-        <f t="shared" ref="E98:E133" si="30">C98*E28</f>
+        <f t="shared" ref="E98" si="28">C98*E27</f>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="C99">
-        <f t="shared" si="28"/>
-        <v>1144</v>
-      </c>
-      <c r="D99">
-        <f t="shared" si="29"/>
-        <v>654368</v>
+        <v>209</v>
+      </c>
+      <c r="D99" t="e">
+        <f>#REF!*D30</f>
+        <v>#REF!</v>
       </c>
       <c r="E99">
-        <f t="shared" si="30"/>
+        <f>C99*E30</f>
         <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B100" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C100">
-        <f t="shared" si="28"/>
-        <v>532</v>
+        <f t="shared" ref="C100:C135" si="29">C30*2</f>
+        <v>524</v>
       </c>
       <c r="D100">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="D100:D129" si="30">C100*D30</f>
         <v>0</v>
       </c>
       <c r="E100">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="E100:E135" si="31">C100*E30</f>
         <v>0</v>
       </c>
     </row>
@@ -10643,83 +10670,78 @@
         <v>40</v>
       </c>
       <c r="B101" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C101">
-        <f t="shared" si="28"/>
-        <v>524</v>
+        <f t="shared" si="29"/>
+        <v>1144</v>
       </c>
       <c r="D101">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="30"/>
+        <v>654368</v>
       </c>
       <c r="E101">
-        <f t="shared" si="30"/>
-        <v>137288</v>
+        <f t="shared" si="31"/>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B102" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C102">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>532</v>
       </c>
       <c r="D102">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E102">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B103" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C103">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="29"/>
+        <v>524</v>
       </c>
       <c r="D103">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E103">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
+        <f t="shared" si="31"/>
+        <v>137288</v>
+      </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>44</v>
       </c>
       <c r="B104" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C104">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D104">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E104">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -10728,178 +10750,183 @@
         <v>44</v>
       </c>
       <c r="B105" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C105">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D105">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E105">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>44</v>
       </c>
       <c r="B106" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C106">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D106">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E106">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B107" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C107">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D107">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E107">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B108" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C108">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D108">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E108">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B109" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C109">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D109">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E109">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B110" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C110">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D110">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E110">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C111">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D111">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E111">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B112" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C112">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D112">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E112">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B113" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C113">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D113">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E113">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -10908,78 +10935,78 @@
         <v>59</v>
       </c>
       <c r="B114" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C114">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D114">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E114">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B115" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C115">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D115">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E115">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B116" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C116">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D116">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E116">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B117" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C117">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D117">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E117">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -10988,18 +11015,18 @@
         <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C118">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D118">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E118">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -11008,58 +11035,58 @@
         <v>65</v>
       </c>
       <c r="B119" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C119">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D119">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E119">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B120" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C120">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D120">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E120">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C121">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D121">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E121">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -11068,58 +11095,58 @@
         <v>70</v>
       </c>
       <c r="B122" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C122">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D122">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E122">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B123" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C123">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D123">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E123">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B124" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C124">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D124">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E124">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -11128,58 +11155,58 @@
         <v>74</v>
       </c>
       <c r="B125" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C125">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D125">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E125">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B126" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C126">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D126">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E126">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B127" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C127">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D127">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E127">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -11188,69 +11215,69 @@
         <v>78</v>
       </c>
       <c r="B128" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C128">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D128">
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E128">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B129" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C129">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D129">
-        <f>C129*D59</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="E129">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B130" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C130">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D130">
-        <f>C130*D60</f>
         <v>0</v>
       </c>
       <c r="E130">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B131" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C131">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D131">
@@ -11258,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
@@ -11267,10 +11294,10 @@
         <v>83</v>
       </c>
       <c r="B132" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C132">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D132">
@@ -11278,19 +11305,19 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B133" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C133">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="D133">
@@ -11298,105 +11325,129 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D141" s="1" t="s">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>83</v>
+      </c>
+      <c r="B134" t="s">
+        <v>86</v>
+      </c>
+      <c r="C134">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <f>C134*D64</f>
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>87</v>
+      </c>
+      <c r="B135" t="s">
+        <v>88</v>
+      </c>
+      <c r="C135">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <f>C135*D65</f>
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D143" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D142" t="e">
-        <f t="shared" ref="D142:E142" si="31">SUM(D77:D133)</f>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D144" t="e">
+        <f t="shared" ref="D144:E144" si="32">SUM(D79:D135)</f>
         <v>#REF!</v>
       </c>
-      <c r="E142" t="e">
-        <f t="shared" si="31"/>
-        <v>#REF!</v>
-      </c>
-      <c r="H142" t="e">
-        <f>SUM(D142:E142)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I142" s="3" t="e">
-        <f>H142/H73</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D143" s="3" t="e">
-        <f t="shared" ref="D143:E143" si="32">D142/D73</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E143" s="3" t="e">
+      <c r="E144" t="e">
         <f t="shared" si="32"/>
         <v>#REF!</v>
       </c>
-      <c r="H143" s="3" t="e">
-        <f>H142/F73</f>
+      <c r="H144" t="e">
+        <f>SUM(D144:E144)</f>
         <v>#REF!</v>
       </c>
-      <c r="I143" t="s">
+      <c r="I144" s="3" t="e">
+        <f>H144/H75</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="145" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D145" s="3" t="e">
+        <f t="shared" ref="D145:E145" si="33">D144/D75</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E145" s="3" t="e">
+        <f t="shared" si="33"/>
+        <v>#REF!</v>
+      </c>
+      <c r="H145" s="3" t="e">
+        <f>H144/F75</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I145" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B213" s="1" t="s">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B215" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C213" s="1"/>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>13</v>
-      </c>
-      <c r="B214">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>17</v>
-      </c>
-      <c r="B215">
-        <v>1</v>
-      </c>
+      <c r="C215" s="1"/>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B216">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B217">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B218">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B219">
         <v>5</v>
@@ -11404,7 +11455,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -11412,47 +11463,47 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B221">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B222">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B223">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B224">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B225">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -11460,91 +11511,107 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B227">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B229">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B230">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B231">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B232">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B233">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B234">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B235">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
+        <v>81</v>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>83</v>
+      </c>
+      <c r="B237">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
         <v>87</v>
       </c>
-      <c r="B236">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A238" s="1"/>
-      <c r="B238" s="1">
-        <f>SUM(B214:B236)</f>
+      <c r="B238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1">
+        <f>SUM(B216:B238)</f>
         <v>53</v>
       </c>
-      <c r="C238" s="1"/>
+      <c r="C240" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B658DCD6-F21E-4822-9645-9087D5E25010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF92C9B-347C-4D46-9E04-B4855863218A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
@@ -9459,18 +9459,20 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="G8" s="8">
+        <v>1</v>
+      </c>
       <c r="H8" s="8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="8">
         <f t="shared" ref="I8:I13" si="4">C8*H8</f>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="J8" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -9644,19 +9646,19 @@
       </c>
       <c r="G17" s="9">
         <f>SUM(G2:G16)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H17" s="9">
         <f>SUM(D17:G17)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I17" s="9">
         <f>SUM(I2:I13)</f>
-        <v>3079</v>
+        <v>3195</v>
       </c>
       <c r="J17" s="9">
         <f>SUM(J2:J13)</f>
-        <v>6158</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -9672,11 +9674,11 @@
       <c r="H18" s="8"/>
       <c r="I18" s="8">
         <f>I17/H17</f>
-        <v>133.86956521739131</v>
+        <v>133.125</v>
       </c>
       <c r="J18" s="8">
         <f>J17/H17</f>
-        <v>267.73913043478262</v>
+        <v>266.25</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -9936,13 +9938,13 @@
       </c>
       <c r="G28" s="8">
         <f>G8*C28</f>
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
@@ -10133,16 +10135,16 @@
       </c>
       <c r="G35" s="9">
         <f t="shared" ref="G35" si="19">SUM(G22:G33)</f>
-        <v>1488</v>
+        <v>1720</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9">
         <f>SUM(D35:G35)</f>
-        <v>6158</v>
+        <v>6390</v>
       </c>
       <c r="J35" s="9">
         <f>SUM(J22:J33)</f>
-        <v>6158</v>
+        <v>6390</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
@@ -10162,13 +10164,13 @@
       <c r="I67" s="2"/>
       <c r="J67" s="4">
         <f>SUM(J2:J65)</f>
-        <v>24899.739130434784</v>
+        <v>25826.25</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J74">
         <f>SUM(J2:J65)</f>
-        <v>24899.739130434784</v>
+        <v>25826.25</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
@@ -10186,15 +10188,15 @@
       </c>
       <c r="H75">
         <f>SUM(H2:H65)</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I75">
         <f>SUM(I2:I65)</f>
-        <v>12449.869565217392</v>
+        <v>12913.125</v>
       </c>
       <c r="J75">
         <f>2*I75</f>
-        <v>24899.739130434784</v>
+        <v>25826.25</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">

--- a/pelipaikat.xlsx
+++ b/pelipaikat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF92C9B-347C-4D46-9E04-B4855863218A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297D4B22-D6FE-4104-8AC4-A449B7122866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="21276" windowHeight="12948" activeTab="1" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
+    <workbookView xWindow="1500" yWindow="0" windowWidth="19104" windowHeight="13776" xr2:uid="{4555F0EC-1DB6-484D-B801-2FC196B7544F}"/>
   </bookViews>
   <sheets>
     <sheet name="pelipaikat" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="143">
   <si>
     <t>Paikkakunta</t>
   </si>
@@ -463,6 +463,9 @@
   </si>
   <si>
     <t>Karkkilan Beach Volley Areena</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
   </si>
 </sst>
 </file>
@@ -928,19 +931,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1185CB8-B7D3-4EC5-84DD-BC18A741831D}">
-  <dimension ref="A1:AD188"/>
+  <dimension ref="A1:AE188"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
     <col min="2" max="2" width="22.77734375" customWidth="1"/>
     <col min="3" max="11" width="9.77734375" customWidth="1"/>
     <col min="12" max="12" width="10.5546875" customWidth="1"/>
-    <col min="13" max="16" width="9.77734375" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="8.88671875" style="17"/>
+    <col min="13" max="17" width="9.77734375" customWidth="1"/>
+    <col min="19" max="19" width="9.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="31" width="8.88671875" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -981,22 +984,25 @@
         <v>117</v>
       </c>
       <c r="N1" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="R1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="R1" s="20">
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" s="20">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
@@ -1022,23 +1028,24 @@
       <c r="M2" s="8">
         <v>2</v>
       </c>
-      <c r="N2" s="8">
-        <f>SUM(D2:M2)</f>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8">
+        <f>SUM(D2:N2)</f>
         <v>4</v>
       </c>
-      <c r="O2" s="8">
-        <f t="shared" ref="O2:O68" si="0">C2*N2</f>
+      <c r="P2" s="8">
+        <f>C2*O2</f>
         <v>32</v>
       </c>
-      <c r="P2" s="8">
-        <f t="shared" ref="P2:P68" si="1">2*O2</f>
+      <c r="Q2" s="8">
+        <f t="shared" ref="Q2:Q68" si="0">2*P2</f>
         <v>64</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="R2" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
@@ -1062,21 +1069,22 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
       <c r="M3" s="8"/>
-      <c r="N3" s="8">
-        <f t="shared" ref="N3:N68" si="2">SUM(D3:M3)</f>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8">
+        <f t="shared" ref="O3:O66" si="1">SUM(D3:N3)</f>
         <v>2</v>
       </c>
-      <c r="O3" s="8">
+      <c r="P3" s="8">
+        <f>C3*O3</f>
+        <v>2</v>
+      </c>
+      <c r="Q3" s="8">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="P3" s="8">
-        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="Q3" s="8"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R3" s="8"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>13</v>
       </c>
@@ -1102,23 +1110,24 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
       <c r="M4" s="8"/>
-      <c r="N4" s="8">
-        <f t="shared" si="2"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="O4" s="8">
+      <c r="P4" s="8">
+        <f>C4*O4</f>
+        <v>40</v>
+      </c>
+      <c r="Q4" s="8">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="P4" s="8">
-        <f t="shared" si="1"/>
         <v>80</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
@@ -1142,23 +1151,24 @@
       <c r="M5" s="6">
         <v>1</v>
       </c>
-      <c r="N5" s="6">
-        <f t="shared" si="2"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="14">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O5" s="6">
+      <c r="P5" s="6">
+        <f>C5*O5</f>
+        <v>564</v>
+      </c>
+      <c r="Q5" s="6">
         <f t="shared" si="0"/>
-        <v>564</v>
-      </c>
-      <c r="P5" s="6">
-        <f t="shared" si="1"/>
         <v>1128</v>
       </c>
-      <c r="Q5" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>129</v>
       </c>
@@ -1180,23 +1190,24 @@
       <c r="M6" s="8">
         <v>1</v>
       </c>
-      <c r="N6" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N6" s="8"/>
       <c r="O6" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P6" s="8">
+        <f>C6*O6</f>
+        <v>74</v>
+      </c>
+      <c r="Q6" s="8">
         <f t="shared" si="0"/>
-        <v>74</v>
-      </c>
-      <c r="P6" s="8">
-        <f t="shared" si="1"/>
         <v>148</v>
       </c>
-      <c r="Q6" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>19</v>
       </c>
@@ -1220,23 +1231,24 @@
       <c r="M7" s="14">
         <v>3</v>
       </c>
-      <c r="N7" s="14">
-        <f t="shared" si="2"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="O7" s="14">
+      <c r="P7" s="14">
+        <f>C7*O7</f>
+        <v>556</v>
+      </c>
+      <c r="Q7" s="14">
         <f t="shared" si="0"/>
-        <v>556</v>
-      </c>
-      <c r="P7" s="14">
-        <f t="shared" si="1"/>
         <v>1112</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="R7" s="14">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>19</v>
       </c>
@@ -1258,21 +1270,22 @@
       <c r="K8" s="14"/>
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
-      <c r="N8" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N8" s="14"/>
       <c r="O8" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P8" s="14">
+        <f>C8*O8</f>
+        <v>141</v>
+      </c>
+      <c r="Q8" s="14">
         <f t="shared" si="0"/>
-        <v>141</v>
-      </c>
-      <c r="P8" s="14">
-        <f t="shared" si="1"/>
         <v>282</v>
       </c>
-      <c r="Q8" s="14"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R8" s="14"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
@@ -1294,21 +1307,22 @@
       <c r="M9" s="14">
         <v>1</v>
       </c>
-      <c r="N9" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N9" s="14"/>
       <c r="O9" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P9" s="14">
+        <f>C9*O9</f>
+        <v>138</v>
+      </c>
+      <c r="Q9" s="14">
         <f t="shared" si="0"/>
-        <v>138</v>
-      </c>
-      <c r="P9" s="14">
-        <f t="shared" si="1"/>
         <v>276</v>
       </c>
-      <c r="Q9" s="14"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R9" s="14"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>19</v>
       </c>
@@ -1330,21 +1344,22 @@
         <v>1</v>
       </c>
       <c r="M10" s="14"/>
-      <c r="N10" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N10" s="14"/>
       <c r="O10" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P10" s="14">
+        <f>C10*O10</f>
+        <v>146</v>
+      </c>
+      <c r="Q10" s="14">
         <f t="shared" si="0"/>
-        <v>146</v>
-      </c>
-      <c r="P10" s="14">
-        <f t="shared" si="1"/>
         <v>292</v>
       </c>
-      <c r="Q10" s="14"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R10" s="14"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>22</v>
       </c>
@@ -1366,23 +1381,24 @@
       </c>
       <c r="L11" s="8"/>
       <c r="M11" s="8"/>
-      <c r="N11" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N11" s="8"/>
       <c r="O11" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P11" s="8">
+        <f>C11*O11</f>
+        <v>33</v>
+      </c>
+      <c r="Q11" s="8">
         <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="P11" s="8">
-        <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="R11" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>22</v>
       </c>
@@ -1404,21 +1420,22 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
-      <c r="N12" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N12" s="8"/>
       <c r="O12" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P12" s="8">
+        <f>C12*O12</f>
+        <v>46</v>
+      </c>
+      <c r="Q12" s="8">
         <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="P12" s="8">
-        <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="Q12" s="8"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R12" s="8"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
@@ -1442,21 +1459,22 @@
       <c r="M13" s="8">
         <v>10</v>
       </c>
-      <c r="N13" s="8">
-        <f t="shared" si="2"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="O13" s="8">
+      <c r="P13" s="8">
+        <f>C13*O13</f>
+        <v>462</v>
+      </c>
+      <c r="Q13" s="8">
         <f t="shared" si="0"/>
-        <v>462</v>
-      </c>
-      <c r="P13" s="8">
-        <f t="shared" si="1"/>
         <v>924</v>
       </c>
-      <c r="Q13" s="8"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>22</v>
       </c>
@@ -1478,21 +1496,22 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
-      <c r="N14" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N14" s="8"/>
       <c r="O14" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P14" s="8">
+        <f>C14*O14</f>
+        <v>60</v>
+      </c>
+      <c r="Q14" s="8">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="Q14" s="8"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R14" s="8"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
@@ -1514,21 +1533,22 @@
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N15" s="8"/>
       <c r="O15" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P15" s="8">
+        <f>C15*O15</f>
+        <v>43</v>
+      </c>
+      <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="P15" s="8">
-        <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="Q15" s="8"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R15" s="8"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>125</v>
       </c>
@@ -1550,23 +1570,24 @@
       <c r="M16" s="14">
         <v>1</v>
       </c>
-      <c r="N16" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N16" s="14"/>
       <c r="O16" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P16" s="14">
+        <f>C16*O16</f>
+        <v>182</v>
+      </c>
+      <c r="Q16" s="14">
         <f t="shared" si="0"/>
-        <v>182</v>
-      </c>
-      <c r="P16" s="14">
-        <f t="shared" si="1"/>
         <v>364</v>
       </c>
-      <c r="Q16" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R16" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>28</v>
       </c>
@@ -1588,23 +1609,24 @@
       <c r="M17" s="8">
         <v>1</v>
       </c>
-      <c r="N17" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N17" s="8"/>
       <c r="O17" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P17" s="8">
+        <f>C17*O17</f>
+        <v>185</v>
+      </c>
+      <c r="Q17" s="8">
         <f t="shared" si="0"/>
-        <v>185</v>
-      </c>
-      <c r="P17" s="8">
-        <f t="shared" si="1"/>
         <v>370</v>
       </c>
-      <c r="Q17" s="8">
+      <c r="R17" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>28</v>
       </c>
@@ -1628,21 +1650,22 @@
         <v>1</v>
       </c>
       <c r="M18" s="8"/>
-      <c r="N18" s="8">
-        <f t="shared" si="2"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O18" s="8">
+      <c r="P18" s="8">
+        <f>C18*O18</f>
+        <v>416</v>
+      </c>
+      <c r="Q18" s="8">
         <f t="shared" si="0"/>
-        <v>416</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" si="1"/>
         <v>832</v>
       </c>
-      <c r="Q18" s="8"/>
-    </row>
-    <row r="19" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R18" s="8"/>
+    </row>
+    <row r="19" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>131</v>
       </c>
@@ -1664,23 +1687,24 @@
       <c r="M19" s="14">
         <v>1</v>
       </c>
-      <c r="N19" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N19" s="14"/>
       <c r="O19" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P19" s="14">
+        <f>C19*O19</f>
+        <v>118</v>
+      </c>
+      <c r="Q19" s="14">
         <f t="shared" si="0"/>
-        <v>118</v>
-      </c>
-      <c r="P19" s="14">
-        <f t="shared" si="1"/>
         <v>236</v>
       </c>
-      <c r="Q19" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R19" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>30</v>
       </c>
@@ -1704,22 +1728,22 @@
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
-      <c r="N20" s="8">
-        <f t="shared" si="2"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O20" s="8">
+      <c r="P20" s="8">
+        <f>C20*O20</f>
+        <v>110</v>
+      </c>
+      <c r="Q20" s="8">
         <f t="shared" si="0"/>
-        <v>110</v>
-      </c>
-      <c r="P20" s="8">
-        <f t="shared" si="1"/>
         <v>220</v>
       </c>
-      <c r="Q20" s="8">
+      <c r="R20" s="8">
         <v>5</v>
       </c>
-      <c r="R20" s="17"/>
       <c r="S20" s="17"/>
       <c r="T20" s="17"/>
       <c r="U20" s="17"/>
@@ -1732,8 +1756,9 @@
       <c r="AB20" s="17"/>
       <c r="AC20" s="17"/>
       <c r="AD20" s="17"/>
-    </row>
-    <row r="21" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE20" s="17"/>
+    </row>
+    <row r="21" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>30</v>
       </c>
@@ -1755,20 +1780,20 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N21" s="8"/>
       <c r="O21" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P21" s="8">
+        <f>C21*O21</f>
+        <v>54</v>
+      </c>
+      <c r="Q21" s="8">
         <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="P21" s="8">
-        <f t="shared" si="1"/>
         <v>108</v>
       </c>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="17"/>
+      <c r="R21" s="8"/>
       <c r="S21" s="17"/>
       <c r="T21" s="17"/>
       <c r="U21" s="17"/>
@@ -1781,8 +1806,9 @@
       <c r="AB21" s="17"/>
       <c r="AC21" s="17"/>
       <c r="AD21" s="17"/>
-    </row>
-    <row r="22" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE21" s="17"/>
+    </row>
+    <row r="22" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>30</v>
       </c>
@@ -1804,20 +1830,20 @@
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
-      <c r="N22" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N22" s="8"/>
       <c r="O22" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P22" s="8">
+        <f>C22*O22</f>
+        <v>55</v>
+      </c>
+      <c r="Q22" s="8">
         <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="P22" s="8">
-        <f t="shared" si="1"/>
         <v>110</v>
       </c>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="17"/>
+      <c r="R22" s="8"/>
       <c r="S22" s="17"/>
       <c r="T22" s="17"/>
       <c r="U22" s="17"/>
@@ -1830,8 +1856,9 @@
       <c r="AB22" s="17"/>
       <c r="AC22" s="17"/>
       <c r="AD22" s="17"/>
-    </row>
-    <row r="23" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE22" s="17"/>
+    </row>
+    <row r="23" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>30</v>
       </c>
@@ -1853,20 +1880,20 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N23" s="8"/>
       <c r="O23" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P23" s="8">
+        <f>C23*O23</f>
+        <v>46</v>
+      </c>
+      <c r="Q23" s="8">
         <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="P23" s="8">
-        <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="17"/>
+      <c r="R23" s="8"/>
       <c r="S23" s="17"/>
       <c r="T23" s="17"/>
       <c r="U23" s="17"/>
@@ -1879,8 +1906,9 @@
       <c r="AB23" s="17"/>
       <c r="AC23" s="17"/>
       <c r="AD23" s="17"/>
-    </row>
-    <row r="24" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE23" s="17"/>
+    </row>
+    <row r="24" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>30</v>
       </c>
@@ -1906,20 +1934,20 @@
       </c>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
-      <c r="N24" s="8">
-        <f t="shared" si="2"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="O24" s="8">
+      <c r="P24" s="8">
+        <f>C24*O24</f>
+        <v>188</v>
+      </c>
+      <c r="Q24" s="8">
         <f t="shared" si="0"/>
-        <v>188</v>
-      </c>
-      <c r="P24" s="8">
-        <f t="shared" si="1"/>
         <v>376</v>
       </c>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="17"/>
+      <c r="R24" s="8"/>
       <c r="S24" s="17"/>
       <c r="T24" s="17"/>
       <c r="U24" s="17"/>
@@ -1932,8 +1960,9 @@
       <c r="AB24" s="17"/>
       <c r="AC24" s="17"/>
       <c r="AD24" s="17"/>
-    </row>
-    <row r="25" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE24" s="17"/>
+    </row>
+    <row r="25" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>98</v>
       </c>
@@ -1955,23 +1984,24 @@
         <v>1</v>
       </c>
       <c r="M25" s="14"/>
-      <c r="N25" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N25" s="14"/>
       <c r="O25" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P25" s="14">
+        <f>C25*O25</f>
+        <v>400</v>
+      </c>
+      <c r="Q25" s="14">
         <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="P25" s="14">
-        <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="Q25" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R25" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>36</v>
       </c>
@@ -1993,22 +2023,22 @@
       </c>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
-      <c r="N26" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N26" s="8"/>
       <c r="O26" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P26" s="8">
+        <f>C26*O26</f>
+        <v>363</v>
+      </c>
+      <c r="Q26" s="8">
         <f t="shared" si="0"/>
-        <v>363</v>
-      </c>
-      <c r="P26" s="8">
-        <f t="shared" si="1"/>
         <v>726</v>
       </c>
-      <c r="Q26" s="8">
-        <v>1</v>
-      </c>
-      <c r="R26" s="17"/>
+      <c r="R26" s="8">
+        <v>1</v>
+      </c>
       <c r="S26" s="17"/>
       <c r="T26" s="17"/>
       <c r="U26" s="17"/>
@@ -2021,8 +2051,9 @@
       <c r="AB26" s="17"/>
       <c r="AC26" s="17"/>
       <c r="AD26" s="17"/>
-    </row>
-    <row r="27" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE26" s="17"/>
+    </row>
+    <row r="27" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>94</v>
       </c>
@@ -2044,23 +2075,24 @@
       <c r="M27" s="14">
         <v>1</v>
       </c>
-      <c r="N27" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N27" s="14"/>
       <c r="O27" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P27" s="14">
+        <f>C27*O27</f>
+        <v>93</v>
+      </c>
+      <c r="Q27" s="14">
         <f t="shared" si="0"/>
-        <v>93</v>
-      </c>
-      <c r="P27" s="14">
-        <f t="shared" si="1"/>
         <v>186</v>
       </c>
-      <c r="Q27" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R27" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>122</v>
       </c>
@@ -2082,22 +2114,22 @@
       <c r="M28" s="8">
         <v>1</v>
       </c>
-      <c r="N28" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N28" s="8"/>
       <c r="O28" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P28" s="8">
+        <f>C28*O28</f>
+        <v>174</v>
+      </c>
+      <c r="Q28" s="8">
         <f t="shared" si="0"/>
-        <v>174</v>
-      </c>
-      <c r="P28" s="8">
-        <f t="shared" si="1"/>
         <v>348</v>
       </c>
-      <c r="Q28" s="8">
-        <v>1</v>
-      </c>
-      <c r="R28" s="17"/>
+      <c r="R28" s="8">
+        <v>1</v>
+      </c>
       <c r="S28" s="17"/>
       <c r="T28" s="17"/>
       <c r="U28" s="17"/>
@@ -2110,8 +2142,9 @@
       <c r="AB28" s="17"/>
       <c r="AC28" s="17"/>
       <c r="AD28" s="17"/>
-    </row>
-    <row r="29" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE28" s="17"/>
+    </row>
+    <row r="29" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>99</v>
       </c>
@@ -2133,23 +2166,24 @@
         <v>1</v>
       </c>
       <c r="M29" s="14"/>
-      <c r="N29" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N29" s="14"/>
       <c r="O29" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P29" s="14">
+        <f>C29*O29</f>
+        <v>209</v>
+      </c>
+      <c r="Q29" s="14">
         <f t="shared" si="0"/>
-        <v>209</v>
-      </c>
-      <c r="P29" s="14">
-        <f t="shared" si="1"/>
         <v>418</v>
       </c>
-      <c r="Q29" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R29" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>38</v>
       </c>
@@ -2171,22 +2205,22 @@
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
-      <c r="N30" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N30" s="8"/>
       <c r="O30" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P30" s="8">
+        <f>C30*O30</f>
+        <v>258</v>
+      </c>
+      <c r="Q30" s="8">
         <f t="shared" si="0"/>
-        <v>258</v>
-      </c>
-      <c r="P30" s="8">
-        <f t="shared" si="1"/>
         <v>516</v>
       </c>
-      <c r="Q30" s="8">
-        <v>1</v>
-      </c>
-      <c r="R30" s="17"/>
+      <c r="R30" s="8">
+        <v>1</v>
+      </c>
       <c r="S30" s="17"/>
       <c r="T30" s="17"/>
       <c r="U30" s="17"/>
@@ -2199,8 +2233,9 @@
       <c r="AB30" s="17"/>
       <c r="AC30" s="17"/>
       <c r="AD30" s="17"/>
-    </row>
-    <row r="31" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE30" s="17"/>
+    </row>
+    <row r="31" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>44</v>
       </c>
@@ -2224,23 +2259,24 @@
       </c>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
-      <c r="N31" s="14">
-        <f t="shared" ref="N31:N36" si="3">SUM(D31:M31)</f>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O31" s="14">
-        <f t="shared" ref="O31:O36" si="4">C31*N31</f>
+      <c r="P31" s="14">
+        <f>C31*O31</f>
         <v>50</v>
       </c>
-      <c r="P31" s="14">
-        <f t="shared" ref="P31:P36" si="5">2*O31</f>
+      <c r="Q31" s="14">
+        <f t="shared" ref="Q31:Q36" si="2">2*P31</f>
         <v>100</v>
       </c>
-      <c r="Q31" s="14">
+      <c r="R31" s="14">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>44</v>
       </c>
@@ -2262,21 +2298,22 @@
       <c r="M32" s="14">
         <v>1</v>
       </c>
-      <c r="N32" s="14">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
+      <c r="N32" s="14"/>
       <c r="O32" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P32" s="14">
+        <f>C32*O32</f>
         <v>19</v>
       </c>
-      <c r="P32" s="14">
-        <f t="shared" si="5"/>
+      <c r="Q32" s="14">
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
-      <c r="Q32" s="14"/>
-    </row>
-    <row r="33" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R32" s="14"/>
+    </row>
+    <row r="33" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>44</v>
       </c>
@@ -2302,21 +2339,22 @@
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
-      <c r="N33" s="14">
-        <f t="shared" si="3"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14">
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="O33" s="14">
-        <f t="shared" si="4"/>
+      <c r="P33" s="14">
+        <f>C33*O33</f>
         <v>108</v>
       </c>
-      <c r="P33" s="14">
-        <f t="shared" si="5"/>
+      <c r="Q33" s="14">
+        <f t="shared" si="2"/>
         <v>216</v>
       </c>
-      <c r="Q33" s="14"/>
-    </row>
-    <row r="34" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R33" s="14"/>
+    </row>
+    <row r="34" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>44</v>
       </c>
@@ -2338,23 +2376,24 @@
       </c>
       <c r="L34" s="14"/>
       <c r="M34" s="14">
-        <v>7</v>
-      </c>
-      <c r="N34" s="14">
-        <f t="shared" si="3"/>
         <v>8</v>
       </c>
+      <c r="N34" s="14"/>
       <c r="O34" s="14">
-        <f t="shared" si="4"/>
-        <v>216</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="P34" s="14">
-        <f t="shared" si="5"/>
-        <v>432</v>
-      </c>
-      <c r="Q34" s="14"/>
-    </row>
-    <row r="35" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+        <f>C34*O34</f>
+        <v>243</v>
+      </c>
+      <c r="Q34" s="14">
+        <f t="shared" si="2"/>
+        <v>486</v>
+      </c>
+      <c r="R34" s="14"/>
+    </row>
+    <row r="35" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>44</v>
       </c>
@@ -2386,21 +2425,22 @@
         <v>1</v>
       </c>
       <c r="M35" s="14"/>
-      <c r="N35" s="14">
-        <f t="shared" si="3"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14">
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="O35" s="14">
-        <f t="shared" si="4"/>
+      <c r="P35" s="14">
+        <f>C35*O35</f>
         <v>189</v>
       </c>
-      <c r="P35" s="14">
-        <f t="shared" si="5"/>
+      <c r="Q35" s="14">
+        <f t="shared" si="2"/>
         <v>378</v>
       </c>
-      <c r="Q35" s="14"/>
-    </row>
-    <row r="36" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R35" s="14"/>
+    </row>
+    <row r="36" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>44</v>
       </c>
@@ -2428,21 +2468,22 @@
       <c r="M36" s="14">
         <v>2</v>
       </c>
-      <c r="N36" s="14">
-        <f t="shared" si="3"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="O36" s="14">
-        <f t="shared" si="4"/>
+      <c r="P36" s="14">
+        <f>C36*O36</f>
         <v>248</v>
       </c>
-      <c r="P36" s="14">
-        <f t="shared" si="5"/>
+      <c r="Q36" s="14">
+        <f t="shared" si="2"/>
         <v>496</v>
       </c>
-      <c r="Q36" s="14"/>
-    </row>
-    <row r="37" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R36" s="14"/>
+    </row>
+    <row r="37" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>40</v>
       </c>
@@ -2468,22 +2509,22 @@
         <v>1</v>
       </c>
       <c r="M37" s="8"/>
-      <c r="N37" s="8">
-        <f t="shared" si="2"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="8">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O37" s="8">
+      <c r="P37" s="8">
+        <f>C37*O37</f>
+        <v>237</v>
+      </c>
+      <c r="Q37" s="8">
         <f t="shared" si="0"/>
-        <v>237</v>
-      </c>
-      <c r="P37" s="8">
-        <f t="shared" si="1"/>
         <v>474</v>
       </c>
-      <c r="Q37" s="8">
+      <c r="R37" s="8">
         <v>3</v>
       </c>
-      <c r="R37" s="17"/>
       <c r="S37" s="17"/>
       <c r="T37" s="17"/>
       <c r="U37" s="17"/>
@@ -2496,8 +2537,9 @@
       <c r="AB37" s="17"/>
       <c r="AC37" s="17"/>
       <c r="AD37" s="17"/>
-    </row>
-    <row r="38" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE37" s="17"/>
+    </row>
+    <row r="38" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>40</v>
       </c>
@@ -2519,20 +2561,20 @@
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
-      <c r="N38" s="8">
-        <f t="shared" si="2"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O38" s="8">
+      <c r="P38" s="8">
+        <f>C38*O38</f>
+        <v>140</v>
+      </c>
+      <c r="Q38" s="8">
         <f t="shared" si="0"/>
-        <v>140</v>
-      </c>
-      <c r="P38" s="8">
-        <f t="shared" si="1"/>
         <v>280</v>
       </c>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="17"/>
+      <c r="R38" s="8"/>
       <c r="S38" s="17"/>
       <c r="T38" s="17"/>
       <c r="U38" s="17"/>
@@ -2545,8 +2587,9 @@
       <c r="AB38" s="17"/>
       <c r="AC38" s="17"/>
       <c r="AD38" s="17"/>
-    </row>
-    <row r="39" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE38" s="17"/>
+    </row>
+    <row r="39" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>40</v>
       </c>
@@ -2572,20 +2615,20 @@
         <v>1</v>
       </c>
       <c r="M39" s="8"/>
-      <c r="N39" s="8">
-        <f t="shared" si="2"/>
+      <c r="N39" s="8"/>
+      <c r="O39" s="8">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O39" s="8">
+      <c r="P39" s="8">
+        <f>C39*O39</f>
+        <v>198</v>
+      </c>
+      <c r="Q39" s="8">
         <f t="shared" si="0"/>
-        <v>198</v>
-      </c>
-      <c r="P39" s="8">
-        <f t="shared" si="1"/>
         <v>396</v>
       </c>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="17"/>
+      <c r="R39" s="8"/>
       <c r="S39" s="17"/>
       <c r="T39" s="17"/>
       <c r="U39" s="17"/>
@@ -2598,8 +2641,9 @@
       <c r="AB39" s="17"/>
       <c r="AC39" s="17"/>
       <c r="AD39" s="17"/>
-    </row>
-    <row r="40" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE39" s="17"/>
+    </row>
+    <row r="40" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>50</v>
       </c>
@@ -2621,23 +2665,24 @@
       </c>
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
-      <c r="N40" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N40" s="14"/>
       <c r="O40" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P40" s="14">
+        <f>C40*O40</f>
+        <v>420</v>
+      </c>
+      <c r="Q40" s="14">
         <f t="shared" si="0"/>
-        <v>420</v>
-      </c>
-      <c r="P40" s="14">
-        <f t="shared" si="1"/>
         <v>840</v>
       </c>
-      <c r="Q40" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R40" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>52</v>
       </c>
@@ -2659,22 +2704,22 @@
       </c>
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
-      <c r="N41" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N41" s="8"/>
       <c r="O41" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P41" s="8">
+        <f>C41*O41</f>
+        <v>141</v>
+      </c>
+      <c r="Q41" s="8">
         <f t="shared" si="0"/>
-        <v>141</v>
-      </c>
-      <c r="P41" s="8">
-        <f t="shared" si="1"/>
         <v>282</v>
       </c>
-      <c r="Q41" s="8">
-        <v>1</v>
-      </c>
-      <c r="R41" s="17"/>
+      <c r="R41" s="8">
+        <v>1</v>
+      </c>
       <c r="S41" s="17"/>
       <c r="T41" s="17"/>
       <c r="U41" s="17"/>
@@ -2687,8 +2732,9 @@
       <c r="AB41" s="17"/>
       <c r="AC41" s="17"/>
       <c r="AD41" s="17"/>
-    </row>
-    <row r="42" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE41" s="17"/>
+    </row>
+    <row r="42" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>54</v>
       </c>
@@ -2720,23 +2766,24 @@
       </c>
       <c r="L42" s="14"/>
       <c r="M42" s="14"/>
-      <c r="N42" s="14">
-        <f t="shared" si="2"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14">
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="O42" s="14">
+      <c r="P42" s="14">
+        <f>C42*O42</f>
+        <v>720</v>
+      </c>
+      <c r="Q42" s="14">
         <f t="shared" si="0"/>
-        <v>720</v>
-      </c>
-      <c r="P42" s="14">
-        <f t="shared" si="1"/>
         <v>1440</v>
       </c>
-      <c r="Q42" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R42" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>120</v>
       </c>
@@ -2758,22 +2805,22 @@
       <c r="M43" s="8">
         <v>2</v>
       </c>
-      <c r="N43" s="8">
-        <f t="shared" si="2"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O43" s="8">
+      <c r="P43" s="8">
+        <f>C43*O43</f>
+        <v>1044</v>
+      </c>
+      <c r="Q43" s="8">
         <f t="shared" si="0"/>
-        <v>1044</v>
-      </c>
-      <c r="P43" s="8">
-        <f t="shared" si="1"/>
         <v>2088</v>
       </c>
-      <c r="Q43" s="8">
-        <v>1</v>
-      </c>
-      <c r="R43" s="17"/>
+      <c r="R43" s="8">
+        <v>1</v>
+      </c>
       <c r="S43" s="17"/>
       <c r="T43" s="17"/>
       <c r="U43" s="17"/>
@@ -2786,8 +2833,9 @@
       <c r="AB43" s="17"/>
       <c r="AC43" s="17"/>
       <c r="AD43" s="17"/>
-    </row>
-    <row r="44" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE43" s="17"/>
+    </row>
+    <row r="44" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>56</v>
       </c>
@@ -2815,23 +2863,24 @@
         <v>1</v>
       </c>
       <c r="M44" s="14"/>
-      <c r="N44" s="14">
-        <f t="shared" si="2"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="14">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="O44" s="14">
+      <c r="P44" s="14">
+        <f>C44*O44</f>
+        <v>204</v>
+      </c>
+      <c r="Q44" s="14">
         <f t="shared" si="0"/>
-        <v>204</v>
-      </c>
-      <c r="P44" s="14">
-        <f t="shared" si="1"/>
         <v>408</v>
       </c>
-      <c r="Q44" s="14">
+      <c r="R44" s="14">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>56</v>
       </c>
@@ -2853,21 +2902,22 @@
       <c r="K45" s="14"/>
       <c r="L45" s="14"/>
       <c r="M45" s="14"/>
-      <c r="N45" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N45" s="14"/>
       <c r="O45" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P45" s="14">
+        <f>C45*O45</f>
+        <v>45</v>
+      </c>
+      <c r="Q45" s="14">
         <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="P45" s="14">
-        <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="Q45" s="14"/>
-    </row>
-    <row r="46" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R45" s="14"/>
+    </row>
+    <row r="46" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>59</v>
       </c>
@@ -2889,22 +2939,22 @@
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
       <c r="M46" s="8"/>
-      <c r="N46" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N46" s="8"/>
       <c r="O46" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P46" s="8">
+        <f>C46*O46</f>
+        <v>132</v>
+      </c>
+      <c r="Q46" s="8">
         <f t="shared" si="0"/>
-        <v>132</v>
-      </c>
-      <c r="P46" s="8">
-        <f t="shared" si="1"/>
         <v>264</v>
       </c>
-      <c r="Q46" s="8">
+      <c r="R46" s="8">
         <v>3</v>
       </c>
-      <c r="R46" s="17"/>
       <c r="S46" s="17"/>
       <c r="T46" s="17"/>
       <c r="U46" s="17"/>
@@ -2917,8 +2967,9 @@
       <c r="AB46" s="17"/>
       <c r="AC46" s="17"/>
       <c r="AD46" s="17"/>
-    </row>
-    <row r="47" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE46" s="17"/>
+    </row>
+    <row r="47" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>59</v>
       </c>
@@ -2940,20 +2991,20 @@
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
-      <c r="N47" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N47" s="8"/>
       <c r="O47" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P47" s="8">
+        <f>C47*O47</f>
+        <v>131</v>
+      </c>
+      <c r="Q47" s="8">
         <f t="shared" si="0"/>
-        <v>131</v>
-      </c>
-      <c r="P47" s="8">
-        <f t="shared" si="1"/>
         <v>262</v>
       </c>
-      <c r="Q47" s="8"/>
-      <c r="R47" s="17"/>
+      <c r="R47" s="8"/>
       <c r="S47" s="17"/>
       <c r="T47" s="17"/>
       <c r="U47" s="17"/>
@@ -2966,8 +3017,9 @@
       <c r="AB47" s="17"/>
       <c r="AC47" s="17"/>
       <c r="AD47" s="17"/>
-    </row>
-    <row r="48" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE47" s="17"/>
+    </row>
+    <row r="48" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>59</v>
       </c>
@@ -2991,20 +3043,20 @@
       </c>
       <c r="L48" s="8"/>
       <c r="M48" s="8"/>
-      <c r="N48" s="8">
-        <f t="shared" si="2"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O48" s="8">
+      <c r="P48" s="8">
+        <f>C48*O48</f>
+        <v>262</v>
+      </c>
+      <c r="Q48" s="8">
         <f t="shared" si="0"/>
-        <v>262</v>
-      </c>
-      <c r="P48" s="8">
-        <f t="shared" si="1"/>
         <v>524</v>
       </c>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="17"/>
+      <c r="R48" s="8"/>
       <c r="S48" s="17"/>
       <c r="T48" s="17"/>
       <c r="U48" s="17"/>
@@ -3017,8 +3069,9 @@
       <c r="AB48" s="17"/>
       <c r="AC48" s="17"/>
       <c r="AD48" s="17"/>
-    </row>
-    <row r="49" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE48" s="17"/>
+    </row>
+    <row r="49" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>63</v>
       </c>
@@ -3042,23 +3095,24 @@
       </c>
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
-      <c r="N49" s="14">
-        <f t="shared" si="2"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="O49" s="14">
+      <c r="P49" s="14">
+        <f>C49*O49</f>
+        <v>408</v>
+      </c>
+      <c r="Q49" s="14">
         <f t="shared" si="0"/>
-        <v>408</v>
-      </c>
-      <c r="P49" s="14">
-        <f t="shared" si="1"/>
         <v>816</v>
       </c>
-      <c r="Q49" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R49" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>65</v>
       </c>
@@ -3082,22 +3136,22 @@
       </c>
       <c r="L50" s="8"/>
       <c r="M50" s="8"/>
-      <c r="N50" s="8">
-        <f t="shared" si="2"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O50" s="8">
+      <c r="P50" s="8">
+        <f>C50*O50</f>
+        <v>266</v>
+      </c>
+      <c r="Q50" s="8">
         <f t="shared" si="0"/>
-        <v>266</v>
-      </c>
-      <c r="P50" s="8">
-        <f t="shared" si="1"/>
         <v>532</v>
       </c>
-      <c r="Q50" s="8">
+      <c r="R50" s="8">
         <v>4</v>
       </c>
-      <c r="R50" s="17"/>
       <c r="S50" s="17"/>
       <c r="T50" s="17"/>
       <c r="U50" s="17"/>
@@ -3110,8 +3164,9 @@
       <c r="AB50" s="17"/>
       <c r="AC50" s="17"/>
       <c r="AD50" s="17"/>
-    </row>
-    <row r="51" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE50" s="17"/>
+    </row>
+    <row r="51" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>65</v>
       </c>
@@ -3133,20 +3188,20 @@
       </c>
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
-      <c r="N51" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N51" s="8"/>
       <c r="O51" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P51" s="8">
+        <f>C51*O51</f>
+        <v>152</v>
+      </c>
+      <c r="Q51" s="8">
         <f t="shared" si="0"/>
-        <v>152</v>
-      </c>
-      <c r="P51" s="8">
-        <f t="shared" si="1"/>
         <v>304</v>
       </c>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="17"/>
+      <c r="R51" s="8"/>
       <c r="S51" s="17"/>
       <c r="T51" s="17"/>
       <c r="U51" s="17"/>
@@ -3159,8 +3214,9 @@
       <c r="AB51" s="17"/>
       <c r="AC51" s="17"/>
       <c r="AD51" s="17"/>
-    </row>
-    <row r="52" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE51" s="17"/>
+    </row>
+    <row r="52" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>65</v>
       </c>
@@ -3182,20 +3238,20 @@
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
       <c r="M52" s="8"/>
-      <c r="N52" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N52" s="8"/>
       <c r="O52" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P52" s="8">
+        <f>C52*O52</f>
+        <v>127</v>
+      </c>
+      <c r="Q52" s="8">
         <f t="shared" si="0"/>
-        <v>127</v>
-      </c>
-      <c r="P52" s="8">
-        <f t="shared" si="1"/>
         <v>254</v>
       </c>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="17"/>
+      <c r="R52" s="8"/>
       <c r="S52" s="17"/>
       <c r="T52" s="17"/>
       <c r="U52" s="17"/>
@@ -3208,8 +3264,9 @@
       <c r="AB52" s="17"/>
       <c r="AC52" s="17"/>
       <c r="AD52" s="17"/>
-    </row>
-    <row r="53" spans="1:30" s="18" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE52" s="17"/>
+    </row>
+    <row r="53" spans="1:31" s="18" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>65</v>
       </c>
@@ -3231,20 +3288,20 @@
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
       <c r="M53" s="8"/>
-      <c r="N53" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N53" s="8"/>
       <c r="O53" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P53" s="8">
+        <f>C53*O53</f>
+        <v>153</v>
+      </c>
+      <c r="Q53" s="8">
         <f t="shared" si="0"/>
-        <v>153</v>
-      </c>
-      <c r="P53" s="8">
-        <f t="shared" si="1"/>
         <v>306</v>
       </c>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="17"/>
+      <c r="R53" s="8"/>
       <c r="S53" s="17"/>
       <c r="T53" s="17"/>
       <c r="U53" s="17"/>
@@ -3257,8 +3314,9 @@
       <c r="AB53" s="17"/>
       <c r="AC53" s="17"/>
       <c r="AD53" s="17"/>
-    </row>
-    <row r="54" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE53" s="17"/>
+    </row>
+    <row r="54" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
         <v>70</v>
       </c>
@@ -3286,23 +3344,24 @@
       <c r="M54" s="14">
         <v>1</v>
       </c>
-      <c r="N54" s="14">
-        <f t="shared" si="2"/>
+      <c r="N54" s="14"/>
+      <c r="O54" s="14">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="O54" s="14">
+      <c r="P54" s="14">
+        <f>C54*O54</f>
+        <v>310</v>
+      </c>
+      <c r="Q54" s="14">
         <f t="shared" si="0"/>
-        <v>310</v>
-      </c>
-      <c r="P54" s="14">
-        <f t="shared" si="1"/>
         <v>620</v>
       </c>
-      <c r="Q54" s="14">
+      <c r="R54" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>70</v>
       </c>
@@ -3324,21 +3383,22 @@
       <c r="K55" s="14"/>
       <c r="L55" s="14"/>
       <c r="M55" s="14"/>
-      <c r="N55" s="14">
-        <f t="shared" si="2"/>
+      <c r="N55" s="14"/>
+      <c r="O55" s="14">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O55" s="14">
+      <c r="P55" s="14">
+        <f>C55*O55</f>
+        <v>130</v>
+      </c>
+      <c r="Q55" s="14">
         <f t="shared" si="0"/>
-        <v>130</v>
-      </c>
-      <c r="P55" s="14">
-        <f t="shared" si="1"/>
         <v>260</v>
       </c>
-      <c r="Q55" s="14"/>
-    </row>
-    <row r="56" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R55" s="14"/>
+    </row>
+    <row r="56" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
         <v>70</v>
       </c>
@@ -3360,21 +3420,22 @@
       </c>
       <c r="L56" s="14"/>
       <c r="M56" s="14"/>
-      <c r="N56" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N56" s="14"/>
       <c r="O56" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P56" s="14">
+        <f>C56*O56</f>
+        <v>62</v>
+      </c>
+      <c r="Q56" s="14">
         <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="P56" s="14">
-        <f t="shared" si="1"/>
         <v>124</v>
       </c>
-      <c r="Q56" s="14"/>
-    </row>
-    <row r="57" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R56" s="14"/>
+    </row>
+    <row r="57" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>74</v>
       </c>
@@ -3396,22 +3457,22 @@
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
       <c r="M57" s="8"/>
-      <c r="N57" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N57" s="8"/>
       <c r="O57" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P57" s="8">
+        <f>C57*O57</f>
+        <v>45</v>
+      </c>
+      <c r="Q57" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="P57" s="8">
-        <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="Q57" s="8">
+      <c r="R57" s="8">
         <v>3</v>
       </c>
-      <c r="R57" s="17"/>
       <c r="S57" s="17"/>
       <c r="T57" s="17"/>
       <c r="U57" s="17"/>
@@ -3424,8 +3485,9 @@
       <c r="AB57" s="17"/>
       <c r="AC57" s="17"/>
       <c r="AD57" s="17"/>
-    </row>
-    <row r="58" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE57" s="17"/>
+    </row>
+    <row r="58" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
         <v>74</v>
       </c>
@@ -3447,20 +3509,20 @@
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
       <c r="M58" s="8"/>
-      <c r="N58" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N58" s="8"/>
       <c r="O58" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P58" s="8">
+        <f>C58*O58</f>
+        <v>53</v>
+      </c>
+      <c r="Q58" s="8">
         <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="P58" s="8">
-        <f t="shared" si="1"/>
         <v>106</v>
       </c>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="17"/>
+      <c r="R58" s="8"/>
       <c r="S58" s="17"/>
       <c r="T58" s="17"/>
       <c r="U58" s="17"/>
@@ -3473,8 +3535,9 @@
       <c r="AB58" s="17"/>
       <c r="AC58" s="17"/>
       <c r="AD58" s="17"/>
-    </row>
-    <row r="59" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE58" s="17"/>
+    </row>
+    <row r="59" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>74</v>
       </c>
@@ -3496,20 +3559,20 @@
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
       <c r="M59" s="8"/>
-      <c r="N59" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N59" s="8"/>
       <c r="O59" s="8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P59" s="8">
+        <f>C59*O59</f>
+        <v>45</v>
+      </c>
+      <c r="Q59" s="8">
         <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="P59" s="8">
-        <f t="shared" si="1"/>
         <v>90</v>
       </c>
-      <c r="Q59" s="8"/>
-      <c r="R59" s="17"/>
+      <c r="R59" s="8"/>
       <c r="S59" s="17"/>
       <c r="T59" s="17"/>
       <c r="U59" s="17"/>
@@ -3522,8 +3585,9 @@
       <c r="AB59" s="17"/>
       <c r="AC59" s="17"/>
       <c r="AD59" s="17"/>
-    </row>
-    <row r="60" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE59" s="17"/>
+    </row>
+    <row r="60" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
         <v>78</v>
       </c>
@@ -3551,23 +3615,24 @@
         <v>1</v>
       </c>
       <c r="M60" s="14"/>
-      <c r="N60" s="14">
-        <f t="shared" si="2"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="14">
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="O60" s="14">
+      <c r="P60" s="14">
+        <f>C60*O60</f>
+        <v>220</v>
+      </c>
+      <c r="Q60" s="14">
         <f t="shared" si="0"/>
-        <v>220</v>
-      </c>
-      <c r="P60" s="14">
-        <f t="shared" si="1"/>
         <v>440</v>
       </c>
-      <c r="Q60" s="14">
+      <c r="R60" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
         <v>78</v>
       </c>
@@ -3591,21 +3656,22 @@
         <v>2</v>
       </c>
       <c r="M61" s="14"/>
-      <c r="N61" s="14">
-        <f t="shared" si="2"/>
+      <c r="N61" s="14"/>
+      <c r="O61" s="14">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="O61" s="14">
+      <c r="P61" s="14">
+        <f>C61*O61</f>
+        <v>102</v>
+      </c>
+      <c r="Q61" s="14">
         <f t="shared" si="0"/>
-        <v>102</v>
-      </c>
-      <c r="P61" s="14">
-        <f t="shared" si="1"/>
         <v>204</v>
       </c>
-      <c r="Q61" s="14"/>
-    </row>
-    <row r="62" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R61" s="14"/>
+    </row>
+    <row r="62" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
         <v>78</v>
       </c>
@@ -3627,21 +3693,22 @@
         <v>2</v>
       </c>
       <c r="M62" s="14"/>
-      <c r="N62" s="14">
-        <f t="shared" si="2"/>
+      <c r="N62" s="14"/>
+      <c r="O62" s="14">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O62" s="14">
+      <c r="P62" s="14">
+        <f>C62*O62</f>
+        <v>34</v>
+      </c>
+      <c r="Q62" s="14">
         <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="P62" s="14">
-        <f t="shared" si="1"/>
         <v>68</v>
       </c>
-      <c r="Q62" s="14"/>
-    </row>
-    <row r="63" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R62" s="14"/>
+    </row>
+    <row r="63" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
         <v>81</v>
       </c>
@@ -3669,22 +3736,22 @@
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
       <c r="M63" s="8"/>
-      <c r="N63" s="8">
-        <f t="shared" si="2"/>
+      <c r="N63" s="8"/>
+      <c r="O63" s="8">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="O63" s="8">
+      <c r="P63" s="8">
+        <f>C63*O63</f>
+        <v>620</v>
+      </c>
+      <c r="Q63" s="8">
         <f t="shared" si="0"/>
-        <v>620</v>
-      </c>
-      <c r="P63" s="8">
-        <f t="shared" si="1"/>
         <v>1240</v>
       </c>
-      <c r="Q63" s="8">
-        <v>1</v>
-      </c>
-      <c r="R63" s="17"/>
+      <c r="R63" s="8">
+        <v>1</v>
+      </c>
       <c r="S63" s="17"/>
       <c r="T63" s="17"/>
       <c r="U63" s="17"/>
@@ -3697,8 +3764,9 @@
       <c r="AB63" s="17"/>
       <c r="AC63" s="17"/>
       <c r="AD63" s="17"/>
-    </row>
-    <row r="64" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE63" s="17"/>
+    </row>
+    <row r="64" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
         <v>83</v>
       </c>
@@ -3722,23 +3790,24 @@
       <c r="K64" s="14"/>
       <c r="L64" s="14"/>
       <c r="M64" s="14"/>
-      <c r="N64" s="14">
-        <f t="shared" si="2"/>
+      <c r="N64" s="14"/>
+      <c r="O64" s="14">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O64" s="14">
+      <c r="P64" s="14">
+        <f>C64*O64</f>
+        <v>124</v>
+      </c>
+      <c r="Q64" s="14">
         <f t="shared" si="0"/>
-        <v>124</v>
-      </c>
-      <c r="P64" s="14">
-        <f t="shared" si="1"/>
         <v>248</v>
       </c>
-      <c r="Q64" s="14">
+      <c r="R64" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
         <v>83</v>
       </c>
@@ -3760,21 +3829,22 @@
       <c r="K65" s="14"/>
       <c r="L65" s="14"/>
       <c r="M65" s="14"/>
-      <c r="N65" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N65" s="14"/>
       <c r="O65" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P65" s="14">
+        <f>C65*O65</f>
+        <v>59</v>
+      </c>
+      <c r="Q65" s="14">
         <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="P65" s="14">
-        <f t="shared" si="1"/>
         <v>118</v>
       </c>
-      <c r="Q65" s="14"/>
-    </row>
-    <row r="66" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R65" s="14"/>
+    </row>
+    <row r="66" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
         <v>83</v>
       </c>
@@ -3796,21 +3866,22 @@
       <c r="K66" s="14"/>
       <c r="L66" s="14"/>
       <c r="M66" s="14"/>
-      <c r="N66" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N66" s="14"/>
       <c r="O66" s="14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P66" s="14">
+        <f>C66*O66</f>
+        <v>58</v>
+      </c>
+      <c r="Q66" s="14">
         <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="P66" s="14">
-        <f t="shared" si="1"/>
         <v>116</v>
       </c>
-      <c r="Q66" s="14"/>
-    </row>
-    <row r="67" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R66" s="14"/>
+    </row>
+    <row r="67" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>87</v>
       </c>
@@ -3835,22 +3906,22 @@
       </c>
       <c r="L67" s="8"/>
       <c r="M67" s="8"/>
-      <c r="N67" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N67" s="8"/>
       <c r="O67" s="8">
+        <f t="shared" ref="O67:O68" si="3">SUM(D67:N67)</f>
+        <v>1</v>
+      </c>
+      <c r="P67" s="8">
+        <f>C67*O67</f>
+        <v>69</v>
+      </c>
+      <c r="Q67" s="8">
         <f t="shared" si="0"/>
-        <v>69</v>
-      </c>
-      <c r="P67" s="8">
-        <f t="shared" si="1"/>
         <v>138</v>
       </c>
-      <c r="Q67" s="8">
-        <v>1</v>
-      </c>
-      <c r="R67" s="17"/>
+      <c r="R67" s="8">
+        <v>1</v>
+      </c>
       <c r="S67" s="17"/>
       <c r="T67" s="17"/>
       <c r="U67" s="17"/>
@@ -3863,8 +3934,9 @@
       <c r="AB67" s="17"/>
       <c r="AC67" s="17"/>
       <c r="AD67" s="17"/>
-    </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE67" s="17"/>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>136</v>
       </c>
@@ -3886,23 +3958,24 @@
       <c r="M68" s="6">
         <v>1</v>
       </c>
-      <c r="N68" s="14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
+      <c r="N68" s="6"/>
       <c r="O68" s="14">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P68" s="14">
+        <f>C68*O68</f>
+        <v>188</v>
+      </c>
+      <c r="Q68" s="14">
         <f t="shared" si="0"/>
-        <v>188</v>
-      </c>
-      <c r="P68" s="14">
-        <f t="shared" si="1"/>
         <v>376</v>
       </c>
-      <c r="Q68" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R68" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -3916,81 +3989,83 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
-      <c r="N69" s="6">
-        <f>SUM(N2:N68)</f>
-        <v>167</v>
-      </c>
+      <c r="N69" s="6"/>
       <c r="O69" s="6">
         <f>SUM(O2:O68)</f>
-        <v>12917</v>
+        <v>168</v>
       </c>
       <c r="P69" s="6">
         <f>SUM(P2:P68)</f>
-        <v>25834</v>
-      </c>
-      <c r="Q69" s="6"/>
-    </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.3">
+        <v>12944</v>
+      </c>
+      <c r="Q69" s="6">
+        <f>SUM(Q2:Q68)</f>
+        <v>25888</v>
+      </c>
+      <c r="R69" s="6"/>
+    </row>
+    <row r="70" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>11</v>
       </c>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
       <c r="D70" s="12">
-        <f t="shared" ref="D70:M70" si="6">SUM(D2:D67)</f>
+        <f t="shared" ref="D70:M70" si="4">SUM(D2:D67)</f>
         <v>5</v>
       </c>
       <c r="E70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="F70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="G70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="H70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="I70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>22</v>
       </c>
       <c r="J70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="K70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="L70" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>16</v>
       </c>
       <c r="M70" s="12">
-        <f t="shared" si="6"/>
-        <v>36</v>
-      </c>
-      <c r="N70" s="12">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12">
         <f>SUM(D70:M70)</f>
-        <v>166</v>
-      </c>
-      <c r="O70" s="12"/>
-      <c r="P70" s="7">
-        <f>SUM(P2:P68)</f>
-        <v>25834</v>
-      </c>
-      <c r="Q70" s="13">
+        <v>167</v>
+      </c>
+      <c r="P70" s="12"/>
+      <c r="Q70" s="7">
         <f>SUM(Q2:Q68)</f>
+        <v>25888</v>
+      </c>
+      <c r="R70" s="13">
+        <f>SUM(R2:R68)</f>
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -4008,8 +4083,9 @@
       <c r="O71" s="6"/>
       <c r="P71" s="6"/>
       <c r="Q71" s="6"/>
-    </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R71" s="6"/>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -4027,8 +4103,9 @@
       <c r="O72" s="6"/>
       <c r="P72" s="6"/>
       <c r="Q72" s="6"/>
-    </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R72" s="6"/>
+    </row>
+    <row r="73" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -4046,8 +4123,9 @@
       <c r="O73" s="6"/>
       <c r="P73" s="6"/>
       <c r="Q73" s="6"/>
-    </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R73" s="6"/>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -4065,8 +4143,9 @@
       <c r="O74" s="6"/>
       <c r="P74" s="6"/>
       <c r="Q74" s="6"/>
-    </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R74" s="6"/>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -4084,8 +4163,9 @@
       <c r="O75" s="6"/>
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
-    </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R75" s="6"/>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -4103,8 +4183,9 @@
       <c r="O76" s="6"/>
       <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
-    </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R76" s="6"/>
+    </row>
+    <row r="77" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -4122,8 +4203,9 @@
       <c r="O77" s="6"/>
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
-    </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R77" s="6"/>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -4141,8 +4223,9 @@
       <c r="O78" s="6"/>
       <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
-    </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R78" s="6"/>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -4159,9 +4242,10 @@
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
       <c r="P79" s="5"/>
-      <c r="Q79" s="6"/>
-    </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="Q79" s="5"/>
+      <c r="R79" s="6"/>
+    </row>
+    <row r="80" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>0</v>
       </c>
@@ -4201,12 +4285,15 @@
       <c r="M80" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="N80" s="9"/>
+      <c r="N80" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="O80" s="9"/>
       <c r="P80" s="9"/>
       <c r="Q80" s="9"/>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R80" s="9"/>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>13</v>
       </c>
@@ -4214,11 +4301,11 @@
         <v>14</v>
       </c>
       <c r="C81" s="8">
-        <f t="shared" ref="C81:C112" si="7">C2*2</f>
+        <f t="shared" ref="C81:C112" si="5">C2*2</f>
         <v>16</v>
       </c>
       <c r="D81" s="8">
-        <f t="shared" ref="D81:D88" si="8">C81*D2</f>
+        <f t="shared" ref="D81:D88" si="6">C81*D2</f>
         <v>0</v>
       </c>
       <c r="E81" s="8">
@@ -4254,21 +4341,22 @@
         <v>16</v>
       </c>
       <c r="M81" s="8">
-        <f t="shared" ref="M81:M94" si="9">C81*M2</f>
+        <f>C81*M2</f>
         <v>32</v>
       </c>
       <c r="N81" s="8"/>
       <c r="O81" s="8"/>
-      <c r="P81" s="8">
-        <f>SUM(D81:M81)</f>
+      <c r="P81" s="8"/>
+      <c r="Q81" s="8">
+        <f>SUM(D81:N81)</f>
         <v>64</v>
       </c>
-      <c r="Q81" s="8">
-        <f>SUM(P81:P83)</f>
+      <c r="R81" s="8">
+        <f>SUM(Q81:Q83)</f>
         <v>148</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>13</v>
       </c>
@@ -4276,11 +4364,11 @@
         <v>15</v>
       </c>
       <c r="C82" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="D82" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E82" s="8">
@@ -4316,18 +4404,19 @@
         <v>0</v>
       </c>
       <c r="M82" s="8">
-        <f t="shared" si="9"/>
+        <f>C82*M3</f>
         <v>0</v>
       </c>
       <c r="N82" s="8"/>
       <c r="O82" s="8"/>
-      <c r="P82" s="8">
-        <f t="shared" ref="P82:P147" si="10">SUM(D82:M82)</f>
+      <c r="P82" s="8"/>
+      <c r="Q82" s="8">
+        <f t="shared" ref="Q82:Q145" si="7">SUM(D82:N82)</f>
         <v>4</v>
       </c>
-      <c r="Q82" s="8"/>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R82" s="8"/>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>13</v>
       </c>
@@ -4335,11 +4424,11 @@
         <v>16</v>
       </c>
       <c r="C83" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="D83" s="8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="E83" s="8">
@@ -4375,18 +4464,19 @@
         <v>0</v>
       </c>
       <c r="M83" s="8">
-        <f t="shared" si="9"/>
+        <f>C83*M4</f>
         <v>0</v>
       </c>
       <c r="N83" s="8"/>
       <c r="O83" s="8"/>
-      <c r="P83" s="8">
-        <f t="shared" si="10"/>
+      <c r="P83" s="8"/>
+      <c r="Q83" s="8">
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="Q83" s="8"/>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R83" s="8"/>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>17</v>
       </c>
@@ -4394,11 +4484,11 @@
         <v>18</v>
       </c>
       <c r="C84" s="6">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>564</v>
       </c>
       <c r="D84" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E84" s="6">
@@ -4434,21 +4524,22 @@
         <v>0</v>
       </c>
       <c r="M84" s="14">
-        <f t="shared" si="9"/>
+        <f>C84*M5</f>
         <v>564</v>
       </c>
-      <c r="N84" s="6"/>
-      <c r="O84" s="14"/>
-      <c r="P84" s="14">
-        <f t="shared" si="10"/>
+      <c r="N84" s="14"/>
+      <c r="O84" s="6"/>
+      <c r="P84" s="14"/>
+      <c r="Q84" s="14">
+        <f t="shared" si="7"/>
         <v>1128</v>
       </c>
-      <c r="Q84" s="6">
-        <f>SUM(P84)</f>
+      <c r="R84" s="6">
+        <f>SUM(Q84)</f>
         <v>1128</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>129</v>
       </c>
@@ -4456,61 +4547,62 @@
         <v>130</v>
       </c>
       <c r="C85" s="8">
+        <f t="shared" si="5"/>
+        <v>148</v>
+      </c>
+      <c r="D85" s="8">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E85" s="8">
+        <f t="shared" ref="E85:L85" si="8">D85*E6</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="G85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="H85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="I85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="K85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="L85" s="8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M85" s="8">
+        <f>C85*M6</f>
+        <v>148</v>
+      </c>
+      <c r="N85" s="8"/>
+      <c r="O85" s="8"/>
+      <c r="P85" s="8"/>
+      <c r="Q85" s="8">
         <f t="shared" si="7"/>
         <v>148</v>
       </c>
-      <c r="D85" s="8">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E85" s="8">
-        <f t="shared" ref="E85:L85" si="11">D85*E6</f>
-        <v>0</v>
-      </c>
-      <c r="F85" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G85" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I85" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J85" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K85" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L85" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M85" s="8">
-        <f t="shared" si="9"/>
+      <c r="R85" s="8">
+        <f>SUM(Q85)</f>
         <v>148</v>
       </c>
-      <c r="N85" s="8"/>
-      <c r="O85" s="8"/>
-      <c r="P85" s="8">
-        <f>SUM(D85:M85)</f>
-        <v>148</v>
-      </c>
-      <c r="Q85" s="8">
-        <f>SUM(P85)</f>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="14" t="s">
         <v>19</v>
       </c>
@@ -4518,11 +4610,11 @@
         <v>20</v>
       </c>
       <c r="C86" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>278</v>
       </c>
       <c r="D86" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E86" s="14">
@@ -4554,25 +4646,26 @@
         <v>278</v>
       </c>
       <c r="L86" s="14">
-        <f t="shared" ref="L86:L94" si="12">C86*L7</f>
+        <f t="shared" ref="L86:L94" si="9">C86*L7</f>
         <v>0</v>
       </c>
       <c r="M86" s="14">
-        <f t="shared" si="9"/>
+        <f>C86*M7</f>
         <v>834</v>
       </c>
       <c r="N86" s="14"/>
       <c r="O86" s="14"/>
-      <c r="P86" s="14">
-        <f t="shared" si="10"/>
+      <c r="P86" s="14"/>
+      <c r="Q86" s="14">
+        <f t="shared" si="7"/>
         <v>1112</v>
       </c>
-      <c r="Q86" s="14">
-        <f>SUM(P86:P89)</f>
+      <c r="R86" s="14">
+        <f>SUM(Q86:Q89)</f>
         <v>1962</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
         <v>19</v>
       </c>
@@ -4580,11 +4673,11 @@
         <v>21</v>
       </c>
       <c r="C87" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>282</v>
       </c>
       <c r="D87" s="14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E87" s="14">
@@ -4616,22 +4709,23 @@
         <v>0</v>
       </c>
       <c r="L87" s="14">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M87" s="14">
-        <f t="shared" si="9"/>
+        <f>C87*M8</f>
         <v>0</v>
       </c>
       <c r="N87" s="14"/>
       <c r="O87" s="14"/>
-      <c r="P87" s="14">
-        <f t="shared" si="10"/>
+      <c r="P87" s="14"/>
+      <c r="Q87" s="14">
+        <f t="shared" si="7"/>
         <v>282</v>
       </c>
-      <c r="Q87" s="14"/>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R87" s="14"/>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
         <v>19</v>
       </c>
@@ -4639,58 +4733,59 @@
         <v>135</v>
       </c>
       <c r="C88" s="14">
+        <f t="shared" si="5"/>
+        <v>276</v>
+      </c>
+      <c r="D88" s="14">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E88" s="14">
+        <f>C88*E9</f>
+        <v>0</v>
+      </c>
+      <c r="F88" s="14">
+        <f>C88*F9</f>
+        <v>0</v>
+      </c>
+      <c r="G88" s="14">
+        <f>C88*G9</f>
+        <v>0</v>
+      </c>
+      <c r="H88" s="14">
+        <f>C88*H9</f>
+        <v>0</v>
+      </c>
+      <c r="I88" s="14">
+        <f>C88*I9</f>
+        <v>0</v>
+      </c>
+      <c r="J88" s="14">
+        <f>C88*J9</f>
+        <v>0</v>
+      </c>
+      <c r="K88" s="14">
+        <f>C88*K9</f>
+        <v>0</v>
+      </c>
+      <c r="L88" s="14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M88" s="14">
+        <f>C88*M9</f>
+        <v>276</v>
+      </c>
+      <c r="N88" s="14"/>
+      <c r="O88" s="14"/>
+      <c r="P88" s="14"/>
+      <c r="Q88" s="14">
         <f t="shared" si="7"/>
         <v>276</v>
       </c>
-      <c r="D88" s="14">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E88" s="14">
-        <f>C88*E9</f>
-        <v>0</v>
-      </c>
-      <c r="F88" s="14">
-        <f>C88*F9</f>
-        <v>0</v>
-      </c>
-      <c r="G88" s="14">
-        <f>C88*G9</f>
-        <v>0</v>
-      </c>
-      <c r="H88" s="14">
-        <f>C88*H9</f>
-        <v>0</v>
-      </c>
-      <c r="I88" s="14">
-        <f>C88*I9</f>
-        <v>0</v>
-      </c>
-      <c r="J88" s="14">
-        <f>C88*J9</f>
-        <v>0</v>
-      </c>
-      <c r="K88" s="14">
-        <f>C88*K9</f>
-        <v>0</v>
-      </c>
-      <c r="L88" s="14">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M88" s="14">
-        <f t="shared" si="9"/>
-        <v>276</v>
-      </c>
-      <c r="N88" s="14"/>
-      <c r="O88" s="14"/>
-      <c r="P88" s="14">
-        <f t="shared" si="10"/>
-        <v>276</v>
-      </c>
-      <c r="Q88" s="14"/>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R88" s="14"/>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="s">
         <v>19</v>
       </c>
@@ -4698,50 +4793,51 @@
         <v>133</v>
       </c>
       <c r="C89" s="14">
+        <f t="shared" si="5"/>
+        <v>292</v>
+      </c>
+      <c r="D89" s="14">
+        <v>0</v>
+      </c>
+      <c r="E89" s="14">
+        <v>0</v>
+      </c>
+      <c r="F89" s="14">
+        <v>0</v>
+      </c>
+      <c r="G89" s="14">
+        <v>0</v>
+      </c>
+      <c r="H89" s="14">
+        <v>0</v>
+      </c>
+      <c r="I89" s="14">
+        <v>0</v>
+      </c>
+      <c r="J89" s="14">
+        <v>0</v>
+      </c>
+      <c r="K89" s="14">
+        <v>0</v>
+      </c>
+      <c r="L89" s="14">
+        <f t="shared" si="9"/>
+        <v>292</v>
+      </c>
+      <c r="M89" s="14">
+        <f>C89*M10</f>
+        <v>0</v>
+      </c>
+      <c r="N89" s="14"/>
+      <c r="O89" s="14"/>
+      <c r="P89" s="14"/>
+      <c r="Q89" s="14">
         <f t="shared" si="7"/>
         <v>292</v>
       </c>
-      <c r="D89" s="14">
-        <v>0</v>
-      </c>
-      <c r="E89" s="14">
-        <v>0</v>
-      </c>
-      <c r="F89" s="14">
-        <v>0</v>
-      </c>
-      <c r="G89" s="14">
-        <v>0</v>
-      </c>
-      <c r="H89" s="14">
-        <v>0</v>
-      </c>
-      <c r="I89" s="14">
-        <v>0</v>
-      </c>
-      <c r="J89" s="14">
-        <v>0</v>
-      </c>
-      <c r="K89" s="14">
-        <v>0</v>
-      </c>
-      <c r="L89" s="14">
-        <f t="shared" si="12"/>
-        <v>292</v>
-      </c>
-      <c r="M89" s="14">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N89" s="14"/>
-      <c r="O89" s="14"/>
-      <c r="P89" s="14">
-        <f t="shared" si="10"/>
-        <v>292</v>
-      </c>
-      <c r="Q89" s="14"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R89" s="14"/>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>22</v>
       </c>
@@ -4749,7 +4845,7 @@
         <v>23</v>
       </c>
       <c r="C90" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>66</v>
       </c>
       <c r="D90" s="8">
@@ -4785,25 +4881,26 @@
         <v>66</v>
       </c>
       <c r="L90" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M90" s="8">
-        <f t="shared" si="9"/>
+        <f>C90*M11</f>
         <v>0</v>
       </c>
       <c r="N90" s="8"/>
       <c r="O90" s="8"/>
-      <c r="P90" s="8">
-        <f t="shared" si="10"/>
+      <c r="P90" s="8"/>
+      <c r="Q90" s="8">
+        <f t="shared" si="7"/>
         <v>66</v>
       </c>
-      <c r="Q90" s="8">
-        <f>SUM(P90:P94)</f>
+      <c r="R90" s="8">
+        <f>SUM(Q90:Q94)</f>
         <v>1288</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
         <v>22</v>
       </c>
@@ -4811,7 +4908,7 @@
         <v>24</v>
       </c>
       <c r="C91" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>92</v>
       </c>
       <c r="D91" s="8">
@@ -4847,22 +4944,23 @@
         <v>0</v>
       </c>
       <c r="L91" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M91" s="8">
-        <f t="shared" si="9"/>
+        <f>C91*M12</f>
         <v>0</v>
       </c>
       <c r="N91" s="8"/>
       <c r="O91" s="8"/>
-      <c r="P91" s="8">
-        <f t="shared" si="10"/>
+      <c r="P91" s="8"/>
+      <c r="Q91" s="8">
+        <f t="shared" si="7"/>
         <v>92</v>
       </c>
-      <c r="Q91" s="8"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R91" s="8"/>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="8" t="s">
         <v>22</v>
       </c>
@@ -4870,7 +4968,7 @@
         <v>25</v>
       </c>
       <c r="C92" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>84</v>
       </c>
       <c r="D92" s="8">
@@ -4906,22 +5004,23 @@
         <v>84</v>
       </c>
       <c r="L92" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M92" s="8">
-        <f t="shared" si="9"/>
+        <f>C92*M13</f>
         <v>840</v>
       </c>
       <c r="N92" s="8"/>
       <c r="O92" s="8"/>
-      <c r="P92" s="8">
-        <f t="shared" si="10"/>
+      <c r="P92" s="8"/>
+      <c r="Q92" s="8">
+        <f t="shared" si="7"/>
         <v>924</v>
       </c>
-      <c r="Q92" s="8"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R92" s="8"/>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="8" t="s">
         <v>22</v>
       </c>
@@ -4929,7 +5028,7 @@
         <v>26</v>
       </c>
       <c r="C93" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>120</v>
       </c>
       <c r="D93" s="8">
@@ -4965,22 +5064,23 @@
         <v>0</v>
       </c>
       <c r="L93" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M93" s="8">
-        <f t="shared" si="9"/>
+        <f>C93*M14</f>
         <v>0</v>
       </c>
       <c r="N93" s="8"/>
       <c r="O93" s="8"/>
-      <c r="P93" s="8">
-        <f t="shared" si="10"/>
+      <c r="P93" s="8"/>
+      <c r="Q93" s="8">
+        <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="Q93" s="8"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R93" s="8"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
         <v>22</v>
       </c>
@@ -4988,7 +5088,7 @@
         <v>27</v>
       </c>
       <c r="C94" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>86</v>
       </c>
       <c r="D94" s="8">
@@ -5024,22 +5124,23 @@
         <v>0</v>
       </c>
       <c r="L94" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M94" s="8">
-        <f t="shared" si="9"/>
+        <f>C94*M15</f>
         <v>0</v>
       </c>
       <c r="N94" s="8"/>
       <c r="O94" s="8"/>
-      <c r="P94" s="8">
-        <f t="shared" si="10"/>
+      <c r="P94" s="8"/>
+      <c r="Q94" s="8">
+        <f t="shared" si="7"/>
         <v>86</v>
       </c>
-      <c r="Q94" s="8"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R94" s="8"/>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="14" t="s">
         <v>125</v>
       </c>
@@ -5047,7 +5148,7 @@
         <v>126</v>
       </c>
       <c r="C95" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>364</v>
       </c>
       <c r="D95" s="14">
@@ -5083,16 +5184,17 @@
       </c>
       <c r="N95" s="14"/>
       <c r="O95" s="14"/>
-      <c r="P95" s="14">
-        <f t="shared" si="10"/>
+      <c r="P95" s="14"/>
+      <c r="Q95" s="14">
+        <f t="shared" si="7"/>
         <v>364</v>
       </c>
-      <c r="Q95" s="14">
-        <f>P95</f>
+      <c r="R95" s="14">
+        <f>Q95</f>
         <v>364</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="8" t="s">
         <v>28</v>
       </c>
@@ -5100,61 +5202,62 @@
         <v>29</v>
       </c>
       <c r="C96" s="8">
+        <f t="shared" si="5"/>
+        <v>370</v>
+      </c>
+      <c r="D96" s="8">
+        <f t="shared" ref="D96:D106" si="10">C96*D17</f>
+        <v>0</v>
+      </c>
+      <c r="E96" s="8">
+        <f>C96*E17</f>
+        <v>0</v>
+      </c>
+      <c r="F96" s="8">
+        <f>C96*F17</f>
+        <v>0</v>
+      </c>
+      <c r="G96" s="8">
+        <f>C96*G17</f>
+        <v>0</v>
+      </c>
+      <c r="H96" s="8">
+        <f>D96*H17</f>
+        <v>0</v>
+      </c>
+      <c r="I96" s="8">
+        <f>C96*I17</f>
+        <v>0</v>
+      </c>
+      <c r="J96" s="8">
+        <f>C96*J17</f>
+        <v>0</v>
+      </c>
+      <c r="K96" s="8">
+        <f>C96*K17</f>
+        <v>0</v>
+      </c>
+      <c r="L96" s="8">
+        <f>C96*L17</f>
+        <v>0</v>
+      </c>
+      <c r="M96" s="8">
+        <f>C96*M17</f>
+        <v>370</v>
+      </c>
+      <c r="N96" s="8"/>
+      <c r="O96" s="8"/>
+      <c r="P96" s="8"/>
+      <c r="Q96" s="8">
         <f t="shared" si="7"/>
         <v>370</v>
       </c>
-      <c r="D96" s="8">
-        <f t="shared" ref="D96:D106" si="13">C96*D17</f>
-        <v>0</v>
-      </c>
-      <c r="E96" s="8">
-        <f>C96*E17</f>
-        <v>0</v>
-      </c>
-      <c r="F96" s="8">
-        <f>C96*F17</f>
-        <v>0</v>
-      </c>
-      <c r="G96" s="8">
-        <f>C96*G17</f>
-        <v>0</v>
-      </c>
-      <c r="H96" s="8">
-        <f>D96*H17</f>
-        <v>0</v>
-      </c>
-      <c r="I96" s="8">
-        <f>C96*I17</f>
-        <v>0</v>
-      </c>
-      <c r="J96" s="8">
-        <f>C96*J17</f>
-        <v>0</v>
-      </c>
-      <c r="K96" s="8">
-        <f>C96*K17</f>
-        <v>0</v>
-      </c>
-      <c r="L96" s="8">
-        <f>C96*L17</f>
-        <v>0</v>
-      </c>
-      <c r="M96" s="8">
-        <f t="shared" ref="M96:M127" si="14">C96*M17</f>
-        <v>370</v>
-      </c>
-      <c r="N96" s="8"/>
-      <c r="O96" s="8"/>
-      <c r="P96" s="8">
-        <f t="shared" si="10"/>
-        <v>370</v>
-      </c>
-      <c r="Q96" s="8">
-        <f>SUM(P96:P97)</f>
+      <c r="R96" s="8">
+        <f>SUM(Q96:Q97)</f>
         <v>1202</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
         <v>28</v>
       </c>
@@ -5162,11 +5265,11 @@
         <v>29</v>
       </c>
       <c r="C97" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>416</v>
       </c>
       <c r="D97" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E97" s="8">
@@ -5202,18 +5305,19 @@
         <v>416</v>
       </c>
       <c r="M97" s="8">
-        <f t="shared" si="14"/>
+        <f>C97*M18</f>
         <v>0</v>
       </c>
       <c r="N97" s="8"/>
       <c r="O97" s="8"/>
-      <c r="P97" s="8">
-        <f t="shared" si="10"/>
+      <c r="P97" s="8"/>
+      <c r="Q97" s="8">
+        <f t="shared" si="7"/>
         <v>832</v>
       </c>
-      <c r="Q97" s="8"/>
-    </row>
-    <row r="98" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R97" s="8"/>
+    </row>
+    <row r="98" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="14" t="s">
         <v>131</v>
       </c>
@@ -5221,61 +5325,62 @@
         <v>132</v>
       </c>
       <c r="C98" s="14">
+        <f t="shared" si="5"/>
+        <v>236</v>
+      </c>
+      <c r="D98" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E98" s="14">
+        <f t="shared" ref="E98:L98" si="11">D98*E19</f>
+        <v>0</v>
+      </c>
+      <c r="F98" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="G98" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I98" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J98" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K98" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="L98" s="14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="M98" s="14">
+        <f>C98*M19</f>
+        <v>236</v>
+      </c>
+      <c r="N98" s="14"/>
+      <c r="O98" s="14"/>
+      <c r="P98" s="14"/>
+      <c r="Q98" s="14">
         <f t="shared" si="7"/>
         <v>236</v>
       </c>
-      <c r="D98" s="14">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E98" s="14">
-        <f t="shared" ref="E98:L98" si="15">D98*E19</f>
-        <v>0</v>
-      </c>
-      <c r="F98" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="G98" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="I98" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J98" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="K98" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="L98" s="14">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="M98" s="14">
-        <f t="shared" si="14"/>
+      <c r="R98" s="14">
+        <f>Q98</f>
         <v>236</v>
       </c>
-      <c r="N98" s="14"/>
-      <c r="O98" s="14"/>
-      <c r="P98" s="14">
-        <f t="shared" si="10"/>
-        <v>236</v>
-      </c>
-      <c r="Q98" s="14">
-        <f>P98</f>
-        <v>236</v>
-      </c>
-    </row>
-    <row r="99" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
         <v>30</v>
       </c>
@@ -5283,179 +5388,182 @@
         <v>31</v>
       </c>
       <c r="C99" s="8">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D99" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E99" s="8">
+        <f t="shared" ref="E99:E106" si="12">C99*E20</f>
+        <v>110</v>
+      </c>
+      <c r="F99" s="8">
+        <f t="shared" ref="F99:F106" si="13">C99*F20</f>
+        <v>110</v>
+      </c>
+      <c r="G99" s="8">
+        <f t="shared" ref="G99:G106" si="14">C99*G20</f>
+        <v>0</v>
+      </c>
+      <c r="H99" s="8">
+        <f t="shared" ref="H99:H106" si="15">C99*H20</f>
+        <v>0</v>
+      </c>
+      <c r="I99" s="8">
+        <f t="shared" ref="I99:I106" si="16">C99*I20</f>
+        <v>0</v>
+      </c>
+      <c r="J99" s="8">
+        <f t="shared" ref="J99:J106" si="17">C99*J20</f>
+        <v>0</v>
+      </c>
+      <c r="K99" s="8">
+        <f t="shared" ref="K99:K106" si="18">C99*K20</f>
+        <v>0</v>
+      </c>
+      <c r="L99" s="8">
+        <f t="shared" ref="L99:L106" si="19">C99*L20</f>
+        <v>0</v>
+      </c>
+      <c r="M99" s="8">
+        <f>C99*M20</f>
+        <v>0</v>
+      </c>
+      <c r="N99" s="8"/>
+      <c r="O99" s="8"/>
+      <c r="P99" s="8"/>
+      <c r="Q99" s="8">
+        <f t="shared" si="7"/>
+        <v>220</v>
+      </c>
+      <c r="R99" s="8">
+        <f>SUM(Q99:Q103)</f>
+        <v>906</v>
+      </c>
+    </row>
+    <row r="100" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C100" s="8">
+        <f t="shared" si="5"/>
+        <v>108</v>
+      </c>
+      <c r="D100" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E100" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F100" s="8">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G100" s="8">
+        <f t="shared" si="14"/>
+        <v>108</v>
+      </c>
+      <c r="H100" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I100" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J100" s="8">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="K100" s="8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L100" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M100" s="8">
+        <f>C100*M21</f>
+        <v>0</v>
+      </c>
+      <c r="N100" s="8"/>
+      <c r="O100" s="8"/>
+      <c r="P100" s="8"/>
+      <c r="Q100" s="8">
+        <f t="shared" si="7"/>
+        <v>108</v>
+      </c>
+      <c r="R100" s="8"/>
+    </row>
+    <row r="101" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" s="8">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="D101" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E101" s="8">
+        <f t="shared" si="12"/>
+        <v>110</v>
+      </c>
+      <c r="F101" s="8">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G101" s="8">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H101" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I101" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J101" s="8">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="K101" s="8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L101" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M101" s="8">
+        <f>C101*M22</f>
+        <v>0</v>
+      </c>
+      <c r="N101" s="8"/>
+      <c r="O101" s="8"/>
+      <c r="P101" s="8"/>
+      <c r="Q101" s="8">
         <f t="shared" si="7"/>
         <v>110</v>
       </c>
-      <c r="D99" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E99" s="8">
-        <f t="shared" ref="E99:E106" si="16">C99*E20</f>
-        <v>110</v>
-      </c>
-      <c r="F99" s="8">
-        <f t="shared" ref="F99:F106" si="17">C99*F20</f>
-        <v>110</v>
-      </c>
-      <c r="G99" s="8">
-        <f t="shared" ref="G99:G106" si="18">C99*G20</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="8">
-        <f t="shared" ref="H99:H106" si="19">C99*H20</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="8">
-        <f t="shared" ref="I99:I106" si="20">C99*I20</f>
-        <v>0</v>
-      </c>
-      <c r="J99" s="8">
-        <f t="shared" ref="J99:J106" si="21">C99*J20</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="8">
-        <f t="shared" ref="K99:K106" si="22">C99*K20</f>
-        <v>0</v>
-      </c>
-      <c r="L99" s="8">
-        <f t="shared" ref="L99:L106" si="23">C99*L20</f>
-        <v>0</v>
-      </c>
-      <c r="M99" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N99" s="8"/>
-      <c r="O99" s="8"/>
-      <c r="P99" s="8">
-        <f t="shared" si="10"/>
-        <v>220</v>
-      </c>
-      <c r="Q99" s="8">
-        <f>SUM(P99:P103)</f>
-        <v>906</v>
-      </c>
-    </row>
-    <row r="100" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C100" s="8">
-        <f t="shared" si="7"/>
-        <v>108</v>
-      </c>
-      <c r="D100" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E100" s="8">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F100" s="8">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G100" s="8">
-        <f t="shared" si="18"/>
-        <v>108</v>
-      </c>
-      <c r="H100" s="8">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="8">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J100" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K100" s="8">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L100" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M100" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N100" s="8"/>
-      <c r="O100" s="8"/>
-      <c r="P100" s="8">
-        <f t="shared" si="10"/>
-        <v>108</v>
-      </c>
-      <c r="Q100" s="8"/>
-    </row>
-    <row r="101" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C101" s="8">
-        <f t="shared" si="7"/>
-        <v>110</v>
-      </c>
-      <c r="D101" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E101" s="8">
-        <f t="shared" si="16"/>
-        <v>110</v>
-      </c>
-      <c r="F101" s="8">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G101" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H101" s="8">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I101" s="8">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J101" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K101" s="8">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L101" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M101" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
-      <c r="P101" s="8">
-        <f t="shared" si="10"/>
-        <v>110</v>
-      </c>
-      <c r="Q101" s="8"/>
-    </row>
-    <row r="102" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R101" s="8"/>
+    </row>
+    <row r="102" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
         <v>30</v>
       </c>
@@ -5463,58 +5571,59 @@
         <v>34</v>
       </c>
       <c r="C102" s="8">
+        <f t="shared" si="5"/>
+        <v>92</v>
+      </c>
+      <c r="D102" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E102" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F102" s="8">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G102" s="8">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H102" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I102" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J102" s="8">
+        <f t="shared" si="17"/>
+        <v>92</v>
+      </c>
+      <c r="K102" s="8">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L102" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M102" s="8">
+        <f>C102*M23</f>
+        <v>0</v>
+      </c>
+      <c r="N102" s="8"/>
+      <c r="O102" s="8"/>
+      <c r="P102" s="8"/>
+      <c r="Q102" s="8">
         <f t="shared" si="7"/>
         <v>92</v>
       </c>
-      <c r="D102" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E102" s="8">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F102" s="8">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G102" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H102" s="8">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I102" s="8">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J102" s="8">
-        <f t="shared" si="21"/>
-        <v>92</v>
-      </c>
-      <c r="K102" s="8">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L102" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M102" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N102" s="8"/>
-      <c r="O102" s="8"/>
-      <c r="P102" s="8">
-        <f t="shared" si="10"/>
-        <v>92</v>
-      </c>
-      <c r="Q102" s="8"/>
-    </row>
-    <row r="103" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R102" s="8"/>
+    </row>
+    <row r="103" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>30</v>
       </c>
@@ -5522,58 +5631,59 @@
         <v>35</v>
       </c>
       <c r="C103" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>94</v>
       </c>
       <c r="D103" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E103" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F103" s="8">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="E103" s="8">
+      <c r="G103" s="8">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H103" s="8">
+        <f t="shared" si="15"/>
+        <v>94</v>
+      </c>
+      <c r="I103" s="8">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F103" s="8">
+        <v>188</v>
+      </c>
+      <c r="J103" s="8">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G103" s="8">
+      <c r="K103" s="8">
         <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H103" s="8">
+        <v>94</v>
+      </c>
+      <c r="L103" s="8">
         <f t="shared" si="19"/>
-        <v>94</v>
-      </c>
-      <c r="I103" s="8">
-        <f t="shared" si="20"/>
-        <v>188</v>
-      </c>
-      <c r="J103" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K103" s="8">
-        <f t="shared" si="22"/>
-        <v>94</v>
-      </c>
-      <c r="L103" s="8">
-        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="M103" s="8">
-        <f t="shared" si="14"/>
+        <f>C103*M24</f>
         <v>0</v>
       </c>
       <c r="N103" s="8"/>
       <c r="O103" s="8"/>
-      <c r="P103" s="8">
-        <f t="shared" si="10"/>
+      <c r="P103" s="8"/>
+      <c r="Q103" s="8">
+        <f t="shared" si="7"/>
         <v>376</v>
       </c>
-      <c r="Q103" s="8"/>
-    </row>
-    <row r="104" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R103" s="8"/>
+    </row>
+    <row r="104" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="14" t="s">
         <v>98</v>
       </c>
@@ -5581,61 +5691,62 @@
         <v>101</v>
       </c>
       <c r="C104" s="14">
+        <f t="shared" si="5"/>
+        <v>800</v>
+      </c>
+      <c r="D104" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E104" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F104" s="14">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G104" s="14">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H104" s="14">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I104" s="14">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J104" s="14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="K104" s="14">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L104" s="14">
+        <f t="shared" si="19"/>
+        <v>800</v>
+      </c>
+      <c r="M104" s="14">
+        <f>C104*M25</f>
+        <v>0</v>
+      </c>
+      <c r="N104" s="14"/>
+      <c r="O104" s="14"/>
+      <c r="P104" s="14"/>
+      <c r="Q104" s="14">
         <f t="shared" si="7"/>
         <v>800</v>
       </c>
-      <c r="D104" s="14">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E104" s="14">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F104" s="14">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G104" s="14">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H104" s="14">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I104" s="14">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J104" s="14">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K104" s="14">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L104" s="14">
-        <f t="shared" si="23"/>
+      <c r="R104" s="14">
+        <f t="shared" ref="R104:R109" si="20">Q104</f>
         <v>800</v>
       </c>
-      <c r="M104" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N104" s="14"/>
-      <c r="O104" s="14"/>
-      <c r="P104" s="14">
-        <f t="shared" si="10"/>
-        <v>800</v>
-      </c>
-      <c r="Q104" s="14">
-        <f t="shared" ref="Q104:Q109" si="24">P104</f>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="105" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>36</v>
       </c>
@@ -5643,60 +5754,60 @@
         <v>37</v>
       </c>
       <c r="C105" s="8">
+        <f t="shared" si="5"/>
+        <v>726</v>
+      </c>
+      <c r="D105" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E105" s="8">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F105" s="8">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G105" s="8">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H105" s="8">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I105" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J105" s="8">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="K105" s="8">
+        <f t="shared" si="18"/>
+        <v>726</v>
+      </c>
+      <c r="L105" s="8">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M105" s="8">
+        <f>C105*M26</f>
+        <v>0</v>
+      </c>
+      <c r="N105" s="8"/>
+      <c r="O105" s="8"/>
+      <c r="P105" s="8"/>
+      <c r="Q105" s="8">
         <f t="shared" si="7"/>
         <v>726</v>
       </c>
-      <c r="D105" s="8">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E105" s="8">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F105" s="8">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G105" s="8">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H105" s="8">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I105" s="8">
+      <c r="R105" s="8">
         <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J105" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K105" s="8">
-        <f t="shared" si="22"/>
         <v>726</v>
       </c>
-      <c r="L105" s="8">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M105" s="8">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N105" s="8"/>
-      <c r="O105" s="8"/>
-      <c r="P105" s="8">
-        <f t="shared" si="10"/>
-        <v>726</v>
-      </c>
-      <c r="Q105" s="8">
-        <f t="shared" si="24"/>
-        <v>726</v>
-      </c>
-      <c r="R105" s="17"/>
       <c r="S105" s="17"/>
       <c r="T105" s="17"/>
       <c r="U105" s="17"/>
@@ -5709,8 +5820,9 @@
       <c r="AB105" s="17"/>
       <c r="AC105" s="17"/>
       <c r="AD105" s="17"/>
-    </row>
-    <row r="106" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE105" s="17"/>
+    </row>
+    <row r="106" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="14" t="s">
         <v>96</v>
       </c>
@@ -5718,61 +5830,62 @@
         <v>95</v>
       </c>
       <c r="C106" s="14">
+        <f t="shared" si="5"/>
+        <v>186</v>
+      </c>
+      <c r="D106" s="14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="E106" s="14">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F106" s="14">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G106" s="14">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H106" s="14">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="I106" s="14">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J106" s="14">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="K106" s="14">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L106" s="14">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M106" s="14">
+        <f>C106*M27</f>
+        <v>186</v>
+      </c>
+      <c r="N106" s="14"/>
+      <c r="O106" s="14"/>
+      <c r="P106" s="14"/>
+      <c r="Q106" s="14">
         <f t="shared" si="7"/>
         <v>186</v>
       </c>
-      <c r="D106" s="14">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E106" s="14">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="F106" s="14">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="G106" s="14">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="H106" s="14">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="14">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="J106" s="14">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="K106" s="14">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="L106" s="14">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M106" s="14">
-        <f t="shared" si="14"/>
+      <c r="R106" s="14">
+        <f>Q106</f>
         <v>186</v>
       </c>
-      <c r="N106" s="14"/>
-      <c r="O106" s="14"/>
-      <c r="P106" s="14">
-        <f t="shared" si="10"/>
-        <v>186</v>
-      </c>
-      <c r="Q106" s="14">
-        <f>P106</f>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="107" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>122</v>
       </c>
@@ -5780,51 +5893,51 @@
         <v>123</v>
       </c>
       <c r="C107" s="8">
+        <f t="shared" si="5"/>
+        <v>348</v>
+      </c>
+      <c r="D107" s="8">
+        <v>0</v>
+      </c>
+      <c r="E107" s="8">
+        <v>0</v>
+      </c>
+      <c r="F107" s="8">
+        <v>0</v>
+      </c>
+      <c r="G107" s="8">
+        <v>0</v>
+      </c>
+      <c r="H107" s="8">
+        <v>0</v>
+      </c>
+      <c r="I107" s="8">
+        <v>0</v>
+      </c>
+      <c r="J107" s="8">
+        <v>0</v>
+      </c>
+      <c r="K107" s="8">
+        <v>0</v>
+      </c>
+      <c r="L107" s="8">
+        <v>0</v>
+      </c>
+      <c r="M107" s="8">
+        <f>C107*M28</f>
+        <v>348</v>
+      </c>
+      <c r="N107" s="8"/>
+      <c r="O107" s="8"/>
+      <c r="P107" s="8"/>
+      <c r="Q107" s="8">
         <f t="shared" si="7"/>
         <v>348</v>
       </c>
-      <c r="D107" s="8">
-        <v>0</v>
-      </c>
-      <c r="E107" s="8">
-        <v>0</v>
-      </c>
-      <c r="F107" s="8">
-        <v>0</v>
-      </c>
-      <c r="G107" s="8">
-        <v>0</v>
-      </c>
-      <c r="H107" s="8">
-        <v>0</v>
-      </c>
-      <c r="I107" s="8">
-        <v>0</v>
-      </c>
-      <c r="J107" s="8">
-        <v>0</v>
-      </c>
-      <c r="K107" s="8">
-        <v>0</v>
-      </c>
-      <c r="L107" s="8">
-        <v>0</v>
-      </c>
-      <c r="M107" s="8">
-        <f t="shared" si="14"/>
+      <c r="R107" s="8">
+        <f>Q107</f>
         <v>348</v>
       </c>
-      <c r="N107" s="8"/>
-      <c r="O107" s="8"/>
-      <c r="P107" s="8">
-        <f>SUM(D107:M107)</f>
-        <v>348</v>
-      </c>
-      <c r="Q107" s="8">
-        <f>P107</f>
-        <v>348</v>
-      </c>
-      <c r="R107" s="17"/>
       <c r="S107" s="17"/>
       <c r="T107" s="17"/>
       <c r="U107" s="17"/>
@@ -5837,8 +5950,9 @@
       <c r="AB107" s="17"/>
       <c r="AC107" s="17"/>
       <c r="AD107" s="17"/>
-    </row>
-    <row r="108" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE107" s="17"/>
+    </row>
+    <row r="108" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="14" t="s">
         <v>99</v>
       </c>
@@ -5846,39 +5960,39 @@
         <v>100</v>
       </c>
       <c r="C108" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>418</v>
       </c>
       <c r="D108" s="14">
-        <f t="shared" ref="D108:K108" si="25">C108*D30</f>
+        <f t="shared" ref="D108:K108" si="21">C108*D30</f>
         <v>0</v>
       </c>
       <c r="E108" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F108" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="G108" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H108" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I108" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="J108" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="K108" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="L108" s="14">
@@ -5886,21 +6000,22 @@
         <v>418</v>
       </c>
       <c r="M108" s="14">
-        <f t="shared" si="14"/>
+        <f>C108*M29</f>
         <v>0</v>
       </c>
       <c r="N108" s="14"/>
       <c r="O108" s="14"/>
-      <c r="P108" s="14">
-        <f t="shared" si="10"/>
+      <c r="P108" s="14"/>
+      <c r="Q108" s="14">
+        <f t="shared" si="7"/>
         <v>418</v>
       </c>
-      <c r="Q108" s="14">
-        <f t="shared" si="24"/>
+      <c r="R108" s="14">
+        <f t="shared" si="20"/>
         <v>418</v>
       </c>
     </row>
-    <row r="109" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>38</v>
       </c>
@@ -5908,11 +6023,11 @@
         <v>39</v>
       </c>
       <c r="C109" s="8">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>516</v>
       </c>
       <c r="D109" s="8">
-        <f t="shared" ref="D109:D140" si="26">C109*D30</f>
+        <f t="shared" ref="D109:D140" si="22">C109*D30</f>
         <v>0</v>
       </c>
       <c r="E109" s="8">
@@ -5928,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="8">
-        <f t="shared" ref="H109:H140" si="27">C109*H30</f>
+        <f t="shared" ref="H109:H140" si="23">C109*H30</f>
         <v>0</v>
       </c>
       <c r="I109" s="8">
@@ -5948,20 +6063,20 @@
         <v>0</v>
       </c>
       <c r="M109" s="8">
-        <f t="shared" si="14"/>
+        <f>C109*M30</f>
         <v>0</v>
       </c>
       <c r="N109" s="8"/>
       <c r="O109" s="8"/>
-      <c r="P109" s="8">
-        <f t="shared" si="10"/>
+      <c r="P109" s="8"/>
+      <c r="Q109" s="8">
+        <f t="shared" si="7"/>
         <v>516</v>
       </c>
-      <c r="Q109" s="8">
-        <f t="shared" si="24"/>
+      <c r="R109" s="8">
+        <f t="shared" si="20"/>
         <v>516</v>
       </c>
-      <c r="R109" s="17"/>
       <c r="S109" s="17"/>
       <c r="T109" s="17"/>
       <c r="U109" s="17"/>
@@ -5974,8 +6089,9 @@
       <c r="AB109" s="17"/>
       <c r="AC109" s="17"/>
       <c r="AD109" s="17"/>
-    </row>
-    <row r="110" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE109" s="17"/>
+    </row>
+    <row r="110" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="14" t="s">
         <v>44</v>
       </c>
@@ -5983,11 +6099,11 @@
         <v>45</v>
       </c>
       <c r="C110" s="14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="D110" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="E110" s="14">
@@ -6003,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I110" s="14">
@@ -6023,21 +6139,22 @@
         <v>0</v>
       </c>
       <c r="M110" s="14">
-        <f t="shared" si="14"/>
+        <f>C110*M31</f>
         <v>0</v>
       </c>
       <c r="N110" s="14"/>
       <c r="O110" s="14"/>
-      <c r="P110" s="14">
-        <f t="shared" ref="P110:P115" si="28">SUM(D110:M110)</f>
+      <c r="P110" s="14"/>
+      <c r="Q110" s="14">
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="Q110" s="14">
-        <f>SUM(P110:P115)</f>
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="111" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R110" s="14">
+        <f>SUM(Q110:Q115)</f>
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="111" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="14" t="s">
         <v>44</v>
       </c>
@@ -6045,58 +6162,59 @@
         <v>128</v>
       </c>
       <c r="C111" s="14">
+        <f t="shared" si="5"/>
+        <v>38</v>
+      </c>
+      <c r="D111" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E111" s="14">
+        <f>D111*E32</f>
+        <v>0</v>
+      </c>
+      <c r="F111" s="14">
+        <f>E111*F32</f>
+        <v>0</v>
+      </c>
+      <c r="G111" s="14">
+        <f>F111*G32</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I111" s="14">
+        <f>D111*I32</f>
+        <v>0</v>
+      </c>
+      <c r="J111" s="14">
+        <f>E111*J32</f>
+        <v>0</v>
+      </c>
+      <c r="K111" s="14">
+        <f>F111*K32</f>
+        <v>0</v>
+      </c>
+      <c r="L111" s="14">
+        <f>G111*L32</f>
+        <v>0</v>
+      </c>
+      <c r="M111" s="14">
+        <f>C111*M32</f>
+        <v>38</v>
+      </c>
+      <c r="N111" s="14"/>
+      <c r="O111" s="14"/>
+      <c r="P111" s="14"/>
+      <c r="Q111" s="14">
         <f t="shared" si="7"/>
         <v>38</v>
       </c>
-      <c r="D111" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E111" s="14">
-        <f>D111*E32</f>
-        <v>0</v>
-      </c>
-      <c r="F111" s="14">
-        <f>E111*F32</f>
-        <v>0</v>
-      </c>
-      <c r="G111" s="14">
-        <f>F111*G32</f>
-        <v>0</v>
-      </c>
-      <c r="H111" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I111" s="14">
-        <f>D111*I32</f>
-        <v>0</v>
-      </c>
-      <c r="J111" s="14">
-        <f>E111*J32</f>
-        <v>0</v>
-      </c>
-      <c r="K111" s="14">
-        <f>F111*K32</f>
-        <v>0</v>
-      </c>
-      <c r="L111" s="14">
-        <f>G111*L32</f>
-        <v>0</v>
-      </c>
-      <c r="M111" s="14">
-        <f t="shared" si="14"/>
-        <v>38</v>
-      </c>
-      <c r="N111" s="14"/>
-      <c r="O111" s="14"/>
-      <c r="P111" s="14">
-        <f t="shared" si="28"/>
-        <v>38</v>
-      </c>
-      <c r="Q111" s="14"/>
-    </row>
-    <row r="112" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R111" s="14"/>
+    </row>
+    <row r="112" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
         <v>44</v>
       </c>
@@ -6104,58 +6222,59 @@
         <v>46</v>
       </c>
       <c r="C112" s="14">
+        <f t="shared" si="5"/>
+        <v>54</v>
+      </c>
+      <c r="D112" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E112" s="14">
+        <f t="shared" ref="E112:E140" si="24">C112*E33</f>
+        <v>0</v>
+      </c>
+      <c r="F112" s="14">
+        <f t="shared" ref="F112:F140" si="25">C112*F33</f>
+        <v>0</v>
+      </c>
+      <c r="G112" s="14">
+        <f t="shared" ref="G112:G140" si="26">C112*G33</f>
+        <v>54</v>
+      </c>
+      <c r="H112" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I112" s="14">
+        <f t="shared" ref="I112:I140" si="27">C112*I33</f>
+        <v>54</v>
+      </c>
+      <c r="J112" s="14">
+        <f t="shared" ref="J112:J140" si="28">C112*J33</f>
+        <v>108</v>
+      </c>
+      <c r="K112" s="14">
+        <f t="shared" ref="K112:K140" si="29">C112*K33</f>
+        <v>0</v>
+      </c>
+      <c r="L112" s="14">
+        <f t="shared" ref="L112:L147" si="30">C112*L33</f>
+        <v>0</v>
+      </c>
+      <c r="M112" s="14">
+        <f>C112*M33</f>
+        <v>0</v>
+      </c>
+      <c r="N112" s="14"/>
+      <c r="O112" s="19"/>
+      <c r="P112" s="14"/>
+      <c r="Q112" s="14">
         <f t="shared" si="7"/>
-        <v>54</v>
-      </c>
-      <c r="D112" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E112" s="14">
-        <f t="shared" ref="E112:E140" si="29">C112*E33</f>
-        <v>0</v>
-      </c>
-      <c r="F112" s="14">
-        <f t="shared" ref="F112:F140" si="30">C112*F33</f>
-        <v>0</v>
-      </c>
-      <c r="G112" s="14">
-        <f t="shared" ref="G112:G140" si="31">C112*G33</f>
-        <v>54</v>
-      </c>
-      <c r="H112" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I112" s="14">
-        <f t="shared" ref="I112:I140" si="32">C112*I33</f>
-        <v>54</v>
-      </c>
-      <c r="J112" s="14">
-        <f t="shared" ref="J112:J140" si="33">C112*J33</f>
-        <v>108</v>
-      </c>
-      <c r="K112" s="14">
-        <f t="shared" ref="K112:K140" si="34">C112*K33</f>
-        <v>0</v>
-      </c>
-      <c r="L112" s="14">
-        <f t="shared" ref="L112:L147" si="35">C112*L33</f>
-        <v>0</v>
-      </c>
-      <c r="M112" s="14">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="N112" s="19"/>
-      <c r="O112" s="14"/>
-      <c r="P112" s="14">
-        <f t="shared" si="28"/>
         <v>216</v>
       </c>
-      <c r="Q112" s="14"/>
-    </row>
-    <row r="113" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R112" s="14"/>
+    </row>
+    <row r="113" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="14" t="s">
         <v>44</v>
       </c>
@@ -6163,58 +6282,59 @@
         <v>47</v>
       </c>
       <c r="C113" s="14">
-        <f t="shared" ref="C113:C144" si="36">C34*2</f>
+        <f t="shared" ref="C113:C144" si="31">C34*2</f>
         <v>54</v>
       </c>
       <c r="D113" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E113" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F113" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G113" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E113" s="14">
+      <c r="H113" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I113" s="14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J113" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K113" s="14">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F113" s="14">
+        <v>54</v>
+      </c>
+      <c r="L113" s="14">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G113" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H113" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I113" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J113" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K113" s="14">
-        <f t="shared" si="34"/>
-        <v>54</v>
-      </c>
-      <c r="L113" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M113" s="14">
-        <f t="shared" si="14"/>
-        <v>378</v>
+        <f>C113*M34</f>
+        <v>432</v>
       </c>
       <c r="N113" s="14"/>
       <c r="O113" s="14"/>
-      <c r="P113" s="14">
-        <f t="shared" si="28"/>
-        <v>432</v>
-      </c>
-      <c r="Q113" s="14"/>
-    </row>
-    <row r="114" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="P113" s="14"/>
+      <c r="Q113" s="14">
+        <f t="shared" si="7"/>
+        <v>486</v>
+      </c>
+      <c r="R113" s="14"/>
+    </row>
+    <row r="114" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="14" t="s">
         <v>44</v>
       </c>
@@ -6222,58 +6342,59 @@
         <v>48</v>
       </c>
       <c r="C114" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>54</v>
       </c>
       <c r="D114" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E114" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F114" s="14">
+        <f t="shared" si="25"/>
+        <v>54</v>
+      </c>
+      <c r="G114" s="14">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E114" s="14">
+        <v>108</v>
+      </c>
+      <c r="H114" s="14">
+        <f t="shared" si="23"/>
+        <v>54</v>
+      </c>
+      <c r="I114" s="14">
+        <f t="shared" si="27"/>
+        <v>54</v>
+      </c>
+      <c r="J114" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K114" s="14">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F114" s="14">
+        <v>54</v>
+      </c>
+      <c r="L114" s="14">
         <f t="shared" si="30"/>
         <v>54</v>
       </c>
-      <c r="G114" s="14">
-        <f t="shared" si="31"/>
-        <v>108</v>
-      </c>
-      <c r="H114" s="14">
-        <f t="shared" si="27"/>
-        <v>54</v>
-      </c>
-      <c r="I114" s="14">
-        <f t="shared" si="32"/>
-        <v>54</v>
-      </c>
-      <c r="J114" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K114" s="14">
-        <f t="shared" si="34"/>
-        <v>54</v>
-      </c>
-      <c r="L114" s="14">
-        <f t="shared" si="35"/>
-        <v>54</v>
-      </c>
       <c r="M114" s="14">
-        <f t="shared" si="14"/>
+        <f>C114*M35</f>
         <v>0</v>
       </c>
       <c r="N114" s="14"/>
       <c r="O114" s="14"/>
-      <c r="P114" s="14">
-        <f t="shared" si="28"/>
+      <c r="P114" s="14"/>
+      <c r="Q114" s="14">
+        <f t="shared" si="7"/>
         <v>378</v>
       </c>
-      <c r="Q114" s="14"/>
-    </row>
-    <row r="115" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R114" s="14"/>
+    </row>
+    <row r="115" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="14" t="s">
         <v>44</v>
       </c>
@@ -6281,58 +6402,59 @@
         <v>49</v>
       </c>
       <c r="C115" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>62</v>
       </c>
       <c r="D115" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E115" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F115" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G115" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E115" s="14">
+      <c r="H115" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I115" s="14">
+        <f t="shared" si="27"/>
+        <v>62</v>
+      </c>
+      <c r="J115" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K115" s="14">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F115" s="14">
+        <v>186</v>
+      </c>
+      <c r="L115" s="14">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G115" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H115" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I115" s="14">
-        <f t="shared" si="32"/>
-        <v>62</v>
-      </c>
-      <c r="J115" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K115" s="14">
-        <f t="shared" si="34"/>
-        <v>186</v>
-      </c>
-      <c r="L115" s="14">
-        <f t="shared" si="35"/>
         <v>124</v>
       </c>
       <c r="M115" s="14">
-        <f t="shared" si="14"/>
+        <f>C115*M36</f>
         <v>124</v>
       </c>
       <c r="N115" s="14"/>
       <c r="O115" s="14"/>
-      <c r="P115" s="14">
-        <f t="shared" si="28"/>
+      <c r="P115" s="14"/>
+      <c r="Q115" s="14">
+        <f t="shared" si="7"/>
         <v>496</v>
       </c>
-      <c r="Q115" s="14"/>
-    </row>
-    <row r="116" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R115" s="14"/>
+    </row>
+    <row r="116" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>40</v>
       </c>
@@ -6340,60 +6462,60 @@
         <v>41</v>
       </c>
       <c r="C116" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>158</v>
       </c>
       <c r="D116" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E116" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F116" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G116" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E116" s="8">
+      <c r="H116" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I116" s="8">
+        <f t="shared" si="27"/>
+        <v>158</v>
+      </c>
+      <c r="J116" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K116" s="8">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F116" s="8">
+        <v>158</v>
+      </c>
+      <c r="L116" s="8">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G116" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H116" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I116" s="8">
-        <f t="shared" si="32"/>
         <v>158</v>
       </c>
-      <c r="J116" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K116" s="8">
-        <f t="shared" si="34"/>
-        <v>158</v>
-      </c>
-      <c r="L116" s="8">
-        <f t="shared" si="35"/>
-        <v>158</v>
-      </c>
       <c r="M116" s="8">
-        <f t="shared" si="14"/>
+        <f>C116*M37</f>
         <v>0</v>
       </c>
       <c r="N116" s="8"/>
       <c r="O116" s="8"/>
-      <c r="P116" s="8">
-        <f t="shared" si="10"/>
+      <c r="P116" s="8"/>
+      <c r="Q116" s="8">
+        <f t="shared" si="7"/>
         <v>474</v>
       </c>
-      <c r="Q116" s="8">
-        <f>SUM(P116:P118)</f>
+      <c r="R116" s="8">
+        <f>SUM(Q116:Q118)</f>
         <v>1150</v>
       </c>
-      <c r="R116" s="17"/>
       <c r="S116" s="17"/>
       <c r="T116" s="17"/>
       <c r="U116" s="17"/>
@@ -6406,8 +6528,9 @@
       <c r="AB116" s="17"/>
       <c r="AC116" s="17"/>
       <c r="AD116" s="17"/>
-    </row>
-    <row r="117" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE116" s="17"/>
+    </row>
+    <row r="117" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>40</v>
       </c>
@@ -6415,57 +6538,57 @@
         <v>42</v>
       </c>
       <c r="C117" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>140</v>
       </c>
       <c r="D117" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E117" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F117" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G117" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E117" s="8">
+      <c r="H117" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I117" s="8">
+        <f t="shared" si="27"/>
+        <v>280</v>
+      </c>
+      <c r="J117" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K117" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F117" s="8">
+      <c r="L117" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G117" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H117" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I117" s="8">
-        <f t="shared" si="32"/>
-        <v>280</v>
-      </c>
-      <c r="J117" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K117" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L117" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M117" s="8">
-        <f t="shared" si="14"/>
+        <f>C117*M38</f>
         <v>0</v>
       </c>
       <c r="N117" s="8"/>
       <c r="O117" s="8"/>
-      <c r="P117" s="8">
-        <f t="shared" si="10"/>
+      <c r="P117" s="8"/>
+      <c r="Q117" s="8">
+        <f t="shared" si="7"/>
         <v>280</v>
       </c>
-      <c r="Q117" s="8"/>
-      <c r="R117" s="17"/>
+      <c r="R117" s="8"/>
       <c r="S117" s="17"/>
       <c r="T117" s="17"/>
       <c r="U117" s="17"/>
@@ -6478,8 +6601,9 @@
       <c r="AB117" s="17"/>
       <c r="AC117" s="17"/>
       <c r="AD117" s="17"/>
-    </row>
-    <row r="118" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE117" s="17"/>
+    </row>
+    <row r="118" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>40</v>
       </c>
@@ -6487,57 +6611,57 @@
         <v>43</v>
       </c>
       <c r="C118" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>132</v>
       </c>
       <c r="D118" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E118" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F118" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G118" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E118" s="8">
+      <c r="H118" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I118" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J118" s="8">
+        <f t="shared" si="28"/>
+        <v>132</v>
+      </c>
+      <c r="K118" s="8">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F118" s="8">
+        <v>132</v>
+      </c>
+      <c r="L118" s="8">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G118" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H118" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I118" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J118" s="8">
-        <f t="shared" si="33"/>
         <v>132</v>
       </c>
-      <c r="K118" s="8">
-        <f t="shared" si="34"/>
-        <v>132</v>
-      </c>
-      <c r="L118" s="8">
-        <f t="shared" si="35"/>
-        <v>132</v>
-      </c>
       <c r="M118" s="8">
-        <f t="shared" si="14"/>
+        <f>C118*M39</f>
         <v>0</v>
       </c>
       <c r="N118" s="8"/>
       <c r="O118" s="8"/>
-      <c r="P118" s="8">
-        <f t="shared" si="10"/>
+      <c r="P118" s="8"/>
+      <c r="Q118" s="8">
+        <f t="shared" si="7"/>
         <v>396</v>
       </c>
-      <c r="Q118" s="8"/>
-      <c r="R118" s="17"/>
+      <c r="R118" s="8"/>
       <c r="S118" s="17"/>
       <c r="T118" s="17"/>
       <c r="U118" s="17"/>
@@ -6550,8 +6674,9 @@
       <c r="AB118" s="17"/>
       <c r="AC118" s="17"/>
       <c r="AD118" s="17"/>
-    </row>
-    <row r="119" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE118" s="17"/>
+    </row>
+    <row r="119" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="14" t="s">
         <v>50</v>
       </c>
@@ -6559,61 +6684,62 @@
         <v>51</v>
       </c>
       <c r="C119" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>840</v>
       </c>
       <c r="D119" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E119" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F119" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G119" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E119" s="14">
+      <c r="H119" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I119" s="14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J119" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K119" s="14">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F119" s="14">
+        <v>840</v>
+      </c>
+      <c r="L119" s="14">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G119" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H119" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I119" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J119" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K119" s="14">
-        <f t="shared" si="34"/>
-        <v>840</v>
-      </c>
-      <c r="L119" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M119" s="14">
-        <f t="shared" si="14"/>
+        <f>C119*M40</f>
         <v>0</v>
       </c>
       <c r="N119" s="14"/>
       <c r="O119" s="14"/>
-      <c r="P119" s="14">
-        <f t="shared" si="10"/>
+      <c r="P119" s="14"/>
+      <c r="Q119" s="14">
+        <f t="shared" si="7"/>
         <v>840</v>
       </c>
-      <c r="Q119" s="14">
-        <f>P119</f>
+      <c r="R119" s="14">
+        <f>Q119</f>
         <v>840</v>
       </c>
     </row>
-    <row r="120" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>52</v>
       </c>
@@ -6621,60 +6747,60 @@
         <v>53</v>
       </c>
       <c r="C120" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>282</v>
       </c>
       <c r="D120" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E120" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F120" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G120" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E120" s="8">
+      <c r="H120" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I120" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J120" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K120" s="8">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F120" s="8">
+        <v>282</v>
+      </c>
+      <c r="L120" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G120" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H120" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I120" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J120" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K120" s="8">
-        <f t="shared" si="34"/>
-        <v>282</v>
-      </c>
-      <c r="L120" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M120" s="8">
-        <f t="shared" si="14"/>
+        <f>C120*M41</f>
         <v>0</v>
       </c>
       <c r="N120" s="8"/>
       <c r="O120" s="8"/>
-      <c r="P120" s="8">
-        <f t="shared" si="10"/>
+      <c r="P120" s="8"/>
+      <c r="Q120" s="8">
+        <f t="shared" si="7"/>
         <v>282</v>
       </c>
-      <c r="Q120" s="8">
-        <f>P120</f>
+      <c r="R120" s="8">
+        <f>Q120</f>
         <v>282</v>
       </c>
-      <c r="R120" s="17"/>
       <c r="S120" s="17"/>
       <c r="T120" s="17"/>
       <c r="U120" s="17"/>
@@ -6687,8 +6813,9 @@
       <c r="AB120" s="17"/>
       <c r="AC120" s="17"/>
       <c r="AD120" s="17"/>
-    </row>
-    <row r="121" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE120" s="17"/>
+    </row>
+    <row r="121" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="14" t="s">
         <v>54</v>
       </c>
@@ -6696,61 +6823,62 @@
         <v>55</v>
       </c>
       <c r="C121" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>160</v>
       </c>
       <c r="D121" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E121" s="14">
+        <f t="shared" si="24"/>
+        <v>160</v>
+      </c>
+      <c r="F121" s="14">
+        <f t="shared" si="25"/>
+        <v>160</v>
+      </c>
+      <c r="G121" s="14">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E121" s="14">
+        <v>320</v>
+      </c>
+      <c r="H121" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I121" s="14">
+        <f t="shared" si="27"/>
+        <v>480</v>
+      </c>
+      <c r="J121" s="14">
+        <f t="shared" si="28"/>
+        <v>160</v>
+      </c>
+      <c r="K121" s="14">
         <f t="shared" si="29"/>
         <v>160</v>
       </c>
-      <c r="F121" s="14">
+      <c r="L121" s="14">
         <f t="shared" si="30"/>
-        <v>160</v>
-      </c>
-      <c r="G121" s="14">
-        <f t="shared" si="31"/>
-        <v>320</v>
-      </c>
-      <c r="H121" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I121" s="14">
-        <f t="shared" si="32"/>
-        <v>480</v>
-      </c>
-      <c r="J121" s="14">
-        <f t="shared" si="33"/>
-        <v>160</v>
-      </c>
-      <c r="K121" s="14">
-        <f t="shared" si="34"/>
-        <v>160</v>
-      </c>
-      <c r="L121" s="14">
-        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M121" s="14">
-        <f t="shared" si="14"/>
+        <f>C121*M42</f>
         <v>0</v>
       </c>
       <c r="N121" s="14"/>
       <c r="O121" s="14"/>
-      <c r="P121" s="14">
-        <f t="shared" si="10"/>
+      <c r="P121" s="14"/>
+      <c r="Q121" s="14">
+        <f t="shared" si="7"/>
         <v>1440</v>
       </c>
-      <c r="Q121" s="14">
-        <f>P121</f>
+      <c r="R121" s="14">
+        <f>Q121</f>
         <v>1440</v>
       </c>
     </row>
-    <row r="122" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>120</v>
       </c>
@@ -6758,60 +6886,60 @@
         <v>119</v>
       </c>
       <c r="C122" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>1044</v>
       </c>
       <c r="D122" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E122" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F122" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G122" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E122" s="8">
+      <c r="H122" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I122" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J122" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K122" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F122" s="8">
+      <c r="L122" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G122" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H122" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I122" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J122" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K122" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L122" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M122" s="8">
-        <f t="shared" si="14"/>
+        <f>C122*M43</f>
         <v>2088</v>
       </c>
       <c r="N122" s="8"/>
       <c r="O122" s="8"/>
-      <c r="P122" s="8">
-        <f t="shared" si="10"/>
+      <c r="P122" s="8"/>
+      <c r="Q122" s="8">
+        <f t="shared" si="7"/>
         <v>2088</v>
       </c>
-      <c r="Q122" s="8">
-        <f>P122</f>
+      <c r="R122" s="8">
+        <f>Q122</f>
         <v>2088</v>
       </c>
-      <c r="R122" s="17"/>
       <c r="S122" s="17"/>
       <c r="T122" s="17"/>
       <c r="U122" s="17"/>
@@ -6824,8 +6952,9 @@
       <c r="AB122" s="17"/>
       <c r="AC122" s="17"/>
       <c r="AD122" s="17"/>
-    </row>
-    <row r="123" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE122" s="17"/>
+    </row>
+    <row r="123" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="14" t="s">
         <v>56</v>
       </c>
@@ -6833,61 +6962,62 @@
         <v>57</v>
       </c>
       <c r="C123" s="14">
-        <f t="shared" si="36"/>
-        <v>68</v>
-      </c>
-      <c r="D123" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E123" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F123" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G123" s="14">
         <f t="shared" si="31"/>
         <v>68</v>
       </c>
+      <c r="D123" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E123" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F123" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G123" s="14">
+        <f t="shared" si="26"/>
+        <v>68</v>
+      </c>
       <c r="H123" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I123" s="14">
         <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I123" s="14">
-        <f t="shared" si="32"/>
         <v>136</v>
       </c>
       <c r="J123" s="14">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="K123" s="14">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>136</v>
       </c>
       <c r="L123" s="14">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>68</v>
       </c>
       <c r="M123" s="14">
-        <f t="shared" si="14"/>
+        <f>C123*M44</f>
         <v>0</v>
       </c>
       <c r="N123" s="14"/>
       <c r="O123" s="14"/>
-      <c r="P123" s="14">
-        <f t="shared" si="10"/>
+      <c r="P123" s="14"/>
+      <c r="Q123" s="14">
+        <f t="shared" si="7"/>
         <v>408</v>
       </c>
-      <c r="Q123" s="14">
-        <f>SUM(P123:P124)</f>
+      <c r="R123" s="14">
+        <f>SUM(Q123:Q124)</f>
         <v>498</v>
       </c>
     </row>
-    <row r="124" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="14" t="s">
         <v>56</v>
       </c>
@@ -6895,58 +7025,59 @@
         <v>58</v>
       </c>
       <c r="C124" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>90</v>
       </c>
       <c r="D124" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E124" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F124" s="14">
+        <f t="shared" si="25"/>
+        <v>90</v>
+      </c>
+      <c r="G124" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E124" s="14">
+      <c r="H124" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I124" s="14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J124" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K124" s="14">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F124" s="14">
+      <c r="L124" s="14">
         <f t="shared" si="30"/>
-        <v>90</v>
-      </c>
-      <c r="G124" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H124" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I124" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J124" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K124" s="14">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L124" s="14">
-        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M124" s="14">
-        <f t="shared" si="14"/>
+        <f>C124*M45</f>
         <v>0</v>
       </c>
       <c r="N124" s="14"/>
       <c r="O124" s="14"/>
-      <c r="P124" s="14">
-        <f t="shared" si="10"/>
+      <c r="P124" s="14"/>
+      <c r="Q124" s="14">
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
-      <c r="Q124" s="14"/>
-    </row>
-    <row r="125" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R124" s="14"/>
+    </row>
+    <row r="125" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>59</v>
       </c>
@@ -6954,60 +7085,60 @@
         <v>60</v>
       </c>
       <c r="C125" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>264</v>
       </c>
       <c r="D125" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E125" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F125" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G125" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E125" s="8">
+      <c r="H125" s="8">
+        <f t="shared" si="23"/>
+        <v>264</v>
+      </c>
+      <c r="I125" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J125" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K125" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F125" s="8">
+      <c r="L125" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G125" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H125" s="8">
-        <f t="shared" si="27"/>
-        <v>264</v>
-      </c>
-      <c r="I125" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J125" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K125" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L125" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M125" s="8">
-        <f t="shared" si="14"/>
+        <f>C125*M46</f>
         <v>0</v>
       </c>
       <c r="N125" s="8"/>
       <c r="O125" s="8"/>
-      <c r="P125" s="8">
-        <f t="shared" si="10"/>
+      <c r="P125" s="8"/>
+      <c r="Q125" s="8">
+        <f t="shared" si="7"/>
         <v>264</v>
       </c>
-      <c r="Q125" s="8">
-        <f>SUM(P125:P127)</f>
+      <c r="R125" s="8">
+        <f>SUM(Q125:Q127)</f>
         <v>1050</v>
       </c>
-      <c r="R125" s="17"/>
       <c r="S125" s="17"/>
       <c r="T125" s="17"/>
       <c r="U125" s="17"/>
@@ -7020,8 +7151,9 @@
       <c r="AB125" s="17"/>
       <c r="AC125" s="17"/>
       <c r="AD125" s="17"/>
-    </row>
-    <row r="126" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE125" s="17"/>
+    </row>
+    <row r="126" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>59</v>
       </c>
@@ -7029,57 +7161,57 @@
         <v>61</v>
       </c>
       <c r="C126" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>262</v>
       </c>
       <c r="D126" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E126" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F126" s="8">
+        <f t="shared" si="25"/>
+        <v>262</v>
+      </c>
+      <c r="G126" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E126" s="8">
+      <c r="H126" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I126" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J126" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K126" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F126" s="8">
+      <c r="L126" s="8">
         <f t="shared" si="30"/>
-        <v>262</v>
-      </c>
-      <c r="G126" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H126" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I126" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J126" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K126" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L126" s="8">
-        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="M126" s="8">
-        <f t="shared" si="14"/>
+        <f>C126*M47</f>
         <v>0</v>
       </c>
       <c r="N126" s="8"/>
       <c r="O126" s="8"/>
-      <c r="P126" s="8">
-        <f t="shared" si="10"/>
+      <c r="P126" s="8"/>
+      <c r="Q126" s="8">
+        <f t="shared" si="7"/>
         <v>262</v>
       </c>
-      <c r="Q126" s="8"/>
-      <c r="R126" s="17"/>
+      <c r="R126" s="8"/>
       <c r="S126" s="17"/>
       <c r="T126" s="17"/>
       <c r="U126" s="17"/>
@@ -7092,8 +7224,9 @@
       <c r="AB126" s="17"/>
       <c r="AC126" s="17"/>
       <c r="AD126" s="17"/>
-    </row>
-    <row r="127" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE126" s="17"/>
+    </row>
+    <row r="127" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>59</v>
       </c>
@@ -7101,57 +7234,57 @@
         <v>62</v>
       </c>
       <c r="C127" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>262</v>
       </c>
       <c r="D127" s="8">
+        <f t="shared" si="22"/>
+        <v>262</v>
+      </c>
+      <c r="E127" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F127" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G127" s="8">
         <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H127" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I127" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J127" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K127" s="8">
+        <f t="shared" si="29"/>
         <v>262</v>
       </c>
-      <c r="E127" s="8">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F127" s="8">
+      <c r="L127" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G127" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H127" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I127" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J127" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K127" s="8">
-        <f t="shared" si="34"/>
-        <v>262</v>
-      </c>
-      <c r="L127" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M127" s="8">
-        <f t="shared" si="14"/>
+        <f>C127*M48</f>
         <v>0</v>
       </c>
       <c r="N127" s="8"/>
       <c r="O127" s="8"/>
-      <c r="P127" s="8">
-        <f t="shared" si="10"/>
+      <c r="P127" s="8"/>
+      <c r="Q127" s="8">
+        <f t="shared" si="7"/>
         <v>524</v>
       </c>
-      <c r="Q127" s="8"/>
-      <c r="R127" s="17"/>
+      <c r="R127" s="8"/>
       <c r="S127" s="17"/>
       <c r="T127" s="17"/>
       <c r="U127" s="17"/>
@@ -7164,8 +7297,9 @@
       <c r="AB127" s="17"/>
       <c r="AC127" s="17"/>
       <c r="AD127" s="17"/>
-    </row>
-    <row r="128" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE127" s="17"/>
+    </row>
+    <row r="128" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="14" t="s">
         <v>63</v>
       </c>
@@ -7173,61 +7307,62 @@
         <v>64</v>
       </c>
       <c r="C128" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>272</v>
       </c>
       <c r="D128" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E128" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F128" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G128" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E128" s="14">
+      <c r="H128" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I128" s="14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J128" s="14">
+        <f t="shared" si="28"/>
+        <v>544</v>
+      </c>
+      <c r="K128" s="14">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F128" s="14">
+        <v>272</v>
+      </c>
+      <c r="L128" s="14">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G128" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H128" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I128" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J128" s="14">
-        <f t="shared" si="33"/>
-        <v>544</v>
-      </c>
-      <c r="K128" s="14">
-        <f t="shared" si="34"/>
-        <v>272</v>
-      </c>
-      <c r="L128" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M128" s="14">
-        <f t="shared" ref="M128:M147" si="37">C128*M49</f>
+        <f>C128*M49</f>
         <v>0</v>
       </c>
       <c r="N128" s="14"/>
       <c r="O128" s="14"/>
-      <c r="P128" s="14">
-        <f t="shared" si="10"/>
+      <c r="P128" s="14"/>
+      <c r="Q128" s="14">
+        <f t="shared" si="7"/>
         <v>816</v>
       </c>
-      <c r="Q128" s="14">
-        <f>P128</f>
+      <c r="R128" s="14">
+        <f>Q128</f>
         <v>816</v>
       </c>
     </row>
-    <row r="129" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>65</v>
       </c>
@@ -7235,60 +7370,60 @@
         <v>66</v>
       </c>
       <c r="C129" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>266</v>
       </c>
       <c r="D129" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E129" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F129" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G129" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E129" s="8">
+      <c r="H129" s="8">
+        <f t="shared" si="23"/>
+        <v>266</v>
+      </c>
+      <c r="I129" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J129" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K129" s="8">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F129" s="8">
+        <v>266</v>
+      </c>
+      <c r="L129" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G129" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H129" s="8">
-        <f t="shared" si="27"/>
-        <v>266</v>
-      </c>
-      <c r="I129" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J129" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K129" s="8">
-        <f t="shared" si="34"/>
-        <v>266</v>
-      </c>
-      <c r="L129" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M129" s="8">
-        <f t="shared" si="37"/>
+        <f>C129*M50</f>
         <v>0</v>
       </c>
       <c r="N129" s="8"/>
       <c r="O129" s="8"/>
-      <c r="P129" s="8">
-        <f t="shared" si="10"/>
+      <c r="P129" s="8"/>
+      <c r="Q129" s="8">
+        <f t="shared" si="7"/>
         <v>532</v>
       </c>
-      <c r="Q129" s="8">
-        <f>SUM(P129:P132)</f>
+      <c r="R129" s="8">
+        <f>SUM(Q129:Q132)</f>
         <v>1396</v>
       </c>
-      <c r="R129" s="17"/>
       <c r="S129" s="17"/>
       <c r="T129" s="17"/>
       <c r="U129" s="17"/>
@@ -7301,8 +7436,9 @@
       <c r="AB129" s="17"/>
       <c r="AC129" s="17"/>
       <c r="AD129" s="17"/>
-    </row>
-    <row r="130" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE129" s="17"/>
+    </row>
+    <row r="130" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>65</v>
       </c>
@@ -7310,57 +7446,57 @@
         <v>67</v>
       </c>
       <c r="C130" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>304</v>
       </c>
       <c r="D130" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E130" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F130" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G130" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E130" s="8">
+      <c r="H130" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I130" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J130" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K130" s="8">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F130" s="8">
+        <v>304</v>
+      </c>
+      <c r="L130" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G130" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H130" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I130" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J130" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K130" s="8">
-        <f t="shared" si="34"/>
-        <v>304</v>
-      </c>
-      <c r="L130" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M130" s="8">
-        <f t="shared" si="37"/>
+        <f>C130*M51</f>
         <v>0</v>
       </c>
       <c r="N130" s="8"/>
       <c r="O130" s="8"/>
-      <c r="P130" s="8">
-        <f t="shared" si="10"/>
+      <c r="P130" s="8"/>
+      <c r="Q130" s="8">
+        <f t="shared" si="7"/>
         <v>304</v>
       </c>
-      <c r="Q130" s="8"/>
-      <c r="R130" s="17"/>
+      <c r="R130" s="8"/>
       <c r="S130" s="17"/>
       <c r="T130" s="17"/>
       <c r="U130" s="17"/>
@@ -7373,8 +7509,9 @@
       <c r="AB130" s="17"/>
       <c r="AC130" s="17"/>
       <c r="AD130" s="17"/>
-    </row>
-    <row r="131" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE130" s="17"/>
+    </row>
+    <row r="131" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>65</v>
       </c>
@@ -7382,57 +7519,57 @@
         <v>68</v>
       </c>
       <c r="C131" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>254</v>
       </c>
       <c r="D131" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E131" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F131" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G131" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E131" s="8">
+      <c r="H131" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I131" s="8">
+        <f t="shared" si="27"/>
+        <v>254</v>
+      </c>
+      <c r="J131" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K131" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F131" s="8">
+      <c r="L131" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G131" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H131" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I131" s="8">
-        <f t="shared" si="32"/>
-        <v>254</v>
-      </c>
-      <c r="J131" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K131" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L131" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M131" s="8">
-        <f t="shared" si="37"/>
+        <f>C131*M52</f>
         <v>0</v>
       </c>
       <c r="N131" s="8"/>
       <c r="O131" s="8"/>
-      <c r="P131" s="8">
-        <f t="shared" si="10"/>
+      <c r="P131" s="8"/>
+      <c r="Q131" s="8">
+        <f t="shared" si="7"/>
         <v>254</v>
       </c>
-      <c r="Q131" s="8"/>
-      <c r="R131" s="17"/>
+      <c r="R131" s="8"/>
       <c r="S131" s="17"/>
       <c r="T131" s="17"/>
       <c r="U131" s="17"/>
@@ -7445,8 +7582,9 @@
       <c r="AB131" s="17"/>
       <c r="AC131" s="17"/>
       <c r="AD131" s="17"/>
-    </row>
-    <row r="132" spans="1:30" s="18" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AE131" s="17"/>
+    </row>
+    <row r="132" spans="1:31" s="18" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>65</v>
       </c>
@@ -7454,57 +7592,57 @@
         <v>69</v>
       </c>
       <c r="C132" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>306</v>
       </c>
       <c r="D132" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E132" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F132" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G132" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E132" s="8">
+      <c r="H132" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I132" s="8">
+        <f t="shared" si="27"/>
+        <v>306</v>
+      </c>
+      <c r="J132" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K132" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F132" s="8">
+      <c r="L132" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G132" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H132" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I132" s="8">
-        <f t="shared" si="32"/>
-        <v>306</v>
-      </c>
-      <c r="J132" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K132" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L132" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M132" s="8">
-        <f t="shared" si="37"/>
+        <f>C132*M53</f>
         <v>0</v>
       </c>
       <c r="N132" s="8"/>
       <c r="O132" s="8"/>
-      <c r="P132" s="8">
-        <f t="shared" si="10"/>
+      <c r="P132" s="8"/>
+      <c r="Q132" s="8">
+        <f t="shared" si="7"/>
         <v>306</v>
       </c>
-      <c r="Q132" s="8"/>
-      <c r="R132" s="17"/>
+      <c r="R132" s="8"/>
       <c r="S132" s="17"/>
       <c r="T132" s="17"/>
       <c r="U132" s="17"/>
@@ -7517,8 +7655,9 @@
       <c r="AB132" s="17"/>
       <c r="AC132" s="17"/>
       <c r="AD132" s="17"/>
-    </row>
-    <row r="133" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE132" s="17"/>
+    </row>
+    <row r="133" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="14" t="s">
         <v>70</v>
       </c>
@@ -7526,179 +7665,182 @@
         <v>71</v>
       </c>
       <c r="C133" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>124</v>
       </c>
       <c r="D133" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E133" s="14">
+        <f t="shared" si="24"/>
+        <v>124</v>
+      </c>
+      <c r="F133" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G133" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E133" s="14">
+      <c r="H133" s="14">
+        <f t="shared" si="23"/>
+        <v>124</v>
+      </c>
+      <c r="I133" s="14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J133" s="14">
+        <f t="shared" si="28"/>
+        <v>248</v>
+      </c>
+      <c r="K133" s="14">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L133" s="14">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M133" s="14">
+        <f>C133*M54</f>
+        <v>124</v>
+      </c>
+      <c r="N133" s="14"/>
+      <c r="O133" s="14"/>
+      <c r="P133" s="14"/>
+      <c r="Q133" s="14">
+        <f t="shared" si="7"/>
+        <v>620</v>
+      </c>
+      <c r="R133" s="14">
+        <f>SUM(Q133:Q135)</f>
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="134" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C134" s="14">
+        <f t="shared" si="31"/>
+        <v>130</v>
+      </c>
+      <c r="D134" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E134" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F134" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G134" s="14">
+        <f t="shared" si="26"/>
+        <v>260</v>
+      </c>
+      <c r="H134" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I134" s="14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J134" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K134" s="14">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="L134" s="14">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M134" s="14">
+        <f>C134*M55</f>
+        <v>0</v>
+      </c>
+      <c r="N134" s="14"/>
+      <c r="O134" s="14"/>
+      <c r="P134" s="14"/>
+      <c r="Q134" s="14">
+        <f t="shared" si="7"/>
+        <v>260</v>
+      </c>
+      <c r="R134" s="14"/>
+    </row>
+    <row r="135" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C135" s="14">
+        <f t="shared" si="31"/>
+        <v>124</v>
+      </c>
+      <c r="D135" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E135" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F135" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G135" s="14">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H135" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I135" s="14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J135" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K135" s="14">
         <f t="shared" si="29"/>
         <v>124</v>
       </c>
-      <c r="F133" s="14">
+      <c r="L135" s="14">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G133" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H133" s="14">
-        <f t="shared" si="27"/>
-        <v>124</v>
-      </c>
-      <c r="I133" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J133" s="14">
-        <f t="shared" si="33"/>
-        <v>248</v>
-      </c>
-      <c r="K133" s="14">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L133" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M133" s="14">
-        <f t="shared" si="37"/>
-        <v>124</v>
-      </c>
-      <c r="N133" s="14"/>
-      <c r="O133" s="14"/>
-      <c r="P133" s="14">
-        <f t="shared" si="10"/>
-        <v>620</v>
-      </c>
-      <c r="Q133" s="14">
-        <f>SUM(P133:P135)</f>
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="134" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B134" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C134" s="14">
-        <f t="shared" si="36"/>
-        <v>130</v>
-      </c>
-      <c r="D134" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E134" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F134" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G134" s="14">
-        <f t="shared" si="31"/>
-        <v>260</v>
-      </c>
-      <c r="H134" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I134" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J134" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K134" s="14">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L134" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M134" s="14">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="N134" s="14"/>
-      <c r="O134" s="14"/>
-      <c r="P134" s="14">
-        <f t="shared" si="10"/>
-        <v>260</v>
-      </c>
-      <c r="Q134" s="14"/>
-    </row>
-    <row r="135" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B135" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C135" s="14">
-        <f t="shared" si="36"/>
-        <v>124</v>
-      </c>
-      <c r="D135" s="14">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E135" s="14">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F135" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G135" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H135" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I135" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J135" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K135" s="14">
-        <f t="shared" si="34"/>
-        <v>124</v>
-      </c>
-      <c r="L135" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M135" s="14">
-        <f t="shared" si="37"/>
+        <f>C135*M56</f>
         <v>0</v>
       </c>
       <c r="N135" s="14"/>
       <c r="O135" s="14"/>
-      <c r="P135" s="14">
-        <f t="shared" si="10"/>
+      <c r="P135" s="14"/>
+      <c r="Q135" s="14">
+        <f t="shared" si="7"/>
         <v>124</v>
       </c>
-      <c r="Q135" s="14"/>
-    </row>
-    <row r="136" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R135" s="14"/>
+    </row>
+    <row r="136" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>74</v>
       </c>
@@ -7706,60 +7848,60 @@
         <v>124</v>
       </c>
       <c r="C136" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>90</v>
       </c>
       <c r="D136" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E136" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F136" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G136" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E136" s="8">
+      <c r="H136" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I136" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J136" s="8">
+        <f t="shared" si="28"/>
+        <v>90</v>
+      </c>
+      <c r="K136" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F136" s="8">
+      <c r="L136" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G136" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H136" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I136" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J136" s="8">
-        <f t="shared" si="33"/>
-        <v>90</v>
-      </c>
-      <c r="K136" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L136" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M136" s="8">
-        <f t="shared" si="37"/>
+        <f>C136*M57</f>
         <v>0</v>
       </c>
       <c r="N136" s="8"/>
       <c r="O136" s="8"/>
-      <c r="P136" s="8">
-        <f t="shared" si="10"/>
+      <c r="P136" s="8"/>
+      <c r="Q136" s="8">
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
-      <c r="Q136" s="8">
-        <f>SUM(P136:P138)</f>
+      <c r="R136" s="8">
+        <f>SUM(Q136:Q138)</f>
         <v>286</v>
       </c>
-      <c r="R136" s="17"/>
       <c r="S136" s="17"/>
       <c r="T136" s="17"/>
       <c r="U136" s="17"/>
@@ -7772,8 +7914,9 @@
       <c r="AB136" s="17"/>
       <c r="AC136" s="17"/>
       <c r="AD136" s="17"/>
-    </row>
-    <row r="137" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE136" s="17"/>
+    </row>
+    <row r="137" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>74</v>
       </c>
@@ -7781,57 +7924,57 @@
         <v>76</v>
       </c>
       <c r="C137" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>106</v>
       </c>
       <c r="D137" s="8">
+        <f t="shared" si="22"/>
+        <v>106</v>
+      </c>
+      <c r="E137" s="8">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F137" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G137" s="8">
         <f t="shared" si="26"/>
-        <v>106</v>
-      </c>
-      <c r="E137" s="8">
+        <v>0</v>
+      </c>
+      <c r="H137" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I137" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J137" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K137" s="8">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F137" s="8">
+      <c r="L137" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G137" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H137" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I137" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J137" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K137" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L137" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M137" s="8">
-        <f t="shared" si="37"/>
+        <f>C137*M58</f>
         <v>0</v>
       </c>
       <c r="N137" s="8"/>
       <c r="O137" s="8"/>
-      <c r="P137" s="8">
-        <f t="shared" si="10"/>
+      <c r="P137" s="8"/>
+      <c r="Q137" s="8">
+        <f t="shared" si="7"/>
         <v>106</v>
       </c>
-      <c r="Q137" s="8"/>
-      <c r="R137" s="17"/>
+      <c r="R137" s="8"/>
       <c r="S137" s="17"/>
       <c r="T137" s="17"/>
       <c r="U137" s="17"/>
@@ -7844,8 +7987,9 @@
       <c r="AB137" s="17"/>
       <c r="AC137" s="17"/>
       <c r="AD137" s="17"/>
-    </row>
-    <row r="138" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE137" s="17"/>
+    </row>
+    <row r="138" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>74</v>
       </c>
@@ -7853,57 +7997,57 @@
         <v>77</v>
       </c>
       <c r="C138" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>90</v>
       </c>
       <c r="D138" s="8">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E138" s="8">
+        <f t="shared" si="24"/>
+        <v>90</v>
+      </c>
+      <c r="F138" s="8">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G138" s="8">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E138" s="8">
+      <c r="H138" s="8">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I138" s="8">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J138" s="8">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K138" s="8">
         <f t="shared" si="29"/>
-        <v>90</v>
-      </c>
-      <c r="F138" s="8">
+        <v>0</v>
+      </c>
+      <c r="L138" s="8">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G138" s="8">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H138" s="8">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I138" s="8">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J138" s="8">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K138" s="8">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L138" s="8">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
       <c r="M138" s="8">
-        <f t="shared" si="37"/>
+        <f>C138*M59</f>
         <v>0</v>
       </c>
       <c r="N138" s="8"/>
       <c r="O138" s="8"/>
-      <c r="P138" s="8">
-        <f t="shared" si="10"/>
+      <c r="P138" s="8"/>
+      <c r="Q138" s="8">
+        <f t="shared" si="7"/>
         <v>90</v>
       </c>
-      <c r="Q138" s="8"/>
-      <c r="R138" s="17"/>
+      <c r="R138" s="8"/>
       <c r="S138" s="17"/>
       <c r="T138" s="17"/>
       <c r="U138" s="17"/>
@@ -7916,8 +8060,9 @@
       <c r="AB138" s="17"/>
       <c r="AC138" s="17"/>
       <c r="AD138" s="17"/>
-    </row>
-    <row r="139" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE138" s="17"/>
+    </row>
+    <row r="139" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="14" t="s">
         <v>78</v>
       </c>
@@ -7925,61 +8070,62 @@
         <v>79</v>
       </c>
       <c r="C139" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>40</v>
       </c>
       <c r="D139" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E139" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F139" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G139" s="14">
         <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="E139" s="14">
+        <v>80</v>
+      </c>
+      <c r="H139" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I139" s="14">
+        <f t="shared" si="27"/>
+        <v>160</v>
+      </c>
+      <c r="J139" s="14">
+        <f t="shared" si="28"/>
+        <v>160</v>
+      </c>
+      <c r="K139" s="14">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F139" s="14">
+      <c r="L139" s="14">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G139" s="14">
-        <f t="shared" si="31"/>
-        <v>80</v>
-      </c>
-      <c r="H139" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I139" s="14">
-        <f t="shared" si="32"/>
-        <v>160</v>
-      </c>
-      <c r="J139" s="14">
-        <f t="shared" si="33"/>
-        <v>160</v>
-      </c>
-      <c r="K139" s="14">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L139" s="14">
-        <f t="shared" si="35"/>
         <v>40</v>
       </c>
       <c r="M139" s="14">
-        <f t="shared" si="37"/>
+        <f>C139*M60</f>
         <v>0</v>
       </c>
       <c r="N139" s="14"/>
       <c r="O139" s="14"/>
-      <c r="P139" s="14">
-        <f t="shared" si="10"/>
+      <c r="P139" s="14"/>
+      <c r="Q139" s="14">
+        <f t="shared" si="7"/>
         <v>440</v>
       </c>
-      <c r="Q139" s="14">
-        <f>SUM(P139:P141)</f>
+      <c r="R139" s="14">
+        <f>SUM(Q139:Q141)</f>
         <v>712</v>
       </c>
     </row>
-    <row r="140" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="14" t="s">
         <v>78</v>
       </c>
@@ -7987,58 +8133,59 @@
         <v>80</v>
       </c>
       <c r="C140" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>34</v>
       </c>
       <c r="D140" s="14">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="E140" s="14">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F140" s="14">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="G140" s="14">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E140" s="14">
+      <c r="H140" s="14">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="I140" s="14">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="J140" s="14">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="K140" s="14">
         <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="F140" s="14">
+        <v>136</v>
+      </c>
+      <c r="L140" s="14">
         <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="G140" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H140" s="14">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="I140" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="J140" s="14">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="K140" s="14">
-        <f t="shared" si="34"/>
-        <v>136</v>
-      </c>
-      <c r="L140" s="14">
-        <f t="shared" si="35"/>
         <v>68</v>
       </c>
       <c r="M140" s="14">
-        <f t="shared" si="37"/>
+        <f>C140*M61</f>
         <v>0</v>
       </c>
       <c r="N140" s="14"/>
       <c r="O140" s="14"/>
-      <c r="P140" s="14">
-        <f t="shared" si="10"/>
+      <c r="P140" s="14"/>
+      <c r="Q140" s="14">
+        <f t="shared" si="7"/>
         <v>204</v>
       </c>
-      <c r="Q140" s="14"/>
-    </row>
-    <row r="141" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R140" s="14"/>
+    </row>
+    <row r="141" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="14" t="s">
         <v>78</v>
       </c>
@@ -8046,7 +8193,7 @@
         <v>102</v>
       </c>
       <c r="C141" s="14">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>34</v>
       </c>
       <c r="D141" s="14">
@@ -8074,22 +8221,23 @@
         <v>0</v>
       </c>
       <c r="L141" s="14">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>68</v>
       </c>
       <c r="M141" s="14">
-        <f t="shared" si="37"/>
+        <f>C141*M62</f>
         <v>0</v>
       </c>
       <c r="N141" s="14"/>
       <c r="O141" s="14"/>
-      <c r="P141" s="14">
-        <f t="shared" si="10"/>
+      <c r="P141" s="14"/>
+      <c r="Q141" s="14">
+        <f t="shared" si="7"/>
         <v>68</v>
       </c>
-      <c r="Q141" s="14"/>
-    </row>
-    <row r="142" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R141" s="14"/>
+    </row>
+    <row r="142" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>81</v>
       </c>
@@ -8097,60 +8245,60 @@
         <v>82</v>
       </c>
       <c r="C142" s="8">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>248</v>
       </c>
       <c r="D142" s="8">
-        <f t="shared" ref="D142:D147" si="38">C142*D63</f>
+        <f t="shared" ref="D142:D147" si="32">C142*D63</f>
         <v>248</v>
       </c>
       <c r="E142" s="8">
-        <f t="shared" ref="E142:E147" si="39">C142*E63</f>
+        <f t="shared" ref="E142:E147" si="33">C142*E63</f>
         <v>248</v>
       </c>
       <c r="F142" s="8">
-        <f t="shared" ref="F142:F147" si="40">C142*F63</f>
+        <f t="shared" ref="F142:F147" si="34">C142*F63</f>
         <v>248</v>
       </c>
       <c r="G142" s="8">
-        <f t="shared" ref="G142:G147" si="41">C142*G63</f>
+        <f t="shared" ref="G142:G147" si="35">C142*G63</f>
         <v>496</v>
       </c>
       <c r="H142" s="8">
-        <f t="shared" ref="H142:H147" si="42">C142*H63</f>
+        <f t="shared" ref="H142:H147" si="36">C142*H63</f>
         <v>0</v>
       </c>
       <c r="I142" s="8">
-        <f t="shared" ref="I142:I147" si="43">C142*I63</f>
+        <f t="shared" ref="I142:I147" si="37">C142*I63</f>
         <v>0</v>
       </c>
       <c r="J142" s="8">
-        <f t="shared" ref="J142:J147" si="44">C142*J63</f>
+        <f t="shared" ref="J142:J147" si="38">C142*J63</f>
         <v>0</v>
       </c>
       <c r="K142" s="8">
-        <f t="shared" ref="K142:K147" si="45">C142*K63</f>
+        <f t="shared" ref="K142:K147" si="39">C142*K63</f>
         <v>0</v>
       </c>
       <c r="L142" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M142" s="8">
-        <f t="shared" si="37"/>
+        <f>C142*M63</f>
         <v>0</v>
       </c>
       <c r="N142" s="8"/>
       <c r="O142" s="8"/>
-      <c r="P142" s="8">
-        <f t="shared" si="10"/>
+      <c r="P142" s="8"/>
+      <c r="Q142" s="8">
+        <f t="shared" si="7"/>
         <v>1240</v>
       </c>
-      <c r="Q142" s="8">
-        <f>SUM(P142)</f>
+      <c r="R142" s="8">
+        <f>SUM(Q142)</f>
         <v>1240</v>
       </c>
-      <c r="R142" s="17"/>
       <c r="S142" s="17"/>
       <c r="T142" s="17"/>
       <c r="U142" s="17"/>
@@ -8163,8 +8311,9 @@
       <c r="AB142" s="17"/>
       <c r="AC142" s="17"/>
       <c r="AD142" s="17"/>
-    </row>
-    <row r="143" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="AE142" s="17"/>
+    </row>
+    <row r="143" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="14" t="s">
         <v>83</v>
       </c>
@@ -8172,61 +8321,62 @@
         <v>84</v>
       </c>
       <c r="C143" s="14">
+        <f t="shared" si="31"/>
+        <v>124</v>
+      </c>
+      <c r="D143" s="14">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="E143" s="14">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="F143" s="14">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="G143" s="14">
+        <f t="shared" si="35"/>
+        <v>124</v>
+      </c>
+      <c r="H143" s="14">
         <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I143" s="14">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="J143" s="14">
+        <f t="shared" si="38"/>
         <v>124</v>
       </c>
-      <c r="D143" s="14">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="E143" s="14">
+      <c r="K143" s="14">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="F143" s="14">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G143" s="14">
-        <f t="shared" si="41"/>
-        <v>124</v>
-      </c>
-      <c r="H143" s="14">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="I143" s="14">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="J143" s="14">
-        <f t="shared" si="44"/>
-        <v>124</v>
-      </c>
-      <c r="K143" s="14">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
       <c r="L143" s="14">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M143" s="14">
-        <f t="shared" si="37"/>
+        <f>C143*M64</f>
         <v>0</v>
       </c>
       <c r="N143" s="14"/>
       <c r="O143" s="14"/>
-      <c r="P143" s="14">
-        <f t="shared" si="10"/>
+      <c r="P143" s="14"/>
+      <c r="Q143" s="14">
+        <f t="shared" si="7"/>
         <v>248</v>
       </c>
-      <c r="Q143" s="14">
-        <f>SUM(P143:P145)</f>
+      <c r="R143" s="14">
+        <f>SUM(Q143:Q145)</f>
         <v>482</v>
       </c>
     </row>
-    <row r="144" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="14" t="s">
         <v>83</v>
       </c>
@@ -8234,58 +8384,59 @@
         <v>85</v>
       </c>
       <c r="C144" s="14">
+        <f t="shared" si="31"/>
+        <v>118</v>
+      </c>
+      <c r="D144" s="14">
+        <f t="shared" si="32"/>
+        <v>118</v>
+      </c>
+      <c r="E144" s="14">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="F144" s="14">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="G144" s="14">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="H144" s="14">
         <f t="shared" si="36"/>
-        <v>118</v>
-      </c>
-      <c r="D144" s="14">
+        <v>0</v>
+      </c>
+      <c r="I144" s="14">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="J144" s="14">
         <f t="shared" si="38"/>
-        <v>118</v>
-      </c>
-      <c r="E144" s="14">
+        <v>0</v>
+      </c>
+      <c r="K144" s="14">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="F144" s="14">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G144" s="14">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="H144" s="14">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="I144" s="14">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="J144" s="14">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="K144" s="14">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
       <c r="L144" s="14">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M144" s="14">
-        <f t="shared" si="37"/>
+        <f>C144*M65</f>
         <v>0</v>
       </c>
       <c r="N144" s="14"/>
       <c r="O144" s="14"/>
-      <c r="P144" s="14">
-        <f t="shared" si="10"/>
+      <c r="P144" s="14"/>
+      <c r="Q144" s="14">
+        <f t="shared" si="7"/>
         <v>118</v>
       </c>
-      <c r="Q144" s="14"/>
-    </row>
-    <row r="145" spans="1:30" s="17" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R144" s="14"/>
+    </row>
+    <row r="145" spans="1:31" s="17" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="14" t="s">
         <v>83</v>
       </c>
@@ -8293,58 +8444,59 @@
         <v>86</v>
       </c>
       <c r="C145" s="14">
-        <f t="shared" ref="C145:C147" si="46">C66*2</f>
+        <f t="shared" ref="C145:C147" si="40">C66*2</f>
         <v>116</v>
       </c>
       <c r="D145" s="14">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="E145" s="14">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="F145" s="14">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="G145" s="14">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="H145" s="14">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I145" s="14">
+        <f t="shared" si="37"/>
+        <v>116</v>
+      </c>
+      <c r="J145" s="14">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="E145" s="14">
+      <c r="K145" s="14">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="F145" s="14">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G145" s="14">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="H145" s="14">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="I145" s="14">
-        <f t="shared" si="43"/>
-        <v>116</v>
-      </c>
-      <c r="J145" s="14">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="K145" s="14">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
       <c r="L145" s="14">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M145" s="14">
-        <f t="shared" si="37"/>
+        <f>C145*M66</f>
         <v>0</v>
       </c>
       <c r="N145" s="14"/>
       <c r="O145" s="14"/>
-      <c r="P145" s="14">
-        <f t="shared" si="10"/>
+      <c r="P145" s="14"/>
+      <c r="Q145" s="14">
+        <f t="shared" si="7"/>
         <v>116</v>
       </c>
-      <c r="Q145" s="14"/>
-    </row>
-    <row r="146" spans="1:30" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="R145" s="14"/>
+    </row>
+    <row r="146" spans="1:31" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>87</v>
       </c>
@@ -8352,60 +8504,60 @@
         <v>88</v>
       </c>
       <c r="C146" s="8">
-        <f t="shared" si="46"/>
-        <v>138</v>
-      </c>
-      <c r="D146" s="8">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="E146" s="8">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="F146" s="8">
         <f t="shared" si="40"/>
         <v>138</v>
       </c>
+      <c r="D146" s="8">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="E146" s="8">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="F146" s="8">
+        <f t="shared" si="34"/>
+        <v>138</v>
+      </c>
       <c r="G146" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="H146" s="8">
-        <f t="shared" si="42"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="I146" s="8">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="J146" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="K146" s="8">
-        <f t="shared" si="45"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="L146" s="8">
-        <f t="shared" si="35"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M146" s="8">
-        <f t="shared" si="37"/>
+        <f>C146*M67</f>
         <v>0</v>
       </c>
       <c r="N146" s="8"/>
       <c r="O146" s="8"/>
-      <c r="P146" s="8">
-        <f t="shared" si="10"/>
+      <c r="P146" s="8"/>
+      <c r="Q146" s="8">
+        <f t="shared" ref="Q146:Q147" si="41">SUM(D146:N146)</f>
         <v>138</v>
       </c>
-      <c r="Q146" s="8">
-        <f>P146</f>
+      <c r="R146" s="8">
+        <f>Q146</f>
         <v>138</v>
       </c>
-      <c r="R146" s="17"/>
       <c r="S146" s="17"/>
       <c r="T146" s="17"/>
       <c r="U146" s="17"/>
@@ -8418,8 +8570,9 @@
       <c r="AB146" s="17"/>
       <c r="AC146" s="17"/>
       <c r="AD146" s="17"/>
-    </row>
-    <row r="147" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE146" s="17"/>
+    </row>
+    <row r="147" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A147" s="14" t="s">
         <v>136</v>
       </c>
@@ -8427,61 +8580,62 @@
         <v>137</v>
       </c>
       <c r="C147" s="14">
-        <f t="shared" si="46"/>
+        <f t="shared" si="40"/>
         <v>376</v>
       </c>
       <c r="D147" s="14">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="E147" s="14">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="F147" s="14">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="G147" s="14">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="H147" s="14">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I147" s="14">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="J147" s="14">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="E147" s="14">
+      <c r="K147" s="14">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="F147" s="14">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="G147" s="14">
+      <c r="L147" s="14">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="M147" s="14">
+        <f>C147*M68</f>
+        <v>376</v>
+      </c>
+      <c r="N147" s="14"/>
+      <c r="O147" s="6"/>
+      <c r="P147" s="6"/>
+      <c r="Q147" s="14">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="H147" s="14">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="I147" s="14">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="J147" s="14">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="K147" s="14">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="L147" s="14">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="M147" s="14">
-        <f t="shared" si="37"/>
         <v>376</v>
       </c>
-      <c r="N147" s="6"/>
-      <c r="O147" s="6"/>
-      <c r="P147" s="14">
-        <f t="shared" si="10"/>
+      <c r="R147" s="14">
+        <f>Q147</f>
         <v>376</v>
       </c>
-      <c r="Q147" s="14">
-        <f>P147</f>
-        <v>376</v>
-      </c>
-    </row>
-    <row r="150" spans="1:30" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A150" s="7" t="s">
         <v>11</v>
       </c>
@@ -8518,15 +8672,18 @@
         <v>117</v>
       </c>
       <c r="N150" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="O150" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="O150" s="9" t="s">
+      <c r="P150" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="P150" s="7"/>
-      <c r="Q150" s="9"/>
-    </row>
-    <row r="151" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="Q150" s="7"/>
+      <c r="R150" s="9"/>
+    </row>
+    <row r="151" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A151" s="8"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -8535,113 +8692,121 @@
         <v>750</v>
       </c>
       <c r="E151" s="8">
-        <f t="shared" ref="E151:M151" si="47">SUM(E81:E147)</f>
+        <f t="shared" ref="E151:N151" si="42">SUM(E81:E147)</f>
         <v>892</v>
       </c>
       <c r="F151" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>1166</v>
       </c>
       <c r="G151" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>1830</v>
       </c>
       <c r="H151" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>802</v>
       </c>
       <c r="I151" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>3046</v>
       </c>
       <c r="J151" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>2704</v>
       </c>
       <c r="K151" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>4664</v>
       </c>
       <c r="L151" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="42"/>
         <v>2654</v>
       </c>
       <c r="M151" s="8">
-        <f t="shared" si="47"/>
-        <v>7326</v>
+        <f t="shared" si="42"/>
+        <v>7380</v>
       </c>
       <c r="N151" s="8">
-        <f>SUM(D151:M151)</f>
-        <v>25834</v>
-      </c>
-      <c r="O151" s="15">
-        <f>N151/N70</f>
-        <v>155.62650602409639</v>
-      </c>
-      <c r="P151" s="8">
-        <f>SUM(P81:P147)</f>
-        <v>25834</v>
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="O151" s="8">
+        <f>SUM(D151:N151)</f>
+        <v>25888</v>
+      </c>
+      <c r="P151" s="15">
+        <f>O151/O70</f>
+        <v>155.01796407185628</v>
       </c>
       <c r="Q151" s="8">
         <f>SUM(Q81:Q147)</f>
-        <v>25834</v>
-      </c>
-    </row>
-    <row r="152" spans="1:30" x14ac:dyDescent="0.3">
+        <v>25888</v>
+      </c>
+      <c r="R151" s="8">
+        <f>SUM(R81:R147)</f>
+        <v>25888</v>
+      </c>
+    </row>
+    <row r="152" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
       <c r="D152" s="16">
-        <f t="shared" ref="D152:N152" si="48">D151/D70</f>
+        <f t="shared" ref="D152:O152" si="43">D151/D70</f>
         <v>150</v>
       </c>
       <c r="E152" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>89.2</v>
       </c>
       <c r="F152" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>116.6</v>
       </c>
       <c r="G152" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>114.375</v>
       </c>
       <c r="H152" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>160.4</v>
       </c>
       <c r="I152" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>138.45454545454547</v>
       </c>
       <c r="J152" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>142.31578947368422</v>
       </c>
       <c r="K152" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>172.74074074074073</v>
       </c>
       <c r="L152" s="16">
-        <f t="shared" si="48"/>
+        <f t="shared" si="43"/>
         <v>165.875</v>
       </c>
       <c r="M152" s="16">
-        <f t="shared" si="48"/>
-        <v>203.5</v>
-      </c>
-      <c r="N152" s="16">
-        <f t="shared" si="48"/>
-        <v>155.62650602409639</v>
-      </c>
-      <c r="O152" s="6" t="s">
+        <f t="shared" si="43"/>
+        <v>199.45945945945945</v>
+      </c>
+      <c r="N152" s="16" t="e">
+        <f t="shared" si="43"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O152" s="16">
+        <f t="shared" si="43"/>
+        <v>155.01796407185628</v>
+      </c>
+      <c r="P152" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="P152" s="6"/>
       <c r="Q152" s="6"/>
-    </row>
-    <row r="155" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="R152" s="6"/>
+    </row>
+    <row r="155" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="s">
         <v>0</v>
       </c>
@@ -8655,88 +8820,88 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A156" s="8" t="s">
         <v>13</v>
       </c>
       <c r="B156" s="8">
-        <f>Q2</f>
+        <f>R2</f>
         <v>3</v>
       </c>
       <c r="C156" s="8">
-        <f>SUM(N2:N4)</f>
+        <f>SUM(O2:O4)</f>
         <v>11</v>
       </c>
       <c r="D156" s="8">
-        <f>Q81</f>
+        <f>R81</f>
         <v>148</v>
       </c>
     </row>
-    <row r="157" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A157" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B157" s="14">
-        <f>Q5</f>
+        <f>R5</f>
         <v>1</v>
       </c>
       <c r="C157" s="14">
-        <f>N5</f>
+        <f>O5</f>
         <v>2</v>
       </c>
       <c r="D157" s="14">
-        <f>Q84</f>
+        <f>R84</f>
         <v>1128</v>
       </c>
     </row>
-    <row r="158" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>129</v>
       </c>
       <c r="B158" s="8">
-        <f>Q6</f>
+        <f>R6</f>
         <v>1</v>
       </c>
       <c r="C158" s="8">
-        <f>Q6</f>
+        <f>R6</f>
         <v>1</v>
       </c>
       <c r="D158" s="8">
-        <f>Q85</f>
+        <f>R85</f>
         <v>148</v>
       </c>
     </row>
-    <row r="159" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A159" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B159" s="14">
-        <f>Q7</f>
+        <f>R7</f>
         <v>4</v>
       </c>
       <c r="C159" s="14">
-        <f>SUM(N7:N10)</f>
+        <f>SUM(O7:O10)</f>
         <v>7</v>
       </c>
       <c r="D159" s="14">
-        <f>Q86</f>
+        <f>R86</f>
         <v>1962</v>
       </c>
     </row>
-    <row r="160" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B160" s="8">
-        <f>Q11</f>
+        <f>R11</f>
         <v>5</v>
       </c>
       <c r="C160" s="8">
-        <f>SUM(N11:N15)</f>
+        <f>SUM(O11:O15)</f>
         <v>15</v>
       </c>
       <c r="D160" s="8">
-        <f>Q90</f>
+        <f>R90</f>
         <v>1288</v>
       </c>
     </row>
@@ -8745,15 +8910,15 @@
         <v>125</v>
       </c>
       <c r="B161" s="14">
-        <f>Q16</f>
+        <f>R16</f>
         <v>1</v>
       </c>
       <c r="C161" s="14">
-        <f>N16</f>
+        <f>O16</f>
         <v>1</v>
       </c>
       <c r="D161" s="14">
-        <f>Q95</f>
+        <f>R95</f>
         <v>364</v>
       </c>
     </row>
@@ -8762,15 +8927,15 @@
         <v>28</v>
       </c>
       <c r="B162" s="8">
-        <f>Q17</f>
+        <f>R17</f>
         <v>2</v>
       </c>
       <c r="C162" s="8">
-        <f>SUM(N17:N18)</f>
+        <f>SUM(O17:O18)</f>
         <v>3</v>
       </c>
       <c r="D162" s="8">
-        <f>Q96</f>
+        <f>R96</f>
         <v>1202</v>
       </c>
     </row>
@@ -8779,15 +8944,15 @@
         <v>131</v>
       </c>
       <c r="B163" s="14">
-        <f>Q19</f>
+        <f>R19</f>
         <v>1</v>
       </c>
       <c r="C163" s="14">
-        <f>N19</f>
+        <f>O19</f>
         <v>1</v>
       </c>
       <c r="D163" s="14">
-        <f>Q98</f>
+        <f>R98</f>
         <v>236</v>
       </c>
     </row>
@@ -8796,15 +8961,15 @@
         <v>30</v>
       </c>
       <c r="B164" s="8">
-        <f>Q20</f>
+        <f>R20</f>
         <v>5</v>
       </c>
       <c r="C164" s="8">
-        <f>SUM(N20:N24)</f>
+        <f>SUM(O20:O24)</f>
         <v>9</v>
       </c>
       <c r="D164" s="8">
-        <f>Q99</f>
+        <f>R99</f>
         <v>906</v>
       </c>
     </row>
@@ -8813,15 +8978,15 @@
         <v>134</v>
       </c>
       <c r="B165" s="14">
-        <f>Q25</f>
+        <f>R25</f>
         <v>1</v>
       </c>
       <c r="C165" s="14">
-        <f>N25</f>
+        <f>O25</f>
         <v>1</v>
       </c>
       <c r="D165" s="14">
-        <f t="shared" ref="D165:D171" si="49">Q104</f>
+        <f t="shared" ref="D165:D171" si="44">R104</f>
         <v>800</v>
       </c>
     </row>
@@ -8830,15 +8995,15 @@
         <v>36</v>
       </c>
       <c r="B166" s="8">
-        <f>Q26</f>
+        <f>R26</f>
         <v>1</v>
       </c>
       <c r="C166" s="8">
-        <f>N26</f>
+        <f>O26</f>
         <v>1</v>
       </c>
       <c r="D166" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>726</v>
       </c>
     </row>
@@ -8847,15 +9012,15 @@
         <v>96</v>
       </c>
       <c r="B167" s="14">
-        <f>Q27</f>
+        <f>R27</f>
         <v>1</v>
       </c>
       <c r="C167" s="14">
-        <f>N27</f>
+        <f>O27</f>
         <v>1</v>
       </c>
       <c r="D167" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>186</v>
       </c>
     </row>
@@ -8864,15 +9029,15 @@
         <v>122</v>
       </c>
       <c r="B168" s="8">
-        <f>N28</f>
+        <f>O28</f>
         <v>1</v>
       </c>
       <c r="C168" s="8">
-        <f>Q28</f>
+        <f>R28</f>
         <v>1</v>
       </c>
       <c r="D168" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>348</v>
       </c>
     </row>
@@ -8881,15 +9046,15 @@
         <v>99</v>
       </c>
       <c r="B169" s="14">
-        <f>Q29</f>
+        <f>R29</f>
         <v>1</v>
       </c>
       <c r="C169" s="14">
-        <f>N29</f>
+        <f>O29</f>
         <v>1</v>
       </c>
       <c r="D169" s="14">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>418</v>
       </c>
     </row>
@@ -8898,15 +9063,15 @@
         <v>38</v>
       </c>
       <c r="B170" s="8">
-        <f>N30</f>
+        <f>O30</f>
         <v>1</v>
       </c>
       <c r="C170" s="8">
-        <f>Q30</f>
+        <f>R30</f>
         <v>1</v>
       </c>
       <c r="D170" s="8">
-        <f t="shared" si="49"/>
+        <f t="shared" si="44"/>
         <v>516</v>
       </c>
     </row>
@@ -8915,16 +9080,16 @@
         <v>44</v>
       </c>
       <c r="B171" s="14">
-        <f>Q31</f>
+        <f>R31</f>
         <v>6</v>
       </c>
       <c r="C171" s="14">
-        <f>SUM(N31:N36)</f>
-        <v>30</v>
+        <f>SUM(O31:O36)</f>
+        <v>31</v>
       </c>
       <c r="D171" s="14">
-        <f t="shared" si="49"/>
-        <v>1660</v>
+        <f t="shared" si="44"/>
+        <v>1714</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
@@ -8932,15 +9097,15 @@
         <v>40</v>
       </c>
       <c r="B172" s="8">
-        <f>Q37</f>
+        <f>R37</f>
         <v>3</v>
       </c>
       <c r="C172" s="8">
-        <f>SUM(N37:N39)</f>
+        <f>SUM(O37:O39)</f>
         <v>8</v>
       </c>
       <c r="D172" s="8">
-        <f>Q116</f>
+        <f>R116</f>
         <v>1150</v>
       </c>
     </row>
@@ -8949,15 +9114,15 @@
         <v>50</v>
       </c>
       <c r="B173" s="14">
-        <f>Q40</f>
+        <f>R40</f>
         <v>1</v>
       </c>
       <c r="C173" s="14">
-        <f>N40</f>
+        <f>O40</f>
         <v>1</v>
       </c>
       <c r="D173" s="14">
-        <f>Q119</f>
+        <f>R119</f>
         <v>840</v>
       </c>
     </row>
@@ -8966,15 +9131,15 @@
         <v>52</v>
       </c>
       <c r="B174" s="8">
-        <f>Q41</f>
+        <f>R41</f>
         <v>1</v>
       </c>
       <c r="C174" s="8">
-        <f>N41</f>
+        <f>O41</f>
         <v>1</v>
       </c>
       <c r="D174" s="8">
-        <f>Q120</f>
+        <f>R120</f>
         <v>282</v>
       </c>
     </row>
@@ -8983,15 +9148,15 @@
         <v>91</v>
       </c>
       <c r="B175" s="14">
-        <f>Q42</f>
+        <f>R42</f>
         <v>1</v>
       </c>
       <c r="C175" s="14">
-        <f>N42</f>
+        <f>O42</f>
         <v>9</v>
       </c>
       <c r="D175" s="14">
-        <f>Q121</f>
+        <f>R121</f>
         <v>1440</v>
       </c>
     </row>
@@ -9000,7 +9165,7 @@
         <v>120</v>
       </c>
       <c r="B176" s="8">
-        <f>Q43</f>
+        <f>R43</f>
         <v>1</v>
       </c>
       <c r="C176" s="8">
@@ -9008,7 +9173,7 @@
         <v>2</v>
       </c>
       <c r="D176" s="8">
-        <f>Q122</f>
+        <f>R122</f>
         <v>2088</v>
       </c>
     </row>
@@ -9017,15 +9182,15 @@
         <v>56</v>
       </c>
       <c r="B177" s="14">
-        <f>Q44</f>
+        <f>R44</f>
         <v>2</v>
       </c>
       <c r="C177" s="14">
-        <f>SUM(N44:N45)</f>
+        <f>SUM(O44:O45)</f>
         <v>7</v>
       </c>
       <c r="D177" s="14">
-        <f>Q123</f>
+        <f>R123</f>
         <v>498</v>
       </c>
     </row>
@@ -9034,15 +9199,15 @@
         <v>59</v>
       </c>
       <c r="B178" s="8">
-        <f>Q46</f>
+        <f>R46</f>
         <v>3</v>
       </c>
       <c r="C178" s="8">
-        <f>SUM(N46:N48)</f>
+        <f>SUM(O46:O48)</f>
         <v>4</v>
       </c>
       <c r="D178" s="8">
-        <f>Q125</f>
+        <f>R125</f>
         <v>1050</v>
       </c>
     </row>
@@ -9051,15 +9216,15 @@
         <v>92</v>
       </c>
       <c r="B179" s="14">
-        <f>Q49</f>
+        <f>R49</f>
         <v>1</v>
       </c>
       <c r="C179" s="14">
-        <f>N49</f>
+        <f>O49</f>
         <v>3</v>
       </c>
       <c r="D179" s="14">
-        <f>Q128</f>
+        <f>R128</f>
         <v>816</v>
       </c>
     </row>
@@ -9068,15 +9233,15 @@
         <v>65</v>
       </c>
       <c r="B180" s="8">
-        <f>Q50</f>
+        <f>R50</f>
         <v>4</v>
       </c>
       <c r="C180" s="8">
-        <f>SUM(N50:N53)</f>
+        <f>SUM(O50:O53)</f>
         <v>5</v>
       </c>
       <c r="D180" s="8">
-        <f>Q129</f>
+        <f>R129</f>
         <v>1396</v>
       </c>
     </row>
@@ -9085,15 +9250,15 @@
         <v>70</v>
       </c>
       <c r="B181" s="14">
-        <f>Q54</f>
+        <f>R54</f>
         <v>3</v>
       </c>
       <c r="C181" s="14">
-        <f>SUM(N54:N56)</f>
+        <f>SUM(O54:O56)</f>
         <v>8</v>
       </c>
       <c r="D181" s="14">
-        <f>Q133</f>
+        <f>R133</f>
         <v>1004</v>
       </c>
     </row>
@@ -9102,15 +9267,15 @@
         <v>74</v>
       </c>
       <c r="B182" s="8">
-        <f>Q57</f>
+        <f>R57</f>
         <v>3</v>
       </c>
       <c r="C182" s="8">
-        <f>SUM(N57:N59)</f>
+        <f>SUM(O57:O59)</f>
         <v>3</v>
       </c>
       <c r="D182" s="8">
-        <f>Q136</f>
+        <f>R136</f>
         <v>286</v>
       </c>
     </row>
@@ -9119,15 +9284,15 @@
         <v>78</v>
       </c>
       <c r="B183" s="14">
-        <f>Q60</f>
+        <f>R60</f>
         <v>3</v>
       </c>
       <c r="C183" s="14">
-        <f>SUM(N60:N62)</f>
+        <f>SUM(O60:O62)</f>
         <v>19</v>
       </c>
       <c r="D183" s="14">
-        <f>Q139</f>
+        <f>R139</f>
         <v>712</v>
       </c>
     </row>
@@ -9136,15 +9301,15 @@
         <v>81</v>
       </c>
       <c r="B184" s="8">
-        <f>Q63</f>
+        <f>R63</f>
         <v>1</v>
       </c>
       <c r="C184" s="8">
-        <f>N63</f>
+        <f>O63</f>
         <v>5</v>
       </c>
       <c r="D184" s="8">
-        <f>Q142</f>
+        <f>R142</f>
         <v>1240</v>
       </c>
     </row>
@@ -9153,15 +9318,15 @@
         <v>83</v>
       </c>
       <c r="B185" s="14">
-        <f>Q64</f>
+        <f>R64</f>
         <v>3</v>
       </c>
       <c r="C185" s="14">
-        <f>SUM(N64:N66)</f>
+        <f>SUM(O64:O66)</f>
         <v>4</v>
       </c>
       <c r="D185" s="14">
-        <f>Q143</f>
+        <f>R143</f>
         <v>482</v>
       </c>
     </row>
@@ -9170,15 +9335,15 @@
         <v>87</v>
       </c>
       <c r="B186" s="8">
-        <f>Q67</f>
+        <f>R67</f>
         <v>1</v>
       </c>
       <c r="C186" s="8">
-        <f>N67</f>
+        <f>O67</f>
         <v>1</v>
       </c>
       <c r="D186" s="8">
-        <f>Q146</f>
+        <f>R146</f>
         <v>138</v>
       </c>
     </row>
@@ -9187,15 +9352,15 @@
         <v>136</v>
       </c>
       <c r="B187" s="14">
-        <f>Q68</f>
+        <f>R68</f>
         <v>1</v>
       </c>
       <c r="C187" s="14">
-        <f>N68</f>
+        <f>O68</f>
         <v>1</v>
       </c>
       <c r="D187" s="14">
-        <f>Q145</f>
+        <f>R145</f>
         <v>0</v>
       </c>
     </row>
@@ -9207,11 +9372,11 @@
       </c>
       <c r="C188" s="21">
         <f>SUM(C156:C187)</f>
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D188" s="21">
         <f>SUM(D156:D187)</f>
-        <v>25458</v>
+        <v>25512</v>
       </c>
     </row>
   </sheetData>
